--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>228.3763856088694</v>
+        <v>236.1277410783948</v>
       </c>
       <c r="C2" t="n">
-        <v>233.6469097348115</v>
+        <v>237.3133638141207</v>
       </c>
       <c r="D2" t="n">
-        <v>228.177124724439</v>
+        <v>234.1649902844441</v>
       </c>
       <c r="E2" t="n">
-        <v>233.2085418701172</v>
+        <v>235.8288421630859</v>
       </c>
       <c r="F2" t="n">
-        <v>55824200</v>
+        <v>42699500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>236.1277563565235</v>
+        <v>236.3070825366735</v>
       </c>
       <c r="C3" t="n">
-        <v>237.3133791689625</v>
+        <v>240.3322223551857</v>
       </c>
       <c r="D3" t="n">
-        <v>234.1650054355773</v>
+        <v>235.4502622494337</v>
       </c>
       <c r="E3" t="n">
-        <v>235.828857421875</v>
+        <v>237.2735137939453</v>
       </c>
       <c r="F3" t="n">
-        <v>42699500</v>
+        <v>63421100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>236.3070825366735</v>
+        <v>238.0905124651219</v>
       </c>
       <c r="C4" t="n">
-        <v>240.3322223551857</v>
+        <v>239.216358555688</v>
       </c>
       <c r="D4" t="n">
-        <v>235.4502622494337</v>
+        <v>236.8550706028844</v>
       </c>
       <c r="E4" t="n">
-        <v>237.2735137939453</v>
+        <v>238.1104431152344</v>
       </c>
       <c r="F4" t="n">
-        <v>63421100</v>
+        <v>46508000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>238.0905124651219</v>
+        <v>239.0868055705458</v>
       </c>
       <c r="C5" t="n">
-        <v>239.216358555688</v>
+        <v>240.3122743702574</v>
       </c>
       <c r="D5" t="n">
-        <v>236.8550706028844</v>
+        <v>235.7790173404318</v>
       </c>
       <c r="E5" t="n">
-        <v>238.1104431152344</v>
+        <v>237.0045013427734</v>
       </c>
       <c r="F5" t="n">
-        <v>46508000</v>
+        <v>44249600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>239.0868055705458</v>
+        <v>240.3421770415445</v>
       </c>
       <c r="C6" t="n">
-        <v>240.3122743702574</v>
+        <v>245.3935247988757</v>
       </c>
       <c r="D6" t="n">
-        <v>235.7790173404318</v>
+        <v>239.3259419777209</v>
       </c>
       <c r="E6" t="n">
-        <v>237.0045013427734</v>
+        <v>244.5964660644531</v>
       </c>
       <c r="F6" t="n">
-        <v>44249600</v>
+        <v>163741300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>240.3421770415445</v>
+        <v>247.3861620644307</v>
       </c>
       <c r="C7" t="n">
-        <v>245.3935247988757</v>
+        <v>255.6954791611581</v>
       </c>
       <c r="D7" t="n">
-        <v>239.3259419777209</v>
+        <v>247.2068166293636</v>
       </c>
       <c r="E7" t="n">
-        <v>244.5964660644531</v>
+        <v>255.1375122070312</v>
       </c>
       <c r="F7" t="n">
-        <v>163741300</v>
+        <v>105517400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>247.3861620644307</v>
+        <v>254.9382669065294</v>
       </c>
       <c r="C8" t="n">
-        <v>255.6954791611581</v>
+        <v>256.3928850249964</v>
       </c>
       <c r="D8" t="n">
-        <v>247.2068166293636</v>
+        <v>252.646728760892</v>
       </c>
       <c r="E8" t="n">
-        <v>255.1375122070312</v>
+        <v>253.4935913085938</v>
       </c>
       <c r="F8" t="n">
-        <v>105517400</v>
+        <v>60275200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>254.9382515607796</v>
+        <v>254.2807025242173</v>
       </c>
       <c r="C9" t="n">
-        <v>256.3928695916873</v>
+        <v>254.7987929994329</v>
       </c>
       <c r="D9" t="n">
-        <v>252.6467135530789</v>
+        <v>250.116078478</v>
       </c>
       <c r="E9" t="n">
-        <v>253.4935760498047</v>
+        <v>251.3814086914062</v>
       </c>
       <c r="F9" t="n">
-        <v>60275200</v>
+        <v>42303700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>254.2807025242173</v>
+        <v>252.2780882048451</v>
       </c>
       <c r="C10" t="n">
-        <v>254.7987929994329</v>
+        <v>256.2235204411851</v>
       </c>
       <c r="D10" t="n">
-        <v>250.116078478</v>
+        <v>250.7836088309123</v>
       </c>
       <c r="E10" t="n">
-        <v>251.3814086914062</v>
+        <v>255.9246063232422</v>
       </c>
       <c r="F10" t="n">
-        <v>42303700</v>
+        <v>55202100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>252.2780882048451</v>
+        <v>253.1648106749593</v>
       </c>
       <c r="C11" t="n">
-        <v>256.2235204411851</v>
+        <v>256.6519291955366</v>
       </c>
       <c r="D11" t="n">
-        <v>250.7836088309123</v>
+        <v>252.8459811129583</v>
       </c>
       <c r="E11" t="n">
-        <v>255.9246063232422</v>
+        <v>254.5198059082031</v>
       </c>
       <c r="F11" t="n">
-        <v>55202100</v>
+        <v>46076300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>253.1648106749593</v>
+        <v>253.6231177228549</v>
       </c>
       <c r="C12" t="n">
-        <v>256.6519291955366</v>
+        <v>254.0615007840798</v>
       </c>
       <c r="D12" t="n">
-        <v>252.8459811129583</v>
+        <v>252.0788192854059</v>
       </c>
       <c r="E12" t="n">
-        <v>254.5198059082031</v>
+        <v>253.4935913085938</v>
       </c>
       <c r="F12" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>253.6231024562692</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C13" t="n">
-        <v>254.061485491106</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D13" t="n">
-        <v>252.0788041117777</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E13" t="n">
-        <v>253.4935760498047</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F13" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C14" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D14" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E14" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F14" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>254.1013624635733</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C15" t="n">
-        <v>257.8375764362911</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D15" t="n">
-        <v>253.9917666915456</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E15" t="n">
-        <v>254.5098571777344</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F15" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C16" t="n">
-        <v>257.229778167004</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D16" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E16" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F16" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0405037108186</v>
       </c>
       <c r="C17" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165459888059</v>
       </c>
       <c r="D17" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113366309766</v>
       </c>
       <c r="E17" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7453002929688</v>
       </c>
       <c r="F17" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>257.0404883747525</v>
+        <v>255.8648286012466</v>
       </c>
       <c r="C18" t="n">
-        <v>258.1165305885388</v>
+        <v>256.452653504112</v>
       </c>
       <c r="D18" t="n">
-        <v>254.1113214696764</v>
+        <v>254.48990271765</v>
       </c>
       <c r="E18" t="n">
-        <v>255.7452850341797</v>
+        <v>255.5360565185547</v>
       </c>
       <c r="F18" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>255.8648286012466</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C19" t="n">
-        <v>256.452653504112</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D19" t="n">
-        <v>254.48990271765</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E19" t="n">
-        <v>255.5360565185547</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F19" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>255.5759191543519</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C20" t="n">
-        <v>257.5685585594684</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D20" t="n">
-        <v>255.1674244276712</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E20" t="n">
-        <v>257.1102600097656</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F20" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>256.8611554198282</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C21" t="n">
-        <v>257.0504585775582</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D21" t="n">
-        <v>252.2083446799687</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E21" t="n">
-        <v>253.1050262451172</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F21" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C22" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D22" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E22" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F22" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C23" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D23" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E23" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F23" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>245.6924164271231</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C24" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D24" t="n">
-        <v>243.7994000887665</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E24" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F24" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C25" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D25" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E25" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F25" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>247.3363501327598</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C26" t="n">
-        <v>248.1234359576197</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D26" t="n">
-        <v>244.2278377270511</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E26" t="n">
-        <v>246.5392913818359</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F26" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C27" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D27" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E27" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F27" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>254.9482507697476</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C28" t="n">
-        <v>263.4070106066718</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D28" t="n">
-        <v>254.6892131172966</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E28" t="n">
-        <v>261.2748718261719</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F28" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>260.9162087553024</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C29" t="n">
-        <v>264.3136625920602</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D29" t="n">
-        <v>260.8663745269806</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E29" t="n">
-        <v>261.8029174804688</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F29" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>261.6833648565789</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C30" t="n">
-        <v>261.882640960004</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D30" t="n">
-        <v>254.4899353587398</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E30" t="n">
-        <v>257.4988403320312</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F30" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>258.9833246632869</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C31" t="n">
-        <v>259.6608147081683</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D31" t="n">
-        <v>257.0604350924048</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E31" t="n">
-        <v>258.6246337890625</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F31" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C32" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D32" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E32" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F32" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>263.9051799132</v>
+        <v>268.0000063221084</v>
       </c>
       <c r="C33" t="n">
-        <v>268.1295659182063</v>
+        <v>268.8967183092298</v>
       </c>
       <c r="D33" t="n">
-        <v>263.6760154250923</v>
+        <v>267.1631014853557</v>
       </c>
       <c r="E33" t="n">
-        <v>267.8207092285156</v>
+        <v>268.0099792480469</v>
       </c>
       <c r="F33" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>268.000036838551</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C34" t="n">
-        <v>268.8967489277785</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D34" t="n">
-        <v>267.1631319065021</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E34" t="n">
-        <v>268.010009765625</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F34" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C35" t="n">
-        <v>270.4110953948544</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D35" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E35" t="n">
-        <v>268.7073974609375</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F35" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>270.9889785237465</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C36" t="n">
-        <v>273.131090148023</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D36" t="n">
-        <v>267.4919171420091</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E36" t="n">
-        <v>270.4011535644531</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F36" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>275.9705701844509</v>
+        <v>269.424736694289</v>
       </c>
       <c r="C37" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531467885877</v>
       </c>
       <c r="D37" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2700709373508</v>
       </c>
       <c r="E37" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597534179688</v>
       </c>
       <c r="F37" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>269.424736694289</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C38" t="n">
-        <v>269.8531467885877</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D38" t="n">
-        <v>265.2700709373508</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E38" t="n">
-        <v>268.0597534179688</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F38" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C39" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D39" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E39" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F39" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C40" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D40" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E40" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F40" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C41" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D41" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E41" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F41" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,25 +1509,25 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>268.8069946610708</v>
+        <v>268.2298830249396</v>
       </c>
       <c r="C42" t="n">
-        <v>271.2878509444664</v>
+        <v>272.9869540449525</v>
       </c>
       <c r="D42" t="n">
-        <v>265.7881477280068</v>
+        <v>266.7339548671466</v>
       </c>
       <c r="E42" t="n">
-        <v>267.4819030761719</v>
+        <v>268.6986083984375</v>
       </c>
       <c r="F42" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1535,25 +1535,25 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>268.2298830249396</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C43" t="n">
-        <v>272.9869540449525</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D43" t="n">
-        <v>266.7339548671466</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E43" t="n">
-        <v>268.6986083984375</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F43" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G43" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C44" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D44" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E44" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F44" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C45" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D45" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E45" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F45" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3141778275755</v>
       </c>
       <c r="C46" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108524736826</v>
       </c>
       <c r="D46" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681323529343</v>
       </c>
       <c r="E46" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705017089844</v>
       </c>
       <c r="F46" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>270.3141778275755</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C47" t="n">
-        <v>275.2108524736826</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D47" t="n">
-        <v>268.8681323529343</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E47" t="n">
-        <v>271.6705017089844</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F47" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>268.0902717401977</v>
+        <v>269.2570854665072</v>
       </c>
       <c r="C48" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751321987233</v>
       </c>
       <c r="D48" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997795179588</v>
       </c>
       <c r="E48" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7140197753906</v>
       </c>
       <c r="F48" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>269.2570854665072</v>
+        <v>264.8091896065648</v>
       </c>
       <c r="C49" t="n">
-        <v>269.9751321987233</v>
+        <v>271.4710487380511</v>
       </c>
       <c r="D49" t="n">
-        <v>264.5997795179588</v>
+        <v>264.7792722621166</v>
       </c>
       <c r="E49" t="n">
-        <v>266.7140197753906</v>
+        <v>267.8309631347656</v>
       </c>
       <c r="F49" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>264.8091896065648</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C50" t="n">
-        <v>271.4710487380511</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D50" t="n">
-        <v>264.7792722621166</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E50" t="n">
-        <v>267.8309631347656</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F50" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C51" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D51" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E51" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F51" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>265.2280517805383</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="C52" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480447880167</v>
       </c>
       <c r="D52" t="n">
-        <v>264.9488130991126</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="E52" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1709899902344</v>
       </c>
       <c r="F52" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5227726174851</v>
       </c>
       <c r="C53" t="n">
-        <v>276.2480447880167</v>
+        <v>279.6189174225992</v>
       </c>
       <c r="D53" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5028378637012</v>
       </c>
       <c r="E53" t="n">
-        <v>275.1709899902344</v>
+        <v>276.2181701660156</v>
       </c>
       <c r="F53" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>274.5227726174851</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C54" t="n">
-        <v>279.6189174225992</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D54" t="n">
-        <v>274.5028378637012</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E54" t="n">
-        <v>276.2181701660156</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F54" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C55" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D55" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E55" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F55" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>276.5073679150082</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C56" t="n">
-        <v>278.242634823177</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D56" t="n">
-        <v>275.2407959413455</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E56" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F56" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>277.2553332443013</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C57" t="n">
-        <v>282.6506510943872</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D57" t="n">
-        <v>275.3904143522869</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E57" t="n">
-        <v>282.3315124511719</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F57" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C58" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D58" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E58" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F58" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>285.4231155973949</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C59" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D59" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E59" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F59" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>283.3287830094401</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C60" t="n">
-        <v>283.9570776694276</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D60" t="n">
-        <v>277.8337308175164</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E60" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F60" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C61" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D61" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E61" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F61" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C62" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D62" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E62" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F62" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C63" t="n">
-        <v>279.269820658071</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D63" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E63" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F63" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C64" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D64" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E64" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F64" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>278.342371275548</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C65" t="n">
-        <v>278.8310314000742</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D65" t="n">
-        <v>273.0667227973629</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E65" t="n">
-        <v>277.2752685546875</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F65" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C66" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D66" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E66" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F66" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C67" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D67" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E67" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F67" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C68" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D68" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E68" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F68" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C69" t="n">
-        <v>275.4103308752873</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D69" t="n">
-        <v>270.9026119684932</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E69" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F69" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>272.8672697170699</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C70" t="n">
-        <v>272.887234905205</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D70" t="n">
-        <v>266.225375101995</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E70" t="n">
-        <v>271.4511413574219</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F70" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C71" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D71" t="n">
-        <v>269.1673383776201</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E71" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F71" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C72" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D72" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E72" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F72" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C73" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D73" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E73" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F73" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C74" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D74" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E74" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F74" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C75" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D75" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E75" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F75" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694584675055</v>
       </c>
       <c r="C76" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3360001129787</v>
       </c>
       <c r="D76" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408983628093</v>
       </c>
       <c r="E76" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3387145996094</v>
       </c>
       <c r="F76" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>272.0694584675055</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C77" t="n">
-        <v>273.3360001129787</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D77" t="n">
-        <v>271.5408983628093</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E77" t="n">
-        <v>272.3387145996094</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F77" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209292436991</v>
       </c>
       <c r="C78" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857683126949</v>
       </c>
       <c r="D78" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697691424855</v>
       </c>
       <c r="E78" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743225097656</v>
       </c>
       <c r="F78" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>271.5209292436991</v>
+        <v>269.9053450243044</v>
       </c>
       <c r="C79" t="n">
-        <v>277.0857683126949</v>
+        <v>270.7729784841199</v>
       </c>
       <c r="D79" t="n">
-        <v>268.2697691424855</v>
+        <v>265.4175605620285</v>
       </c>
       <c r="E79" t="n">
-        <v>270.2743225097656</v>
+        <v>266.5345153808594</v>
       </c>
       <c r="F79" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>269.9053450243044</v>
+        <v>266.275215737747</v>
       </c>
       <c r="C80" t="n">
-        <v>270.7729784841199</v>
+        <v>266.8237105625631</v>
       </c>
       <c r="D80" t="n">
-        <v>265.4175605620285</v>
+        <v>261.4084578614468</v>
       </c>
       <c r="E80" t="n">
-        <v>266.5345153808594</v>
+        <v>261.6477966308594</v>
       </c>
       <c r="F80" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>266.275215737747</v>
+        <v>262.4855256371837</v>
       </c>
       <c r="C81" t="n">
-        <v>266.8237105625631</v>
+        <v>262.964203143993</v>
       </c>
       <c r="D81" t="n">
-        <v>261.4084578614468</v>
+        <v>259.1047135716701</v>
       </c>
       <c r="E81" t="n">
-        <v>261.6477966308594</v>
+        <v>259.623291015625</v>
       </c>
       <c r="F81" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>262.4855256371837</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C82" t="n">
-        <v>262.964203143993</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D82" t="n">
-        <v>259.1047135716701</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E82" t="n">
-        <v>259.623291015625</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F82" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>256.3222864925608</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C83" t="n">
-        <v>258.586143863599</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D83" t="n">
-        <v>255.0058776573516</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E83" t="n">
-        <v>258.3368225097656</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F83" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4565110528425</v>
       </c>
       <c r="C84" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906861738287</v>
       </c>
       <c r="D84" t="n">
-        <v>255.524480970152</v>
+        <v>256.1029014720883</v>
       </c>
       <c r="E84" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435485839844</v>
       </c>
       <c r="F84" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>258.4565110528425</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C85" t="n">
-        <v>260.5906861738287</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D85" t="n">
-        <v>256.1029014720883</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E85" t="n">
-        <v>259.5435485839844</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F85" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>258.017707787092</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C86" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D86" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E86" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F86" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>258.7855776250856</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C87" t="n">
-        <v>261.1092696408236</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D87" t="n">
-        <v>256.0131254420647</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E87" t="n">
-        <v>259.2543029785156</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F87" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1999111311508</v>
       </c>
       <c r="C88" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1971965798445</v>
       </c>
       <c r="D88" t="n">
-        <v>256.3522089636155</v>
+        <v>254.2379721311412</v>
       </c>
       <c r="E88" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363494873047</v>
       </c>
       <c r="F88" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>257.1999111311508</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C89" t="n">
-        <v>258.1971965798445</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D89" t="n">
-        <v>254.2379721311412</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E89" t="n">
-        <v>254.8363494873047</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F89" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C90" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D90" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E90" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F90" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>248.0248902004531</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C91" t="n">
-        <v>250.8771272171802</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D91" t="n">
-        <v>244.5144411297041</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E91" t="n">
-        <v>246.9777374267578</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F91" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C92" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D92" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E92" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F92" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>246.6486371992728</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C93" t="n">
-        <v>248.7329600733879</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D93" t="n">
-        <v>244.0157890837153</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E93" t="n">
-        <v>247.3666687011719</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F93" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664593428383</v>
       </c>
       <c r="C94" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389114176715</v>
       </c>
       <c r="D94" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090434871919</v>
       </c>
       <c r="E94" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5688781738281</v>
       </c>
       <c r="F94" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>258.4664593428383</v>
+        <v>256.9506034196754</v>
       </c>
       <c r="C95" t="n">
-        <v>261.2389114176715</v>
+        <v>258.1573103549757</v>
       </c>
       <c r="D95" t="n">
-        <v>257.5090434871919</v>
+        <v>253.8191275531099</v>
       </c>
       <c r="E95" t="n">
-        <v>257.5688781738281</v>
+        <v>255.743896484375</v>
       </c>
       <c r="F95" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>256.9506034196754</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C96" t="n">
-        <v>258.1573103549757</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D96" t="n">
-        <v>253.8191275531099</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E96" t="n">
-        <v>255.743896484375</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F96" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C97" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D97" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E97" t="n">
-        <v>257.5788879394531</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F97" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C98" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D98" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E98" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F98" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C99" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D99" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E99" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F99" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C100" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D100" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E100" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F100" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>271.5508302866565</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C101" t="n">
-        <v>278.1927542185059</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D101" t="n">
-        <v>271.5508302866565</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E101" t="n">
-        <v>275.7394104003906</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F101" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>277.3750162493594</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C102" t="n">
-        <v>278.7412924914769</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D102" t="n">
-        <v>272.48832346973</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E102" t="n">
-        <v>275.1610412597656</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F102" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,25 +3095,25 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>276.3677049075235</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C103" t="n">
-        <v>280.1474248180158</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D103" t="n">
-        <v>276.1782182606431</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E103" t="n">
-        <v>277.364990234375</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F103" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3121,25 +3121,25 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C104" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D104" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E104" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F104" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C105" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D105" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E105" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F105" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C106" t="n">
-        <v>279.6808719096702</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D106" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E106" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F106" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>275.0990906441111</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C107" t="n">
-        <v>275.228863950531</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D107" t="n">
-        <v>259.7165366668213</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E107" t="n">
-        <v>261.2637939453125</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F107" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C108" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D108" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E108" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F108" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C109" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D109" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E109" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F109" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C110" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D110" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E110" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F110" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C111" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D111" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E111" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F111" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C112" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D112" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E112" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F112" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C113" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D113" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E113" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F113" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C114" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D114" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E114" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F114" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C115" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D115" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E115" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F115" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C116" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D116" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E116" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F116" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>272.3240124520744</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C117" t="n">
-        <v>272.3240124520744</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D117" t="n">
-        <v>262.4217010495403</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E117" t="n">
-        <v>263.7093811035156</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F117" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C118" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D118" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E118" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F118" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C119" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D119" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E119" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F119" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C120" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D120" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E120" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F120" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C121" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D121" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E121" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F121" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C122" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D122" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E122" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F122" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C123" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D123" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E123" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F123" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>257.1910284571696</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C124" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D124" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E124" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F124" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>260.6248673962081</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C125" t="n">
-        <v>261.6630231774062</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D125" t="n">
-        <v>259.0876023594815</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E125" t="n">
-        <v>260.3453674316406</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F125" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>258.1992253881205</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C126" t="n">
-        <v>258.4887173103141</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D126" t="n">
-        <v>253.7271951166323</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E126" t="n">
-        <v>255.3043823242188</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F126" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C127" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D127" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E127" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F127" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C128" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D128" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E128" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F128" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C129" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D129" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E129" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F129" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C130" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D130" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E130" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F130" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C131" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D131" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E131" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F131" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C132" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D132" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E132" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F132" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C133" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D133" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E133" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F133" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C134" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D134" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E134" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F134" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C135" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D135" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E135" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F135" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C136" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D136" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E136" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F136" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C137" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D137" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E137" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F137" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C138" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D138" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E138" t="n">
-        <v>246.1906585693359</v>
+        <v>253.337890625</v>
       </c>
       <c r="F138" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>247.4683756415328</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C139" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D139" t="n">
-        <v>246.6598210163149</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E139" t="n">
-        <v>253.337890625</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F139" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>253.6273797300248</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C140" t="n">
-        <v>255.7236296181179</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D140" t="n">
-        <v>252.8787157917901</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E140" t="n">
-        <v>255.1746215820312</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F140" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>253.7471740568136</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C141" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D141" t="n">
-        <v>250.2034948550391</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E141" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F141" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>256.053045051996</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C142" t="n">
-        <v>261.6929736576745</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D142" t="n">
-        <v>256.003115847535</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E142" t="n">
-        <v>258.3988342285156</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F142" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C143" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D143" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E143" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F143" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>257.9896016596085</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C144" t="n">
-        <v>259.2872736156141</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D144" t="n">
-        <v>256.0730086009651</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E144" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F144" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>258.5386040524215</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C145" t="n">
-        <v>260.6548225010532</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D145" t="n">
-        <v>255.6138310165902</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E145" t="n">
-        <v>260.0259399414062</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F145" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C146" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D146" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E146" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F146" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C147" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D147" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E147" t="n">
-        <v>258.73828125</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F147" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>258.7881616833942</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C148" t="n">
-        <v>261.4633801130582</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D148" t="n">
-        <v>256.7318338868242</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E148" t="n">
-        <v>258.368896484375</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F148" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C149" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D149" t="n">
-        <v>257.3507435512608</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E149" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F149" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>266.3246925362851</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C150" t="n">
-        <v>266.6840670491935</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D150" t="n">
-        <v>260.804545264895</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E150" t="n">
-        <v>262.9307556152344</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F150" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C151" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D151" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E151" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F151" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C152" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D152" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E152" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F152" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C153" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D153" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E153" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F153" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C154" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D154" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E154" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F154" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C155" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D155" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E155" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F155" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C156" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D156" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E156" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F156" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C157" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D157" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E157" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F157" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C158" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D158" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E158" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F158" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C159" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D159" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E159" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F159" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C160" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D160" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E160" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F160" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>278.3632116979401</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C161" t="n">
-        <v>286.7083346607987</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D161" t="n">
-        <v>277.8740943540899</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E161" t="n">
-        <v>279.6409606933594</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F161" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>279.1618288412153</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C162" t="n">
-        <v>280.130102141665</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D162" t="n">
-        <v>274.3703610857382</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E162" t="n">
-        <v>276.3368530273438</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F162" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>276.43668191704</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C163" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D163" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E163" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F163" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>281.4177950537395</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C164" t="n">
-        <v>287.5168959460148</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D164" t="n">
-        <v>280.5693031693742</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E164" t="n">
-        <v>286.9978332519531</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F164" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>288.7546745760609</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C165" t="n">
-        <v>291.6095955251437</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D165" t="n">
-        <v>285.2709015174152</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E165" t="n">
-        <v>286.9279479980469</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F165" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,25 +4733,25 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C166" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D166" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E166" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F166" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -4759,25 +4759,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C167" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D167" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E167" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F167" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G167" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C168" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D168" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E168" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F168" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C169" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D169" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E169" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F169" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C170" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D170" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E170" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F170" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C171" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D171" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E171" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F171" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C172" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D172" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E172" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F172" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C173" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D173" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E173" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F173" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C174" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D174" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E174" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F174" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C175" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D175" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E175" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F175" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C176" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D176" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E176" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F176" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C177" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D177" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E177" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F177" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C178" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D178" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E178" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F178" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C179" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D179" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E179" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F179" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C180" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D180" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E180" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F180" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C181" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D181" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E181" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F181" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C182" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D182" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E182" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F182" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C183" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D183" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E183" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F183" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C184" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D184" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E184" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F184" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C185" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D185" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E185" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F185" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C186" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D186" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E186" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F186" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C187" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D187" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E187" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F187" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C188" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D188" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E188" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F188" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C189" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D189" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E189" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F189" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C190" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D190" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E190" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F190" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C191" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D191" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E191" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F191" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C192" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D192" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E192" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F192" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C193" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D193" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E193" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F193" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C194" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D194" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E194" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F194" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C195" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D195" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E195" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F195" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C196" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D196" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E196" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F196" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C197" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D197" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E197" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F197" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C198" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D198" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E198" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F198" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C199" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D199" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E199" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F199" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C200" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D200" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E200" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F200" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C201" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D201" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E201" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F201" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C202" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D202" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E202" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F202" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C203" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D203" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E203" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F203" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C204" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D204" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E204" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F204" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C205" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D205" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E205" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F205" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C206" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D206" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E206" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F206" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C207" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D207" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E207" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F207" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C208" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D208" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E208" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F208" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C209" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D209" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E209" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F209" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C210" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D210" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E210" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F210" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C211" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D211" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E211" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F211" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C212" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D212" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E212" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F212" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C213" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D213" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E213" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F213" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C214" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D214" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E214" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F214" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C215" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D215" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E215" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F215" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C216" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D216" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E216" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F216" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C217" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D217" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E217" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F217" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C218" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D218" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E218" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F218" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C219" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D219" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E219" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F219" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C220" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D220" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E220" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F220" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C221" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D221" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E221" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F221" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C222" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D222" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E222" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F222" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C223" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D223" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E223" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F223" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C224" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D224" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E224" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F224" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C225" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D225" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E225" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F225" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C226" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D226" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E226" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F226" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C227" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D227" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E227" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F227" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,25 +6345,25 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C228" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D228" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E228" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F228" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -6371,25 +6371,25 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C229" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D229" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E229" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F229" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G229" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C230" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D230" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E230" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F230" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C231" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D231" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E231" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F231" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C232" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D232" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E232" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F232" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C233" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D233" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E233" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F233" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C234" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E234" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F234" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C235" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D235" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E235" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F235" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C236" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D236" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E236" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F236" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C237" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D237" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E237" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F237" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C238" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D238" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E238" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F238" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C239" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D239" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E239" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F239" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C240" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D240" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F240" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C241" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D241" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E241" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F241" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C242" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D242" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E242" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F242" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C243" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D243" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E243" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C243" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D243" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E243" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F243" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C244" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D244" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E244" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C245" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D245" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F245" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C246" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D246" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E246" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F246" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C247" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D247" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E247" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F247" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D248" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E248" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F248" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C249" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D249" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E249" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F249" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D250" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E250" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C251" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D251" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F251" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C252" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D252" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E252" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F252" t="n">
-        <v>50659000</v>
+        <v>39223900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,34 +10498,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>333.08</v>
+      </c>
+      <c r="D2" t="n">
         <v>332.27</v>
       </c>
-      <c r="D2" t="n">
-        <v>326.57</v>
-      </c>
       <c r="E2" t="n">
-        <v>327.63</v>
+        <v>334.83</v>
       </c>
       <c r="F2" t="n">
-        <v>336.219</v>
+        <v>335.5</v>
       </c>
       <c r="G2" t="n">
-        <v>326.3</v>
+        <v>331.34</v>
       </c>
       <c r="H2" t="n">
-        <v>50423955</v>
+        <v>38702066</v>
       </c>
       <c r="I2" t="n">
-        <v>54055456</v>
+        <v>53820953</v>
       </c>
       <c r="J2" t="n">
-        <v>4849207869440</v>
+        <v>4861029515264</v>
       </c>
       <c r="K2" t="n">
-        <v>38.148106</v>
+        <v>38.2411</v>
       </c>
       <c r="L2" t="n">
-        <v>34.703167</v>
+        <v>34.757923</v>
       </c>
       <c r="M2" t="n">
         <v>8.710000000000001</v>
@@ -10564,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.14538</v>
+        <v>45.255432</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4871152992256</v>
+        <v>4882974638080</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:46:42</t>
+          <t>2026-09-15 14:13:48</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>236.1277410783948</v>
+        <v>238.0905124651219</v>
       </c>
       <c r="C2" t="n">
-        <v>237.3133638141207</v>
+        <v>239.216358555688</v>
       </c>
       <c r="D2" t="n">
-        <v>234.1649902844441</v>
+        <v>236.8550706028844</v>
       </c>
       <c r="E2" t="n">
-        <v>235.8288421630859</v>
+        <v>238.1104431152344</v>
       </c>
       <c r="F2" t="n">
-        <v>42699500</v>
+        <v>46508000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>236.3070825366735</v>
+        <v>239.0868055705458</v>
       </c>
       <c r="C3" t="n">
-        <v>240.3322223551857</v>
+        <v>240.3122743702574</v>
       </c>
       <c r="D3" t="n">
-        <v>235.4502622494337</v>
+        <v>235.7790173404318</v>
       </c>
       <c r="E3" t="n">
-        <v>237.2735137939453</v>
+        <v>237.0045013427734</v>
       </c>
       <c r="F3" t="n">
-        <v>63421100</v>
+        <v>44249600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>238.0905124651219</v>
+        <v>240.3421770415445</v>
       </c>
       <c r="C4" t="n">
-        <v>239.216358555688</v>
+        <v>245.3935247988757</v>
       </c>
       <c r="D4" t="n">
-        <v>236.8550706028844</v>
+        <v>239.3259419777209</v>
       </c>
       <c r="E4" t="n">
-        <v>238.1104431152344</v>
+        <v>244.5964660644531</v>
       </c>
       <c r="F4" t="n">
-        <v>46508000</v>
+        <v>163741300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>239.0868055705458</v>
+        <v>247.3861620644307</v>
       </c>
       <c r="C5" t="n">
-        <v>240.3122743702574</v>
+        <v>255.6954791611581</v>
       </c>
       <c r="D5" t="n">
-        <v>235.7790173404318</v>
+        <v>247.2068166293636</v>
       </c>
       <c r="E5" t="n">
-        <v>237.0045013427734</v>
+        <v>255.1375122070312</v>
       </c>
       <c r="F5" t="n">
-        <v>44249600</v>
+        <v>105517400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>240.3421770415445</v>
+        <v>254.9382515607796</v>
       </c>
       <c r="C6" t="n">
-        <v>245.3935247988757</v>
+        <v>256.3928695916873</v>
       </c>
       <c r="D6" t="n">
-        <v>239.3259419777209</v>
+        <v>252.6467135530789</v>
       </c>
       <c r="E6" t="n">
-        <v>244.5964660644531</v>
+        <v>253.4935760498047</v>
       </c>
       <c r="F6" t="n">
-        <v>163741300</v>
+        <v>60275200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>247.3861620644307</v>
+        <v>254.2807025242173</v>
       </c>
       <c r="C7" t="n">
-        <v>255.6954791611581</v>
+        <v>254.7987929994329</v>
       </c>
       <c r="D7" t="n">
-        <v>247.2068166293636</v>
+        <v>250.116078478</v>
       </c>
       <c r="E7" t="n">
-        <v>255.1375122070312</v>
+        <v>251.3814086914062</v>
       </c>
       <c r="F7" t="n">
-        <v>105517400</v>
+        <v>42303700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>254.9382669065294</v>
+        <v>252.2780882048451</v>
       </c>
       <c r="C8" t="n">
-        <v>256.3928850249964</v>
+        <v>256.2235204411851</v>
       </c>
       <c r="D8" t="n">
-        <v>252.646728760892</v>
+        <v>250.7836088309123</v>
       </c>
       <c r="E8" t="n">
-        <v>253.4935913085938</v>
+        <v>255.9246063232422</v>
       </c>
       <c r="F8" t="n">
-        <v>60275200</v>
+        <v>55202100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>254.2807025242173</v>
+        <v>253.1648106749593</v>
       </c>
       <c r="C9" t="n">
-        <v>254.7987929994329</v>
+        <v>256.6519291955366</v>
       </c>
       <c r="D9" t="n">
-        <v>250.116078478</v>
+        <v>252.8459811129583</v>
       </c>
       <c r="E9" t="n">
-        <v>251.3814086914062</v>
+        <v>254.5198059082031</v>
       </c>
       <c r="F9" t="n">
-        <v>42303700</v>
+        <v>46076300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>252.2780882048451</v>
+        <v>253.6231024562692</v>
       </c>
       <c r="C10" t="n">
-        <v>256.2235204411851</v>
+        <v>254.061485491106</v>
       </c>
       <c r="D10" t="n">
-        <v>250.7836088309123</v>
+        <v>252.0788041117777</v>
       </c>
       <c r="E10" t="n">
-        <v>255.9246063232422</v>
+        <v>253.4935760498047</v>
       </c>
       <c r="F10" t="n">
-        <v>55202100</v>
+        <v>40127700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>253.1648106749593</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C11" t="n">
-        <v>256.6519291955366</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D11" t="n">
-        <v>252.8459811129583</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E11" t="n">
-        <v>254.5198059082031</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F11" t="n">
-        <v>46076300</v>
+        <v>37704300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>253.6231177228549</v>
+        <v>254.1013624635733</v>
       </c>
       <c r="C12" t="n">
-        <v>254.0615007840798</v>
+        <v>257.8375764362911</v>
       </c>
       <c r="D12" t="n">
-        <v>252.0788192854059</v>
+        <v>253.9917666915456</v>
       </c>
       <c r="E12" t="n">
-        <v>253.4935913085938</v>
+        <v>254.5098571777344</v>
       </c>
       <c r="F12" t="n">
-        <v>40127700</v>
+        <v>48713900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>253.9220203508673</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C13" t="n">
-        <v>254.9781167214257</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D13" t="n">
-        <v>252.1784610063259</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E13" t="n">
-        <v>253.69287109375</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F13" t="n">
-        <v>37704300</v>
+        <v>42630200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>254.101347229275</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C14" t="n">
-        <v>257.8375609779932</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D14" t="n">
-        <v>253.9917514638179</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E14" t="n">
-        <v>254.5098419189453</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F14" t="n">
-        <v>48713900</v>
+        <v>49155600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>255.6356607808825</v>
+        <v>257.0404883747525</v>
       </c>
       <c r="C15" t="n">
-        <v>257.229778167004</v>
+        <v>258.1165305885388</v>
       </c>
       <c r="D15" t="n">
-        <v>253.2146115335708</v>
+        <v>254.1113214696764</v>
       </c>
       <c r="E15" t="n">
-        <v>256.1836547851562</v>
+        <v>255.7452850341797</v>
       </c>
       <c r="F15" t="n">
-        <v>42630200</v>
+        <v>44664100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>253.7327119799983</v>
+        <v>255.8648286012466</v>
       </c>
       <c r="C16" t="n">
-        <v>258.2858846694617</v>
+        <v>256.452653504112</v>
       </c>
       <c r="D16" t="n">
-        <v>253.0153606481908</v>
+        <v>254.48990271765</v>
       </c>
       <c r="E16" t="n">
-        <v>257.0703735351562</v>
+        <v>255.5360565185547</v>
       </c>
       <c r="F16" t="n">
-        <v>49155600</v>
+        <v>31955800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>257.0405037108186</v>
+        <v>255.5759191543519</v>
       </c>
       <c r="C17" t="n">
-        <v>258.1165459888059</v>
+        <v>257.5685585594684</v>
       </c>
       <c r="D17" t="n">
-        <v>254.1113366309766</v>
+        <v>255.1674244276712</v>
       </c>
       <c r="E17" t="n">
-        <v>255.7453002929688</v>
+        <v>257.1102600097656</v>
       </c>
       <c r="F17" t="n">
-        <v>44664100</v>
+        <v>36496900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>255.8648286012466</v>
+        <v>256.8611554198282</v>
       </c>
       <c r="C18" t="n">
-        <v>256.452653504112</v>
+        <v>257.0504585775582</v>
       </c>
       <c r="D18" t="n">
-        <v>254.48990271765</v>
+        <v>252.2083446799687</v>
       </c>
       <c r="E18" t="n">
-        <v>255.5360565185547</v>
+        <v>253.1050262451172</v>
       </c>
       <c r="F18" t="n">
-        <v>31955800</v>
+        <v>38322000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>255.5758888188916</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C19" t="n">
-        <v>257.5685279874928</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D19" t="n">
-        <v>255.1673941406971</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E19" t="n">
-        <v>257.1102294921875</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F19" t="n">
-        <v>36496900</v>
+        <v>61999100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>256.8611399345957</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C20" t="n">
-        <v>257.0504430809132</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D20" t="n">
-        <v>252.2083294752373</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E20" t="n">
-        <v>253.1050109863281</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F20" t="n">
-        <v>38322000</v>
+        <v>38142900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>254.0017181605697</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C21" t="n">
-        <v>255.436420799504</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D21" t="n">
-        <v>243.1019794369982</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E21" t="n">
-        <v>244.3673095703125</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F21" t="n">
-        <v>61999100</v>
+        <v>35478000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>248.462190854235</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C22" t="n">
-        <v>248.7710475029622</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D22" t="n">
-        <v>244.6562426215344</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E22" t="n">
-        <v>246.7485198974609</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F22" t="n">
-        <v>38142900</v>
+        <v>33893600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>245.6924164271231</v>
+        <v>247.3363501327598</v>
       </c>
       <c r="C23" t="n">
-        <v>247.9341354996238</v>
+        <v>248.1234359576197</v>
       </c>
       <c r="D23" t="n">
-        <v>243.7994000887665</v>
+        <v>244.2278377270511</v>
       </c>
       <c r="E23" t="n">
-        <v>246.8581085205078</v>
+        <v>246.5392913818359</v>
       </c>
       <c r="F23" t="n">
-        <v>35478000</v>
+        <v>39777000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>248.571774561702</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C24" t="n">
-        <v>250.8932009800968</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D24" t="n">
-        <v>246.5592047770515</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E24" t="n">
-        <v>248.4223175048828</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F24" t="n">
-        <v>33893600</v>
+        <v>49147000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>247.3363348246392</v>
+        <v>254.9482507697476</v>
       </c>
       <c r="C25" t="n">
-        <v>248.1234206007849</v>
+        <v>263.4070106066718</v>
       </c>
       <c r="D25" t="n">
-        <v>244.2278226113223</v>
+        <v>254.6892131172966</v>
       </c>
       <c r="E25" t="n">
-        <v>246.5392761230469</v>
+        <v>261.2748718261719</v>
       </c>
       <c r="F25" t="n">
-        <v>39777000</v>
+        <v>90483000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>247.1071917036077</v>
+        <v>260.9162087553024</v>
       </c>
       <c r="C26" t="n">
-        <v>252.447465373221</v>
+        <v>264.3136625920602</v>
       </c>
       <c r="D26" t="n">
-        <v>246.359952002837</v>
+        <v>260.8663745269806</v>
       </c>
       <c r="E26" t="n">
-        <v>251.3614654541016</v>
+        <v>261.8029174804688</v>
       </c>
       <c r="F26" t="n">
-        <v>49147000</v>
+        <v>46695900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>254.9482209911351</v>
+        <v>261.6833648565789</v>
       </c>
       <c r="C27" t="n">
-        <v>263.4069798400544</v>
+        <v>261.882640960004</v>
       </c>
       <c r="D27" t="n">
-        <v>254.6891833689404</v>
+        <v>254.4899353587398</v>
       </c>
       <c r="E27" t="n">
-        <v>261.2748413085938</v>
+        <v>257.4988403320312</v>
       </c>
       <c r="F27" t="n">
-        <v>90483000</v>
+        <v>45015300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>260.9161783410852</v>
+        <v>258.9833246632869</v>
       </c>
       <c r="C28" t="n">
-        <v>264.3136317818121</v>
+        <v>259.6608147081683</v>
       </c>
       <c r="D28" t="n">
-        <v>260.8663441185724</v>
+        <v>257.0604350924048</v>
       </c>
       <c r="E28" t="n">
-        <v>261.8028869628906</v>
+        <v>258.6246337890625</v>
       </c>
       <c r="F28" t="n">
-        <v>46695900</v>
+        <v>32754900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>261.6833338430701</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C29" t="n">
-        <v>261.882609922878</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D29" t="n">
-        <v>254.4899051977633</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E29" t="n">
-        <v>257.4988098144531</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F29" t="n">
-        <v>45015300</v>
+        <v>38253700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>258.9832941033833</v>
+        <v>263.9051799132</v>
       </c>
       <c r="C30" t="n">
-        <v>259.6607840683213</v>
+        <v>268.1295659182063</v>
       </c>
       <c r="D30" t="n">
-        <v>257.0604047594014</v>
+        <v>263.6760154250923</v>
       </c>
       <c r="E30" t="n">
-        <v>258.6246032714844</v>
+        <v>267.8207092285156</v>
       </c>
       <c r="F30" t="n">
-        <v>32754900</v>
+        <v>44888200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>260.2287163700197</v>
+        <v>268.000036838551</v>
       </c>
       <c r="C31" t="n">
-        <v>263.1578983995789</v>
+        <v>268.8967489277785</v>
       </c>
       <c r="D31" t="n">
-        <v>258.2261042627009</v>
+        <v>267.1631319065021</v>
       </c>
       <c r="E31" t="n">
-        <v>261.8527221679688</v>
+        <v>268.010009765625</v>
       </c>
       <c r="F31" t="n">
-        <v>38253700</v>
+        <v>41534800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>263.9051498417878</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C32" t="n">
-        <v>268.1295353654346</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D32" t="n">
-        <v>263.6759853797928</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E32" t="n">
-        <v>267.8206787109375</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F32" t="n">
-        <v>44888200</v>
+        <v>51086700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>268.0000063221084</v>
+        <v>270.9889785237465</v>
       </c>
       <c r="C33" t="n">
-        <v>268.8967183092298</v>
+        <v>273.131090148023</v>
       </c>
       <c r="D33" t="n">
-        <v>267.1631014853557</v>
+        <v>267.4919171420091</v>
       </c>
       <c r="E33" t="n">
-        <v>268.0099792480469</v>
+        <v>270.4011535644531</v>
       </c>
       <c r="F33" t="n">
-        <v>41534800</v>
+        <v>69886500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>268.2889298674747</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C34" t="n">
-        <v>270.4110953948544</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D34" t="n">
-        <v>266.1269030442272</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E34" t="n">
-        <v>268.7073974609375</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F34" t="n">
-        <v>51086700</v>
+        <v>86167100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>270.9889479398262</v>
+        <v>269.424736694289</v>
       </c>
       <c r="C35" t="n">
-        <v>273.1310593223432</v>
+        <v>269.8531467885877</v>
       </c>
       <c r="D35" t="n">
-        <v>267.4918869527685</v>
+        <v>265.2700709373508</v>
       </c>
       <c r="E35" t="n">
-        <v>270.401123046875</v>
+        <v>268.0597534179688</v>
       </c>
       <c r="F35" t="n">
-        <v>69886500</v>
+        <v>50194600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>275.9705701844509</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C36" t="n">
-        <v>276.2993726959702</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D36" t="n">
-        <v>268.1694007015524</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E36" t="n">
-        <v>269.3749389648438</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F36" t="n">
-        <v>86167100</v>
+        <v>49274800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>269.424736694289</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C37" t="n">
-        <v>269.8531467885877</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D37" t="n">
-        <v>265.2700709373508</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E37" t="n">
-        <v>268.0597534179688</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F37" t="n">
-        <v>50194600</v>
+        <v>43683100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>267.3424445625432</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C38" t="n">
-        <v>270.4908183788531</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D38" t="n">
-        <v>266.6350661079627</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E38" t="n">
-        <v>269.0461730957031</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F38" t="n">
-        <v>49274800</v>
+        <v>51204000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>267.6214146886098</v>
+        <v>268.8069946610708</v>
       </c>
       <c r="C39" t="n">
-        <v>270.7000692568828</v>
+        <v>271.2878509444664</v>
       </c>
       <c r="D39" t="n">
-        <v>265.9476049232333</v>
+        <v>265.7881477280068</v>
       </c>
       <c r="E39" t="n">
-        <v>269.1458129882812</v>
+        <v>267.4819030761719</v>
       </c>
       <c r="F39" t="n">
-        <v>43683100</v>
+        <v>48227400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,25 +1457,25 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>266.9040748013871</v>
+        <v>268.2298830249396</v>
       </c>
       <c r="C40" t="n">
-        <v>272.3937751745226</v>
+        <v>272.9869540449525</v>
       </c>
       <c r="D40" t="n">
-        <v>266.9040748013871</v>
+        <v>266.7339548671466</v>
       </c>
       <c r="E40" t="n">
-        <v>268.7771301269531</v>
+        <v>268.6986083984375</v>
       </c>
       <c r="F40" t="n">
-        <v>51204000</v>
+        <v>41312400</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>268.8070253298314</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C41" t="n">
-        <v>271.2878818962731</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D41" t="n">
-        <v>265.7881780523408</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E41" t="n">
-        <v>267.48193359375</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F41" t="n">
-        <v>48227400</v>
+        <v>46208300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,25 +1509,25 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>268.2298830249396</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C42" t="n">
-        <v>272.9869540449525</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D42" t="n">
-        <v>266.7339548671466</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E42" t="n">
-        <v>268.6986083984375</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F42" t="n">
-        <v>41312400</v>
+        <v>48398000</v>
       </c>
       <c r="G42" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>269.0775725813642</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C43" t="n">
-        <v>275.1610196363943</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D43" t="n">
-        <v>269.0675899882029</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E43" t="n">
-        <v>274.5028076171875</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F43" t="n">
-        <v>46208300</v>
+        <v>49602800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>274.2535066981436</v>
+        <v>270.3141778275755</v>
       </c>
       <c r="C44" t="n">
-        <v>274.9815360542478</v>
+        <v>275.2108524736826</v>
       </c>
       <c r="D44" t="n">
-        <v>270.9624767916609</v>
+        <v>268.8681323529343</v>
       </c>
       <c r="E44" t="n">
-        <v>272.7276611328125</v>
+        <v>271.6705017089844</v>
       </c>
       <c r="F44" t="n">
-        <v>48398000</v>
+        <v>47431300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>273.3659002679155</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C45" t="n">
-        <v>275.9488963676571</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D45" t="n">
-        <v>271.3513946141157</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E45" t="n">
-        <v>272.2090759277344</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F45" t="n">
-        <v>49602800</v>
+        <v>45018300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>270.3141778275755</v>
+        <v>269.2570854665072</v>
       </c>
       <c r="C46" t="n">
-        <v>275.2108524736826</v>
+        <v>269.9751321987233</v>
       </c>
       <c r="D46" t="n">
-        <v>268.8681323529343</v>
+        <v>264.5997795179588</v>
       </c>
       <c r="E46" t="n">
-        <v>271.6705017089844</v>
+        <v>266.7140197753906</v>
       </c>
       <c r="F46" t="n">
-        <v>47431300</v>
+        <v>45677300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>268.0902717401977</v>
+        <v>264.8091896065648</v>
       </c>
       <c r="C47" t="n">
-        <v>269.7557213346742</v>
+        <v>271.4710487380511</v>
       </c>
       <c r="D47" t="n">
-        <v>265.0086634694927</v>
+        <v>264.7792722621166</v>
       </c>
       <c r="E47" t="n">
-        <v>266.7339477539062</v>
+        <v>267.8309631347656</v>
       </c>
       <c r="F47" t="n">
-        <v>45018300</v>
+        <v>40424500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>269.2570854665072</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C48" t="n">
-        <v>269.9751321987233</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D48" t="n">
-        <v>264.5997795179588</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E48" t="n">
-        <v>266.7140197753906</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F48" t="n">
-        <v>45677300</v>
+        <v>45823600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>264.8091896065648</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C49" t="n">
-        <v>271.4710487380511</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D49" t="n">
-        <v>264.7792722621166</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E49" t="n">
-        <v>267.8309631347656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F49" t="n">
-        <v>40424500</v>
+        <v>59030800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>270.0948061865016</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="C50" t="n">
-        <v>274.6823253630542</v>
+        <v>276.2480447880167</v>
       </c>
       <c r="D50" t="n">
-        <v>265.1981613886433</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="E50" t="n">
-        <v>265.5272521972656</v>
+        <v>275.1709899902344</v>
       </c>
       <c r="F50" t="n">
-        <v>45823600</v>
+        <v>65585800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>265.2280517805383</v>
+        <v>274.5227726174851</v>
       </c>
       <c r="C51" t="n">
-        <v>272.5879921198442</v>
+        <v>279.6189174225992</v>
       </c>
       <c r="D51" t="n">
-        <v>264.9488130991126</v>
+        <v>274.5028378637012</v>
       </c>
       <c r="E51" t="n">
-        <v>270.7529907226562</v>
+        <v>276.2181701660156</v>
       </c>
       <c r="F51" t="n">
-        <v>59030800</v>
+        <v>46914200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>270.1645980035721</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C52" t="n">
-        <v>276.2480447880167</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D52" t="n">
-        <v>270.1645980035721</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E52" t="n">
-        <v>275.1709899902344</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F52" t="n">
-        <v>65585800</v>
+        <v>33431400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>274.5227726174851</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C53" t="n">
-        <v>279.6189174225992</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D53" t="n">
-        <v>274.5028378637012</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E53" t="n">
-        <v>276.2181701660156</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F53" t="n">
-        <v>46914200</v>
+        <v>20135600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>276.2081750495132</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C54" t="n">
-        <v>278.7712060098946</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D54" t="n">
-        <v>275.8790842359358</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E54" t="n">
-        <v>276.7965698242188</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F54" t="n">
-        <v>33431400</v>
+        <v>46587700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>276.5073679150082</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C55" t="n">
-        <v>278.242634823177</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D55" t="n">
-        <v>275.2407959413455</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E55" t="n">
-        <v>278.0930480957031</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F55" t="n">
-        <v>20135600</v>
+        <v>53669500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>277.2553332443013</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C56" t="n">
-        <v>282.6506510943872</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D56" t="n">
-        <v>275.3904143522869</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E56" t="n">
-        <v>282.3315124511719</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F56" t="n">
-        <v>46587700</v>
+        <v>43538700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>282.231773534172</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C57" t="n">
-        <v>286.619823290159</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D57" t="n">
-        <v>281.8627827987557</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E57" t="n">
-        <v>285.4131164550781</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F57" t="n">
-        <v>53669500</v>
+        <v>43989100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>285.4231155973949</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C58" t="n">
-        <v>287.8365294074879</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D58" t="n">
-        <v>282.5309633672564</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E58" t="n">
-        <v>283.378662109375</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F58" t="n">
-        <v>43538700</v>
+        <v>47265800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>283.3287830094401</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C59" t="n">
-        <v>283.9570776694276</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D59" t="n">
-        <v>277.8337308175164</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E59" t="n">
-        <v>279.9380187988281</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F59" t="n">
-        <v>43989100</v>
+        <v>38211800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>279.7784559281641</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C60" t="n">
-        <v>280.3768332578711</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D60" t="n">
-        <v>277.2951945750906</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E60" t="n">
-        <v>278.0232238769531</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F60" t="n">
-        <v>47265800</v>
+        <v>32193300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>277.374989388386</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C61" t="n">
-        <v>278.9108174051644</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D61" t="n">
-        <v>275.4003533668138</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E61" t="n">
-        <v>277.1356506347656</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F61" t="n">
-        <v>38211800</v>
+        <v>33038300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>277.4049018876359</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C62" t="n">
-        <v>279.269820658071</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D62" t="n">
-        <v>276.1682777692156</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E62" t="n">
-        <v>276.4275512695312</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F62" t="n">
-        <v>32193300</v>
+        <v>33248000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>276.9960211276047</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C63" t="n">
-        <v>278.9905919368044</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D63" t="n">
-        <v>275.6895796823578</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E63" t="n">
-        <v>278.0232238769531</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F63" t="n">
-        <v>33038300</v>
+        <v>39532900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>278.342371275548</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C64" t="n">
-        <v>278.8310314000742</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D64" t="n">
-        <v>273.0667227973629</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E64" t="n">
-        <v>277.2752685546875</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F64" t="n">
-        <v>33248000</v>
+        <v>50409100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>277.1456238228236</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C65" t="n">
-        <v>278.4620479370953</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D65" t="n">
-        <v>276.0685689150702</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E65" t="n">
-        <v>277.5245971679688</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F65" t="n">
-        <v>39532900</v>
+        <v>37648600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>279.3894873363706</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C66" t="n">
-        <v>279.3894873363706</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D66" t="n">
-        <v>272.0993337942639</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E66" t="n">
-        <v>273.3658752441406</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F66" t="n">
-        <v>50409100</v>
+        <v>50138700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>272.0794134956457</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C67" t="n">
-        <v>274.752131096348</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D67" t="n">
-        <v>271.0522107383373</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E67" t="n">
-        <v>273.8645324707031</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F67" t="n">
-        <v>37648600</v>
+        <v>51630700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>274.2634587890498</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C68" t="n">
-        <v>275.4103308752873</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D68" t="n">
-        <v>270.9026119684932</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E68" t="n">
-        <v>271.10205078125</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F68" t="n">
-        <v>50138700</v>
+        <v>144632000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>272.8672697170699</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C69" t="n">
-        <v>272.887234905205</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D69" t="n">
-        <v>266.225375101995</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E69" t="n">
-        <v>271.4511413574219</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F69" t="n">
-        <v>51630700</v>
+        <v>36571800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>271.4112306527045</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C70" t="n">
-        <v>273.8545921928022</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D70" t="n">
-        <v>269.1673383776201</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E70" t="n">
-        <v>272.9271240234375</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F70" t="n">
-        <v>144632000</v>
+        <v>29642000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>272.1192896847017</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C71" t="n">
-        <v>273.1365403084993</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D71" t="n">
-        <v>269.7756932559407</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E71" t="n">
-        <v>270.2344360351562</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F71" t="n">
-        <v>36571800</v>
+        <v>17910600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>270.1048034873943</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C72" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D72" t="n">
-        <v>268.8282792538215</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E72" t="n">
-        <v>271.6206665039062</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F72" t="n">
-        <v>29642000</v>
+        <v>21521800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>271.6007006785171</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C73" t="n">
-        <v>274.6823088952694</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D73" t="n">
-        <v>271.461096549353</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E73" t="n">
-        <v>273.0667114257812</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F73" t="n">
-        <v>17910600</v>
+        <v>23715200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>273.4157835978775</v>
+        <v>272.0694584675055</v>
       </c>
       <c r="C74" t="n">
-        <v>274.6224904749486</v>
+        <v>273.3360001129787</v>
       </c>
       <c r="D74" t="n">
-        <v>272.1192942474183</v>
+        <v>271.5408983628093</v>
       </c>
       <c r="E74" t="n">
-        <v>272.6578369140625</v>
+        <v>272.3387145996094</v>
       </c>
       <c r="F74" t="n">
-        <v>21521800</v>
+        <v>22139600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>271.9497734782625</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C75" t="n">
-        <v>273.6152231466168</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D75" t="n">
-        <v>271.6107000753325</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E75" t="n">
-        <v>273.0168762207031</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F75" t="n">
-        <v>23715200</v>
+        <v>27293600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>272.0694584675055</v>
+        <v>271.5209292436991</v>
       </c>
       <c r="C76" t="n">
-        <v>273.3360001129787</v>
+        <v>277.0857683126949</v>
       </c>
       <c r="D76" t="n">
-        <v>271.5408983628093</v>
+        <v>268.2697691424855</v>
       </c>
       <c r="E76" t="n">
-        <v>272.3387145996094</v>
+        <v>270.2743225097656</v>
       </c>
       <c r="F76" t="n">
-        <v>22139600</v>
+        <v>37838100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>272.3187639976345</v>
+        <v>269.9053450243044</v>
       </c>
       <c r="C77" t="n">
-        <v>272.9370761103812</v>
+        <v>270.7729784841199</v>
       </c>
       <c r="D77" t="n">
-        <v>271.0123224859311</v>
+        <v>265.4175605620285</v>
       </c>
       <c r="E77" t="n">
-        <v>271.1220092773438</v>
+        <v>266.5345153808594</v>
       </c>
       <c r="F77" t="n">
-        <v>27293600</v>
+        <v>45647200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>271.5209292436991</v>
+        <v>266.275215737747</v>
       </c>
       <c r="C78" t="n">
-        <v>277.0857683126949</v>
+        <v>266.8237105625631</v>
       </c>
       <c r="D78" t="n">
-        <v>268.2697691424855</v>
+        <v>261.4084578614468</v>
       </c>
       <c r="E78" t="n">
-        <v>270.2743225097656</v>
+        <v>261.6477966308594</v>
       </c>
       <c r="F78" t="n">
-        <v>37838100</v>
+        <v>52352100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>269.9053450243044</v>
+        <v>262.4855256371837</v>
       </c>
       <c r="C79" t="n">
-        <v>270.7729784841199</v>
+        <v>262.964203143993</v>
       </c>
       <c r="D79" t="n">
-        <v>265.4175605620285</v>
+        <v>259.1047135716701</v>
       </c>
       <c r="E79" t="n">
-        <v>266.5345153808594</v>
+        <v>259.623291015625</v>
       </c>
       <c r="F79" t="n">
-        <v>45647200</v>
+        <v>48309800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>266.275215737747</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C80" t="n">
-        <v>266.8237105625631</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D80" t="n">
-        <v>261.4084578614468</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E80" t="n">
-        <v>261.6477966308594</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F80" t="n">
-        <v>52352100</v>
+        <v>50419300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>262.4855256371837</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C81" t="n">
-        <v>262.964203143993</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D81" t="n">
-        <v>259.1047135716701</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E81" t="n">
-        <v>259.623291015625</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F81" t="n">
-        <v>48309800</v>
+        <v>39997000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>256.3222864925608</v>
+        <v>258.4565110528425</v>
       </c>
       <c r="C82" t="n">
-        <v>258.586143863599</v>
+        <v>260.5906861738287</v>
       </c>
       <c r="D82" t="n">
-        <v>255.0058776573516</v>
+        <v>256.1029014720883</v>
       </c>
       <c r="E82" t="n">
-        <v>258.3368225097656</v>
+        <v>259.5435485839844</v>
       </c>
       <c r="F82" t="n">
-        <v>50419300</v>
+        <v>45263800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>258.3767027680543</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C83" t="n">
-        <v>259.5036402038468</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D83" t="n">
-        <v>255.524480970152</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E83" t="n">
-        <v>258.6659240722656</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F83" t="n">
-        <v>39997000</v>
+        <v>45730800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>258.4565110528425</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C84" t="n">
-        <v>260.5906861738287</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D84" t="n">
-        <v>256.1029014720883</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E84" t="n">
-        <v>259.5435485839844</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F84" t="n">
-        <v>45263800</v>
+        <v>40019400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>258.017707787092</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C85" t="n">
-        <v>261.0993163539261</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D85" t="n">
-        <v>257.6886169608135</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E85" t="n">
-        <v>260.3413696289062</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F85" t="n">
-        <v>45730800</v>
+        <v>39388600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>258.7855776250856</v>
+        <v>257.1999111311508</v>
       </c>
       <c r="C86" t="n">
-        <v>261.1092696408236</v>
+        <v>258.1971965798445</v>
       </c>
       <c r="D86" t="n">
-        <v>256.0131254420647</v>
+        <v>254.2379721311412</v>
       </c>
       <c r="E86" t="n">
-        <v>259.2543029785156</v>
+        <v>254.8363494873047</v>
       </c>
       <c r="F86" t="n">
-        <v>40019400</v>
+        <v>72142800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>259.9424426175537</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C87" t="n">
-        <v>260.3313985459844</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D87" t="n">
-        <v>256.3522089636155</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E87" t="n">
-        <v>257.5090637207031</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F87" t="n">
-        <v>39388600</v>
+        <v>80267500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>257.1999111311508</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C88" t="n">
-        <v>258.1971965798445</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D88" t="n">
-        <v>254.2379721311412</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E88" t="n">
-        <v>254.8363494873047</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F88" t="n">
-        <v>72142800</v>
+        <v>54641700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>252.0439493025651</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C89" t="n">
-        <v>254.0983549093351</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D89" t="n">
-        <v>242.7592241320914</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E89" t="n">
-        <v>246.0303192138672</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F89" t="n">
-        <v>80267500</v>
+        <v>39708300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>248.0248902004531</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C90" t="n">
-        <v>250.8771272171802</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D90" t="n">
-        <v>244.5144411297041</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E90" t="n">
-        <v>246.9777374267578</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F90" t="n">
-        <v>54641700</v>
+        <v>41689000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>248.523525769064</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C91" t="n">
-        <v>250.3186425840567</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D91" t="n">
-        <v>247.4763730255375</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E91" t="n">
-        <v>247.6758422851562</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F91" t="n">
-        <v>39708300</v>
+        <v>55969200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>246.6486371992728</v>
+        <v>258.4664593428383</v>
       </c>
       <c r="C92" t="n">
-        <v>248.7329600733879</v>
+        <v>261.2389114176715</v>
       </c>
       <c r="D92" t="n">
-        <v>244.0157890837153</v>
+        <v>257.5090434871919</v>
       </c>
       <c r="E92" t="n">
-        <v>247.3666687011719</v>
+        <v>257.5688781738281</v>
       </c>
       <c r="F92" t="n">
-        <v>41689000</v>
+        <v>49648300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>250.7973351598156</v>
+        <v>256.9506034196754</v>
       </c>
       <c r="C93" t="n">
-        <v>255.863546959882</v>
+        <v>258.1573103549757</v>
       </c>
       <c r="D93" t="n">
-        <v>249.1219029451975</v>
+        <v>253.8191275531099</v>
       </c>
       <c r="E93" t="n">
-        <v>254.7166748046875</v>
+        <v>255.743896484375</v>
       </c>
       <c r="F93" t="n">
-        <v>55969200</v>
+        <v>41288000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>258.4664593428383</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C94" t="n">
-        <v>261.2389114176715</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D94" t="n">
-        <v>257.5090434871919</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E94" t="n">
-        <v>257.5688781738281</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F94" t="n">
-        <v>49648300</v>
+        <v>67253000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>256.9506034196754</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C95" t="n">
-        <v>258.1573103549757</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D95" t="n">
-        <v>253.8191275531099</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E95" t="n">
-        <v>255.743896484375</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F95" t="n">
-        <v>41288000</v>
+        <v>92443400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>257.2996492274485</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C96" t="n">
-        <v>258.9451641530022</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D96" t="n">
-        <v>253.7193980705993</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E96" t="n">
-        <v>257.5788879394531</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F96" t="n">
-        <v>67253000</v>
+        <v>73913400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>254.4773217725483</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C97" t="n">
-        <v>261.1890484668085</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D97" t="n">
-        <v>251.4954328536096</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E97" t="n">
-        <v>258.775634765625</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F97" t="n">
-        <v>92443400</v>
+        <v>64394700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>259.3241487899344</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C98" t="n">
-        <v>269.7557466562268</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D98" t="n">
-        <v>258.5063673710488</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E98" t="n">
-        <v>269.2770690917969</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F98" t="n">
-        <v>73913400</v>
+        <v>90545700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>268.4692659190308</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C99" t="n">
-        <v>271.1419837262723</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D99" t="n">
-        <v>266.8835552083235</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E99" t="n">
-        <v>268.7485046386719</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F99" t="n">
-        <v>64394700</v>
+        <v>52977400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>271.5508302866565</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C100" t="n">
-        <v>278.1927542185059</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D100" t="n">
-        <v>271.5508302866565</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E100" t="n">
-        <v>275.7394104003906</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F100" t="n">
-        <v>90545700</v>
+        <v>50453400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,25 +3043,25 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>277.3750162493594</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C101" t="n">
-        <v>278.7412924914769</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D101" t="n">
-        <v>272.48832346973</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E101" t="n">
-        <v>275.1610412597656</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F101" t="n">
-        <v>52977400</v>
+        <v>44623400</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>276.3677049075235</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C102" t="n">
-        <v>280.1474248180158</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D102" t="n">
-        <v>276.1782182606431</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E102" t="n">
-        <v>277.364990234375</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F102" t="n">
-        <v>50453400</v>
+        <v>34376900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,25 +3095,25 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>277.4149461987041</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C103" t="n">
-        <v>277.7044381343181</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D103" t="n">
-        <v>271.2160169672847</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E103" t="n">
-        <v>274.1307983398438</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F103" t="n">
-        <v>44623400</v>
+        <v>51931300</v>
       </c>
       <c r="G103" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>274.4003102195724</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C104" t="n">
-        <v>274.8794356243012</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D104" t="n">
-        <v>272.4537718732244</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E104" t="n">
-        <v>273.1924438476562</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F104" t="n">
-        <v>34376900</v>
+        <v>81077200</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>274.2106536370846</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C105" t="n">
-        <v>279.6808719096702</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D105" t="n">
-        <v>273.9610989943363</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E105" t="n">
-        <v>275.0092163085938</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F105" t="n">
-        <v>51931300</v>
+        <v>56290700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>275.0990906441111</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C106" t="n">
-        <v>275.228863950531</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D106" t="n">
-        <v>259.7165366668213</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E106" t="n">
-        <v>261.2637939453125</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F106" t="n">
-        <v>81077200</v>
+        <v>58469100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>261.5432690161623</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C107" t="n">
-        <v>261.7628783299504</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D107" t="n">
-        <v>254.9949421084194</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E107" t="n">
-        <v>255.3243560791016</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F107" t="n">
-        <v>56290700</v>
+        <v>34203300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>257.5903108294174</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C108" t="n">
-        <v>265.8156532326085</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D108" t="n">
-        <v>255.0847874975786</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E108" t="n">
-        <v>263.4099426269531</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F108" t="n">
-        <v>58469100</v>
+        <v>30845300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>263.1304558468116</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C109" t="n">
-        <v>266.3447212846438</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D109" t="n">
-        <v>261.9825104325609</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E109" t="n">
-        <v>263.8791198730469</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F109" t="n">
-        <v>34203300</v>
+        <v>42070500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>262.1322047157328</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C110" t="n">
-        <v>264.0088605167754</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D110" t="n">
-        <v>259.5867290635135</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E110" t="n">
-        <v>260.1157836914062</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F110" t="n">
-        <v>30845300</v>
+        <v>37308200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>258.5086811746104</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C111" t="n">
-        <v>264.2783836675007</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D111" t="n">
-        <v>257.7001265171608</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E111" t="n">
-        <v>264.1086730957031</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F111" t="n">
-        <v>42070500</v>
+        <v>47014600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>263.0206001676805</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C112" t="n">
-        <v>268.9500208858886</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D112" t="n">
-        <v>262.9108107477792</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E112" t="n">
-        <v>265.705810546875</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F112" t="n">
-        <v>37308200</v>
+        <v>33714300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>267.3828377763821</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C113" t="n">
-        <v>274.4003442568012</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D113" t="n">
-        <v>267.233111068832</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E113" t="n">
-        <v>271.6552429199219</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F113" t="n">
-        <v>47014600</v>
+        <v>32345100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>271.295868192995</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C114" t="n">
-        <v>274.450242837397</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D114" t="n">
-        <v>270.567157599074</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E114" t="n">
-        <v>273.7415161132812</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F114" t="n">
-        <v>33714300</v>
+        <v>72366500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>274.4602128097023</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C115" t="n">
-        <v>275.6181195635374</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D115" t="n">
-        <v>270.3175813011377</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E115" t="n">
-        <v>272.4637756347656</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F115" t="n">
-        <v>32345100</v>
+        <v>41827900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>272.3240124520744</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C116" t="n">
-        <v>272.3240124520744</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D116" t="n">
-        <v>262.4217010495403</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E116" t="n">
-        <v>263.7093811035156</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F116" t="n">
-        <v>72366500</v>
+        <v>38568900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>261.9425306959557</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C117" t="n">
-        <v>266.0551862059975</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D117" t="n">
-        <v>259.7364762526007</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E117" t="n">
-        <v>264.2484130859375</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F117" t="n">
-        <v>41827900</v>
+        <v>39803100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>263.0106738027697</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C118" t="n">
-        <v>265.0869552930596</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D118" t="n">
-        <v>259.6666350681776</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E118" t="n">
-        <v>263.2801818847656</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F118" t="n">
-        <v>38568900</v>
+        <v>49658600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>264.1785481527265</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C119" t="n">
-        <v>265.6758760626757</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D119" t="n">
-        <v>260.9543215497598</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E119" t="n">
-        <v>262.0523376464844</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F119" t="n">
-        <v>39803100</v>
+        <v>41120000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>260.3254337562426</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C120" t="n">
-        <v>261.0940511012478</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D120" t="n">
-        <v>256.7917314296105</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E120" t="n">
-        <v>259.8263244628906</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F120" t="n">
-        <v>49658600</v>
+        <v>38218500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>258.1692718962937</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C121" t="n">
-        <v>258.3090066542827</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D121" t="n">
-        <v>253.916851068475</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E121" t="n">
-        <v>257.0013427734375</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F121" t="n">
-        <v>41120000</v>
+        <v>30590800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>255.2345148744848</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C122" t="n">
-        <v>260.6847798709625</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D122" t="n">
-        <v>253.2280857512349</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E122" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F122" t="n">
-        <v>38218500</v>
+        <v>26218900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>257.1910284571696</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C123" t="n">
-        <v>262.0124415843973</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D123" t="n">
-        <v>256.4922936817907</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E123" t="n">
-        <v>260.3653564453125</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F123" t="n">
-        <v>30590800</v>
+        <v>40794000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>260.6248673962081</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C124" t="n">
-        <v>261.6630231774062</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D124" t="n">
-        <v>259.0876023594815</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E124" t="n">
-        <v>260.3453674316406</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F124" t="n">
-        <v>26218900</v>
+        <v>36930000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>258.1992253881205</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C125" t="n">
-        <v>258.4887173103141</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D125" t="n">
-        <v>253.7271951166323</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E125" t="n">
-        <v>255.3043823242188</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F125" t="n">
-        <v>40794000</v>
+        <v>32074200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>255.024890934378</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C126" t="n">
-        <v>255.8733676296054</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D126" t="n">
-        <v>249.0755164384504</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E126" t="n">
-        <v>249.6744384765625</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F126" t="n">
-        <v>36930000</v>
+        <v>32361600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>251.6609022279199</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C127" t="n">
-        <v>253.4377301906265</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D127" t="n">
-        <v>249.4348789230203</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E127" t="n">
-        <v>252.3696441650391</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F127" t="n">
-        <v>32074200</v>
+        <v>35757900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>252.5093881906664</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C128" t="n">
-        <v>254.6755207628997</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D128" t="n">
-        <v>251.7307636559193</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E128" t="n">
-        <v>253.7771148681641</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F128" t="n">
-        <v>32361600</v>
+        <v>34864100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>252.1799767808244</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C129" t="n">
-        <v>254.4858593736706</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D129" t="n">
-        <v>248.5564382882904</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E129" t="n">
-        <v>249.4947662353516</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F129" t="n">
-        <v>35757900</v>
+        <v>88331100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>248.9557286861236</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C130" t="n">
-        <v>251.3814079598573</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D130" t="n">
-        <v>246.8594786308807</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E130" t="n">
-        <v>248.5165252685547</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F130" t="n">
-        <v>34864100</v>
+        <v>40546100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>247.5382410981218</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C131" t="n">
-        <v>248.7560689935711</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D131" t="n">
-        <v>245.5617725594444</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E131" t="n">
-        <v>247.5482330322266</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F131" t="n">
-        <v>88331100</v>
+        <v>45152300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>253.5175853710609</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C132" t="n">
-        <v>254.1464679788293</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D132" t="n">
-        <v>249.8341562083163</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E132" t="n">
-        <v>251.0420074462891</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F132" t="n">
-        <v>40546100</v>
+        <v>28476700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>249.9040313986812</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C133" t="n">
-        <v>254.3760464402864</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D133" t="n">
-        <v>249.105453476207</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E133" t="n">
-        <v>251.1917266845703</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F133" t="n">
-        <v>45152300</v>
+        <v>41796700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>253.6473574345128</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C134" t="n">
-        <v>254.5457480998694</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D134" t="n">
-        <v>251.1518108845141</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E134" t="n">
-        <v>252.1699829101562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F134" t="n">
-        <v>28476700</v>
+        <v>47900000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>251.6708815336767</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C135" t="n">
-        <v>256.5421934269488</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D135" t="n">
-        <v>250.3232954931613</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E135" t="n">
-        <v>252.4395141601562</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F135" t="n">
-        <v>41796700</v>
+        <v>39446200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>253.4477020992108</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C136" t="n">
-        <v>255.0348812846261</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D136" t="n">
-        <v>247.6281009352486</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E136" t="n">
-        <v>248.3567962646484</v>
+        <v>253.337890625</v>
       </c>
       <c r="F136" t="n">
-        <v>47900000</v>
+        <v>49598100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>249.6245329956546</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C137" t="n">
-        <v>250.4230956915925</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D137" t="n">
-        <v>245.0726433781301</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E137" t="n">
-        <v>246.1906585693359</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F137" t="n">
-        <v>39446200</v>
+        <v>40059400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>247.4683756415328</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C138" t="n">
-        <v>255.0248824882854</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D138" t="n">
-        <v>246.6598210163149</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E138" t="n">
-        <v>253.337890625</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F138" t="n">
-        <v>49598100</v>
+        <v>31289400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>253.6273797300248</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C139" t="n">
-        <v>255.7236296181179</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D139" t="n">
-        <v>252.8787157917901</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E139" t="n">
-        <v>255.1746215820312</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F139" t="n">
-        <v>40059400</v>
+        <v>29329900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>253.7471740568136</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C140" t="n">
-        <v>255.6737439434535</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D140" t="n">
-        <v>250.2034948550391</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E140" t="n">
-        <v>255.464111328125</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F140" t="n">
-        <v>31289400</v>
+        <v>62148000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>256.053045051996</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C141" t="n">
-        <v>261.6929736576745</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D141" t="n">
-        <v>256.003115847535</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E141" t="n">
-        <v>258.3988342285156</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F141" t="n">
-        <v>29329900</v>
+        <v>41032800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>255.7036812801697</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C142" t="n">
-        <v>255.7436185540334</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D142" t="n">
-        <v>245.2623079794448</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E142" t="n">
-        <v>253.0484161376953</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F142" t="n">
-        <v>62148000</v>
+        <v>28121600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>257.9896016596085</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C143" t="n">
-        <v>259.2872736156141</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D143" t="n">
-        <v>256.0730086009651</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E143" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F143" t="n">
-        <v>41032800</v>
+        <v>31291500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>258.5386040524215</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C144" t="n">
-        <v>260.6548225010532</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D144" t="n">
-        <v>255.6138310165902</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E144" t="n">
-        <v>260.0259399414062</v>
+        <v>258.73828125</v>
       </c>
       <c r="F144" t="n">
-        <v>28121600</v>
+        <v>36234700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>259.5168819122501</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C145" t="n">
-        <v>261.7229364827484</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D145" t="n">
-        <v>258.5585701252562</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E145" t="n">
-        <v>260.0159912109375</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F145" t="n">
-        <v>31291500</v>
+        <v>48370700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>259.2673359057164</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C146" t="n">
-        <v>259.7165160115803</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D146" t="n">
-        <v>256.2027973984465</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E146" t="n">
-        <v>258.73828125</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F146" t="n">
-        <v>36234700</v>
+        <v>49913500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>258.7881616833942</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C147" t="n">
-        <v>261.4633801130582</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D147" t="n">
-        <v>256.7318338868242</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E147" t="n">
-        <v>258.368896484375</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F147" t="n">
-        <v>48370700</v>
+        <v>43323100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>257.7001261657452</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C148" t="n">
-        <v>266.0851565972939</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D148" t="n">
-        <v>257.3507435512608</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E148" t="n">
-        <v>265.9553833007812</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F148" t="n">
-        <v>49913500</v>
+        <v>61436200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>266.3246925362851</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C149" t="n">
-        <v>266.6840670491935</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D149" t="n">
-        <v>260.804545264895</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E149" t="n">
-        <v>262.9307556152344</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F149" t="n">
-        <v>43323100</v>
+        <v>36590200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>266.4844323486072</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C150" t="n">
-        <v>271.8149160854778</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D150" t="n">
-        <v>266.2448696297591</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E150" t="n">
-        <v>269.7486267089844</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F150" t="n">
-        <v>61436200</v>
+        <v>50209800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>269.8484123886765</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C151" t="n">
-        <v>273.7913879220191</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D151" t="n">
-        <v>269.8085055794248</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E151" t="n">
-        <v>272.5635681152344</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F151" t="n">
-        <v>36590200</v>
+        <v>43249200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>271.0163536236942</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C152" t="n">
-        <v>272.3140256362382</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D152" t="n">
-        <v>264.9272139873882</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E152" t="n">
-        <v>265.6958618164062</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F152" t="n">
-        <v>50209800</v>
+        <v>33399600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>267.3429346055621</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C153" t="n">
-        <v>273.2523721409737</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D153" t="n">
-        <v>266.394614672797</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E153" t="n">
-        <v>272.6834106445312</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F153" t="n">
-        <v>43249200</v>
+        <v>38157100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>274.5600108521774</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C154" t="n">
-        <v>275.2787294551341</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D154" t="n">
-        <v>271.1660737405759</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E154" t="n">
-        <v>272.9429016113281</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F154" t="n">
-        <v>33399600</v>
+        <v>41466800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>272.2741016414235</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C155" t="n">
-        <v>272.5735550213531</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D155" t="n">
-        <v>269.1696261078274</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E155" t="n">
-        <v>270.5771179199219</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F155" t="n">
-        <v>38157100</v>
+        <v>40018900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>265.6159889280984</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C156" t="n">
-        <v>267.8819342286378</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D156" t="n">
-        <v>264.5978169025021</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E156" t="n">
-        <v>267.1332702636719</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F156" t="n">
-        <v>41466800</v>
+        <v>30047900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>271.8548539018017</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C157" t="n">
-        <v>272.7432830913257</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D157" t="n">
-        <v>268.181416710472</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E157" t="n">
-        <v>270.2277526855469</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F157" t="n">
-        <v>40018900</v>
+        <v>91848200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>267.0733624970658</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C158" t="n">
-        <v>270.5571659728108</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D158" t="n">
-        <v>266.5642917484437</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E158" t="n">
-        <v>269.688720703125</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F158" t="n">
-        <v>30047900</v>
+        <v>79915400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>270.018146234023</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C159" t="n">
-        <v>275.5083488376723</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D159" t="n">
-        <v>267.6623648300734</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E159" t="n">
-        <v>270.8666381835938</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F159" t="n">
-        <v>91848200</v>
+        <v>46668400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>278.3632116979401</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C160" t="n">
-        <v>286.7083346607987</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D160" t="n">
-        <v>277.8740943540899</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E160" t="n">
-        <v>279.6409606933594</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F160" t="n">
-        <v>79915400</v>
+        <v>49311700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>279.1618288412153</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C161" t="n">
-        <v>280.130102141665</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D161" t="n">
-        <v>274.3703610857382</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E161" t="n">
-        <v>276.3368530273438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F161" t="n">
-        <v>46668400</v>
+        <v>58336100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>276.43668191704</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C162" t="n">
-        <v>284.0630869835518</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D162" t="n">
-        <v>276.0074552110661</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E162" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F162" t="n">
-        <v>49311700</v>
+        <v>45224300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>281.4177950537395</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C163" t="n">
-        <v>287.5168959460148</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D163" t="n">
-        <v>280.5693031693742</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E163" t="n">
-        <v>286.9978332519531</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F163" t="n">
-        <v>58336100</v>
+        <v>52692800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,25 +4681,25 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>288.7546745760609</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C164" t="n">
-        <v>291.6095955251437</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D164" t="n">
-        <v>285.2709015174152</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E164" t="n">
-        <v>286.9279479980469</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F164" t="n">
-        <v>45224300</v>
+        <v>42247300</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>289.4933842419345</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C165" t="n">
-        <v>294.2349225642168</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D165" t="n">
-        <v>289.4833923077643</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E165" t="n">
-        <v>292.7974853515625</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F165" t="n">
-        <v>52692800</v>
+        <v>45748100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,25 +4733,25 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>291.7284168827658</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C166" t="n">
-        <v>293.6267735875138</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D166" t="n">
-        <v>289.979924827367</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E166" t="n">
-        <v>292.4277954101562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F166" t="n">
-        <v>42247300</v>
+        <v>52684300</v>
       </c>
       <c r="G166" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>292.3078994315659</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C167" t="n">
-        <v>295.0155556946294</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D167" t="n">
-        <v>292.3078994315659</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E167" t="n">
-        <v>294.5459594726562</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F167" t="n">
-        <v>45748100</v>
+        <v>35324900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>293.247089511151</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C168" t="n">
-        <v>300.6607090744109</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D168" t="n">
-        <v>293.247089511151</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E168" t="n">
-        <v>298.6124572753906</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F168" t="n">
-        <v>52684300</v>
+        <v>54862800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>299.5616620172475</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C169" t="n">
-        <v>300.1911240450107</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D169" t="n">
-        <v>295.1254853838782</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E169" t="n">
-        <v>297.9530334472656</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F169" t="n">
-        <v>35324900</v>
+        <v>34483000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>297.643304079477</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C170" t="n">
-        <v>302.9387555529706</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D170" t="n">
-        <v>296.2644882977323</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E170" t="n">
-        <v>299.9713134765625</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F170" t="n">
-        <v>54862800</v>
+        <v>42243600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>299.9812692945075</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C171" t="n">
-        <v>300.4009207908792</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D171" t="n">
-        <v>294.6558756451712</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E171" t="n">
-        <v>297.5833435058594</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F171" t="n">
-        <v>34483000</v>
+        <v>38229800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>296.7140952726279</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C172" t="n">
-        <v>300.2510533099592</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D172" t="n">
-        <v>296.0946344196341</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E172" t="n">
-        <v>298.7123718261719</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F172" t="n">
-        <v>42243600</v>
+        <v>42965100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>297.9230626302997</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C173" t="n">
-        <v>302.5390768782648</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D173" t="n">
-        <v>297.8231426981347</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E173" t="n">
-        <v>301.9895629882812</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F173" t="n">
-        <v>38229800</v>
+        <v>43670200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>300.8005667472183</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C174" t="n">
-        <v>305.2767171977908</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D174" t="n">
-        <v>300.1411318265125</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E174" t="n">
-        <v>304.7271728515625</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F174" t="n">
-        <v>42965100</v>
+        <v>48000500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>305.8562084633929</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C175" t="n">
-        <v>311.1316574150658</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D175" t="n">
-        <v>305.5764509618376</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E175" t="n">
-        <v>308.5538940429688</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F175" t="n">
-        <v>43670200</v>
+        <v>50430900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>309.2932516306071</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C176" t="n">
-        <v>311.5513139598484</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D176" t="n">
-        <v>307.4048960873393</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E176" t="n">
-        <v>308.0643005371094</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F176" t="n">
-        <v>48000500</v>
+        <v>48220400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>308.0643052358437</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C177" t="n">
-        <v>312.9900803339556</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D177" t="n">
-        <v>308.0343323058515</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E177" t="n">
-        <v>310.5821533203125</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F177" t="n">
-        <v>50430900</v>
+        <v>70026800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>310.412282475935</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C178" t="n">
-        <v>312.5304508120942</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D178" t="n">
-        <v>309.3032535889254</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E178" t="n">
-        <v>312.24072265625</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F178" t="n">
-        <v>48220400</v>
+        <v>48849900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>311.5113496628706</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C179" t="n">
-        <v>314.7285763294451</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D179" t="n">
-        <v>309.2632884033746</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E179" t="n">
-        <v>311.7911071777344</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F179" t="n">
-        <v>70026800</v>
+        <v>44534700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>309.363197507879</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C180" t="n">
-        <v>310.6720662449624</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D180" t="n">
-        <v>304.7571540774977</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E180" t="n">
-        <v>306.0460510253906</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F180" t="n">
-        <v>48849900</v>
+        <v>50836700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>307.1950545511415</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C181" t="n">
-        <v>315.1781903378333</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D181" t="n">
-        <v>306.42572903357</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E181" t="n">
-        <v>314.9284057617188</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F181" t="n">
-        <v>44534700</v>
+        <v>44869100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>313.9092501546009</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C182" t="n">
-        <v>316.6668815001487</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D182" t="n">
-        <v>308.5838566628498</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E182" t="n">
-        <v>309.9926452636719</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F182" t="n">
-        <v>50836700</v>
+        <v>65310500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>312.9600990996374</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C183" t="n">
-        <v>313.2698295317651</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D183" t="n">
-        <v>309.3831669286495</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E183" t="n">
-        <v>310.9618225097656</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F183" t="n">
-        <v>44869100</v>
+        <v>77949100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>312.5903972939029</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C184" t="n">
-        <v>314.8984348439246</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D184" t="n">
-        <v>306.8853260765596</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E184" t="n">
-        <v>307.0751647949219</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F184" t="n">
-        <v>65310500</v>
+        <v>70108800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>308.4739595974908</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C185" t="n">
-        <v>317.1265012321255</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D185" t="n">
-        <v>300.9105055796523</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E185" t="n">
-        <v>301.2801818847656</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F185" t="n">
-        <v>77949100</v>
+        <v>52793300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>300.0212482417878</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C186" t="n">
-        <v>300.4908444635933</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D186" t="n">
-        <v>287.5320194610898</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E186" t="n">
-        <v>290.2996215820312</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F186" t="n">
-        <v>70108800</v>
+        <v>42572500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>290.4894628291428</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C187" t="n">
-        <v>294.4960172141002</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D187" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E187" t="n">
-        <v>291.3287353515625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F187" t="n">
-        <v>52793300</v>
+        <v>38742100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>293.4668864344149</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C188" t="n">
-        <v>296.7440586571729</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D188" t="n">
-        <v>289.3404406054596</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E188" t="n">
-        <v>295.375244140625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F188" t="n">
-        <v>42572500</v>
+        <v>45732600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>295.7749221682621</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C189" t="n">
-        <v>296.8839815833701</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D189" t="n">
-        <v>289.3704417369658</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E189" t="n">
-        <v>290.879150390625</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F189" t="n">
-        <v>38742100</v>
+        <v>39874400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>293.8665449684006</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C190" t="n">
-        <v>297.5233947188816</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D190" t="n">
-        <v>291.4486474146935</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E190" t="n">
-        <v>296.1645812988281</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F190" t="n">
-        <v>45732600</v>
+        <v>42745100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>294.9955949959084</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C191" t="n">
-        <v>300.2210994929347</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D191" t="n">
-        <v>293.7166991398789</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E191" t="n">
-        <v>298.9821472167969</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F191" t="n">
-        <v>39874400</v>
+        <v>85962200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>300.590748125481</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C192" t="n">
-        <v>301.8096980081642</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D192" t="n">
-        <v>294.1063201593793</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E192" t="n">
-        <v>295.6949768066406</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F192" t="n">
-        <v>42745100</v>
+        <v>44879900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>297.8530937792582</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C193" t="n">
-        <v>300.3109958668267</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D193" t="n">
-        <v>295.3652492546472</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E193" t="n">
-        <v>297.7532043457031</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F193" t="n">
-        <v>85962200</v>
+        <v>52010900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>297.0538186622031</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C194" t="n">
-        <v>302.1594314563154</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D194" t="n">
-        <v>296.5043047694293</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E194" t="n">
-        <v>296.7540893554688</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F194" t="n">
-        <v>44879900</v>
+        <v>53081900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>297.2836155142734</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C195" t="n">
-        <v>301.3800886038737</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D195" t="n">
-        <v>293.9264950024863</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E195" t="n">
-        <v>294.04638671875</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F195" t="n">
-        <v>52010900</v>
+        <v>107013700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>295.1054570720635</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C196" t="n">
-        <v>299.4417438827621</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D196" t="n">
-        <v>292.6875595970274</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E196" t="n">
-        <v>292.8274230957031</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F196" t="n">
-        <v>53081900</v>
+        <v>261775500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>287.1523472601469</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C197" t="n">
-        <v>288.551134810818</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D197" t="n">
-        <v>273.5141152813601</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E197" t="n">
-        <v>274.9129028320312</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F197" t="n">
-        <v>107013700</v>
+        <v>66427000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>274.7630284991681</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C198" t="n">
-        <v>285.7036049213746</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D198" t="n">
-        <v>273.9737007161028</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E198" t="n">
-        <v>283.5354614257812</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F198" t="n">
-        <v>261775500</v>
+        <v>65100200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>286.4829438934296</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C199" t="n">
-        <v>288.1215148966215</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D199" t="n">
-        <v>279.6088673150861</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E199" t="n">
-        <v>281.4972229003906</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F199" t="n">
-        <v>66427000</v>
+        <v>50164200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>280.9277417485351</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C200" t="n">
-        <v>289.6901740532286</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D200" t="n">
-        <v>280.4581455069533</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E200" t="n">
-        <v>289.1106567382812</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F200" t="n">
-        <v>65100200</v>
+        <v>75352800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>293.1871503157195</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C201" t="n">
-        <v>296.3344299174724</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D201" t="n">
-        <v>288.9508136068854</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E201" t="n">
-        <v>294.1263427734375</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F201" t="n">
-        <v>50164200</v>
+        <v>53590000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>293.866538367699</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C202" t="n">
-        <v>309.1533719476172</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D202" t="n">
-        <v>293.4269150966668</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E202" t="n">
-        <v>308.3640441894531</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F202" t="n">
-        <v>75352800</v>
+        <v>42490000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>307.0951430290638</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C203" t="n">
-        <v>313.9292760509671</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D203" t="n">
-        <v>306.7354678654279</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E203" t="n">
-        <v>312.3905944824219</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F203" t="n">
-        <v>53590000</v>
+        <v>41323500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>315.0183186077797</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C204" t="n">
-        <v>315.2081573213482</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D204" t="n">
-        <v>309.8827331839256</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E204" t="n">
-        <v>310.3923034667969</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F204" t="n">
-        <v>42490000</v>
+        <v>48124500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>311.6412289475945</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C205" t="n">
-        <v>314.5487250421545</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D205" t="n">
-        <v>306.7854009831778</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E205" t="n">
-        <v>313.1199645996094</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F205" t="n">
-        <v>41323500</v>
+        <v>34132300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>310.242438694691</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C206" t="n">
-        <v>316.2572401947346</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D206" t="n">
-        <v>307.8944576262147</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E206" t="n">
-        <v>315.947509765625</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F206" t="n">
-        <v>48124500</v>
+        <v>43257800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>314.4488202226986</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C207" t="n">
-        <v>316.6369356310425</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D207" t="n">
-        <v>311.9010296470402</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E207" t="n">
-        <v>315.0483093261719</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F207" t="n">
-        <v>34132300</v>
+        <v>36336800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>316.7468014245228</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C208" t="n">
-        <v>323.171283634363</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D208" t="n">
-        <v>315.5078797345754</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E208" t="n">
-        <v>317.0365600585938</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F208" t="n">
-        <v>43257800</v>
+        <v>60957600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>313.4896562976144</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C209" t="n">
-        <v>315.9175551535121</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D209" t="n">
-        <v>311.6412442645678</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E209" t="n">
-        <v>314.5886840820312</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F209" t="n">
-        <v>36336800</v>
+        <v>62970600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>317.3463123495229</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C210" t="n">
-        <v>328.4467550811451</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D210" t="n">
-        <v>317.0465830462295</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E210" t="n">
-        <v>327.2178039550781</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F210" t="n">
-        <v>60957600</v>
+        <v>63407100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>327.7273632845606</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C211" t="n">
-        <v>334.3915986652446</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D211" t="n">
-        <v>326.5084133398602</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E211" t="n">
-        <v>332.9728393554688</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F211" t="n">
-        <v>62970600</v>
+        <v>53468000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>331.693929977533</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C212" t="n">
-        <v>334.7013154010385</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D212" t="n">
-        <v>328.7164869908464</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E212" t="n">
-        <v>333.452392578125</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F212" t="n">
-        <v>63407100</v>
+        <v>41338900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>333.2226134619852</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C213" t="n">
-        <v>333.4224228207836</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D213" t="n">
-        <v>323.4010672140761</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E213" t="n">
-        <v>326.3085632324219</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F213" t="n">
-        <v>53468000</v>
+        <v>38755900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>322.8515675846224</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C214" t="n">
-        <v>329.3159936819017</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D214" t="n">
-        <v>321.942348061891</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E214" t="n">
-        <v>327.4575805664062</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F214" t="n">
-        <v>41338900</v>
+        <v>40840800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>327.58746619389</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C215" t="n">
-        <v>328.7164973399543</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D215" t="n">
-        <v>323.0613709608057</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E215" t="n">
-        <v>325.6091918945312</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F215" t="n">
-        <v>38755900</v>
+        <v>47489400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>321.4527900194849</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C216" t="n">
-        <v>323.0214140443725</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D216" t="n">
-        <v>319.0748358849152</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E216" t="n">
-        <v>321.3828430175781</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F216" t="n">
-        <v>40840800</v>
+        <v>49604300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>321.5127284115298</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C217" t="n">
-        <v>334.0818750563203</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D217" t="n">
-        <v>321.3428614810286</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E217" t="n">
-        <v>332.7330322265625</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F217" t="n">
-        <v>47489400</v>
+        <v>51859000</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>334.2517370375488</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C218" t="n">
-        <v>339.277401491225</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D218" t="n">
-        <v>333.7321656046138</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E218" t="n">
-        <v>336.6196899414062</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F218" t="n">
-        <v>49604300</v>
+        <v>56090800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>339.7369815530101</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C219" t="n">
-        <v>342.594532833967</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D219" t="n">
-        <v>335.3108063761878</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E219" t="n">
-        <v>339.7869262695312</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F219" t="n">
-        <v>51859000</v>
+        <v>74817800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>339.4372716346421</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C220" t="n">
-        <v>344.2730974331505</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D220" t="n">
-        <v>337.0593175600121</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E220" t="n">
-        <v>337.8985900878906</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F220" t="n">
-        <v>56090800</v>
+        <v>132489100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>332.8129674612056</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C221" t="n">
-        <v>334.4615395264105</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D221" t="n">
-        <v>329.3059823380879</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E221" t="n">
-        <v>333.1426696777344</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F221" t="n">
-        <v>74817800</v>
+        <v>75052000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>304.5473560391475</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C222" t="n">
-        <v>310.4222943774597</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D222" t="n">
-        <v>299.7415030462749</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E222" t="n">
-        <v>308.6438293457031</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F222" t="n">
-        <v>132489100</v>
+        <v>68001000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>309.313234694189</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C223" t="n">
-        <v>311.5313230344714</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D223" t="n">
-        <v>302.2992945058118</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E223" t="n">
-        <v>303.1585693359375</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F223" t="n">
-        <v>75052000</v>
+        <v>49438800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>302.4691399129853</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C224" t="n">
-        <v>310.1525156602479</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D224" t="n">
-        <v>301.0603512911937</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E224" t="n">
-        <v>309.1134033203125</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F224" t="n">
-        <v>68001000</v>
+        <v>46139900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>309.093423625652</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C225" t="n">
-        <v>311.4414048335362</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D225" t="n">
-        <v>305.4066311863439</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E225" t="n">
-        <v>310.7320251464844</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F225" t="n">
-        <v>49438800</v>
+        <v>34437200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,25 +6293,25 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>314.06913775687</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C226" t="n">
-        <v>316.0174696892129</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D226" t="n">
-        <v>308.9635555464841</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E226" t="n">
-        <v>312.1408081054688</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F226" t="n">
-        <v>46139900</v>
+        <v>44812500</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>311.1816431226555</v>
+        <v>307.75</v>
       </c>
       <c r="C227" t="n">
-        <v>314.5387332545777</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D227" t="n">
-        <v>310.4722329590833</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E227" t="n">
-        <v>313.0599975585938</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F227" t="n">
-        <v>34437200</v>
+        <v>37476700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,25 +6345,25 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>306.8299865722656</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C228" t="n">
-        <v>308.260009765625</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D228" t="n">
-        <v>304.6099853515625</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E228" t="n">
-        <v>308.260009765625</v>
+        <v>302.25</v>
       </c>
       <c r="F228" t="n">
-        <v>44812500</v>
+        <v>41657800</v>
       </c>
       <c r="G228" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>307.75</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C229" t="n">
-        <v>309.9700012207031</v>
+        <v>306</v>
       </c>
       <c r="D229" t="n">
-        <v>302.7900085449219</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>304.9100036621094</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F229" t="n">
-        <v>37476700</v>
+        <v>40349300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>305.1000061035156</v>
+        <v>306</v>
       </c>
       <c r="C230" t="n">
-        <v>305.6600036621094</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>300.5700073242188</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E230" t="n">
-        <v>302.25</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F230" t="n">
-        <v>41657800</v>
+        <v>28229400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>304.2099914550781</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C231" t="n">
-        <v>306</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D231" t="n">
-        <v>302.0499877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E231" t="n">
-        <v>305.260009765625</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F231" t="n">
-        <v>40349300</v>
+        <v>38169300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>306</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C232" t="n">
-        <v>307.489990234375</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D232" t="n">
-        <v>304.2999877929688</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E232" t="n">
-        <v>305.9299926757812</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F232" t="n">
-        <v>28229400</v>
+        <v>53424500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>306.2099914550781</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C233" t="n">
-        <v>307.6600036621094</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D233" t="n">
-        <v>302.9400024414062</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E233" t="n">
-        <v>305.5899963378906</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F233" t="n">
-        <v>38169300</v>
+        <v>50505600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>307.5799865722656</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C234" t="n">
-        <v>311.489990234375</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D234" t="n">
-        <v>305.739990234375</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E234" t="n">
-        <v>310.0299987792969</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F234" t="n">
-        <v>53424500</v>
+        <v>40959200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>310.1400146484375</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C235" t="n">
-        <v>319.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D235" t="n">
-        <v>309.6000061035156</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E235" t="n">
-        <v>316.8299865722656</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F235" t="n">
-        <v>50505600</v>
+        <v>46876800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>317.4599914550781</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C236" t="n">
-        <v>320.2799987792969</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D236" t="n">
-        <v>310.6499938964844</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E236" t="n">
-        <v>311.2999877929688</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F236" t="n">
-        <v>40959200</v>
+        <v>34673600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>312.0499877929688</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C237" t="n">
-        <v>312.3800048828125</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D237" t="n">
-        <v>307.010009765625</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E237" t="n">
-        <v>309.3500061035156</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F237" t="n">
-        <v>46876800</v>
+        <v>25869800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>311.4700012207031</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>313.3599853515625</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D238" t="n">
-        <v>309.9700012207031</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>310.3399963378906</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F238" t="n">
-        <v>34673600</v>
+        <v>34024500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>310.7900085449219</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C239" t="n">
-        <v>313.5899963378906</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D239" t="n">
-        <v>308.2099914550781</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E239" t="n">
-        <v>309.8999938964844</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F239" t="n">
-        <v>25869800</v>
+        <v>32419200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>310.2999877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>315.4299926757812</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D240" t="n">
-        <v>308.7999877929688</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E240" t="n">
-        <v>313.4500122070312</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F240" t="n">
-        <v>34024500</v>
+        <v>38649400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>310.5499877929688</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="C241" t="n">
-        <v>315.3999938964844</v>
+        <v>321.239990234375</v>
       </c>
       <c r="D241" t="n">
-        <v>309.3999938964844</v>
+        <v>312.7999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>314.5799865722656</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="F241" t="n">
-        <v>32419200</v>
+        <v>41242700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>316.8500061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C242" t="n">
-        <v>322.3699951171875</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D242" t="n">
-        <v>315.4500122070312</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E242" t="n">
-        <v>319.7000122070312</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F242" t="n">
-        <v>38649400</v>
+        <v>53167400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>319.6000061035156</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C243" t="n">
-        <v>321.239990234375</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D243" t="n">
-        <v>312.7999877929688</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>316.8500061035156</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F243" t="n">
-        <v>41242700</v>
+        <v>33776400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>316.9800109863281</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C244" t="n">
-        <v>327.2999877929688</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D244" t="n">
-        <v>314.7300109863281</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E244" t="n">
-        <v>325.1300048828125</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F244" t="n">
-        <v>53167400</v>
+        <v>37225800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>326.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C245" t="n">
-        <v>328.3999938964844</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D245" t="n">
-        <v>323.5299987792969</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E245" t="n">
-        <v>324.9599914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F245" t="n">
-        <v>33776400</v>
+        <v>39606900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>324.8699951171875</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>330.8099975585938</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D246" t="n">
-        <v>324.1099853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E246" t="n">
-        <v>328.2099914550781</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F246" t="n">
-        <v>37225800</v>
+        <v>35477100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>328.3099975585938</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C247" t="n">
-        <v>328.9299926757812</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D247" t="n">
-        <v>317.8599853515625</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E247" t="n">
-        <v>319.9700012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F247" t="n">
-        <v>39606900</v>
+        <v>65640000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>317.1000061035156</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C248" t="n">
-        <v>320.7000122070312</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D248" t="n">
-        <v>314.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>316.2200012207031</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>35477100</v>
+        <v>70011900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>315.489990234375</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C249" t="n">
-        <v>319.1499938964844</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D249" t="n">
-        <v>309.8999938964844</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>315.3399963378906</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F249" t="n">
-        <v>65640000</v>
+        <v>50716900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>316.6700134277344</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C250" t="n">
-        <v>326.739990234375</v>
+        <v>335.5</v>
       </c>
       <c r="D250" t="n">
-        <v>316.510009765625</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E250" t="n">
-        <v>326.5700073242188</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F250" t="n">
-        <v>70011900</v>
+        <v>39269100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>327.4500122070312</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C251" t="n">
-        <v>336.2200012207031</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D251" t="n">
-        <v>326.2999877929688</v>
+        <v>328.3500061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>332.2699890136719</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="F251" t="n">
-        <v>50716900</v>
+        <v>31748200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>334.7900085449219</v>
-      </c>
-      <c r="C252" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D252" t="n">
-        <v>331.3399963378906</v>
-      </c>
-      <c r="E252" t="n">
-        <v>333.0799865722656</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>39223900</v>
+        <v>35923957</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,34 +10490,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>333.08</v>
+        <v>332.41</v>
       </c>
       <c r="D2" t="n">
-        <v>332.27</v>
+        <v>331.34</v>
       </c>
       <c r="E2" t="n">
-        <v>334.83</v>
+        <v>332.42</v>
       </c>
       <c r="F2" t="n">
-        <v>335.5</v>
+        <v>335.48</v>
       </c>
       <c r="G2" t="n">
-        <v>331.34</v>
+        <v>330.7</v>
       </c>
       <c r="H2" t="n">
-        <v>38702066</v>
+        <v>35923957</v>
       </c>
       <c r="I2" t="n">
-        <v>53820953</v>
+        <v>53820200</v>
       </c>
       <c r="J2" t="n">
-        <v>4861029515264</v>
+        <v>4851251544064</v>
       </c>
       <c r="K2" t="n">
-        <v>38.2411</v>
+        <v>38.033184</v>
       </c>
       <c r="L2" t="n">
-        <v>34.757923</v>
+        <v>34.688007</v>
       </c>
       <c r="M2" t="n">
         <v>8.710000000000001</v>
@@ -10534,7 +10526,7 @@
         <v>344.57</v>
       </c>
       <c r="O2" t="n">
-        <v>235.03</v>
+        <v>236.65</v>
       </c>
       <c r="P2" t="n">
         <v>1.085</v>
@@ -10564,7 +10556,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.255432</v>
+        <v>45.164402</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10568,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4882974638080</v>
+        <v>4857580748800</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10595,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:13:48</t>
+          <t>2026-09-17 08:09:36</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>238.0905124651219</v>
+        <v>239.0868209633975</v>
       </c>
       <c r="C2" t="n">
-        <v>239.216358555688</v>
+        <v>240.312289842007</v>
       </c>
       <c r="D2" t="n">
-        <v>236.8550706028844</v>
+        <v>235.7790325203219</v>
       </c>
       <c r="E2" t="n">
-        <v>238.1104431152344</v>
+        <v>237.0045166015625</v>
       </c>
       <c r="F2" t="n">
-        <v>46508000</v>
+        <v>44249600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>239.0868055705458</v>
+        <v>240.3421770415445</v>
       </c>
       <c r="C3" t="n">
-        <v>240.3122743702574</v>
+        <v>245.3935247988757</v>
       </c>
       <c r="D3" t="n">
-        <v>235.7790173404318</v>
+        <v>239.3259419777209</v>
       </c>
       <c r="E3" t="n">
-        <v>237.0045013427734</v>
+        <v>244.5964660644531</v>
       </c>
       <c r="F3" t="n">
-        <v>44249600</v>
+        <v>163741300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>240.3421770415445</v>
+        <v>247.3861620644307</v>
       </c>
       <c r="C4" t="n">
-        <v>245.3935247988757</v>
+        <v>255.6954791611581</v>
       </c>
       <c r="D4" t="n">
-        <v>239.3259419777209</v>
+        <v>247.2068166293636</v>
       </c>
       <c r="E4" t="n">
-        <v>244.5964660644531</v>
+        <v>255.1375122070312</v>
       </c>
       <c r="F4" t="n">
-        <v>163741300</v>
+        <v>105517400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>247.3861620644307</v>
+        <v>254.9382822522792</v>
       </c>
       <c r="C5" t="n">
-        <v>255.6954791611581</v>
+        <v>256.3929004583055</v>
       </c>
       <c r="D5" t="n">
-        <v>247.2068166293636</v>
+        <v>252.646743968705</v>
       </c>
       <c r="E5" t="n">
-        <v>255.1375122070312</v>
+        <v>253.4936065673828</v>
       </c>
       <c r="F5" t="n">
-        <v>105517400</v>
+        <v>60275200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>254.9382515607796</v>
+        <v>254.2807025242173</v>
       </c>
       <c r="C6" t="n">
-        <v>256.3928695916873</v>
+        <v>254.7987929994329</v>
       </c>
       <c r="D6" t="n">
-        <v>252.6467135530789</v>
+        <v>250.116078478</v>
       </c>
       <c r="E6" t="n">
-        <v>253.4935760498047</v>
+        <v>251.3814086914062</v>
       </c>
       <c r="F6" t="n">
-        <v>60275200</v>
+        <v>42303700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>254.2807025242173</v>
+        <v>252.2780882048451</v>
       </c>
       <c r="C7" t="n">
-        <v>254.7987929994329</v>
+        <v>256.2235204411851</v>
       </c>
       <c r="D7" t="n">
-        <v>250.116078478</v>
+        <v>250.7836088309123</v>
       </c>
       <c r="E7" t="n">
-        <v>251.3814086914062</v>
+        <v>255.9246063232422</v>
       </c>
       <c r="F7" t="n">
-        <v>42303700</v>
+        <v>55202100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>252.2780882048451</v>
+        <v>253.1648258525147</v>
       </c>
       <c r="C8" t="n">
-        <v>256.2235204411851</v>
+        <v>256.6519445821492</v>
       </c>
       <c r="D8" t="n">
-        <v>250.7836088309123</v>
+        <v>252.8459962713995</v>
       </c>
       <c r="E8" t="n">
-        <v>255.9246063232422</v>
+        <v>254.5198211669922</v>
       </c>
       <c r="F8" t="n">
-        <v>55202100</v>
+        <v>46076300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>253.1648106749593</v>
+        <v>253.6231329894407</v>
       </c>
       <c r="C9" t="n">
-        <v>256.6519291955366</v>
+        <v>254.0615160770535</v>
       </c>
       <c r="D9" t="n">
-        <v>252.8459811129583</v>
+        <v>252.0788344590342</v>
       </c>
       <c r="E9" t="n">
-        <v>254.5198059082031</v>
+        <v>253.4936065673828</v>
       </c>
       <c r="F9" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>253.6231024562692</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C10" t="n">
-        <v>254.061485491106</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D10" t="n">
-        <v>252.0788041117777</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E10" t="n">
-        <v>253.4935760498047</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F10" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C11" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D11" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E11" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F11" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>254.1013624635733</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C12" t="n">
-        <v>257.8375764362911</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D12" t="n">
-        <v>253.9917666915456</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E12" t="n">
-        <v>254.5098571777344</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F12" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C13" t="n">
-        <v>257.229778167004</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D13" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E13" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F13" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0405037108186</v>
       </c>
       <c r="C14" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165459888059</v>
       </c>
       <c r="D14" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113366309766</v>
       </c>
       <c r="E14" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7453002929688</v>
       </c>
       <c r="F14" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>257.0404883747525</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C15" t="n">
-        <v>258.1165305885388</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D15" t="n">
-        <v>254.1113214696764</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E15" t="n">
-        <v>255.7452850341797</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F15" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>255.8648286012466</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C16" t="n">
-        <v>256.452653504112</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D16" t="n">
-        <v>254.48990271765</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E16" t="n">
-        <v>255.5360565185547</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F16" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>255.5759191543519</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C17" t="n">
-        <v>257.5685585594684</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D17" t="n">
-        <v>255.1674244276712</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E17" t="n">
-        <v>257.1102600097656</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F17" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>256.8611554198282</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C18" t="n">
-        <v>257.0504585775582</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D18" t="n">
-        <v>252.2083446799687</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E18" t="n">
-        <v>253.1050262451172</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F18" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C19" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D19" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E19" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F19" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C20" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D20" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E20" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F20" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>245.6924164271231</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C21" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D21" t="n">
-        <v>243.7994000887665</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E21" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F21" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C22" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D22" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E22" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F22" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>247.3363501327598</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C23" t="n">
-        <v>248.1234359576197</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D23" t="n">
-        <v>244.2278377270511</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E23" t="n">
-        <v>246.5392913818359</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F23" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C24" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D24" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E24" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F24" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>254.9482507697476</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C25" t="n">
-        <v>263.4070106066718</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D25" t="n">
-        <v>254.6892131172966</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E25" t="n">
-        <v>261.2748718261719</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F25" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>260.9162087553024</v>
+        <v>261.6833648565789</v>
       </c>
       <c r="C26" t="n">
-        <v>264.3136625920602</v>
+        <v>261.882640960004</v>
       </c>
       <c r="D26" t="n">
-        <v>260.8663745269806</v>
+        <v>254.4899353587398</v>
       </c>
       <c r="E26" t="n">
-        <v>261.8029174804688</v>
+        <v>257.4988403320312</v>
       </c>
       <c r="F26" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>261.6833648565789</v>
+        <v>258.9833246632869</v>
       </c>
       <c r="C27" t="n">
-        <v>261.882640960004</v>
+        <v>259.6608147081683</v>
       </c>
       <c r="D27" t="n">
-        <v>254.4899353587398</v>
+        <v>257.0604350924048</v>
       </c>
       <c r="E27" t="n">
-        <v>257.4988403320312</v>
+        <v>258.6246337890625</v>
       </c>
       <c r="F27" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>258.9833246632869</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C28" t="n">
-        <v>259.6608147081683</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D28" t="n">
-        <v>257.0604350924048</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E28" t="n">
-        <v>258.6246337890625</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F28" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051197703755</v>
       </c>
       <c r="C29" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295048126629</v>
       </c>
       <c r="D29" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759553344934</v>
       </c>
       <c r="E29" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206481933594</v>
       </c>
       <c r="F29" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>263.9051799132</v>
+        <v>267.9999758056659</v>
       </c>
       <c r="C30" t="n">
-        <v>268.1295659182063</v>
+        <v>268.896687690681</v>
       </c>
       <c r="D30" t="n">
-        <v>263.6760154250923</v>
+        <v>267.1630710642092</v>
       </c>
       <c r="E30" t="n">
-        <v>267.8207092285156</v>
+        <v>268.0099487304688</v>
       </c>
       <c r="F30" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>268.000036838551</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C31" t="n">
-        <v>268.8967489277785</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D31" t="n">
-        <v>267.1631319065021</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E31" t="n">
-        <v>268.010009765625</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F31" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C32" t="n">
-        <v>270.4110953948544</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D32" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E32" t="n">
-        <v>268.7073974609375</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F32" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>270.9889785237465</v>
+        <v>275.9705389196515</v>
       </c>
       <c r="C33" t="n">
-        <v>273.131090148023</v>
+        <v>276.2993413939207</v>
       </c>
       <c r="D33" t="n">
-        <v>267.4919171420091</v>
+        <v>268.1693703205502</v>
       </c>
       <c r="E33" t="n">
-        <v>270.4011535644531</v>
+        <v>269.3749084472656</v>
       </c>
       <c r="F33" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>275.9705701844509</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C34" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D34" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E34" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F34" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>269.424736694289</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C35" t="n">
-        <v>269.8531467885877</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D35" t="n">
-        <v>265.2700709373508</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E35" t="n">
-        <v>268.0597534179688</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F35" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6213843438783</v>
       </c>
       <c r="C36" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000385630726</v>
       </c>
       <c r="D36" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9475747682897</v>
       </c>
       <c r="E36" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1457824707031</v>
       </c>
       <c r="F36" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C37" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D37" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E37" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F37" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C38" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D38" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E38" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F38" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,25 +1431,25 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>268.8069946610708</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C39" t="n">
-        <v>271.2878509444664</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D39" t="n">
-        <v>265.7881477280068</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E39" t="n">
-        <v>267.4819030761719</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F39" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1457,25 +1457,25 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>268.2298830249396</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C40" t="n">
-        <v>272.9869540449525</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D40" t="n">
-        <v>266.7339548671466</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E40" t="n">
-        <v>268.6986083984375</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F40" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G40" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535373864602</v>
       </c>
       <c r="C41" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815668240292</v>
       </c>
       <c r="D41" t="n">
-        <v>269.0675899882029</v>
+        <v>270.962507111719</v>
       </c>
       <c r="E41" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276916503906</v>
       </c>
       <c r="F41" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3658696206449</v>
       </c>
       <c r="C42" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488654308047</v>
       </c>
       <c r="D42" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513641926929</v>
       </c>
       <c r="E42" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090454101562</v>
       </c>
       <c r="F42" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C43" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D43" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E43" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F43" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>270.3141778275755</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C44" t="n">
-        <v>275.2108524736826</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D44" t="n">
-        <v>268.8681323529343</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E44" t="n">
-        <v>271.6705017089844</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F44" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>268.0902717401977</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C45" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D45" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E45" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F45" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>269.2570854665072</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C46" t="n">
-        <v>269.9751321987233</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D46" t="n">
-        <v>264.5997795179588</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E46" t="n">
-        <v>266.7140197753906</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F46" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>264.8091896065648</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C47" t="n">
-        <v>271.4710487380511</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D47" t="n">
-        <v>264.7792722621166</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E47" t="n">
-        <v>267.8309631347656</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F47" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C48" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D48" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E48" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F48" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>265.2280517805383</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C49" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D49" t="n">
-        <v>264.9488130991126</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E49" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F49" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C50" t="n">
-        <v>276.2480447880167</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D50" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E50" t="n">
-        <v>275.1709899902344</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F50" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>274.5227726174851</v>
+        <v>276.2082055022192</v>
       </c>
       <c r="C51" t="n">
-        <v>279.6189174225992</v>
+        <v>278.7712367451818</v>
       </c>
       <c r="D51" t="n">
-        <v>274.5028378637012</v>
+        <v>275.8791146523587</v>
       </c>
       <c r="E51" t="n">
-        <v>276.2181701660156</v>
+        <v>276.7966003417969</v>
       </c>
       <c r="F51" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C52" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D52" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E52" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F52" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>276.5073679150082</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C53" t="n">
-        <v>278.242634823177</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D53" t="n">
-        <v>275.2407959413455</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E53" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F53" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>277.2553332443013</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C54" t="n">
-        <v>282.6506510943872</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D54" t="n">
-        <v>275.3904143522869</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E54" t="n">
-        <v>282.3315124511719</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F54" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C55" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D55" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E55" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F55" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>285.4231155973949</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C56" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D56" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E56" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F56" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>283.3287830094401</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C57" t="n">
-        <v>283.9570776694276</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D57" t="n">
-        <v>277.8337308175164</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E57" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F57" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C58" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D58" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E58" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F58" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049325131135</v>
       </c>
       <c r="C59" t="n">
-        <v>278.9108174051644</v>
+        <v>279.2698514894354</v>
       </c>
       <c r="D59" t="n">
-        <v>275.4003533668138</v>
+        <v>276.16830825817</v>
       </c>
       <c r="E59" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275817871094</v>
       </c>
       <c r="F59" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C60" t="n">
-        <v>279.269820658071</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D60" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E60" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F60" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C61" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D61" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E61" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F61" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>278.342371275548</v>
+        <v>277.1455933469186</v>
       </c>
       <c r="C62" t="n">
-        <v>278.8310314000742</v>
+        <v>278.4620173164318</v>
       </c>
       <c r="D62" t="n">
-        <v>273.0667227973629</v>
+        <v>276.068538557602</v>
       </c>
       <c r="E62" t="n">
-        <v>277.2752685546875</v>
+        <v>277.5245666503906</v>
       </c>
       <c r="F62" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C63" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D63" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E63" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F63" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C64" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D64" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E64" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F64" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C65" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D65" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E65" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F65" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C66" t="n">
-        <v>275.4103308752873</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D66" t="n">
-        <v>270.9026119684932</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E66" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F66" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>272.8672697170699</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C67" t="n">
-        <v>272.887234905205</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D67" t="n">
-        <v>266.225375101995</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E67" t="n">
-        <v>271.4511413574219</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F67" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C68" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D68" t="n">
-        <v>269.1673383776201</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E68" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F68" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C69" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D69" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E69" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F69" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C70" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D70" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E70" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F70" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4158142002898</v>
       </c>
       <c r="C71" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6225212124231</v>
       </c>
       <c r="D71" t="n">
-        <v>271.461096549353</v>
+        <v>272.1193247047194</v>
       </c>
       <c r="E71" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578674316406</v>
       </c>
       <c r="F71" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C72" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D72" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E72" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F72" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C73" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D73" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E73" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F73" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>272.0694584675055</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C74" t="n">
-        <v>273.3360001129787</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D74" t="n">
-        <v>271.5408983628093</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E74" t="n">
-        <v>272.3387145996094</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F74" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C75" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D75" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E75" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F75" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>271.5209292436991</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C76" t="n">
-        <v>277.0857683126949</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D76" t="n">
-        <v>268.2697691424855</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E76" t="n">
-        <v>270.2743225097656</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F76" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>269.9053450243044</v>
+        <v>266.2752467950493</v>
       </c>
       <c r="C77" t="n">
-        <v>270.7729784841199</v>
+        <v>266.8237416838396</v>
       </c>
       <c r="D77" t="n">
-        <v>265.4175605620285</v>
+        <v>261.4084883511094</v>
       </c>
       <c r="E77" t="n">
-        <v>266.5345153808594</v>
+        <v>261.6478271484375</v>
       </c>
       <c r="F77" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>266.275215737747</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C78" t="n">
-        <v>266.8237105625631</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D78" t="n">
-        <v>261.4084578614468</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E78" t="n">
-        <v>261.6477966308594</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F78" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>262.4855256371837</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C79" t="n">
-        <v>262.964203143993</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D79" t="n">
-        <v>259.1047135716701</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E79" t="n">
-        <v>259.623291015625</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F79" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>256.3222864925608</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C80" t="n">
-        <v>258.586143863599</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D80" t="n">
-        <v>255.0058776573516</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E80" t="n">
-        <v>258.3368225097656</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F80" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C81" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D81" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E81" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F81" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>258.4565110528425</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C82" t="n">
-        <v>260.5906861738287</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D82" t="n">
-        <v>256.1029014720883</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E82" t="n">
-        <v>259.5435485839844</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F82" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>258.017707787092</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C83" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D83" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E83" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F83" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>258.7855776250856</v>
+        <v>259.9424734235133</v>
       </c>
       <c r="C84" t="n">
-        <v>261.1092696408236</v>
+        <v>260.3314293980394</v>
       </c>
       <c r="D84" t="n">
-        <v>256.0131254420647</v>
+        <v>256.352239344094</v>
       </c>
       <c r="E84" t="n">
-        <v>259.2543029785156</v>
+        <v>257.5090942382812</v>
       </c>
       <c r="F84" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1998957308392</v>
       </c>
       <c r="C85" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1971811198186</v>
       </c>
       <c r="D85" t="n">
-        <v>256.3522089636155</v>
+        <v>254.237956908181</v>
       </c>
       <c r="E85" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363342285156</v>
       </c>
       <c r="F85" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>257.1999111311508</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C86" t="n">
-        <v>258.1971965798445</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D86" t="n">
-        <v>254.2379721311412</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E86" t="n">
-        <v>254.8363494873047</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F86" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C87" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D87" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E87" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F87" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>248.0248902004531</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C88" t="n">
-        <v>250.8771272171802</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D88" t="n">
-        <v>244.5144411297041</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E88" t="n">
-        <v>246.9777374267578</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F88" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C89" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D89" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E89" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F89" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>246.6486371992728</v>
+        <v>250.7973501838168</v>
       </c>
       <c r="C90" t="n">
-        <v>248.7329600733879</v>
+        <v>255.8635622873743</v>
       </c>
       <c r="D90" t="n">
-        <v>244.0157890837153</v>
+        <v>249.121917868832</v>
       </c>
       <c r="E90" t="n">
-        <v>247.3666687011719</v>
+        <v>254.7166900634766</v>
       </c>
       <c r="F90" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C91" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D91" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E91" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F91" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>258.4664593428383</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C92" t="n">
-        <v>261.2389114176715</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D92" t="n">
-        <v>257.5090434871919</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E92" t="n">
-        <v>257.5688781738281</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F92" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>256.9506034196754</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C93" t="n">
-        <v>258.1573103549757</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D93" t="n">
-        <v>253.8191275531099</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E93" t="n">
-        <v>255.743896484375</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F93" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773517832236</v>
       </c>
       <c r="C94" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890792690021</v>
       </c>
       <c r="D94" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954625126288</v>
       </c>
       <c r="E94" t="n">
-        <v>257.5788879394531</v>
+        <v>258.7756652832031</v>
       </c>
       <c r="F94" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241194003358</v>
       </c>
       <c r="C95" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557160843994</v>
       </c>
       <c r="D95" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063380741307</v>
       </c>
       <c r="E95" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770385742188</v>
       </c>
       <c r="F95" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C96" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D96" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E96" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F96" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C97" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D97" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E97" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F97" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>271.5508302866565</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C98" t="n">
-        <v>278.1927542185059</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D98" t="n">
-        <v>271.5508302866565</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E98" t="n">
-        <v>275.7394104003906</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F98" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>277.3750162493594</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C99" t="n">
-        <v>278.7412924914769</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D99" t="n">
-        <v>272.48832346973</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E99" t="n">
-        <v>275.1610412597656</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F99" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,25 +3017,25 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>276.3677049075235</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C100" t="n">
-        <v>280.1474248180158</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D100" t="n">
-        <v>276.1782182606431</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E100" t="n">
-        <v>277.364990234375</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F100" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3043,25 +3043,25 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C101" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D101" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E101" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F101" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G101" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C102" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D102" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E102" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F102" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C103" t="n">
-        <v>279.6808719096702</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D103" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E103" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F103" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>275.0990906441111</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C104" t="n">
-        <v>275.228863950531</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D104" t="n">
-        <v>259.7165366668213</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E104" t="n">
-        <v>261.2637939453125</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F104" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C105" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D105" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E105" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F105" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C106" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D106" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E106" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F106" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C107" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D107" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E107" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F107" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C108" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D108" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E108" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F108" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C109" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D109" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E109" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F109" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C110" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D110" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E110" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F110" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C111" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D111" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E111" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F111" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C112" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D112" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E112" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F112" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C113" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D113" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E113" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F113" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>272.3240124520744</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C114" t="n">
-        <v>272.3240124520744</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D114" t="n">
-        <v>262.4217010495403</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E114" t="n">
-        <v>263.7093811035156</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F114" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C115" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D115" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E115" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F115" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C116" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D116" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E116" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F116" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C117" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D117" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E117" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F117" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C118" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D118" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E118" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F118" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C119" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D119" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E119" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F119" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C120" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D120" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E120" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F120" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>257.1910284571696</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C121" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D121" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E121" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F121" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>260.6248673962081</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C122" t="n">
-        <v>261.6630231774062</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D122" t="n">
-        <v>259.0876023594815</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E122" t="n">
-        <v>260.3453674316406</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F122" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>258.1992253881205</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C123" t="n">
-        <v>258.4887173103141</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D123" t="n">
-        <v>253.7271951166323</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E123" t="n">
-        <v>255.3043823242188</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F123" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C124" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D124" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E124" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F124" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C125" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D125" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E125" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F125" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C126" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D126" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E126" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F126" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C127" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D127" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E127" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F127" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C128" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D128" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E128" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F128" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C129" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D129" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E129" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F129" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C130" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D130" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E130" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F130" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C131" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D131" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E131" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F131" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C132" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D132" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E132" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F132" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C133" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D133" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E133" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F133" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C134" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D134" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E134" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F134" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C135" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D135" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E135" t="n">
-        <v>246.1906585693359</v>
+        <v>253.337890625</v>
       </c>
       <c r="F135" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>247.4683756415328</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C136" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D136" t="n">
-        <v>246.6598210163149</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E136" t="n">
-        <v>253.337890625</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F136" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>253.6273797300248</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C137" t="n">
-        <v>255.7236296181179</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D137" t="n">
-        <v>252.8787157917901</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E137" t="n">
-        <v>255.1746215820312</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F137" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>253.7471740568136</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C138" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D138" t="n">
-        <v>250.2034948550391</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E138" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F138" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>256.053045051996</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C139" t="n">
-        <v>261.6929736576745</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D139" t="n">
-        <v>256.003115847535</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E139" t="n">
-        <v>258.3988342285156</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F139" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C140" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D140" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E140" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F140" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>257.9896016596085</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C141" t="n">
-        <v>259.2872736156141</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D141" t="n">
-        <v>256.0730086009651</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E141" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F141" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>258.5386040524215</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C142" t="n">
-        <v>260.6548225010532</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D142" t="n">
-        <v>255.6138310165902</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E142" t="n">
-        <v>260.0259399414062</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F142" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C143" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D143" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E143" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F143" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C144" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D144" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E144" t="n">
-        <v>258.73828125</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F144" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>258.7881616833942</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C145" t="n">
-        <v>261.4633801130582</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D145" t="n">
-        <v>256.7318338868242</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E145" t="n">
-        <v>258.368896484375</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F145" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C146" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D146" t="n">
-        <v>257.3507435512608</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E146" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F146" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>266.3246925362851</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C147" t="n">
-        <v>266.6840670491935</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D147" t="n">
-        <v>260.804545264895</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E147" t="n">
-        <v>262.9307556152344</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F147" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C148" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D148" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E148" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F148" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C149" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D149" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E149" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F149" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C150" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D150" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E150" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F150" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C151" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D151" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E151" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F151" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C152" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D152" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E152" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F152" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C153" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D153" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E153" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F153" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C154" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D154" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E154" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F154" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C155" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D155" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E155" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F155" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C156" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D156" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E156" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F156" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C157" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D157" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E157" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F157" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>278.3632116979401</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C158" t="n">
-        <v>286.7083346607987</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D158" t="n">
-        <v>277.8740943540899</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E158" t="n">
-        <v>279.6409606933594</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F158" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>279.1618288412153</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C159" t="n">
-        <v>280.130102141665</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D159" t="n">
-        <v>274.3703610857382</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E159" t="n">
-        <v>276.3368530273438</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F159" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>276.43668191704</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C160" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D160" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E160" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F160" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>281.4177950537395</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C161" t="n">
-        <v>287.5168959460148</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D161" t="n">
-        <v>280.5693031693742</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E161" t="n">
-        <v>286.9978332519531</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F161" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>288.7546745760609</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C162" t="n">
-        <v>291.6095955251437</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D162" t="n">
-        <v>285.2709015174152</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E162" t="n">
-        <v>286.9279479980469</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F162" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,25 +4655,25 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C163" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D163" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E163" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F163" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -4681,25 +4681,25 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C164" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D164" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E164" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F164" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G164" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C165" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D165" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E165" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F165" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C166" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D166" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E166" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F166" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C167" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D167" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E167" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F167" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C168" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D168" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E168" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F168" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C169" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D169" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E169" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F169" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C170" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D170" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E170" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F170" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C171" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D171" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E171" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F171" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C172" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D172" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E172" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F172" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C173" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D173" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E173" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F173" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C174" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D174" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E174" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F174" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C175" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D175" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E175" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F175" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C176" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D176" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E176" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F176" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C177" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D177" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E177" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F177" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C178" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D178" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E178" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F178" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C179" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D179" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E179" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F179" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C180" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D180" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E180" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F180" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C181" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D181" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E181" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F181" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C182" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D182" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E182" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F182" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C183" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D183" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E183" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F183" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C184" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D184" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E184" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F184" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C185" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D185" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E185" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F185" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C186" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D186" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E186" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F186" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C187" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D187" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E187" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F187" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C188" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D188" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E188" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F188" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C189" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D189" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E189" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F189" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C190" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D190" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E190" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F190" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C191" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D191" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E191" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F191" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C192" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D192" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E192" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F192" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C193" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D193" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E193" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F193" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C194" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D194" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E194" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F194" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C195" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D195" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E195" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F195" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C196" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D196" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E196" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F196" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C197" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D197" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E197" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F197" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C198" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D198" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E198" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F198" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C199" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D199" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E199" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F199" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C200" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D200" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E200" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F200" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C201" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D201" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E201" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F201" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C202" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D202" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E202" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F202" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C203" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D203" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E203" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F203" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C204" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D204" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E204" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F204" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C205" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D205" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E205" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F205" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C206" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D206" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E206" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F206" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C207" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D207" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E207" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F207" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C208" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D208" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E208" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F208" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C209" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D209" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E209" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F209" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C210" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D210" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E210" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F210" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C211" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D211" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E211" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F211" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C212" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D212" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E212" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F212" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C213" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D213" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E213" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F213" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C214" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D214" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E214" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F214" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C215" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D215" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E215" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F215" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C216" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D216" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E216" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F216" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C217" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D217" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E217" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F217" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C218" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D218" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E218" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F218" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C219" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D219" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E219" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F219" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C220" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D220" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E220" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F220" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C221" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D221" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E221" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F221" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C222" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D222" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E222" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F222" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C223" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D223" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E223" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F223" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C224" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D224" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E224" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F224" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,25 +6267,25 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C225" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D225" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E225" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F225" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6293,25 +6293,25 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C226" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D226" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E226" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F226" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G226" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C227" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D227" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E227" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F227" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C228" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D228" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F228" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C229" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D229" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F229" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C230" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D230" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E230" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F230" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C231" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D231" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E231" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F231" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C232" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D232" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E232" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F232" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C233" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D233" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E233" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F233" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C234" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D234" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E234" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F234" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C235" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D235" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E235" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F235" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C236" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D236" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E236" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F236" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C237" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D237" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E237" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F237" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D238" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E238" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F238" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D239" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E239" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F239" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C240" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D240" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E240" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C240" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D240" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E240" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F240" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C241" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E241" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F241" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C242" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D242" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E242" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F242" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C243" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D243" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E243" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F243" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C244" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D244" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E244" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F244" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C245" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E245" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F245" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C246" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D246" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E246" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F246" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C247" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F247" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C248" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D248" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F248" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C249" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D249" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E249" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F249" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D250" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E250" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E250" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F250" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F251" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>334.7699890136719</v>
+      </c>
+      <c r="C252" t="n">
+        <v>338.3399963378906</v>
+      </c>
+      <c r="D252" t="n">
+        <v>330.1799926757812</v>
+      </c>
+      <c r="E252" t="n">
+        <v>337</v>
+      </c>
       <c r="F252" t="n">
-        <v>35923957</v>
+        <v>36632800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10490,49 +10498,49 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>337</v>
+      </c>
+      <c r="D2" t="n">
         <v>332.41</v>
       </c>
-      <c r="D2" t="n">
-        <v>331.34</v>
-      </c>
       <c r="E2" t="n">
-        <v>332.42</v>
+        <v>334.755</v>
       </c>
       <c r="F2" t="n">
-        <v>335.48</v>
+        <v>338.34</v>
       </c>
       <c r="G2" t="n">
-        <v>330.7</v>
+        <v>330.1937</v>
       </c>
       <c r="H2" t="n">
-        <v>35923957</v>
+        <v>36423997</v>
       </c>
       <c r="I2" t="n">
-        <v>53820200</v>
+        <v>53183281</v>
       </c>
       <c r="J2" t="n">
-        <v>4851251544064</v>
+        <v>4918238773248</v>
       </c>
       <c r="K2" t="n">
-        <v>38.033184</v>
+        <v>38.165344</v>
       </c>
       <c r="L2" t="n">
-        <v>34.688007</v>
+        <v>35.1459</v>
       </c>
       <c r="M2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="N2" t="n">
         <v>344.57</v>
       </c>
       <c r="O2" t="n">
-        <v>236.65</v>
+        <v>240.21</v>
       </c>
       <c r="P2" t="n">
         <v>1.085</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="R2" t="n">
         <v>0.27618998</v>
@@ -10556,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.164402</v>
+        <v>45.788044</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10568,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4857580748800</v>
+        <v>4940183896064</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10595,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:09:36</t>
+          <t>2026-09-18 13:15:18</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>239.0868209633975</v>
+        <v>240.3421770415445</v>
       </c>
       <c r="C2" t="n">
-        <v>240.312289842007</v>
+        <v>245.3935247988757</v>
       </c>
       <c r="D2" t="n">
-        <v>235.7790325203219</v>
+        <v>239.3259419777209</v>
       </c>
       <c r="E2" t="n">
-        <v>237.0045166015625</v>
+        <v>244.5964660644531</v>
       </c>
       <c r="F2" t="n">
-        <v>44249600</v>
+        <v>163741300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>240.3421770415445</v>
+        <v>247.3861620644307</v>
       </c>
       <c r="C3" t="n">
-        <v>245.3935247988757</v>
+        <v>255.6954791611581</v>
       </c>
       <c r="D3" t="n">
-        <v>239.3259419777209</v>
+        <v>247.2068166293636</v>
       </c>
       <c r="E3" t="n">
-        <v>244.5964660644531</v>
+        <v>255.1375122070312</v>
       </c>
       <c r="F3" t="n">
-        <v>163741300</v>
+        <v>105517400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>247.3861620644307</v>
+        <v>254.9382669065294</v>
       </c>
       <c r="C4" t="n">
-        <v>255.6954791611581</v>
+        <v>256.3928850249964</v>
       </c>
       <c r="D4" t="n">
-        <v>247.2068166293636</v>
+        <v>252.646728760892</v>
       </c>
       <c r="E4" t="n">
-        <v>255.1375122070312</v>
+        <v>253.4935913085938</v>
       </c>
       <c r="F4" t="n">
-        <v>105517400</v>
+        <v>60275200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>254.9382822522792</v>
+        <v>254.2807025242173</v>
       </c>
       <c r="C5" t="n">
-        <v>256.3929004583055</v>
+        <v>254.7987929994329</v>
       </c>
       <c r="D5" t="n">
-        <v>252.646743968705</v>
+        <v>250.116078478</v>
       </c>
       <c r="E5" t="n">
-        <v>253.4936065673828</v>
+        <v>251.3814086914062</v>
       </c>
       <c r="F5" t="n">
-        <v>60275200</v>
+        <v>42303700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>254.2807025242173</v>
+        <v>252.2780882048451</v>
       </c>
       <c r="C6" t="n">
-        <v>254.7987929994329</v>
+        <v>256.2235204411851</v>
       </c>
       <c r="D6" t="n">
-        <v>250.116078478</v>
+        <v>250.7836088309123</v>
       </c>
       <c r="E6" t="n">
-        <v>251.3814086914062</v>
+        <v>255.9246063232422</v>
       </c>
       <c r="F6" t="n">
-        <v>42303700</v>
+        <v>55202100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>252.2780882048451</v>
+        <v>253.1648106749593</v>
       </c>
       <c r="C7" t="n">
-        <v>256.2235204411851</v>
+        <v>256.6519291955366</v>
       </c>
       <c r="D7" t="n">
-        <v>250.7836088309123</v>
+        <v>252.8459811129583</v>
       </c>
       <c r="E7" t="n">
-        <v>255.9246063232422</v>
+        <v>254.5198059082031</v>
       </c>
       <c r="F7" t="n">
-        <v>55202100</v>
+        <v>46076300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>253.1648258525147</v>
+        <v>253.6231177228549</v>
       </c>
       <c r="C8" t="n">
-        <v>256.6519445821492</v>
+        <v>254.0615007840798</v>
       </c>
       <c r="D8" t="n">
-        <v>252.8459962713995</v>
+        <v>252.0788192854059</v>
       </c>
       <c r="E8" t="n">
-        <v>254.5198211669922</v>
+        <v>253.4935913085938</v>
       </c>
       <c r="F8" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>253.6231329894407</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C9" t="n">
-        <v>254.0615160770535</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D9" t="n">
-        <v>252.0788344590342</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E9" t="n">
-        <v>253.4936065673828</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F9" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C10" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D10" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E10" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F10" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C11" t="n">
-        <v>257.8375609779932</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D11" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E11" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F11" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C12" t="n">
-        <v>257.229778167004</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D12" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E12" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F12" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0405037108186</v>
       </c>
       <c r="C13" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165459888059</v>
       </c>
       <c r="D13" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113366309766</v>
       </c>
       <c r="E13" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7453002929688</v>
       </c>
       <c r="F13" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>257.0405037108186</v>
+        <v>255.8648286012466</v>
       </c>
       <c r="C14" t="n">
-        <v>258.1165459888059</v>
+        <v>256.452653504112</v>
       </c>
       <c r="D14" t="n">
-        <v>254.1113366309766</v>
+        <v>254.48990271765</v>
       </c>
       <c r="E14" t="n">
-        <v>255.7453002929688</v>
+        <v>255.5360565185547</v>
       </c>
       <c r="F14" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>255.8648438796676</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C15" t="n">
-        <v>256.4526688176338</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D15" t="n">
-        <v>254.4899179139702</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E15" t="n">
-        <v>255.5360717773438</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F15" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>255.5758888188916</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C16" t="n">
-        <v>257.5685279874928</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D16" t="n">
-        <v>255.1673941406971</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E16" t="n">
-        <v>257.1102294921875</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F16" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>256.8611399345957</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C17" t="n">
-        <v>257.0504430809132</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D17" t="n">
-        <v>252.2083294752373</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E17" t="n">
-        <v>253.1050109863281</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F17" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C18" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D18" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E18" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F18" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C19" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D19" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E19" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F19" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>245.6924164271231</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C20" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D20" t="n">
-        <v>243.7994000887665</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E20" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F20" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C21" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D21" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E21" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F21" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>247.3363348246392</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C22" t="n">
-        <v>248.1234206007849</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D22" t="n">
-        <v>244.2278226113223</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E22" t="n">
-        <v>246.5392761230469</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F22" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C23" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D23" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E23" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F23" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C24" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D24" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E24" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F24" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>260.9161783410852</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C25" t="n">
-        <v>264.3136317818121</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D25" t="n">
-        <v>260.8663441185724</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E25" t="n">
-        <v>261.8028869628906</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F25" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>261.6833648565789</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C26" t="n">
-        <v>261.882640960004</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D26" t="n">
-        <v>254.4899353587398</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E26" t="n">
-        <v>257.4988403320312</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F26" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>258.9833246632869</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C27" t="n">
-        <v>259.6608147081683</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D27" t="n">
-        <v>257.0604350924048</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E27" t="n">
-        <v>258.6246337890625</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F27" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C28" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D28" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E28" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F28" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>263.9051197703755</v>
+        <v>268.0000063221084</v>
       </c>
       <c r="C29" t="n">
-        <v>268.1295048126629</v>
+        <v>268.8967183092298</v>
       </c>
       <c r="D29" t="n">
-        <v>263.6759553344934</v>
+        <v>267.1631014853557</v>
       </c>
       <c r="E29" t="n">
-        <v>267.8206481933594</v>
+        <v>268.0099792480469</v>
       </c>
       <c r="F29" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>267.9999758056659</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C30" t="n">
-        <v>268.896687690681</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D30" t="n">
-        <v>267.1630710642092</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E30" t="n">
-        <v>268.0099487304688</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F30" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C31" t="n">
-        <v>270.4110953948544</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D31" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E31" t="n">
-        <v>268.7073974609375</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F31" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>270.9889479398262</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C32" t="n">
-        <v>273.1310593223432</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D32" t="n">
-        <v>267.4918869527685</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E32" t="n">
-        <v>270.401123046875</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F32" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>275.9705389196515</v>
+        <v>269.424736694289</v>
       </c>
       <c r="C33" t="n">
-        <v>276.2993413939207</v>
+        <v>269.8531467885877</v>
       </c>
       <c r="D33" t="n">
-        <v>268.1693703205502</v>
+        <v>265.2700709373508</v>
       </c>
       <c r="E33" t="n">
-        <v>269.3749084472656</v>
+        <v>268.0597534179688</v>
       </c>
       <c r="F33" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>269.4247673672652</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C34" t="n">
-        <v>269.8531775103368</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D34" t="n">
-        <v>265.2701011373342</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E34" t="n">
-        <v>268.0597839355469</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F34" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C35" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D35" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E35" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F35" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>267.6213843438783</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C36" t="n">
-        <v>270.7000385630726</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D36" t="n">
-        <v>265.9475747682897</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E36" t="n">
-        <v>269.1457824707031</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F36" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C37" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D37" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E37" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F37" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,25 +1405,25 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298830249396</v>
       </c>
       <c r="C38" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869540449525</v>
       </c>
       <c r="D38" t="n">
-        <v>265.7881780523408</v>
+        <v>266.7339548671466</v>
       </c>
       <c r="E38" t="n">
-        <v>267.48193359375</v>
+        <v>268.6986083984375</v>
       </c>
       <c r="F38" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1431,25 +1431,25 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>268.2298525605972</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C39" t="n">
-        <v>272.9869230403233</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D39" t="n">
-        <v>266.733924572705</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E39" t="n">
-        <v>268.6985778808594</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F39" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G39" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C40" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D40" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E40" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F40" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>274.2535373864602</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C41" t="n">
-        <v>274.9815668240292</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D41" t="n">
-        <v>270.962507111719</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E41" t="n">
-        <v>272.7276916503906</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F41" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>273.3658696206449</v>
+        <v>270.3141778275755</v>
       </c>
       <c r="C42" t="n">
-        <v>275.9488654308047</v>
+        <v>275.2108524736826</v>
       </c>
       <c r="D42" t="n">
-        <v>271.3513641926929</v>
+        <v>268.8681323529343</v>
       </c>
       <c r="E42" t="n">
-        <v>272.2090454101562</v>
+        <v>271.6705017089844</v>
       </c>
       <c r="F42" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C43" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D43" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E43" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F43" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>268.0902717401977</v>
+        <v>269.2570854665072</v>
       </c>
       <c r="C44" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751321987233</v>
       </c>
       <c r="D44" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997795179588</v>
       </c>
       <c r="E44" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7140197753906</v>
       </c>
       <c r="F44" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>269.25705465795</v>
+        <v>264.8091896065648</v>
       </c>
       <c r="C45" t="n">
-        <v>269.9751013080067</v>
+        <v>271.4710487380511</v>
       </c>
       <c r="D45" t="n">
-        <v>264.5997492422933</v>
+        <v>264.7792722621166</v>
       </c>
       <c r="E45" t="n">
-        <v>266.7139892578125</v>
+        <v>267.8309631347656</v>
       </c>
       <c r="F45" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>264.8092197798317</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C46" t="n">
-        <v>271.4710796703931</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D46" t="n">
-        <v>264.7793024319747</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E46" t="n">
-        <v>267.8309936523438</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F46" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C47" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D47" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E47" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F47" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>265.2280517805383</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="C48" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480447880167</v>
       </c>
       <c r="D48" t="n">
-        <v>264.9488130991126</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="E48" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1709899902344</v>
       </c>
       <c r="F48" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227726174851</v>
       </c>
       <c r="C49" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6189174225992</v>
       </c>
       <c r="D49" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028378637012</v>
       </c>
       <c r="E49" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181701660156</v>
       </c>
       <c r="F49" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C50" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D50" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E50" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F50" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>276.2082055022192</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C51" t="n">
-        <v>278.7712367451818</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D51" t="n">
-        <v>275.8791146523587</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E51" t="n">
-        <v>276.7966003417969</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F51" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>276.5073679150082</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C52" t="n">
-        <v>278.242634823177</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D52" t="n">
-        <v>275.2407959413455</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E52" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F52" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>277.2553332443013</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C53" t="n">
-        <v>282.6506510943872</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D53" t="n">
-        <v>275.3904143522869</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E53" t="n">
-        <v>282.3315124511719</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F53" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C54" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D54" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E54" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F54" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>285.4231155973949</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C55" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D55" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E55" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F55" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>283.3287830094401</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C56" t="n">
-        <v>283.9570776694276</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D56" t="n">
-        <v>277.8337308175164</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E56" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F56" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C57" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D57" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E57" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F57" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C58" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D58" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E58" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F58" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>277.4049325131135</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C59" t="n">
-        <v>279.2698514894354</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D59" t="n">
-        <v>276.16830825817</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E59" t="n">
-        <v>276.4275817871094</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F59" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C60" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D60" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E60" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F60" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>278.342371275548</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C61" t="n">
-        <v>278.8310314000742</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D61" t="n">
-        <v>273.0667227973629</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E61" t="n">
-        <v>277.2752685546875</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F61" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>277.1455933469186</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C62" t="n">
-        <v>278.4620173164318</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D62" t="n">
-        <v>276.068538557602</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E62" t="n">
-        <v>277.5245666503906</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F62" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C63" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D63" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E63" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F63" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C64" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D64" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E64" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F64" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C65" t="n">
-        <v>275.4103308752873</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D65" t="n">
-        <v>270.9026119684932</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E65" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F65" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>272.8672697170699</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C66" t="n">
-        <v>272.887234905205</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D66" t="n">
-        <v>266.225375101995</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E66" t="n">
-        <v>271.4511413574219</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F66" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C67" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D67" t="n">
-        <v>269.1673383776201</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E67" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F67" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C68" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D68" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E68" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F68" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C69" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D69" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E69" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F69" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C70" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D70" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E70" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F70" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>273.4158142002898</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C71" t="n">
-        <v>274.6225212124231</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D71" t="n">
-        <v>272.1193247047194</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E71" t="n">
-        <v>272.6578674316406</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F71" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694584675055</v>
       </c>
       <c r="C72" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3360001129787</v>
       </c>
       <c r="D72" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408983628093</v>
       </c>
       <c r="E72" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3387145996094</v>
       </c>
       <c r="F72" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C73" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D73" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E73" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F73" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209292436991</v>
       </c>
       <c r="C74" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857683126949</v>
       </c>
       <c r="D74" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697691424855</v>
       </c>
       <c r="E74" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743225097656</v>
       </c>
       <c r="F74" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>271.5209599020358</v>
+        <v>269.9053450243044</v>
       </c>
       <c r="C75" t="n">
-        <v>277.0857995993762</v>
+        <v>270.7729784841199</v>
       </c>
       <c r="D75" t="n">
-        <v>268.2697994337228</v>
+        <v>265.4175605620285</v>
       </c>
       <c r="E75" t="n">
-        <v>270.2743530273438</v>
+        <v>266.5345153808594</v>
       </c>
       <c r="F75" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>269.9053759278346</v>
+        <v>266.275215737747</v>
       </c>
       <c r="C76" t="n">
-        <v>270.7730094869922</v>
+        <v>266.8237105625631</v>
       </c>
       <c r="D76" t="n">
-        <v>265.417590951718</v>
+        <v>261.4084578614468</v>
       </c>
       <c r="E76" t="n">
-        <v>266.5345458984375</v>
+        <v>261.6477966308594</v>
       </c>
       <c r="F76" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>266.2752467950493</v>
+        <v>262.4855256371837</v>
       </c>
       <c r="C77" t="n">
-        <v>266.8237416838396</v>
+        <v>262.964203143993</v>
       </c>
       <c r="D77" t="n">
-        <v>261.4084883511094</v>
+        <v>259.1047135716701</v>
       </c>
       <c r="E77" t="n">
-        <v>261.6478271484375</v>
+        <v>259.623291015625</v>
       </c>
       <c r="F77" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>262.485556491205</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C78" t="n">
-        <v>262.9642340542807</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D78" t="n">
-        <v>259.1047440282917</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E78" t="n">
-        <v>259.6233215332031</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F78" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>256.3222864925608</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C79" t="n">
-        <v>258.586143863599</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D79" t="n">
-        <v>255.0058776573516</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E79" t="n">
-        <v>258.3368225097656</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F79" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4565110528425</v>
       </c>
       <c r="C80" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906861738287</v>
       </c>
       <c r="D80" t="n">
-        <v>255.524480970152</v>
+        <v>256.1029014720883</v>
       </c>
       <c r="E80" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435485839844</v>
       </c>
       <c r="F80" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C81" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D81" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E81" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F81" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>258.017707787092</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C82" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D82" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E82" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F82" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>258.7855776250856</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C83" t="n">
-        <v>261.1092696408236</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D83" t="n">
-        <v>256.0131254420647</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E83" t="n">
-        <v>259.2543029785156</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F83" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>259.9424734235133</v>
+        <v>257.1999111311508</v>
       </c>
       <c r="C84" t="n">
-        <v>260.3314293980394</v>
+        <v>258.1971965798445</v>
       </c>
       <c r="D84" t="n">
-        <v>256.352239344094</v>
+        <v>254.2379721311412</v>
       </c>
       <c r="E84" t="n">
-        <v>257.5090942382812</v>
+        <v>254.8363494873047</v>
       </c>
       <c r="F84" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>257.1998957308392</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C85" t="n">
-        <v>258.1971811198186</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D85" t="n">
-        <v>254.237956908181</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E85" t="n">
-        <v>254.8363342285156</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F85" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C86" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D86" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E86" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F86" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>248.0248902004531</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C87" t="n">
-        <v>250.8771272171802</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D87" t="n">
-        <v>244.5144411297041</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E87" t="n">
-        <v>246.9777374267578</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F87" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C88" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D88" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E88" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F88" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>246.6486371992728</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C89" t="n">
-        <v>248.7329600733879</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D89" t="n">
-        <v>244.0157890837153</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E89" t="n">
-        <v>247.3666687011719</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F89" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>250.7973501838168</v>
+        <v>258.4664593428383</v>
       </c>
       <c r="C90" t="n">
-        <v>255.8635622873743</v>
+        <v>261.2389114176715</v>
       </c>
       <c r="D90" t="n">
-        <v>249.121917868832</v>
+        <v>257.5090434871919</v>
       </c>
       <c r="E90" t="n">
-        <v>254.7166900634766</v>
+        <v>257.5688781738281</v>
       </c>
       <c r="F90" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>258.4664899667647</v>
+        <v>256.9506034196754</v>
       </c>
       <c r="C91" t="n">
-        <v>261.2389423700868</v>
+        <v>258.1573103549757</v>
       </c>
       <c r="D91" t="n">
-        <v>257.5090739976807</v>
+        <v>253.8191275531099</v>
       </c>
       <c r="E91" t="n">
-        <v>257.5689086914062</v>
+        <v>255.743896484375</v>
       </c>
       <c r="F91" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C92" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D92" t="n">
-        <v>253.8191124091609</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E92" t="n">
-        <v>255.7438812255859</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F92" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C93" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D93" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E93" t="n">
-        <v>257.5788879394531</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F93" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>254.4773517832236</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C94" t="n">
-        <v>261.1890792690021</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D94" t="n">
-        <v>251.4954625126288</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E94" t="n">
-        <v>258.7756652832031</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F94" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>259.3241194003358</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C95" t="n">
-        <v>269.7557160843994</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D95" t="n">
-        <v>258.5063380741307</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E95" t="n">
-        <v>269.2770385742188</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F95" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C96" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D96" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E96" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F96" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>271.5508302866565</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C97" t="n">
-        <v>278.1927542185059</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D97" t="n">
-        <v>271.5508302866565</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E97" t="n">
-        <v>275.7394104003906</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F97" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>277.3750162493594</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C98" t="n">
-        <v>278.7412924914769</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D98" t="n">
-        <v>272.48832346973</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E98" t="n">
-        <v>275.1610412597656</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F98" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,25 +2991,25 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>276.3677049075235</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C99" t="n">
-        <v>280.1474248180158</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D99" t="n">
-        <v>276.1782182606431</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E99" t="n">
-        <v>277.364990234375</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F99" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3017,25 +3017,25 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C100" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D100" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E100" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F100" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G100" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C101" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D101" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E101" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F101" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C102" t="n">
-        <v>279.6808719096702</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D102" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E102" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F102" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>275.0990906441111</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C103" t="n">
-        <v>275.228863950531</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D103" t="n">
-        <v>259.7165366668213</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E103" t="n">
-        <v>261.2637939453125</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F103" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C104" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D104" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E104" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F104" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C105" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D105" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E105" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F105" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C106" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D106" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E106" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F106" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C107" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D107" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E107" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F107" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C108" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D108" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E108" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F108" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C109" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D109" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E109" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F109" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C110" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D110" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E110" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F110" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C111" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D111" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E111" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F111" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C112" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D112" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E112" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F112" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>272.3240124520744</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C113" t="n">
-        <v>272.3240124520744</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D113" t="n">
-        <v>262.4217010495403</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E113" t="n">
-        <v>263.7093811035156</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F113" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C114" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D114" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E114" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F114" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C115" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D115" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E115" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F115" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C116" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D116" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E116" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F116" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C117" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D117" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E117" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F117" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C118" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D118" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E118" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F118" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C119" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D119" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E119" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F119" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>257.1910284571696</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C120" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D120" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E120" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F120" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>260.6248673962081</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C121" t="n">
-        <v>261.6630231774062</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D121" t="n">
-        <v>259.0876023594815</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E121" t="n">
-        <v>260.3453674316406</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F121" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>258.1992253881205</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C122" t="n">
-        <v>258.4887173103141</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D122" t="n">
-        <v>253.7271951166323</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E122" t="n">
-        <v>255.3043823242188</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F122" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C123" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D123" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E123" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F123" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C124" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D124" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E124" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F124" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C125" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D125" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E125" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F125" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C126" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D126" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E126" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F126" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C127" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D127" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E127" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F127" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C128" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D128" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E128" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F128" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C129" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D129" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E129" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F129" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C130" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D130" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E130" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F130" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C131" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D131" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E131" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F131" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C132" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D132" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E132" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F132" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C133" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D133" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E133" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F133" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C134" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D134" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E134" t="n">
-        <v>246.1906585693359</v>
+        <v>253.337890625</v>
       </c>
       <c r="F134" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>247.4683756415328</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C135" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D135" t="n">
-        <v>246.6598210163149</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E135" t="n">
-        <v>253.337890625</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F135" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>253.6273797300248</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C136" t="n">
-        <v>255.7236296181179</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D136" t="n">
-        <v>252.8787157917901</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E136" t="n">
-        <v>255.1746215820312</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F136" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>253.7471740568136</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C137" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D137" t="n">
-        <v>250.2034948550391</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E137" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F137" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>256.053045051996</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C138" t="n">
-        <v>261.6929736576745</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D138" t="n">
-        <v>256.003115847535</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E138" t="n">
-        <v>258.3988342285156</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F138" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C139" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D139" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E139" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F139" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>257.9896016596085</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C140" t="n">
-        <v>259.2872736156141</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D140" t="n">
-        <v>256.0730086009651</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E140" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F140" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>258.5386040524215</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C141" t="n">
-        <v>260.6548225010532</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D141" t="n">
-        <v>255.6138310165902</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E141" t="n">
-        <v>260.0259399414062</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F141" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C142" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D142" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E142" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F142" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C143" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D143" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E143" t="n">
-        <v>258.73828125</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F143" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>258.7881616833942</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C144" t="n">
-        <v>261.4633801130582</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D144" t="n">
-        <v>256.7318338868242</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E144" t="n">
-        <v>258.368896484375</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F144" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C145" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D145" t="n">
-        <v>257.3507435512608</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E145" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F145" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>266.3246925362851</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C146" t="n">
-        <v>266.6840670491935</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D146" t="n">
-        <v>260.804545264895</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E146" t="n">
-        <v>262.9307556152344</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F146" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C147" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D147" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E147" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F147" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C148" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D148" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E148" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F148" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C149" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D149" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E149" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F149" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C150" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D150" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E150" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F150" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C151" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D151" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E151" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F151" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C152" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D152" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E152" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F152" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C153" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D153" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E153" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F153" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C154" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D154" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E154" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F154" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C155" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D155" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E155" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F155" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C156" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D156" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E156" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F156" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>278.3632116979401</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C157" t="n">
-        <v>286.7083346607987</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D157" t="n">
-        <v>277.8740943540899</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E157" t="n">
-        <v>279.6409606933594</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F157" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>279.1618288412153</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C158" t="n">
-        <v>280.130102141665</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D158" t="n">
-        <v>274.3703610857382</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E158" t="n">
-        <v>276.3368530273438</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F158" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>276.43668191704</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C159" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D159" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E159" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F159" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>281.4177950537395</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C160" t="n">
-        <v>287.5168959460148</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D160" t="n">
-        <v>280.5693031693742</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E160" t="n">
-        <v>286.9978332519531</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F160" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>288.7546745760609</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C161" t="n">
-        <v>291.6095955251437</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D161" t="n">
-        <v>285.2709015174152</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E161" t="n">
-        <v>286.9279479980469</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F161" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,25 +4629,25 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C162" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D162" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E162" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F162" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -4655,25 +4655,25 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C163" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D163" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E163" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F163" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G163" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C164" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D164" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E164" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F164" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C165" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D165" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E165" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F165" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C166" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D166" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E166" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F166" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C167" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D167" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E167" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F167" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C168" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D168" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E168" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F168" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C169" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D169" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E169" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F169" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C170" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D170" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E170" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F170" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C171" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D171" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E171" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F171" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C172" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D172" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E172" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F172" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C173" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D173" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E173" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F173" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C174" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D174" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E174" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F174" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C175" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D175" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E175" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F175" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C176" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D176" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E176" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F176" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C177" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D177" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E177" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F177" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C178" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D178" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E178" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F178" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C179" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D179" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E179" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F179" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C180" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D180" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E180" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F180" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C181" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D181" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E181" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F181" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C182" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D182" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E182" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F182" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C183" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D183" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E183" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F183" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C184" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D184" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E184" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F184" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C185" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D185" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E185" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F185" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C186" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D186" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E186" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F186" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C187" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D187" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E187" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F187" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C188" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D188" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E188" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F188" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C189" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D189" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E189" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F189" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C190" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D190" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E190" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F190" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C191" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D191" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E191" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F191" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C192" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D192" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E192" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F192" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C193" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D193" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E193" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F193" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C194" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D194" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E194" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F194" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C195" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D195" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E195" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F195" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C196" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D196" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E196" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F196" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C197" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D197" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E197" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F197" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C198" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D198" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E198" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F198" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C199" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D199" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E199" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F199" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C200" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D200" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E200" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F200" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C201" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D201" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E201" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F201" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C202" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D202" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E202" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F202" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C203" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D203" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E203" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F203" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C204" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D204" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E204" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F204" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C205" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D205" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E205" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F205" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C206" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D206" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E206" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F206" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C207" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D207" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E207" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F207" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C208" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D208" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E208" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F208" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C209" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D209" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E209" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F209" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C210" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D210" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E210" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F210" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C211" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D211" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E211" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F211" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C212" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D212" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E212" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F212" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C213" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D213" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E213" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F213" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C214" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D214" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E214" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F214" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C215" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D215" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E215" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F215" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C216" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D216" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E216" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F216" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C217" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D217" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E217" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F217" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C218" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D218" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E218" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F218" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C219" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D219" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E219" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F219" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C220" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D220" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E220" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F220" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C221" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D221" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E221" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F221" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C222" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D222" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E222" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F222" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C223" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D223" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E223" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F223" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,25 +6241,25 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C224" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D224" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E224" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F224" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6267,25 +6267,25 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C225" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D225" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E225" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F225" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G225" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C226" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D226" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E226" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F226" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C227" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D227" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F227" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C228" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D228" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F228" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C229" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D229" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E229" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F229" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C230" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E230" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F230" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C231" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D231" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E231" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F231" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C232" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D232" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E232" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F232" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C233" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D233" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E233" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F233" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C234" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D234" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E234" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F234" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C235" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D235" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E235" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F235" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C236" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D236" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E236" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F236" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C237" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D237" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E237" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F237" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C238" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D238" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E238" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F238" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C239" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D239" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E239" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C239" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D239" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E239" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F239" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C240" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E240" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F240" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C241" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D241" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E241" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F241" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C242" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D242" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E242" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F242" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C243" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D243" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E243" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F243" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E244" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F244" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C245" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D245" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E245" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F245" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C246" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F246" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C247" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D247" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F247" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C248" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D248" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E248" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F248" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D249" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E249" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E249" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F249" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D250" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E250" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F250" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C251" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E251" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F251" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C252" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D252" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>36632800</v>
+        <v>86433100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,37 +10498,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="D2" t="n">
         <v>337</v>
       </c>
-      <c r="D2" t="n">
-        <v>332.41</v>
-      </c>
       <c r="E2" t="n">
-        <v>334.755</v>
+        <v>337.99</v>
       </c>
       <c r="F2" t="n">
-        <v>338.34</v>
+        <v>338.49</v>
       </c>
       <c r="G2" t="n">
-        <v>330.1937</v>
+        <v>332.53</v>
       </c>
       <c r="H2" t="n">
-        <v>36423997</v>
+        <v>86241049</v>
       </c>
       <c r="I2" t="n">
-        <v>53183281</v>
+        <v>53449420</v>
       </c>
       <c r="J2" t="n">
-        <v>4918238773248</v>
+        <v>4905541566464</v>
       </c>
       <c r="K2" t="n">
-        <v>38.165344</v>
+        <v>38.591274</v>
       </c>
       <c r="L2" t="n">
-        <v>35.1459</v>
+        <v>35.05517</v>
       </c>
       <c r="M2" t="n">
-        <v>8.83</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>344.57</v>
@@ -10564,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.788044</v>
+        <v>45.669838</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4940183896064</v>
+        <v>4927486689280</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:18</t>
+          <t>2026-09-19 15:21:04</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>240.3421770415445</v>
+        <v>252.2780882048451</v>
       </c>
       <c r="C2" t="n">
-        <v>245.3935247988757</v>
+        <v>256.2235204411851</v>
       </c>
       <c r="D2" t="n">
-        <v>239.3259419777209</v>
+        <v>250.7836088309123</v>
       </c>
       <c r="E2" t="n">
-        <v>244.5964660644531</v>
+        <v>255.9246063232422</v>
       </c>
       <c r="F2" t="n">
-        <v>163741300</v>
+        <v>55202100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>247.3861620644307</v>
+        <v>253.1648106749593</v>
       </c>
       <c r="C3" t="n">
-        <v>255.6954791611581</v>
+        <v>256.6519291955366</v>
       </c>
       <c r="D3" t="n">
-        <v>247.2068166293636</v>
+        <v>252.8459811129583</v>
       </c>
       <c r="E3" t="n">
-        <v>255.1375122070312</v>
+        <v>254.5198059082031</v>
       </c>
       <c r="F3" t="n">
-        <v>105517400</v>
+        <v>46076300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>254.9382669065294</v>
+        <v>253.6231329894407</v>
       </c>
       <c r="C4" t="n">
-        <v>256.3928850249964</v>
+        <v>254.0615160770535</v>
       </c>
       <c r="D4" t="n">
-        <v>252.646728760892</v>
+        <v>252.0788344590342</v>
       </c>
       <c r="E4" t="n">
-        <v>253.4935913085938</v>
+        <v>253.4936065673828</v>
       </c>
       <c r="F4" t="n">
-        <v>60275200</v>
+        <v>40127700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>254.2807025242173</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C5" t="n">
-        <v>254.7987929994329</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D5" t="n">
-        <v>250.116078478</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E5" t="n">
-        <v>251.3814086914062</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F5" t="n">
-        <v>42303700</v>
+        <v>37704300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>252.2780882048451</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C6" t="n">
-        <v>256.2235204411851</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D6" t="n">
-        <v>250.7836088309123</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E6" t="n">
-        <v>255.9246063232422</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F6" t="n">
-        <v>55202100</v>
+        <v>48713900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>253.1648106749593</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C7" t="n">
-        <v>256.6519291955366</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D7" t="n">
-        <v>252.8459811129583</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E7" t="n">
-        <v>254.5198059082031</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F7" t="n">
-        <v>46076300</v>
+        <v>42630200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>253.6231177228549</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C8" t="n">
-        <v>254.0615007840798</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D8" t="n">
-        <v>252.0788192854059</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E8" t="n">
-        <v>253.4935913085938</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F8" t="n">
-        <v>40127700</v>
+        <v>49155600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>253.9220203508673</v>
+        <v>257.0404730386864</v>
       </c>
       <c r="C9" t="n">
-        <v>254.9781167214257</v>
+        <v>258.1165151882718</v>
       </c>
       <c r="D9" t="n">
-        <v>252.1784610063259</v>
+        <v>254.1113063083761</v>
       </c>
       <c r="E9" t="n">
-        <v>253.69287109375</v>
+        <v>255.7452697753906</v>
       </c>
       <c r="F9" t="n">
-        <v>37704300</v>
+        <v>44664100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>254.101347229275</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C10" t="n">
-        <v>257.8375609779932</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D10" t="n">
-        <v>253.9917514638179</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E10" t="n">
-        <v>254.5098419189453</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F10" t="n">
-        <v>48713900</v>
+        <v>31955800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>255.6356607808825</v>
+        <v>255.5759191543519</v>
       </c>
       <c r="C11" t="n">
-        <v>257.229778167004</v>
+        <v>257.5685585594684</v>
       </c>
       <c r="D11" t="n">
-        <v>253.2146115335708</v>
+        <v>255.1674244276712</v>
       </c>
       <c r="E11" t="n">
-        <v>256.1836547851562</v>
+        <v>257.1102600097656</v>
       </c>
       <c r="F11" t="n">
-        <v>42630200</v>
+        <v>36496900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>253.7327119799983</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C12" t="n">
-        <v>258.2858846694617</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D12" t="n">
-        <v>253.0153606481908</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E12" t="n">
-        <v>257.0703735351562</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F12" t="n">
-        <v>49155600</v>
+        <v>38322000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>257.0405037108186</v>
+        <v>254.0017340209507</v>
       </c>
       <c r="C13" t="n">
-        <v>258.1165459888059</v>
+        <v>255.4364367494707</v>
       </c>
       <c r="D13" t="n">
-        <v>254.1113366309766</v>
+        <v>243.1019946167774</v>
       </c>
       <c r="E13" t="n">
-        <v>255.7453002929688</v>
+        <v>244.3673248291016</v>
       </c>
       <c r="F13" t="n">
-        <v>44664100</v>
+        <v>61999100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>255.8648286012466</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C14" t="n">
-        <v>256.452653504112</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D14" t="n">
-        <v>254.48990271765</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E14" t="n">
-        <v>255.5360565185547</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F14" t="n">
-        <v>31955800</v>
+        <v>38142900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>255.5758888188916</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C15" t="n">
-        <v>257.5685279874928</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D15" t="n">
-        <v>255.1673941406971</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E15" t="n">
-        <v>257.1102294921875</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F15" t="n">
-        <v>36496900</v>
+        <v>35478000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>256.8611399345957</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C16" t="n">
-        <v>257.0504430809132</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D16" t="n">
-        <v>252.2083294752373</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E16" t="n">
-        <v>253.1050109863281</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F16" t="n">
-        <v>38322000</v>
+        <v>33893600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>254.0017181605697</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C17" t="n">
-        <v>255.436420799504</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D17" t="n">
-        <v>243.1019794369982</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E17" t="n">
-        <v>244.3673095703125</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F17" t="n">
-        <v>61999100</v>
+        <v>39777000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>248.462190854235</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C18" t="n">
-        <v>248.7710475029622</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D18" t="n">
-        <v>244.6562426215344</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E18" t="n">
-        <v>246.7485198974609</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F18" t="n">
-        <v>38142900</v>
+        <v>49147000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>245.6924164271231</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C19" t="n">
-        <v>247.9341354996238</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D19" t="n">
-        <v>243.7994000887665</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E19" t="n">
-        <v>246.8581085205078</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F19" t="n">
-        <v>35478000</v>
+        <v>90483000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>248.571774561702</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C20" t="n">
-        <v>250.8932009800968</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D20" t="n">
-        <v>246.5592047770515</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E20" t="n">
-        <v>248.4223175048828</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F20" t="n">
-        <v>33893600</v>
+        <v>46695900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>247.3363348246392</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C21" t="n">
-        <v>248.1234206007849</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D21" t="n">
-        <v>244.2278226113223</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E21" t="n">
-        <v>246.5392761230469</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F21" t="n">
-        <v>39777000</v>
+        <v>45015300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>247.1071917036077</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C22" t="n">
-        <v>252.447465373221</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D22" t="n">
-        <v>246.359952002837</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E22" t="n">
-        <v>251.3614654541016</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F22" t="n">
-        <v>49147000</v>
+        <v>32754900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>254.9482209911351</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C23" t="n">
-        <v>263.4069798400544</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D23" t="n">
-        <v>254.6891833689404</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E23" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F23" t="n">
-        <v>90483000</v>
+        <v>38253700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>260.9161783410852</v>
+        <v>263.9051197703755</v>
       </c>
       <c r="C24" t="n">
-        <v>264.3136317818121</v>
+        <v>268.1295048126629</v>
       </c>
       <c r="D24" t="n">
-        <v>260.8663441185724</v>
+        <v>263.6759553344934</v>
       </c>
       <c r="E24" t="n">
-        <v>261.8028869628906</v>
+        <v>267.8206481933594</v>
       </c>
       <c r="F24" t="n">
-        <v>46695900</v>
+        <v>44888200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>261.6833338430701</v>
+        <v>267.9999758056659</v>
       </c>
       <c r="C25" t="n">
-        <v>261.882609922878</v>
+        <v>268.896687690681</v>
       </c>
       <c r="D25" t="n">
-        <v>254.4899051977633</v>
+        <v>267.1630710642092</v>
       </c>
       <c r="E25" t="n">
-        <v>257.4988098144531</v>
+        <v>268.0099487304688</v>
       </c>
       <c r="F25" t="n">
-        <v>45015300</v>
+        <v>41534800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>258.9832941033833</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C26" t="n">
-        <v>259.6607840683213</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D26" t="n">
-        <v>257.0604047594014</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E26" t="n">
-        <v>258.6246032714844</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F26" t="n">
-        <v>32754900</v>
+        <v>51086700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>260.2287163700197</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C27" t="n">
-        <v>263.1578983995789</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D27" t="n">
-        <v>258.2261042627009</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E27" t="n">
-        <v>261.8527221679688</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F27" t="n">
-        <v>38253700</v>
+        <v>69886500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>263.9051498417878</v>
+        <v>275.9705389196515</v>
       </c>
       <c r="C28" t="n">
-        <v>268.1295353654346</v>
+        <v>276.2993413939207</v>
       </c>
       <c r="D28" t="n">
-        <v>263.6759853797928</v>
+        <v>268.1693703205502</v>
       </c>
       <c r="E28" t="n">
-        <v>267.8206787109375</v>
+        <v>269.3749084472656</v>
       </c>
       <c r="F28" t="n">
-        <v>44888200</v>
+        <v>86167100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>268.0000063221084</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C29" t="n">
-        <v>268.8967183092298</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D29" t="n">
-        <v>267.1631014853557</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E29" t="n">
-        <v>268.0099792480469</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F29" t="n">
-        <v>41534800</v>
+        <v>50194600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>268.2889298674747</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C30" t="n">
-        <v>270.4110953948544</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D30" t="n">
-        <v>266.1269030442272</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E30" t="n">
-        <v>268.7073974609375</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F30" t="n">
-        <v>51086700</v>
+        <v>49274800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>270.9889479398262</v>
+        <v>267.6213843438783</v>
       </c>
       <c r="C31" t="n">
-        <v>273.1310593223432</v>
+        <v>270.7000385630726</v>
       </c>
       <c r="D31" t="n">
-        <v>267.4918869527685</v>
+        <v>265.9475747682897</v>
       </c>
       <c r="E31" t="n">
-        <v>270.401123046875</v>
+        <v>269.1457824707031</v>
       </c>
       <c r="F31" t="n">
-        <v>69886500</v>
+        <v>43683100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>275.9705701844509</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C32" t="n">
-        <v>276.2993726959702</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D32" t="n">
-        <v>268.1694007015524</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E32" t="n">
-        <v>269.3749389648438</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F32" t="n">
-        <v>86167100</v>
+        <v>51204000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>269.424736694289</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C33" t="n">
-        <v>269.8531467885877</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D33" t="n">
-        <v>265.2700709373508</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E33" t="n">
-        <v>268.0597534179688</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F33" t="n">
-        <v>50194600</v>
+        <v>48227400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,25 +1301,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>267.3424445625432</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C34" t="n">
-        <v>270.4908183788531</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D34" t="n">
-        <v>266.6350661079627</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E34" t="n">
-        <v>269.0461730957031</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F34" t="n">
-        <v>49274800</v>
+        <v>41312400</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>267.6214146886098</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C35" t="n">
-        <v>270.7000692568828</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D35" t="n">
-        <v>265.9476049232333</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E35" t="n">
-        <v>269.1458129882812</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F35" t="n">
-        <v>43683100</v>
+        <v>46208300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>266.9040748013871</v>
+        <v>274.2535373864602</v>
       </c>
       <c r="C36" t="n">
-        <v>272.3937751745226</v>
+        <v>274.9815668240292</v>
       </c>
       <c r="D36" t="n">
-        <v>266.9040748013871</v>
+        <v>270.962507111719</v>
       </c>
       <c r="E36" t="n">
-        <v>268.7771301269531</v>
+        <v>272.7276916503906</v>
       </c>
       <c r="F36" t="n">
-        <v>51204000</v>
+        <v>48398000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>268.8070253298314</v>
+        <v>273.3658696206449</v>
       </c>
       <c r="C37" t="n">
-        <v>271.2878818962731</v>
+        <v>275.9488654308047</v>
       </c>
       <c r="D37" t="n">
-        <v>265.7881780523408</v>
+        <v>271.3513641926929</v>
       </c>
       <c r="E37" t="n">
-        <v>267.48193359375</v>
+        <v>272.2090454101562</v>
       </c>
       <c r="F37" t="n">
-        <v>48227400</v>
+        <v>49602800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,25 +1405,25 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>268.2298830249396</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C38" t="n">
-        <v>272.9869540449525</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D38" t="n">
-        <v>266.7339548671466</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E38" t="n">
-        <v>268.6986083984375</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F38" t="n">
-        <v>41312400</v>
+        <v>47431300</v>
       </c>
       <c r="G38" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>269.0775725813642</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C39" t="n">
-        <v>275.1610196363943</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D39" t="n">
-        <v>269.0675899882029</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E39" t="n">
-        <v>274.5028076171875</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F39" t="n">
-        <v>46208300</v>
+        <v>45018300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>274.2535066981436</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C40" t="n">
-        <v>274.9815360542478</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D40" t="n">
-        <v>270.9624767916609</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E40" t="n">
-        <v>272.7276611328125</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F40" t="n">
-        <v>48398000</v>
+        <v>45677300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>273.3659002679155</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C41" t="n">
-        <v>275.9488963676571</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D41" t="n">
-        <v>271.3513946141157</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E41" t="n">
-        <v>272.2090759277344</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F41" t="n">
-        <v>49602800</v>
+        <v>40424500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>270.3141778275755</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C42" t="n">
-        <v>275.2108524736826</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D42" t="n">
-        <v>268.8681323529343</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E42" t="n">
-        <v>271.6705017089844</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F42" t="n">
-        <v>47431300</v>
+        <v>45823600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>268.0902717401977</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C43" t="n">
-        <v>269.7557213346742</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D43" t="n">
-        <v>265.0086634694927</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E43" t="n">
-        <v>266.7339477539062</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F43" t="n">
-        <v>45018300</v>
+        <v>59030800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>269.2570854665072</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C44" t="n">
-        <v>269.9751321987233</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D44" t="n">
-        <v>264.5997795179588</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E44" t="n">
-        <v>266.7140197753906</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F44" t="n">
-        <v>45677300</v>
+        <v>65585800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>264.8091896065648</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C45" t="n">
-        <v>271.4710487380511</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D45" t="n">
-        <v>264.7792722621166</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E45" t="n">
-        <v>267.8309631347656</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F45" t="n">
-        <v>40424500</v>
+        <v>46914200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>270.0948061865016</v>
+        <v>276.2082055022192</v>
       </c>
       <c r="C46" t="n">
-        <v>274.6823253630542</v>
+        <v>278.7712367451818</v>
       </c>
       <c r="D46" t="n">
-        <v>265.1981613886433</v>
+        <v>275.8791146523587</v>
       </c>
       <c r="E46" t="n">
-        <v>265.5272521972656</v>
+        <v>276.7966003417969</v>
       </c>
       <c r="F46" t="n">
-        <v>45823600</v>
+        <v>33431400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>265.2280517805383</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C47" t="n">
-        <v>272.5879921198442</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D47" t="n">
-        <v>264.9488130991126</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E47" t="n">
-        <v>270.7529907226562</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F47" t="n">
-        <v>59030800</v>
+        <v>20135600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>270.1645980035721</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C48" t="n">
-        <v>276.2480447880167</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D48" t="n">
-        <v>270.1645980035721</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E48" t="n">
-        <v>275.1709899902344</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F48" t="n">
-        <v>65585800</v>
+        <v>46587700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>274.5227726174851</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C49" t="n">
-        <v>279.6189174225992</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D49" t="n">
-        <v>274.5028378637012</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E49" t="n">
-        <v>276.2181701660156</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F49" t="n">
-        <v>46914200</v>
+        <v>53669500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>276.2081750495132</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C50" t="n">
-        <v>278.7712060098946</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D50" t="n">
-        <v>275.8790842359358</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E50" t="n">
-        <v>276.7965698242188</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F50" t="n">
-        <v>33431400</v>
+        <v>43538700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>276.5073679150082</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C51" t="n">
-        <v>278.242634823177</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D51" t="n">
-        <v>275.2407959413455</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E51" t="n">
-        <v>278.0930480957031</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F51" t="n">
-        <v>20135600</v>
+        <v>43989100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>277.2553332443013</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C52" t="n">
-        <v>282.6506510943872</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D52" t="n">
-        <v>275.3904143522869</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E52" t="n">
-        <v>282.3315124511719</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F52" t="n">
-        <v>46587700</v>
+        <v>47265800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>282.231773534172</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C53" t="n">
-        <v>286.619823290159</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D53" t="n">
-        <v>281.8627827987557</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E53" t="n">
-        <v>285.4131164550781</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F53" t="n">
-        <v>53669500</v>
+        <v>38211800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>285.4231155973949</v>
+        <v>277.4049325131135</v>
       </c>
       <c r="C54" t="n">
-        <v>287.8365294074879</v>
+        <v>279.2698514894354</v>
       </c>
       <c r="D54" t="n">
-        <v>282.5309633672564</v>
+        <v>276.16830825817</v>
       </c>
       <c r="E54" t="n">
-        <v>283.378662109375</v>
+        <v>276.4275817871094</v>
       </c>
       <c r="F54" t="n">
-        <v>43538700</v>
+        <v>32193300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>283.3287830094401</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C55" t="n">
-        <v>283.9570776694276</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D55" t="n">
-        <v>277.8337308175164</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E55" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F55" t="n">
-        <v>43989100</v>
+        <v>33038300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>279.7784559281641</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C56" t="n">
-        <v>280.3768332578711</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D56" t="n">
-        <v>277.2951945750906</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E56" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F56" t="n">
-        <v>47265800</v>
+        <v>33248000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>277.374989388386</v>
+        <v>277.1455933469186</v>
       </c>
       <c r="C57" t="n">
-        <v>278.9108174051644</v>
+        <v>278.4620173164318</v>
       </c>
       <c r="D57" t="n">
-        <v>275.4003533668138</v>
+        <v>276.068538557602</v>
       </c>
       <c r="E57" t="n">
-        <v>277.1356506347656</v>
+        <v>277.5245666503906</v>
       </c>
       <c r="F57" t="n">
-        <v>38211800</v>
+        <v>39532900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>277.4049018876359</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C58" t="n">
-        <v>279.269820658071</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D58" t="n">
-        <v>276.1682777692156</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E58" t="n">
-        <v>276.4275512695312</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F58" t="n">
-        <v>32193300</v>
+        <v>50409100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>276.9960211276047</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C59" t="n">
-        <v>278.9905919368044</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D59" t="n">
-        <v>275.6895796823578</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E59" t="n">
-        <v>278.0232238769531</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F59" t="n">
-        <v>33038300</v>
+        <v>37648600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>278.342371275548</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C60" t="n">
-        <v>278.8310314000742</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D60" t="n">
-        <v>273.0667227973629</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E60" t="n">
-        <v>277.2752685546875</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F60" t="n">
-        <v>33248000</v>
+        <v>50138700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>277.1456238228236</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C61" t="n">
-        <v>278.4620479370953</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D61" t="n">
-        <v>276.0685689150702</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E61" t="n">
-        <v>277.5245971679688</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F61" t="n">
-        <v>39532900</v>
+        <v>51630700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>279.3894873363706</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C62" t="n">
-        <v>279.3894873363706</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D62" t="n">
-        <v>272.0993337942639</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E62" t="n">
-        <v>273.3658752441406</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F62" t="n">
-        <v>50409100</v>
+        <v>144632000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>272.0794134956457</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C63" t="n">
-        <v>274.752131096348</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D63" t="n">
-        <v>271.0522107383373</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E63" t="n">
-        <v>273.8645324707031</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F63" t="n">
-        <v>37648600</v>
+        <v>36571800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>274.2634587890498</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C64" t="n">
-        <v>275.4103308752873</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D64" t="n">
-        <v>270.9026119684932</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E64" t="n">
-        <v>271.10205078125</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F64" t="n">
-        <v>50138700</v>
+        <v>29642000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>272.8672697170699</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C65" t="n">
-        <v>272.887234905205</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D65" t="n">
-        <v>266.225375101995</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E65" t="n">
-        <v>271.4511413574219</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F65" t="n">
-        <v>51630700</v>
+        <v>17910600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>271.4112306527045</v>
+        <v>273.4158142002898</v>
       </c>
       <c r="C66" t="n">
-        <v>273.8545921928022</v>
+        <v>274.6225212124231</v>
       </c>
       <c r="D66" t="n">
-        <v>269.1673383776201</v>
+        <v>272.1193247047194</v>
       </c>
       <c r="E66" t="n">
-        <v>272.9271240234375</v>
+        <v>272.6578674316406</v>
       </c>
       <c r="F66" t="n">
-        <v>144632000</v>
+        <v>21521800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>272.1192896847017</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C67" t="n">
-        <v>273.1365403084993</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D67" t="n">
-        <v>269.7756932559407</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E67" t="n">
-        <v>270.2344360351562</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F67" t="n">
-        <v>36571800</v>
+        <v>23715200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>270.1048034873943</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C68" t="n">
-        <v>271.7603010837797</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D68" t="n">
-        <v>268.8282792538215</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E68" t="n">
-        <v>271.6206665039062</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F68" t="n">
-        <v>29642000</v>
+        <v>22139600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>271.6007006785171</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C69" t="n">
-        <v>274.6823088952694</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D69" t="n">
-        <v>271.461096549353</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E69" t="n">
-        <v>273.0667114257812</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F69" t="n">
-        <v>17910600</v>
+        <v>27293600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>273.4157835978775</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C70" t="n">
-        <v>274.6224904749486</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D70" t="n">
-        <v>272.1192942474183</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E70" t="n">
-        <v>272.6578369140625</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F70" t="n">
-        <v>21521800</v>
+        <v>37838100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>271.9497734782625</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C71" t="n">
-        <v>273.6152231466168</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D71" t="n">
-        <v>271.6107000753325</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E71" t="n">
-        <v>273.0168762207031</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F71" t="n">
-        <v>23715200</v>
+        <v>45647200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>272.0694584675055</v>
+        <v>266.2752467950493</v>
       </c>
       <c r="C72" t="n">
-        <v>273.3360001129787</v>
+        <v>266.8237416838396</v>
       </c>
       <c r="D72" t="n">
-        <v>271.5408983628093</v>
+        <v>261.4084883511094</v>
       </c>
       <c r="E72" t="n">
-        <v>272.3387145996094</v>
+        <v>261.6478271484375</v>
       </c>
       <c r="F72" t="n">
-        <v>22139600</v>
+        <v>52352100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>272.3187639976345</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C73" t="n">
-        <v>272.9370761103812</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D73" t="n">
-        <v>271.0123224859311</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E73" t="n">
-        <v>271.1220092773438</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F73" t="n">
-        <v>27293600</v>
+        <v>48309800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>271.5209292436991</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C74" t="n">
-        <v>277.0857683126949</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D74" t="n">
-        <v>268.2697691424855</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E74" t="n">
-        <v>270.2743225097656</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F74" t="n">
-        <v>37838100</v>
+        <v>50419300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>269.9053450243044</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C75" t="n">
-        <v>270.7729784841199</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D75" t="n">
-        <v>265.4175605620285</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E75" t="n">
-        <v>266.5345153808594</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F75" t="n">
-        <v>45647200</v>
+        <v>39997000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>266.275215737747</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C76" t="n">
-        <v>266.8237105625631</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D76" t="n">
-        <v>261.4084578614468</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E76" t="n">
-        <v>261.6477966308594</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F76" t="n">
-        <v>52352100</v>
+        <v>45263800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>262.4855256371837</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C77" t="n">
-        <v>262.964203143993</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D77" t="n">
-        <v>259.1047135716701</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E77" t="n">
-        <v>259.623291015625</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F77" t="n">
-        <v>48309800</v>
+        <v>45730800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>256.3222864925608</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C78" t="n">
-        <v>258.586143863599</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D78" t="n">
-        <v>255.0058776573516</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E78" t="n">
-        <v>258.3368225097656</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F78" t="n">
-        <v>50419300</v>
+        <v>40019400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>258.3767027680543</v>
+        <v>259.9424734235133</v>
       </c>
       <c r="C79" t="n">
-        <v>259.5036402038468</v>
+        <v>260.3314293980394</v>
       </c>
       <c r="D79" t="n">
-        <v>255.524480970152</v>
+        <v>256.352239344094</v>
       </c>
       <c r="E79" t="n">
-        <v>258.6659240722656</v>
+        <v>257.5090942382812</v>
       </c>
       <c r="F79" t="n">
-        <v>39997000</v>
+        <v>39388600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>258.4565110528425</v>
+        <v>257.1998957308392</v>
       </c>
       <c r="C80" t="n">
-        <v>260.5906861738287</v>
+        <v>258.1971811198186</v>
       </c>
       <c r="D80" t="n">
-        <v>256.1029014720883</v>
+        <v>254.237956908181</v>
       </c>
       <c r="E80" t="n">
-        <v>259.5435485839844</v>
+        <v>254.8363342285156</v>
       </c>
       <c r="F80" t="n">
-        <v>45263800</v>
+        <v>72142800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>258.017707787092</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C81" t="n">
-        <v>261.0993163539261</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D81" t="n">
-        <v>257.6886169608135</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E81" t="n">
-        <v>260.3413696289062</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F81" t="n">
-        <v>45730800</v>
+        <v>80267500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>258.7855776250856</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C82" t="n">
-        <v>261.1092696408236</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D82" t="n">
-        <v>256.0131254420647</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E82" t="n">
-        <v>259.2543029785156</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F82" t="n">
-        <v>40019400</v>
+        <v>54641700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>259.9424426175537</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C83" t="n">
-        <v>260.3313985459844</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D83" t="n">
-        <v>256.3522089636155</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E83" t="n">
-        <v>257.5090637207031</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F83" t="n">
-        <v>39388600</v>
+        <v>39708300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>257.1999111311508</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C84" t="n">
-        <v>258.1971965798445</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D84" t="n">
-        <v>254.2379721311412</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E84" t="n">
-        <v>254.8363494873047</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F84" t="n">
-        <v>72142800</v>
+        <v>41689000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>252.0439493025651</v>
+        <v>250.7973501838168</v>
       </c>
       <c r="C85" t="n">
-        <v>254.0983549093351</v>
+        <v>255.8635622873743</v>
       </c>
       <c r="D85" t="n">
-        <v>242.7592241320914</v>
+        <v>249.121917868832</v>
       </c>
       <c r="E85" t="n">
-        <v>246.0303192138672</v>
+        <v>254.7166900634766</v>
       </c>
       <c r="F85" t="n">
-        <v>80267500</v>
+        <v>55969200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>248.0248902004531</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C86" t="n">
-        <v>250.8771272171802</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D86" t="n">
-        <v>244.5144411297041</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E86" t="n">
-        <v>246.9777374267578</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F86" t="n">
-        <v>54641700</v>
+        <v>49648300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>248.523525769064</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C87" t="n">
-        <v>250.3186425840567</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D87" t="n">
-        <v>247.4763730255375</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E87" t="n">
-        <v>247.6758422851562</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F87" t="n">
-        <v>39708300</v>
+        <v>41288000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>246.6486371992728</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C88" t="n">
-        <v>248.7329600733879</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D88" t="n">
-        <v>244.0157890837153</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E88" t="n">
-        <v>247.3666687011719</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F88" t="n">
-        <v>41689000</v>
+        <v>67253000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>250.7973351598156</v>
+        <v>254.4773517832236</v>
       </c>
       <c r="C89" t="n">
-        <v>255.863546959882</v>
+        <v>261.1890792690021</v>
       </c>
       <c r="D89" t="n">
-        <v>249.1219029451975</v>
+        <v>251.4954625126288</v>
       </c>
       <c r="E89" t="n">
-        <v>254.7166748046875</v>
+        <v>258.7756652832031</v>
       </c>
       <c r="F89" t="n">
-        <v>55969200</v>
+        <v>92443400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>258.4664593428383</v>
+        <v>259.3241194003358</v>
       </c>
       <c r="C90" t="n">
-        <v>261.2389114176715</v>
+        <v>269.7557160843994</v>
       </c>
       <c r="D90" t="n">
-        <v>257.5090434871919</v>
+        <v>258.5063380741307</v>
       </c>
       <c r="E90" t="n">
-        <v>257.5688781738281</v>
+        <v>269.2770385742188</v>
       </c>
       <c r="F90" t="n">
-        <v>49648300</v>
+        <v>73913400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>256.9506034196754</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C91" t="n">
-        <v>258.1573103549757</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D91" t="n">
-        <v>253.8191275531099</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E91" t="n">
-        <v>255.743896484375</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F91" t="n">
-        <v>41288000</v>
+        <v>64394700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>257.2996492274485</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C92" t="n">
-        <v>258.9451641530022</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D92" t="n">
-        <v>253.7193980705993</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E92" t="n">
-        <v>257.5788879394531</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F92" t="n">
-        <v>67253000</v>
+        <v>90545700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>254.4773217725483</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C93" t="n">
-        <v>261.1890484668085</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D93" t="n">
-        <v>251.4954328536096</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E93" t="n">
-        <v>258.775634765625</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F93" t="n">
-        <v>92443400</v>
+        <v>52977400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>259.3241487899344</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C94" t="n">
-        <v>269.7557466562268</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D94" t="n">
-        <v>258.5063673710488</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E94" t="n">
-        <v>269.2770690917969</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F94" t="n">
-        <v>73913400</v>
+        <v>50453400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,25 +2887,25 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>268.4692659190308</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C95" t="n">
-        <v>271.1419837262723</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D95" t="n">
-        <v>266.8835552083235</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E95" t="n">
-        <v>268.7485046386719</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F95" t="n">
-        <v>64394700</v>
+        <v>44623400</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>271.5508302866565</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C96" t="n">
-        <v>278.1927542185059</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D96" t="n">
-        <v>271.5508302866565</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E96" t="n">
-        <v>275.7394104003906</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F96" t="n">
-        <v>90545700</v>
+        <v>34376900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>277.3750162493594</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C97" t="n">
-        <v>278.7412924914769</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D97" t="n">
-        <v>272.48832346973</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E97" t="n">
-        <v>275.1610412597656</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F97" t="n">
-        <v>52977400</v>
+        <v>51931300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>276.3677049075235</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C98" t="n">
-        <v>280.1474248180158</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D98" t="n">
-        <v>276.1782182606431</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E98" t="n">
-        <v>277.364990234375</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F98" t="n">
-        <v>50453400</v>
+        <v>81077200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,25 +2991,25 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>277.4149461987041</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C99" t="n">
-        <v>277.7044381343181</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D99" t="n">
-        <v>271.2160169672847</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E99" t="n">
-        <v>274.1307983398438</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F99" t="n">
-        <v>44623400</v>
+        <v>56290700</v>
       </c>
       <c r="G99" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>274.4003102195724</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C100" t="n">
-        <v>274.8794356243012</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D100" t="n">
-        <v>272.4537718732244</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E100" t="n">
-        <v>273.1924438476562</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F100" t="n">
-        <v>34376900</v>
+        <v>58469100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>274.2106536370846</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C101" t="n">
-        <v>279.6808719096702</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D101" t="n">
-        <v>273.9610989943363</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E101" t="n">
-        <v>275.0092163085938</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F101" t="n">
-        <v>51931300</v>
+        <v>34203300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>275.0990906441111</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C102" t="n">
-        <v>275.228863950531</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D102" t="n">
-        <v>259.7165366668213</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E102" t="n">
-        <v>261.2637939453125</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F102" t="n">
-        <v>81077200</v>
+        <v>30845300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>261.5432690161623</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C103" t="n">
-        <v>261.7628783299504</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D103" t="n">
-        <v>254.9949421084194</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E103" t="n">
-        <v>255.3243560791016</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F103" t="n">
-        <v>56290700</v>
+        <v>42070500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>257.5903108294174</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C104" t="n">
-        <v>265.8156532326085</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D104" t="n">
-        <v>255.0847874975786</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E104" t="n">
-        <v>263.4099426269531</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F104" t="n">
-        <v>58469100</v>
+        <v>37308200</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>263.1304558468116</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C105" t="n">
-        <v>266.3447212846438</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D105" t="n">
-        <v>261.9825104325609</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E105" t="n">
-        <v>263.8791198730469</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F105" t="n">
-        <v>34203300</v>
+        <v>47014600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>262.1322047157328</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C106" t="n">
-        <v>264.0088605167754</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D106" t="n">
-        <v>259.5867290635135</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E106" t="n">
-        <v>260.1157836914062</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F106" t="n">
-        <v>30845300</v>
+        <v>33714300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>258.5086811746104</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C107" t="n">
-        <v>264.2783836675007</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D107" t="n">
-        <v>257.7001265171608</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E107" t="n">
-        <v>264.1086730957031</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F107" t="n">
-        <v>42070500</v>
+        <v>32345100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>263.0206001676805</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C108" t="n">
-        <v>268.9500208858886</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D108" t="n">
-        <v>262.9108107477792</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E108" t="n">
-        <v>265.705810546875</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F108" t="n">
-        <v>37308200</v>
+        <v>72366500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>267.3828377763821</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C109" t="n">
-        <v>274.4003442568012</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D109" t="n">
-        <v>267.233111068832</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E109" t="n">
-        <v>271.6552429199219</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F109" t="n">
-        <v>47014600</v>
+        <v>41827900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>271.295868192995</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C110" t="n">
-        <v>274.450242837397</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D110" t="n">
-        <v>270.567157599074</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E110" t="n">
-        <v>273.7415161132812</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F110" t="n">
-        <v>33714300</v>
+        <v>38568900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>274.4602128097023</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C111" t="n">
-        <v>275.6181195635374</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D111" t="n">
-        <v>270.3175813011377</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E111" t="n">
-        <v>272.4637756347656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F111" t="n">
-        <v>32345100</v>
+        <v>39803100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>272.3240124520744</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C112" t="n">
-        <v>272.3240124520744</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D112" t="n">
-        <v>262.4217010495403</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E112" t="n">
-        <v>263.7093811035156</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F112" t="n">
-        <v>72366500</v>
+        <v>49658600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>261.9425306959557</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C113" t="n">
-        <v>266.0551862059975</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D113" t="n">
-        <v>259.7364762526007</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E113" t="n">
-        <v>264.2484130859375</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F113" t="n">
-        <v>41827900</v>
+        <v>41120000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>263.0106738027697</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C114" t="n">
-        <v>265.0869552930596</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D114" t="n">
-        <v>259.6666350681776</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E114" t="n">
-        <v>263.2801818847656</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F114" t="n">
-        <v>38568900</v>
+        <v>38218500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>264.1785481527265</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C115" t="n">
-        <v>265.6758760626757</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D115" t="n">
-        <v>260.9543215497598</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E115" t="n">
-        <v>262.0523376464844</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F115" t="n">
-        <v>39803100</v>
+        <v>30590800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>260.3254337562426</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C116" t="n">
-        <v>261.0940511012478</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D116" t="n">
-        <v>256.7917314296105</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E116" t="n">
-        <v>259.8263244628906</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F116" t="n">
-        <v>49658600</v>
+        <v>26218900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>258.1692718962937</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C117" t="n">
-        <v>258.3090066542827</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D117" t="n">
-        <v>253.916851068475</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E117" t="n">
-        <v>257.0013427734375</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F117" t="n">
-        <v>41120000</v>
+        <v>40794000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>255.2345148744848</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C118" t="n">
-        <v>260.6847798709625</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D118" t="n">
-        <v>253.2280857512349</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E118" t="n">
-        <v>259.4170532226562</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F118" t="n">
-        <v>38218500</v>
+        <v>36930000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>257.1910284571696</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C119" t="n">
-        <v>262.0124415843973</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D119" t="n">
-        <v>256.4922936817907</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E119" t="n">
-        <v>260.3653564453125</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F119" t="n">
-        <v>30590800</v>
+        <v>32074200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>260.6248673962081</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C120" t="n">
-        <v>261.6630231774062</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D120" t="n">
-        <v>259.0876023594815</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E120" t="n">
-        <v>260.3453674316406</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F120" t="n">
-        <v>26218900</v>
+        <v>32361600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>258.1992253881205</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C121" t="n">
-        <v>258.4887173103141</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D121" t="n">
-        <v>253.7271951166323</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E121" t="n">
-        <v>255.3043823242188</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F121" t="n">
-        <v>40794000</v>
+        <v>35757900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>255.024890934378</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C122" t="n">
-        <v>255.8733676296054</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D122" t="n">
-        <v>249.0755164384504</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E122" t="n">
-        <v>249.6744384765625</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F122" t="n">
-        <v>36930000</v>
+        <v>34864100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>251.6609022279199</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C123" t="n">
-        <v>253.4377301906265</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D123" t="n">
-        <v>249.4348789230203</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E123" t="n">
-        <v>252.3696441650391</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F123" t="n">
-        <v>32074200</v>
+        <v>88331100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>252.5093881906664</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C124" t="n">
-        <v>254.6755207628997</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D124" t="n">
-        <v>251.7307636559193</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E124" t="n">
-        <v>253.7771148681641</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F124" t="n">
-        <v>32361600</v>
+        <v>40546100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>252.1799767808244</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C125" t="n">
-        <v>254.4858593736706</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D125" t="n">
-        <v>248.5564382882904</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E125" t="n">
-        <v>249.4947662353516</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F125" t="n">
-        <v>35757900</v>
+        <v>45152300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>248.9557286861236</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C126" t="n">
-        <v>251.3814079598573</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D126" t="n">
-        <v>246.8594786308807</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E126" t="n">
-        <v>248.5165252685547</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F126" t="n">
-        <v>34864100</v>
+        <v>28476700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>247.5382410981218</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C127" t="n">
-        <v>248.7560689935711</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D127" t="n">
-        <v>245.5617725594444</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E127" t="n">
-        <v>247.5482330322266</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F127" t="n">
-        <v>88331100</v>
+        <v>41796700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>253.5175853710609</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C128" t="n">
-        <v>254.1464679788293</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D128" t="n">
-        <v>249.8341562083163</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E128" t="n">
-        <v>251.0420074462891</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F128" t="n">
-        <v>40546100</v>
+        <v>47900000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>249.9040313986812</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C129" t="n">
-        <v>254.3760464402864</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D129" t="n">
-        <v>249.105453476207</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E129" t="n">
-        <v>251.1917266845703</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F129" t="n">
-        <v>45152300</v>
+        <v>39446200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>253.6473574345128</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C130" t="n">
-        <v>254.5457480998694</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D130" t="n">
-        <v>251.1518108845141</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E130" t="n">
-        <v>252.1699829101562</v>
+        <v>253.337890625</v>
       </c>
       <c r="F130" t="n">
-        <v>28476700</v>
+        <v>49598100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>251.6708815336767</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C131" t="n">
-        <v>256.5421934269488</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D131" t="n">
-        <v>250.3232954931613</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E131" t="n">
-        <v>252.4395141601562</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F131" t="n">
-        <v>41796700</v>
+        <v>40059400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>253.4477020992108</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C132" t="n">
-        <v>255.0348812846261</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D132" t="n">
-        <v>247.6281009352486</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E132" t="n">
-        <v>248.3567962646484</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F132" t="n">
-        <v>47900000</v>
+        <v>31289400</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>249.6245329956546</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C133" t="n">
-        <v>250.4230956915925</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D133" t="n">
-        <v>245.0726433781301</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E133" t="n">
-        <v>246.1906585693359</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F133" t="n">
-        <v>39446200</v>
+        <v>29329900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>247.4683756415328</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C134" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D134" t="n">
-        <v>246.6598210163149</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E134" t="n">
-        <v>253.337890625</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F134" t="n">
-        <v>49598100</v>
+        <v>62148000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>253.6273797300248</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C135" t="n">
-        <v>255.7236296181179</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D135" t="n">
-        <v>252.8787157917901</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E135" t="n">
-        <v>255.1746215820312</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F135" t="n">
-        <v>40059400</v>
+        <v>41032800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>253.7471740568136</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C136" t="n">
-        <v>255.6737439434535</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D136" t="n">
-        <v>250.2034948550391</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E136" t="n">
-        <v>255.464111328125</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F136" t="n">
-        <v>31289400</v>
+        <v>28121600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>256.053045051996</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C137" t="n">
-        <v>261.6929736576745</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D137" t="n">
-        <v>256.003115847535</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E137" t="n">
-        <v>258.3988342285156</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F137" t="n">
-        <v>29329900</v>
+        <v>31291500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>255.7036812801697</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C138" t="n">
-        <v>255.7436185540334</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D138" t="n">
-        <v>245.2623079794448</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E138" t="n">
-        <v>253.0484161376953</v>
+        <v>258.73828125</v>
       </c>
       <c r="F138" t="n">
-        <v>62148000</v>
+        <v>36234700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>257.9896016596085</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C139" t="n">
-        <v>259.2872736156141</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D139" t="n">
-        <v>256.0730086009651</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E139" t="n">
-        <v>258.4387817382812</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F139" t="n">
-        <v>41032800</v>
+        <v>48370700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>258.5386040524215</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C140" t="n">
-        <v>260.6548225010532</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D140" t="n">
-        <v>255.6138310165902</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E140" t="n">
-        <v>260.0259399414062</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F140" t="n">
-        <v>28121600</v>
+        <v>49913500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>259.5168819122501</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C141" t="n">
-        <v>261.7229364827484</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D141" t="n">
-        <v>258.5585701252562</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E141" t="n">
-        <v>260.0159912109375</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F141" t="n">
-        <v>31291500</v>
+        <v>43323100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>259.2673359057164</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C142" t="n">
-        <v>259.7165160115803</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D142" t="n">
-        <v>256.2027973984465</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E142" t="n">
-        <v>258.73828125</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F142" t="n">
-        <v>36234700</v>
+        <v>61436200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>258.7881616833942</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C143" t="n">
-        <v>261.4633801130582</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D143" t="n">
-        <v>256.7318338868242</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E143" t="n">
-        <v>258.368896484375</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F143" t="n">
-        <v>48370700</v>
+        <v>36590200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>257.7001261657452</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C144" t="n">
-        <v>266.0851565972939</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D144" t="n">
-        <v>257.3507435512608</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E144" t="n">
-        <v>265.9553833007812</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F144" t="n">
-        <v>49913500</v>
+        <v>50209800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>266.3246925362851</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C145" t="n">
-        <v>266.6840670491935</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D145" t="n">
-        <v>260.804545264895</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E145" t="n">
-        <v>262.9307556152344</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F145" t="n">
-        <v>43323100</v>
+        <v>43249200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>266.4844323486072</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C146" t="n">
-        <v>271.8149160854778</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D146" t="n">
-        <v>266.2448696297591</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E146" t="n">
-        <v>269.7486267089844</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F146" t="n">
-        <v>61436200</v>
+        <v>33399600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>269.8484123886765</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C147" t="n">
-        <v>273.7913879220191</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D147" t="n">
-        <v>269.8085055794248</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E147" t="n">
-        <v>272.5635681152344</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F147" t="n">
-        <v>36590200</v>
+        <v>38157100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>271.0163536236942</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C148" t="n">
-        <v>272.3140256362382</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D148" t="n">
-        <v>264.9272139873882</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E148" t="n">
-        <v>265.6958618164062</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F148" t="n">
-        <v>50209800</v>
+        <v>41466800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>267.3429346055621</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C149" t="n">
-        <v>273.2523721409737</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D149" t="n">
-        <v>266.394614672797</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E149" t="n">
-        <v>272.6834106445312</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F149" t="n">
-        <v>43249200</v>
+        <v>40018900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>274.5600108521774</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C150" t="n">
-        <v>275.2787294551341</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D150" t="n">
-        <v>271.1660737405759</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E150" t="n">
-        <v>272.9429016113281</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F150" t="n">
-        <v>33399600</v>
+        <v>30047900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>272.2741016414235</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C151" t="n">
-        <v>272.5735550213531</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D151" t="n">
-        <v>269.1696261078274</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E151" t="n">
-        <v>270.5771179199219</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F151" t="n">
-        <v>38157100</v>
+        <v>91848200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>265.6159889280984</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C152" t="n">
-        <v>267.8819342286378</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D152" t="n">
-        <v>264.5978169025021</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E152" t="n">
-        <v>267.1332702636719</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F152" t="n">
-        <v>41466800</v>
+        <v>79915400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>271.8548539018017</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C153" t="n">
-        <v>272.7432830913257</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D153" t="n">
-        <v>268.181416710472</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E153" t="n">
-        <v>270.2277526855469</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F153" t="n">
-        <v>40018900</v>
+        <v>46668400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>267.0733624970658</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C154" t="n">
-        <v>270.5571659728108</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D154" t="n">
-        <v>266.5642917484437</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E154" t="n">
-        <v>269.688720703125</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F154" t="n">
-        <v>30047900</v>
+        <v>49311700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>270.018146234023</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C155" t="n">
-        <v>275.5083488376723</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D155" t="n">
-        <v>267.6623648300734</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E155" t="n">
-        <v>270.8666381835938</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F155" t="n">
-        <v>91848200</v>
+        <v>58336100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>278.3632116979401</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C156" t="n">
-        <v>286.7083346607987</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D156" t="n">
-        <v>277.8740943540899</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E156" t="n">
-        <v>279.6409606933594</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F156" t="n">
-        <v>79915400</v>
+        <v>45224300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>279.1618288412153</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C157" t="n">
-        <v>280.130102141665</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D157" t="n">
-        <v>274.3703610857382</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E157" t="n">
-        <v>276.3368530273438</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F157" t="n">
-        <v>46668400</v>
+        <v>52692800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,25 +4525,25 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>276.43668191704</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C158" t="n">
-        <v>284.0630869835518</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D158" t="n">
-        <v>276.0074552110661</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E158" t="n">
-        <v>283.6737670898438</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F158" t="n">
-        <v>49311700</v>
+        <v>42247300</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>281.4177950537395</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C159" t="n">
-        <v>287.5168959460148</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D159" t="n">
-        <v>280.5693031693742</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E159" t="n">
-        <v>286.9978332519531</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F159" t="n">
-        <v>58336100</v>
+        <v>45748100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>288.7546745760609</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C160" t="n">
-        <v>291.6095955251437</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D160" t="n">
-        <v>285.2709015174152</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E160" t="n">
-        <v>286.9279479980469</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F160" t="n">
-        <v>45224300</v>
+        <v>52684300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>289.4933842419345</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C161" t="n">
-        <v>294.2349225642168</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D161" t="n">
-        <v>289.4833923077643</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E161" t="n">
-        <v>292.7974853515625</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F161" t="n">
-        <v>52692800</v>
+        <v>35324900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,25 +4629,25 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>291.7284168827658</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C162" t="n">
-        <v>293.6267735875138</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D162" t="n">
-        <v>289.979924827367</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E162" t="n">
-        <v>292.4277954101562</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F162" t="n">
-        <v>42247300</v>
+        <v>54862800</v>
       </c>
       <c r="G162" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>292.3078994315659</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C163" t="n">
-        <v>295.0155556946294</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D163" t="n">
-        <v>292.3078994315659</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E163" t="n">
-        <v>294.5459594726562</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F163" t="n">
-        <v>45748100</v>
+        <v>34483000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>293.247089511151</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C164" t="n">
-        <v>300.6607090744109</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D164" t="n">
-        <v>293.247089511151</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E164" t="n">
-        <v>298.6124572753906</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F164" t="n">
-        <v>52684300</v>
+        <v>42243600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>299.5616620172475</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C165" t="n">
-        <v>300.1911240450107</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D165" t="n">
-        <v>295.1254853838782</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E165" t="n">
-        <v>297.9530334472656</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F165" t="n">
-        <v>35324900</v>
+        <v>38229800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>297.643304079477</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C166" t="n">
-        <v>302.9387555529706</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D166" t="n">
-        <v>296.2644882977323</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E166" t="n">
-        <v>299.9713134765625</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F166" t="n">
-        <v>54862800</v>
+        <v>42965100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>299.9812692945075</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C167" t="n">
-        <v>300.4009207908792</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D167" t="n">
-        <v>294.6558756451712</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E167" t="n">
-        <v>297.5833435058594</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F167" t="n">
-        <v>34483000</v>
+        <v>43670200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>296.7140952726279</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C168" t="n">
-        <v>300.2510533099592</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D168" t="n">
-        <v>296.0946344196341</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E168" t="n">
-        <v>298.7123718261719</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F168" t="n">
-        <v>42243600</v>
+        <v>48000500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>297.9230626302997</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C169" t="n">
-        <v>302.5390768782648</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D169" t="n">
-        <v>297.8231426981347</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E169" t="n">
-        <v>301.9895629882812</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F169" t="n">
-        <v>38229800</v>
+        <v>50430900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>300.8005667472183</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C170" t="n">
-        <v>305.2767171977908</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D170" t="n">
-        <v>300.1411318265125</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E170" t="n">
-        <v>304.7271728515625</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F170" t="n">
-        <v>42965100</v>
+        <v>48220400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>305.8562084633929</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C171" t="n">
-        <v>311.1316574150658</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D171" t="n">
-        <v>305.5764509618376</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E171" t="n">
-        <v>308.5538940429688</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F171" t="n">
-        <v>43670200</v>
+        <v>70026800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>309.2932516306071</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C172" t="n">
-        <v>311.5513139598484</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D172" t="n">
-        <v>307.4048960873393</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E172" t="n">
-        <v>308.0643005371094</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F172" t="n">
-        <v>48000500</v>
+        <v>48849900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>308.0643052358437</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C173" t="n">
-        <v>312.9900803339556</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D173" t="n">
-        <v>308.0343323058515</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E173" t="n">
-        <v>310.5821533203125</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F173" t="n">
-        <v>50430900</v>
+        <v>44534700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>310.412282475935</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C174" t="n">
-        <v>312.5304508120942</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D174" t="n">
-        <v>309.3032535889254</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E174" t="n">
-        <v>312.24072265625</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F174" t="n">
-        <v>48220400</v>
+        <v>50836700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>311.5113496628706</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C175" t="n">
-        <v>314.7285763294451</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D175" t="n">
-        <v>309.2632884033746</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E175" t="n">
-        <v>311.7911071777344</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F175" t="n">
-        <v>70026800</v>
+        <v>44869100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>309.363197507879</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C176" t="n">
-        <v>310.6720662449624</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D176" t="n">
-        <v>304.7571540774977</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E176" t="n">
-        <v>306.0460510253906</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F176" t="n">
-        <v>48849900</v>
+        <v>65310500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>307.1950545511415</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C177" t="n">
-        <v>315.1781903378333</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D177" t="n">
-        <v>306.42572903357</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E177" t="n">
-        <v>314.9284057617188</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F177" t="n">
-        <v>44534700</v>
+        <v>77949100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>313.9092501546009</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C178" t="n">
-        <v>316.6668815001487</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D178" t="n">
-        <v>308.5838566628498</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E178" t="n">
-        <v>309.9926452636719</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F178" t="n">
-        <v>50836700</v>
+        <v>70108800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>312.9600990996374</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C179" t="n">
-        <v>313.2698295317651</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D179" t="n">
-        <v>309.3831669286495</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E179" t="n">
-        <v>310.9618225097656</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F179" t="n">
-        <v>44869100</v>
+        <v>52793300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>312.5903972939029</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C180" t="n">
-        <v>314.8984348439246</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D180" t="n">
-        <v>306.8853260765596</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E180" t="n">
-        <v>307.0751647949219</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F180" t="n">
-        <v>65310500</v>
+        <v>42572500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>308.4739595974908</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C181" t="n">
-        <v>317.1265012321255</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D181" t="n">
-        <v>300.9105055796523</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E181" t="n">
-        <v>301.2801818847656</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F181" t="n">
-        <v>77949100</v>
+        <v>38742100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>300.0212482417878</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C182" t="n">
-        <v>300.4908444635933</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D182" t="n">
-        <v>287.5320194610898</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E182" t="n">
-        <v>290.2996215820312</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F182" t="n">
-        <v>70108800</v>
+        <v>45732600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>290.4894628291428</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C183" t="n">
-        <v>294.4960172141002</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D183" t="n">
-        <v>287.1323727394638</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E183" t="n">
-        <v>291.3287353515625</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F183" t="n">
-        <v>52793300</v>
+        <v>39874400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>293.4668864344149</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C184" t="n">
-        <v>296.7440586571729</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D184" t="n">
-        <v>289.3404406054596</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E184" t="n">
-        <v>295.375244140625</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F184" t="n">
-        <v>42572500</v>
+        <v>42745100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>295.7749221682621</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C185" t="n">
-        <v>296.8839815833701</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D185" t="n">
-        <v>289.3704417369658</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E185" t="n">
-        <v>290.879150390625</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F185" t="n">
-        <v>38742100</v>
+        <v>85962200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>293.8665449684006</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C186" t="n">
-        <v>297.5233947188816</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D186" t="n">
-        <v>291.4486474146935</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E186" t="n">
-        <v>296.1645812988281</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F186" t="n">
-        <v>45732600</v>
+        <v>44879900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>294.9955949959084</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C187" t="n">
-        <v>300.2210994929347</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D187" t="n">
-        <v>293.7166991398789</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E187" t="n">
-        <v>298.9821472167969</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F187" t="n">
-        <v>39874400</v>
+        <v>52010900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>300.590748125481</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C188" t="n">
-        <v>301.8096980081642</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D188" t="n">
-        <v>294.1063201593793</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E188" t="n">
-        <v>295.6949768066406</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F188" t="n">
-        <v>42745100</v>
+        <v>53081900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>297.8530937792582</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C189" t="n">
-        <v>300.3109958668267</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D189" t="n">
-        <v>295.3652492546472</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E189" t="n">
-        <v>297.7532043457031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F189" t="n">
-        <v>85962200</v>
+        <v>107013700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>297.0538186622031</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C190" t="n">
-        <v>302.1594314563154</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D190" t="n">
-        <v>296.5043047694293</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E190" t="n">
-        <v>296.7540893554688</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F190" t="n">
-        <v>44879900</v>
+        <v>261775500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>297.2836155142734</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C191" t="n">
-        <v>301.3800886038737</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D191" t="n">
-        <v>293.9264950024863</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E191" t="n">
-        <v>294.04638671875</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F191" t="n">
-        <v>52010900</v>
+        <v>66427000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>295.1054570720635</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C192" t="n">
-        <v>299.4417438827621</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D192" t="n">
-        <v>292.6875595970274</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E192" t="n">
-        <v>292.8274230957031</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F192" t="n">
-        <v>53081900</v>
+        <v>65100200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>287.1523472601469</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C193" t="n">
-        <v>288.551134810818</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D193" t="n">
-        <v>273.5141152813601</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E193" t="n">
-        <v>274.9129028320312</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F193" t="n">
-        <v>107013700</v>
+        <v>50164200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>274.7630284991681</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C194" t="n">
-        <v>285.7036049213746</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D194" t="n">
-        <v>273.9737007161028</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E194" t="n">
-        <v>283.5354614257812</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F194" t="n">
-        <v>261775500</v>
+        <v>75352800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>286.4829438934296</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C195" t="n">
-        <v>288.1215148966215</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D195" t="n">
-        <v>279.6088673150861</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E195" t="n">
-        <v>281.4972229003906</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F195" t="n">
-        <v>66427000</v>
+        <v>53590000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>280.9277417485351</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C196" t="n">
-        <v>289.6901740532286</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D196" t="n">
-        <v>280.4581455069533</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E196" t="n">
-        <v>289.1106567382812</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F196" t="n">
-        <v>65100200</v>
+        <v>42490000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>293.1871503157195</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C197" t="n">
-        <v>296.3344299174724</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D197" t="n">
-        <v>288.9508136068854</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E197" t="n">
-        <v>294.1263427734375</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F197" t="n">
-        <v>50164200</v>
+        <v>41323500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>293.866538367699</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C198" t="n">
-        <v>309.1533719476172</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D198" t="n">
-        <v>293.4269150966668</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E198" t="n">
-        <v>308.3640441894531</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F198" t="n">
-        <v>75352800</v>
+        <v>48124500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>307.0951430290638</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C199" t="n">
-        <v>313.9292760509671</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D199" t="n">
-        <v>306.7354678654279</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E199" t="n">
-        <v>312.3905944824219</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F199" t="n">
-        <v>53590000</v>
+        <v>34132300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>315.0183186077797</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C200" t="n">
-        <v>315.2081573213482</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D200" t="n">
-        <v>309.8827331839256</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E200" t="n">
-        <v>310.3923034667969</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F200" t="n">
-        <v>42490000</v>
+        <v>43257800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>311.6412289475945</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C201" t="n">
-        <v>314.5487250421545</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D201" t="n">
-        <v>306.7854009831778</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E201" t="n">
-        <v>313.1199645996094</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F201" t="n">
-        <v>41323500</v>
+        <v>36336800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>310.242438694691</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C202" t="n">
-        <v>316.2572401947346</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D202" t="n">
-        <v>307.8944576262147</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E202" t="n">
-        <v>315.947509765625</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F202" t="n">
-        <v>48124500</v>
+        <v>60957600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>314.4488202226986</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C203" t="n">
-        <v>316.6369356310425</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D203" t="n">
-        <v>311.9010296470402</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E203" t="n">
-        <v>315.0483093261719</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F203" t="n">
-        <v>34132300</v>
+        <v>62970600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>316.7468014245228</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C204" t="n">
-        <v>323.171283634363</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D204" t="n">
-        <v>315.5078797345754</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E204" t="n">
-        <v>317.0365600585938</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F204" t="n">
-        <v>43257800</v>
+        <v>63407100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>313.4896562976144</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C205" t="n">
-        <v>315.9175551535121</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D205" t="n">
-        <v>311.6412442645678</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E205" t="n">
-        <v>314.5886840820312</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F205" t="n">
-        <v>36336800</v>
+        <v>53468000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>317.3463123495229</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C206" t="n">
-        <v>328.4467550811451</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D206" t="n">
-        <v>317.0465830462295</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E206" t="n">
-        <v>327.2178039550781</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F206" t="n">
-        <v>60957600</v>
+        <v>41338900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>327.7273632845606</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C207" t="n">
-        <v>334.3915986652446</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D207" t="n">
-        <v>326.5084133398602</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E207" t="n">
-        <v>332.9728393554688</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F207" t="n">
-        <v>62970600</v>
+        <v>38755900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>331.693929977533</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C208" t="n">
-        <v>334.7013154010385</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D208" t="n">
-        <v>328.7164869908464</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E208" t="n">
-        <v>333.452392578125</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F208" t="n">
-        <v>63407100</v>
+        <v>40840800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>333.2226134619852</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C209" t="n">
-        <v>333.4224228207836</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D209" t="n">
-        <v>323.4010672140761</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E209" t="n">
-        <v>326.3085632324219</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F209" t="n">
-        <v>53468000</v>
+        <v>47489400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>322.8515675846224</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C210" t="n">
-        <v>329.3159936819017</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D210" t="n">
-        <v>321.942348061891</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E210" t="n">
-        <v>327.4575805664062</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F210" t="n">
-        <v>41338900</v>
+        <v>49604300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>327.58746619389</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C211" t="n">
-        <v>328.7164973399543</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D211" t="n">
-        <v>323.0613709608057</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E211" t="n">
-        <v>325.6091918945312</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F211" t="n">
-        <v>38755900</v>
+        <v>51859000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>321.4527900194849</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C212" t="n">
-        <v>323.0214140443725</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D212" t="n">
-        <v>319.0748358849152</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E212" t="n">
-        <v>321.3828430175781</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F212" t="n">
-        <v>40840800</v>
+        <v>56090800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>321.5127284115298</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C213" t="n">
-        <v>334.0818750563203</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D213" t="n">
-        <v>321.3428614810286</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E213" t="n">
-        <v>332.7330322265625</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F213" t="n">
-        <v>47489400</v>
+        <v>74817800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>334.2517370375488</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C214" t="n">
-        <v>339.277401491225</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D214" t="n">
-        <v>333.7321656046138</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E214" t="n">
-        <v>336.6196899414062</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F214" t="n">
-        <v>49604300</v>
+        <v>132489100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>339.7369815530101</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C215" t="n">
-        <v>342.594532833967</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D215" t="n">
-        <v>335.3108063761878</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E215" t="n">
-        <v>339.7869262695312</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F215" t="n">
-        <v>51859000</v>
+        <v>75052000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>339.4372716346421</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C216" t="n">
-        <v>344.2730974331505</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D216" t="n">
-        <v>337.0593175600121</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E216" t="n">
-        <v>337.8985900878906</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F216" t="n">
-        <v>56090800</v>
+        <v>68001000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>332.8129674612056</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C217" t="n">
-        <v>334.4615395264105</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D217" t="n">
-        <v>329.3059823380879</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E217" t="n">
-        <v>333.1426696777344</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F217" t="n">
-        <v>74817800</v>
+        <v>49438800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>304.5473560391475</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C218" t="n">
-        <v>310.4222943774597</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D218" t="n">
-        <v>299.7415030462749</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E218" t="n">
-        <v>308.6438293457031</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F218" t="n">
-        <v>132489100</v>
+        <v>46139900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>309.313234694189</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C219" t="n">
-        <v>311.5313230344714</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D219" t="n">
-        <v>302.2992945058118</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E219" t="n">
-        <v>303.1585693359375</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F219" t="n">
-        <v>75052000</v>
+        <v>34437200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,25 +6137,25 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>302.4691399129853</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C220" t="n">
-        <v>310.1525156602479</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D220" t="n">
-        <v>301.0603512911937</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E220" t="n">
-        <v>309.1134033203125</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F220" t="n">
-        <v>68001000</v>
+        <v>44812500</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>309.093423625652</v>
+        <v>307.75</v>
       </c>
       <c r="C221" t="n">
-        <v>311.4414048335362</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D221" t="n">
-        <v>305.4066311863439</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E221" t="n">
-        <v>310.7320251464844</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F221" t="n">
-        <v>49438800</v>
+        <v>37476700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>314.06913775687</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C222" t="n">
-        <v>316.0174696892129</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D222" t="n">
-        <v>308.9635555464841</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E222" t="n">
-        <v>312.1408081054688</v>
+        <v>302.25</v>
       </c>
       <c r="F222" t="n">
-        <v>46139900</v>
+        <v>41657800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>311.1816431226555</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C223" t="n">
-        <v>314.5387332545777</v>
+        <v>306</v>
       </c>
       <c r="D223" t="n">
-        <v>310.4722329590833</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E223" t="n">
-        <v>313.0599975585938</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F223" t="n">
-        <v>34437200</v>
+        <v>40349300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,25 +6241,25 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>306.8299865722656</v>
+        <v>306</v>
       </c>
       <c r="C224" t="n">
-        <v>308.260009765625</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D224" t="n">
-        <v>304.6099853515625</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E224" t="n">
-        <v>308.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F224" t="n">
-        <v>44812500</v>
+        <v>28229400</v>
       </c>
       <c r="G224" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>307.75</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C225" t="n">
-        <v>309.9700012207031</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D225" t="n">
-        <v>302.7900085449219</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E225" t="n">
-        <v>304.9100036621094</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F225" t="n">
-        <v>37476700</v>
+        <v>38169300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>305.1000061035156</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C226" t="n">
-        <v>305.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D226" t="n">
-        <v>300.5700073242188</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E226" t="n">
-        <v>302.25</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F226" t="n">
-        <v>41657800</v>
+        <v>53424500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>304.2099914550781</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C227" t="n">
-        <v>306</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D227" t="n">
-        <v>302.0499877929688</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E227" t="n">
-        <v>305.260009765625</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F227" t="n">
-        <v>40349300</v>
+        <v>50505600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>306</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C228" t="n">
-        <v>307.489990234375</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D228" t="n">
-        <v>304.2999877929688</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E228" t="n">
-        <v>305.9299926757812</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F228" t="n">
-        <v>28229400</v>
+        <v>40959200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>306.2099914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C229" t="n">
-        <v>307.6600036621094</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D229" t="n">
-        <v>302.9400024414062</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E229" t="n">
-        <v>305.5899963378906</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F229" t="n">
-        <v>38169300</v>
+        <v>46876800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>307.5799865722656</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C230" t="n">
-        <v>311.489990234375</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D230" t="n">
-        <v>305.739990234375</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E230" t="n">
-        <v>310.0299987792969</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F230" t="n">
-        <v>53424500</v>
+        <v>34673600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>310.1400146484375</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C231" t="n">
-        <v>319.2799987792969</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D231" t="n">
-        <v>309.6000061035156</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E231" t="n">
-        <v>316.8299865722656</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F231" t="n">
-        <v>50505600</v>
+        <v>25869800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>317.4599914550781</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C232" t="n">
-        <v>320.2799987792969</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D232" t="n">
-        <v>310.6499938964844</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E232" t="n">
-        <v>311.2999877929688</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>40959200</v>
+        <v>34024500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>312.0499877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C233" t="n">
-        <v>312.3800048828125</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D233" t="n">
-        <v>307.010009765625</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E233" t="n">
-        <v>309.3500061035156</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F233" t="n">
-        <v>46876800</v>
+        <v>32419200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>311.4700012207031</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C234" t="n">
-        <v>313.3599853515625</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D234" t="n">
-        <v>309.9700012207031</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E234" t="n">
-        <v>310.3399963378906</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F234" t="n">
-        <v>34673600</v>
+        <v>38649400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>310.7900085449219</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="C235" t="n">
-        <v>313.5899963378906</v>
+        <v>321.239990234375</v>
       </c>
       <c r="D235" t="n">
-        <v>308.2099914550781</v>
+        <v>312.7999877929688</v>
       </c>
       <c r="E235" t="n">
-        <v>309.8999938964844</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="F235" t="n">
-        <v>25869800</v>
+        <v>41242700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>310.2999877929688</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C236" t="n">
-        <v>315.4299926757812</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D236" t="n">
-        <v>308.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E236" t="n">
-        <v>313.4500122070312</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F236" t="n">
-        <v>34024500</v>
+        <v>53167400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>310.5499877929688</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C237" t="n">
-        <v>315.3999938964844</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D237" t="n">
-        <v>309.3999938964844</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E237" t="n">
-        <v>314.5799865722656</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F237" t="n">
-        <v>32419200</v>
+        <v>33776400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>316.8500061035156</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C238" t="n">
-        <v>322.3699951171875</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D238" t="n">
-        <v>315.4500122070312</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E238" t="n">
-        <v>319.7000122070312</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F238" t="n">
-        <v>38649400</v>
+        <v>37225800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>319.6000061035156</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C239" t="n">
-        <v>321.239990234375</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D239" t="n">
-        <v>312.7999877929688</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E239" t="n">
-        <v>316.8500061035156</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F239" t="n">
-        <v>41242700</v>
+        <v>39606900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>316.9800109863281</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>327.2999877929688</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>314.7300109863281</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E240" t="n">
-        <v>325.1300048828125</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F240" t="n">
-        <v>53167400</v>
+        <v>35477100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>326.8699951171875</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C241" t="n">
-        <v>328.3999938964844</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D241" t="n">
-        <v>323.5299987792969</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E241" t="n">
-        <v>324.9599914550781</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F241" t="n">
-        <v>33776400</v>
+        <v>65640000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>324.8699951171875</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C242" t="n">
-        <v>330.8099975585938</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D242" t="n">
-        <v>324.1099853515625</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E242" t="n">
-        <v>328.2099914550781</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F242" t="n">
-        <v>37225800</v>
+        <v>70011900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>328.3099975585938</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C243" t="n">
-        <v>328.9299926757812</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D243" t="n">
-        <v>317.8599853515625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E243" t="n">
-        <v>319.9700012207031</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F243" t="n">
-        <v>39606900</v>
+        <v>50716900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>317.1000061035156</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C244" t="n">
-        <v>320.7000122070312</v>
+        <v>335.5</v>
       </c>
       <c r="D244" t="n">
-        <v>314.8999938964844</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E244" t="n">
-        <v>316.2200012207031</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F244" t="n">
-        <v>35477100</v>
+        <v>39269100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>315.489990234375</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>319.1499938964844</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D245" t="n">
-        <v>309.8999938964844</v>
+        <v>328.3500061035156</v>
       </c>
       <c r="E245" t="n">
-        <v>315.3399963378906</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="F245" t="n">
-        <v>65640000</v>
+        <v>31748200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>316.6700134277344</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>326.739990234375</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D246" t="n">
-        <v>316.510009765625</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E246" t="n">
-        <v>326.5700073242188</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F246" t="n">
-        <v>70011900</v>
+        <v>35981000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>336.2200012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D247" t="n">
-        <v>326.2999877929688</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E247" t="n">
-        <v>332.2699890136719</v>
+        <v>337</v>
       </c>
       <c r="F247" t="n">
-        <v>50716900</v>
+        <v>36700200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>334.7900085449219</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C248" t="n">
-        <v>335.5</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D248" t="n">
-        <v>331.3399963378906</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>333.0799865722656</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F248" t="n">
-        <v>39269100</v>
+        <v>86588200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>330.1400146484375</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>331.7799987792969</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D249" t="n">
-        <v>328.3500061035156</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>331.3399963378906</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F249" t="n">
-        <v>31748200</v>
+        <v>34999200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B250" t="n">
-        <v>332.5299987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>335.4800109863281</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>330.7000122070312</v>
+        <v>338.75</v>
       </c>
       <c r="E250" t="n">
-        <v>332.4100036621094</v>
+        <v>339.75</v>
       </c>
       <c r="F250" t="n">
-        <v>35981000</v>
+        <v>40711800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B251" t="n">
-        <v>334.7699890136719</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C251" t="n">
-        <v>338.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>330.1799926757812</v>
+        <v>335.5</v>
       </c>
       <c r="E251" t="n">
-        <v>337</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F251" t="n">
-        <v>36700200</v>
+        <v>31658800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B252" t="n">
-        <v>337.9100036621094</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C252" t="n">
-        <v>338.489990234375</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D252" t="n">
-        <v>332.5299987792969</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>336.1300048828125</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F252" t="n">
-        <v>86433100</v>
+        <v>24686400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,43 +10498,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>336.13</v>
+        <v>335.92</v>
       </c>
       <c r="D2" t="n">
-        <v>337</v>
+        <v>337.02</v>
       </c>
       <c r="E2" t="n">
-        <v>337.99</v>
+        <v>336.32</v>
       </c>
       <c r="F2" t="n">
-        <v>338.49</v>
+        <v>338.91</v>
       </c>
       <c r="G2" t="n">
-        <v>332.53</v>
+        <v>334.3</v>
       </c>
       <c r="H2" t="n">
-        <v>86241049</v>
+        <v>24364559</v>
       </c>
       <c r="I2" t="n">
-        <v>53449420</v>
+        <v>52775646</v>
       </c>
       <c r="J2" t="n">
-        <v>4905541566464</v>
+        <v>4902477103104</v>
       </c>
       <c r="K2" t="n">
-        <v>38.591274</v>
+        <v>38.611496</v>
       </c>
       <c r="L2" t="n">
-        <v>35.05517</v>
+        <v>35.033268</v>
       </c>
       <c r="M2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>344.57</v>
+        <v>345.34</v>
       </c>
       <c r="O2" t="n">
-        <v>240.21</v>
+        <v>243.42</v>
       </c>
       <c r="P2" t="n">
         <v>1.085</v>
@@ -10564,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.669838</v>
+        <v>45.641304</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4927486689280</v>
+        <v>4924421701632</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:04</t>
+          <t>2026-09-25 14:28:51</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>252.2780882048451</v>
+        <v>253.1648106749593</v>
       </c>
       <c r="C2" t="n">
-        <v>256.2235204411851</v>
+        <v>256.6519291955366</v>
       </c>
       <c r="D2" t="n">
-        <v>250.7836088309123</v>
+        <v>252.8459811129583</v>
       </c>
       <c r="E2" t="n">
-        <v>255.9246063232422</v>
+        <v>254.5198059082031</v>
       </c>
       <c r="F2" t="n">
-        <v>55202100</v>
+        <v>46076300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>253.1648106749593</v>
+        <v>253.6231329894407</v>
       </c>
       <c r="C3" t="n">
-        <v>256.6519291955366</v>
+        <v>254.0615160770535</v>
       </c>
       <c r="D3" t="n">
-        <v>252.8459811129583</v>
+        <v>252.0788344590342</v>
       </c>
       <c r="E3" t="n">
-        <v>254.5198059082031</v>
+        <v>253.4936065673828</v>
       </c>
       <c r="F3" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>253.6231329894407</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C4" t="n">
-        <v>254.0615160770535</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D4" t="n">
-        <v>252.0788344590342</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E4" t="n">
-        <v>253.4936065673828</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F4" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C5" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D5" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E5" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F5" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356912331815</v>
       </c>
       <c r="C6" t="n">
-        <v>257.8375609779932</v>
+        <v>257.2298088092003</v>
       </c>
       <c r="D6" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146416974651</v>
       </c>
       <c r="E6" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836853027344</v>
       </c>
       <c r="F6" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C7" t="n">
-        <v>257.229778167004</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D7" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E7" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F7" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0404883747525</v>
       </c>
       <c r="C8" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165305885388</v>
       </c>
       <c r="D8" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113214696764</v>
       </c>
       <c r="E8" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7452850341797</v>
       </c>
       <c r="F8" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>257.0404730386864</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C9" t="n">
-        <v>258.1165151882718</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D9" t="n">
-        <v>254.1113063083761</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E9" t="n">
-        <v>255.7452697753906</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F9" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>255.8648438796676</v>
+        <v>255.5759191543519</v>
       </c>
       <c r="C10" t="n">
-        <v>256.4526688176338</v>
+        <v>257.5685585594684</v>
       </c>
       <c r="D10" t="n">
-        <v>254.4899179139702</v>
+        <v>255.1674244276712</v>
       </c>
       <c r="E10" t="n">
-        <v>255.5360717773438</v>
+        <v>257.1102600097656</v>
       </c>
       <c r="F10" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>255.5759191543519</v>
+        <v>256.8611554198282</v>
       </c>
       <c r="C11" t="n">
-        <v>257.5685585594684</v>
+        <v>257.0504585775582</v>
       </c>
       <c r="D11" t="n">
-        <v>255.1674244276712</v>
+        <v>252.2083446799687</v>
       </c>
       <c r="E11" t="n">
-        <v>257.1102600097656</v>
+        <v>253.1050262451172</v>
       </c>
       <c r="F11" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>256.8611399345957</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C12" t="n">
-        <v>257.0504430809132</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D12" t="n">
-        <v>252.2083294752373</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E12" t="n">
-        <v>253.1050109863281</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F12" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>254.0017340209507</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C13" t="n">
-        <v>255.4364367494707</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D13" t="n">
-        <v>243.1019946167774</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E13" t="n">
-        <v>244.3673248291016</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F13" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924316138584</v>
       </c>
       <c r="C14" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341508249242</v>
       </c>
       <c r="D14" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994151584908</v>
       </c>
       <c r="E14" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581237792969</v>
       </c>
       <c r="F14" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>245.6924164271231</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C15" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D15" t="n">
-        <v>243.7994000887665</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E15" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F15" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C16" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D16" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E16" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F16" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>247.3363348246392</v>
+        <v>247.1072067041429</v>
       </c>
       <c r="C17" t="n">
-        <v>248.1234206007849</v>
+        <v>252.4474806979352</v>
       </c>
       <c r="D17" t="n">
-        <v>244.2278226113223</v>
+        <v>246.3599669580113</v>
       </c>
       <c r="E17" t="n">
-        <v>246.5392761230469</v>
+        <v>251.3614807128906</v>
       </c>
       <c r="F17" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C18" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D18" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E18" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F18" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C19" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D19" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E19" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F19" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>260.9161783410852</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C20" t="n">
-        <v>264.3136317818121</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D20" t="n">
-        <v>260.8663441185724</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E20" t="n">
-        <v>261.8028869628906</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F20" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>261.6833338430701</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C21" t="n">
-        <v>261.882609922878</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D21" t="n">
-        <v>254.4899051977633</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E21" t="n">
-        <v>257.4988098144531</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F21" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>258.9832941033833</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C22" t="n">
-        <v>259.6607840683213</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D22" t="n">
-        <v>257.0604047594014</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E22" t="n">
-        <v>258.6246032714844</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F22" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C23" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D23" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E23" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F23" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>263.9051197703755</v>
+        <v>267.9999758056659</v>
       </c>
       <c r="C24" t="n">
-        <v>268.1295048126629</v>
+        <v>268.896687690681</v>
       </c>
       <c r="D24" t="n">
-        <v>263.6759553344934</v>
+        <v>267.1630710642092</v>
       </c>
       <c r="E24" t="n">
-        <v>267.8206481933594</v>
+        <v>268.0099487304688</v>
       </c>
       <c r="F24" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>267.9999758056659</v>
+        <v>268.2889603375268</v>
       </c>
       <c r="C25" t="n">
-        <v>268.896687690681</v>
+        <v>270.4111261059246</v>
       </c>
       <c r="D25" t="n">
-        <v>267.1630710642092</v>
+        <v>266.126933268734</v>
       </c>
       <c r="E25" t="n">
-        <v>268.0099487304688</v>
+        <v>268.7074279785156</v>
       </c>
       <c r="F25" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889785237465</v>
       </c>
       <c r="C26" t="n">
-        <v>270.4110953948544</v>
+        <v>273.131090148023</v>
       </c>
       <c r="D26" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4919171420091</v>
       </c>
       <c r="E26" t="n">
-        <v>268.7073974609375</v>
+        <v>270.4011535644531</v>
       </c>
       <c r="F26" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>270.9889479398262</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C27" t="n">
-        <v>273.1310593223432</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D27" t="n">
-        <v>267.4918869527685</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E27" t="n">
-        <v>270.401123046875</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F27" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>275.9705389196515</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C28" t="n">
-        <v>276.2993413939207</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D28" t="n">
-        <v>268.1693703205502</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E28" t="n">
-        <v>269.3749084472656</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F28" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>269.4247673672652</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C29" t="n">
-        <v>269.8531775103368</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D29" t="n">
-        <v>265.2701011373342</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E29" t="n">
-        <v>268.0597839355469</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F29" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C30" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D30" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E30" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F30" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>267.6213843438783</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C31" t="n">
-        <v>270.7000385630726</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D31" t="n">
-        <v>265.9475747682897</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E31" t="n">
-        <v>269.1457824707031</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F31" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C32" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D32" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E32" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F32" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,25 +1275,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C33" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D33" t="n">
-        <v>265.7881780523408</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E33" t="n">
-        <v>267.48193359375</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F33" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1301,25 +1301,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>268.2298525605972</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C34" t="n">
-        <v>272.9869230403233</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D34" t="n">
-        <v>266.733924572705</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E34" t="n">
-        <v>268.6985778808594</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F34" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G34" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C35" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D35" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E35" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F35" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>274.2535373864602</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C36" t="n">
-        <v>274.9815668240292</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D36" t="n">
-        <v>270.962507111719</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E36" t="n">
-        <v>272.7276916503906</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F36" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>273.3658696206449</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C37" t="n">
-        <v>275.9488654308047</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D37" t="n">
-        <v>271.3513641926929</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E37" t="n">
-        <v>272.2090454101562</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F37" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0903024129557</v>
       </c>
       <c r="C38" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557521979796</v>
       </c>
       <c r="D38" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086937896775</v>
       </c>
       <c r="E38" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339782714844</v>
       </c>
       <c r="F38" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>268.0902717401977</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C39" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D39" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E39" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F39" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>269.25705465795</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C40" t="n">
-        <v>269.9751013080067</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D40" t="n">
-        <v>264.5997492422933</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E40" t="n">
-        <v>266.7139892578125</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F40" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>264.8092197798317</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C41" t="n">
-        <v>271.4710796703931</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D41" t="n">
-        <v>264.7793024319747</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E41" t="n">
-        <v>267.8309936523438</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F41" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C42" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D42" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E42" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F42" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>265.2280517805383</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C43" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D43" t="n">
-        <v>264.9488130991126</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E43" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F43" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C44" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D44" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E44" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F44" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C45" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D45" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E45" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F45" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>276.2082055022192</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C46" t="n">
-        <v>278.7712367451818</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D46" t="n">
-        <v>275.8791146523587</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E46" t="n">
-        <v>276.7966003417969</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F46" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>276.5073679150082</v>
+        <v>277.255303275414</v>
       </c>
       <c r="C47" t="n">
-        <v>278.242634823177</v>
+        <v>282.650620542313</v>
       </c>
       <c r="D47" t="n">
-        <v>275.2407959413455</v>
+        <v>275.390384584981</v>
       </c>
       <c r="E47" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3314819335938</v>
       </c>
       <c r="F47" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>277.2553332443013</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C48" t="n">
-        <v>282.6506510943872</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D48" t="n">
-        <v>275.3904143522869</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E48" t="n">
-        <v>282.3315124511719</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F48" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C49" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D49" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E49" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F49" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>285.4231155973949</v>
+        <v>283.328813896664</v>
       </c>
       <c r="C50" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9571086251454</v>
       </c>
       <c r="D50" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337611056945</v>
       </c>
       <c r="E50" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380493164062</v>
       </c>
       <c r="F50" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>283.3287830094401</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C51" t="n">
-        <v>283.9570776694276</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D51" t="n">
-        <v>277.8337308175164</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E51" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F51" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C52" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D52" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E52" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F52" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C53" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D53" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E53" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F53" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>277.4049325131135</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C54" t="n">
-        <v>279.2698514894354</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D54" t="n">
-        <v>276.16830825817</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E54" t="n">
-        <v>276.4275817871094</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F54" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342340640522</v>
       </c>
       <c r="C55" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310007112651</v>
       </c>
       <c r="D55" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0666927429874</v>
       </c>
       <c r="E55" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752380371094</v>
       </c>
       <c r="F55" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>278.342371275548</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C56" t="n">
-        <v>278.8310314000742</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D56" t="n">
-        <v>273.0667227973629</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E56" t="n">
-        <v>277.2752685546875</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F56" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>277.1455933469186</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C57" t="n">
-        <v>278.4620173164318</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D57" t="n">
-        <v>276.068538557602</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E57" t="n">
-        <v>277.5245666503906</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F57" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C58" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D58" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E58" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F58" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634896625032</v>
       </c>
       <c r="C59" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103618778425</v>
       </c>
       <c r="D59" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026424636208</v>
       </c>
       <c r="E59" t="n">
-        <v>273.8645324707031</v>
+        <v>271.1020812988281</v>
       </c>
       <c r="F59" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672390402853</v>
       </c>
       <c r="C60" t="n">
-        <v>275.4103308752873</v>
+        <v>272.8872042261758</v>
       </c>
       <c r="D60" t="n">
-        <v>270.9026119684932</v>
+        <v>266.2253451719176</v>
       </c>
       <c r="E60" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511108398438</v>
       </c>
       <c r="F60" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>272.8672697170699</v>
+        <v>271.4112610007817</v>
       </c>
       <c r="C61" t="n">
-        <v>272.887234905205</v>
+        <v>273.854622814086</v>
       </c>
       <c r="D61" t="n">
-        <v>266.225375101995</v>
+        <v>269.1673684747946</v>
       </c>
       <c r="E61" t="n">
-        <v>271.4511413574219</v>
+        <v>272.9271545410156</v>
       </c>
       <c r="F61" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C62" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D62" t="n">
-        <v>269.1673383776201</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E62" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F62" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C63" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D63" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E63" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F63" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C64" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D64" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E64" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F64" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C65" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D65" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E65" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F65" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>273.4158142002898</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C66" t="n">
-        <v>274.6225212124231</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D66" t="n">
-        <v>272.1193247047194</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E66" t="n">
-        <v>272.6578674316406</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F66" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C67" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D67" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E67" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F67" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C68" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D68" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E68" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F68" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C69" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D69" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E69" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F69" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>271.5209599020358</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C70" t="n">
-        <v>277.0857995993762</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D70" t="n">
-        <v>268.2697994337228</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E70" t="n">
-        <v>270.2743530273438</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F70" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>269.9053759278346</v>
+        <v>266.2751846804448</v>
       </c>
       <c r="C71" t="n">
-        <v>270.7730094869922</v>
+        <v>266.8236794412865</v>
       </c>
       <c r="D71" t="n">
-        <v>265.417590951718</v>
+        <v>261.4084273717842</v>
       </c>
       <c r="E71" t="n">
-        <v>266.5345458984375</v>
+        <v>261.6477661132812</v>
       </c>
       <c r="F71" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>266.2752467950493</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C72" t="n">
-        <v>266.8237416838396</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D72" t="n">
-        <v>261.4084883511094</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E72" t="n">
-        <v>261.6478271484375</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F72" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>262.485556491205</v>
+        <v>256.3223167721599</v>
       </c>
       <c r="C73" t="n">
-        <v>262.9642340542807</v>
+        <v>258.5861744106298</v>
       </c>
       <c r="D73" t="n">
-        <v>259.1047440282917</v>
+        <v>255.005907781442</v>
       </c>
       <c r="E73" t="n">
-        <v>259.6233215332031</v>
+        <v>258.3368530273438</v>
       </c>
       <c r="F73" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>256.3222864925608</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C74" t="n">
-        <v>258.586143863599</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D74" t="n">
-        <v>255.0058776573516</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E74" t="n">
-        <v>258.3368225097656</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F74" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C75" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D75" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E75" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F75" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C76" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D76" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E76" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F76" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>258.017707787092</v>
+        <v>258.7856080874888</v>
       </c>
       <c r="C77" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1093003767552</v>
       </c>
       <c r="D77" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131555781144</v>
       </c>
       <c r="E77" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543334960938</v>
       </c>
       <c r="F77" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>258.7855776250856</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C78" t="n">
-        <v>261.1092696408236</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D78" t="n">
-        <v>256.0131254420647</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E78" t="n">
-        <v>259.2543029785156</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F78" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>259.9424734235133</v>
+        <v>257.1999265314624</v>
       </c>
       <c r="C79" t="n">
-        <v>260.3314293980394</v>
+        <v>258.1972120398704</v>
       </c>
       <c r="D79" t="n">
-        <v>256.352239344094</v>
+        <v>254.2379873541013</v>
       </c>
       <c r="E79" t="n">
-        <v>257.5090942382812</v>
+        <v>254.8363647460938</v>
       </c>
       <c r="F79" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>257.1998957308392</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C80" t="n">
-        <v>258.1971811198186</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D80" t="n">
-        <v>254.237956908181</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E80" t="n">
-        <v>254.8363342285156</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F80" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0249055239374</v>
       </c>
       <c r="C81" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771427168815</v>
       </c>
       <c r="D81" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144562363057</v>
       </c>
       <c r="E81" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777526855469</v>
       </c>
       <c r="F81" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>248.0248902004531</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C82" t="n">
-        <v>250.8771272171802</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D82" t="n">
-        <v>244.5144411297041</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E82" t="n">
-        <v>246.9777374267578</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F82" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486524137701</v>
       </c>
       <c r="C83" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329754164565</v>
       </c>
       <c r="D83" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0158041358057</v>
       </c>
       <c r="E83" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666839599609</v>
       </c>
       <c r="F83" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>246.6486371992728</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C84" t="n">
-        <v>248.7329600733879</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D84" t="n">
-        <v>244.0157890837153</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E84" t="n">
-        <v>247.3666687011719</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F84" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>250.7973501838168</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C85" t="n">
-        <v>255.8635622873743</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D85" t="n">
-        <v>249.121917868832</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E85" t="n">
-        <v>254.7166900634766</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F85" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>258.4664899667647</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C86" t="n">
-        <v>261.2389423700868</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D86" t="n">
-        <v>257.5090739976807</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E86" t="n">
-        <v>257.5689086914062</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F86" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996187429542</v>
       </c>
       <c r="C87" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451334735496</v>
       </c>
       <c r="D87" t="n">
-        <v>253.8191124091609</v>
+        <v>253.719368010288</v>
       </c>
       <c r="E87" t="n">
-        <v>255.7438812255859</v>
+        <v>257.578857421875</v>
       </c>
       <c r="F87" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C88" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D88" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E88" t="n">
-        <v>257.5788879394531</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F88" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>254.4773517832236</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C89" t="n">
-        <v>261.1890792690021</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D89" t="n">
-        <v>251.4954625126288</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E89" t="n">
-        <v>258.7756652832031</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F89" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>259.3241194003358</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C90" t="n">
-        <v>269.7557160843994</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D90" t="n">
-        <v>258.5063380741307</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E90" t="n">
-        <v>269.2770385742188</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F90" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="C91" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927850076088</v>
       </c>
       <c r="D91" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="E91" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394409179688</v>
       </c>
       <c r="F91" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>271.5508302866565</v>
+        <v>277.3749854862336</v>
       </c>
       <c r="C92" t="n">
-        <v>278.1927542185059</v>
+        <v>278.7412615768201</v>
       </c>
       <c r="D92" t="n">
-        <v>271.5508302866565</v>
+        <v>272.4882932485779</v>
       </c>
       <c r="E92" t="n">
-        <v>275.7394104003906</v>
+        <v>275.1610107421875</v>
       </c>
       <c r="F92" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>277.3750162493594</v>
+        <v>276.3677657232236</v>
       </c>
       <c r="C93" t="n">
-        <v>278.7412924914769</v>
+        <v>280.1474864654567</v>
       </c>
       <c r="D93" t="n">
-        <v>272.48832346973</v>
+        <v>276.1782790346459</v>
       </c>
       <c r="E93" t="n">
-        <v>275.1610412597656</v>
+        <v>277.3650512695312</v>
       </c>
       <c r="F93" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,25 +2861,25 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>276.3677049075235</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C94" t="n">
-        <v>280.1474248180158</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D94" t="n">
-        <v>276.1782182606431</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E94" t="n">
-        <v>277.364990234375</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F94" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -2887,25 +2887,25 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C95" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D95" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E95" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F95" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G95" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C96" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D96" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E96" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F96" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990585104662</v>
       </c>
       <c r="C97" t="n">
-        <v>279.6808719096702</v>
+        <v>275.2288318017276</v>
       </c>
       <c r="D97" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165063299744</v>
       </c>
       <c r="E97" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637634277344</v>
       </c>
       <c r="F97" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>275.0990906441111</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C98" t="n">
-        <v>275.228863950531</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D98" t="n">
-        <v>259.7165366668213</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E98" t="n">
-        <v>261.2637939453125</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F98" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C99" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D99" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E99" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F99" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C100" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D100" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E100" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F100" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C101" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D101" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E101" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F101" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C102" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D102" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E102" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F102" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C103" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D103" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E103" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F103" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C104" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D104" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E104" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F104" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C105" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D105" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E105" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F105" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C106" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D106" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E106" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F106" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="C107" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="D107" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217314181026</v>
       </c>
       <c r="E107" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7094116210938</v>
       </c>
       <c r="F107" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>272.3240124520744</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C108" t="n">
-        <v>272.3240124520744</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D108" t="n">
-        <v>262.4217010495403</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E108" t="n">
-        <v>263.7093811035156</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F108" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C109" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D109" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E109" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F109" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C110" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D110" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E110" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F110" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C111" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D111" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E111" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F111" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C112" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D112" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E112" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F112" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C113" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D113" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E113" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F113" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C114" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D114" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E114" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F114" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>257.1910284571696</v>
+        <v>260.624897946549</v>
       </c>
       <c r="C115" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630538494394</v>
       </c>
       <c r="D115" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876327296249</v>
       </c>
       <c r="E115" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453979492188</v>
       </c>
       <c r="F115" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>260.6248673962081</v>
+        <v>258.1992408199258</v>
       </c>
       <c r="C116" t="n">
-        <v>261.6630231774062</v>
+        <v>258.4887327594216</v>
       </c>
       <c r="D116" t="n">
-        <v>259.0876023594815</v>
+        <v>253.7272102811576</v>
       </c>
       <c r="E116" t="n">
-        <v>260.3453674316406</v>
+        <v>255.3043975830078</v>
       </c>
       <c r="F116" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>258.1992253881205</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C117" t="n">
-        <v>258.4887173103141</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D117" t="n">
-        <v>253.7271951166323</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E117" t="n">
-        <v>255.3043823242188</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F117" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C118" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D118" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E118" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F118" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C119" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D119" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E119" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F119" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C120" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D120" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E120" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F120" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C121" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D121" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E121" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F121" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C122" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D122" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E122" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F122" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C123" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D123" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E123" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F123" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C124" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D124" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E124" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F124" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C125" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D125" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E125" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F125" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C126" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D126" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E126" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F126" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C127" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D127" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E127" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F127" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C128" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D128" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E128" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F128" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683905467953</v>
       </c>
       <c r="C129" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248978486836</v>
       </c>
       <c r="D129" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598358728773</v>
       </c>
       <c r="E129" t="n">
-        <v>246.1906585693359</v>
+        <v>253.3379058837891</v>
       </c>
       <c r="F129" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>247.4683756415328</v>
+        <v>253.6273948962928</v>
       </c>
       <c r="C130" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7236449097363</v>
       </c>
       <c r="D130" t="n">
-        <v>246.6598210163149</v>
+        <v>252.8787309132899</v>
       </c>
       <c r="E130" t="n">
-        <v>253.337890625</v>
+        <v>255.1746368408203</v>
       </c>
       <c r="F130" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>253.6273797300248</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C131" t="n">
-        <v>255.7236296181179</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D131" t="n">
-        <v>252.8787157917901</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E131" t="n">
-        <v>255.1746215820312</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F131" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>253.7471740568136</v>
+        <v>256.0530752925303</v>
       </c>
       <c r="C132" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6930045642991</v>
       </c>
       <c r="D132" t="n">
-        <v>250.2034948550391</v>
+        <v>256.0031460821725</v>
       </c>
       <c r="E132" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988647460938</v>
       </c>
       <c r="F132" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>256.053045051996</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C133" t="n">
-        <v>261.6929736576745</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D133" t="n">
-        <v>256.003115847535</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E133" t="n">
-        <v>258.3988342285156</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F133" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896321241455</v>
       </c>
       <c r="C134" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2873042333858</v>
       </c>
       <c r="D134" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730388391825</v>
       </c>
       <c r="E134" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4388122558594</v>
       </c>
       <c r="F134" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>257.9896016596085</v>
+        <v>258.5386343954405</v>
       </c>
       <c r="C135" t="n">
-        <v>259.2872736156141</v>
+        <v>260.6548530924392</v>
       </c>
       <c r="D135" t="n">
-        <v>256.0730086009651</v>
+        <v>255.6138610163474</v>
       </c>
       <c r="E135" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0259704589844</v>
       </c>
       <c r="F135" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>258.5386040524215</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C136" t="n">
-        <v>260.6548225010532</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D136" t="n">
-        <v>255.6138310165902</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E136" t="n">
-        <v>260.0259399414062</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F136" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C137" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D137" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E137" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F137" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881922504944</v>
       </c>
       <c r="C138" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4634109961452</v>
       </c>
       <c r="D138" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318642110386</v>
       </c>
       <c r="E138" t="n">
-        <v>258.73828125</v>
+        <v>258.3689270019531</v>
       </c>
       <c r="F138" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>258.7881616833942</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C139" t="n">
-        <v>261.4633801130582</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D139" t="n">
-        <v>256.7318338868242</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E139" t="n">
-        <v>258.368896484375</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F139" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3247234477873</v>
       </c>
       <c r="C140" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840980024072</v>
       </c>
       <c r="D140" t="n">
-        <v>257.3507435512608</v>
+        <v>260.8045755356903</v>
       </c>
       <c r="E140" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307861328125</v>
       </c>
       <c r="F140" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>266.3246925362851</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C141" t="n">
-        <v>266.6840670491935</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D141" t="n">
-        <v>260.804545264895</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E141" t="n">
-        <v>262.9307556152344</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F141" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C142" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D142" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E142" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F142" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C143" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D143" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E143" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F143" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C144" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D144" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E144" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F144" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C145" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D145" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E145" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F145" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C146" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D146" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E146" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F146" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C147" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D147" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E147" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F147" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C148" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D148" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E148" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F148" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C149" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D149" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E149" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F149" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C150" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D150" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E150" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F150" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632420760759</v>
       </c>
       <c r="C151" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083659496485</v>
       </c>
       <c r="D151" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8741246788477</v>
       </c>
       <c r="E151" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409912109375</v>
       </c>
       <c r="F151" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>278.3632116979401</v>
+        <v>279.1617980116577</v>
       </c>
       <c r="C152" t="n">
-        <v>286.7083346607987</v>
+        <v>280.1300712051751</v>
       </c>
       <c r="D152" t="n">
-        <v>277.8740943540899</v>
+        <v>274.3703307853319</v>
       </c>
       <c r="E152" t="n">
-        <v>279.6409606933594</v>
+        <v>276.3368225097656</v>
       </c>
       <c r="F152" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>279.1618288412153</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C153" t="n">
-        <v>280.130102141665</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D153" t="n">
-        <v>274.3703610857382</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E153" t="n">
-        <v>276.3368530273438</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F153" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>276.43668191704</v>
+        <v>281.4178249779708</v>
       </c>
       <c r="C154" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5169265187869</v>
       </c>
       <c r="D154" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693330033821</v>
       </c>
       <c r="E154" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978637695312</v>
       </c>
       <c r="F154" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>281.4177950537395</v>
+        <v>288.7547052879293</v>
       </c>
       <c r="C155" t="n">
-        <v>287.5168959460148</v>
+        <v>291.6096265406606</v>
       </c>
       <c r="D155" t="n">
-        <v>280.5693031693742</v>
+        <v>285.2709318587503</v>
       </c>
       <c r="E155" t="n">
-        <v>286.9978332519531</v>
+        <v>286.927978515625</v>
       </c>
       <c r="F155" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>288.7546745760609</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C156" t="n">
-        <v>291.6095955251437</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D156" t="n">
-        <v>285.2709015174152</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E156" t="n">
-        <v>286.9279479980469</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F156" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,25 +4499,25 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C157" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D157" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E157" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F157" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4525,25 +4525,25 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C158" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D158" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E158" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F158" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G158" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C159" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D159" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E159" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F159" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C160" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D160" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E160" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F160" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C161" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D161" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E161" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F161" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C162" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D162" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E162" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F162" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C163" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D163" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E163" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F163" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C164" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D164" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E164" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F164" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C165" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D165" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E165" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F165" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C166" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D166" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E166" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F166" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C167" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D167" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E167" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F167" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C168" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D168" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E168" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F168" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C169" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D169" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E169" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F169" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C170" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D170" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E170" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F170" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C171" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D171" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E171" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F171" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C172" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D172" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E172" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F172" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C173" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D173" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E173" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F173" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C174" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D174" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E174" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F174" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C175" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D175" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E175" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F175" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C176" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D176" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E176" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F176" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C177" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D177" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E177" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F177" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C178" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D178" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E178" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F178" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C179" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D179" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E179" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F179" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C180" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D180" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E180" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F180" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C181" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D181" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E181" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F181" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C182" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D182" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E182" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F182" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C183" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D183" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E183" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F183" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C184" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D184" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E184" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F184" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C185" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D185" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E185" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F185" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C186" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D186" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E186" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F186" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C187" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D187" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E187" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F187" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C188" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D188" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E188" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F188" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C189" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D189" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E189" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F189" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C190" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D190" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E190" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F190" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C191" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D191" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E191" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F191" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C192" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D192" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E192" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F192" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C193" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D193" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E193" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F193" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C194" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D194" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E194" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F194" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C195" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D195" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E195" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F195" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C196" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D196" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E196" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F196" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C197" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D197" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E197" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F197" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C198" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D198" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E198" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F198" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C199" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D199" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E199" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F199" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C200" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D200" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E200" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F200" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C201" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D201" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E201" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F201" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C202" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D202" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E202" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F202" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C203" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D203" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E203" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F203" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C204" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D204" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E204" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F204" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C205" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D205" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E205" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F205" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C206" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D206" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E206" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F206" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C207" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D207" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E207" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F207" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C208" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D208" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E208" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F208" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C209" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D209" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E209" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F209" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C210" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D210" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E210" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F210" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C211" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D211" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E211" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F211" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C212" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D212" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E212" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F212" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C213" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D213" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E213" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F213" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C214" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D214" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E214" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F214" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C215" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D215" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E215" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F215" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C216" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D216" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E216" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F216" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C217" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D217" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E217" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F217" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C218" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D218" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E218" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F218" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,25 +6111,25 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C219" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D219" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E219" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F219" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6137,25 +6137,25 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C220" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D220" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E220" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F220" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G220" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C221" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D221" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E221" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F221" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C222" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D222" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E222" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F222" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C223" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D223" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E223" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F223" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C224" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D224" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E224" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F224" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C225" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D225" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E225" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F225" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C226" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D226" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E226" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F226" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C227" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D227" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E227" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F227" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C228" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D228" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E228" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F228" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C229" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D229" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E229" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F229" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C230" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D230" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E230" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F230" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C231" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D231" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E231" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F231" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C232" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D232" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E232" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F232" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C233" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D233" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E233" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C234" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D234" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E234" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C234" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D234" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E234" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F234" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C235" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E235" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F235" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C236" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D236" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E236" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F236" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C237" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D237" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E237" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F237" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C238" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D238" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E238" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F238" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D239" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E239" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F239" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C240" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D240" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E240" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F240" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C241" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D241" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E241" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F241" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C242" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D242" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F242" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C243" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D243" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E243" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F243" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D244" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E244" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E244" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F244" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D245" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E245" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F245" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C246" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D246" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E246" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F246" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C247" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F247" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C248" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D248" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F248" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D249" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E249" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F249" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C250" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E250" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F250" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D251" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F251" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B252" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C252" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D252" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F252" t="n">
-        <v>24686400</v>
+        <v>29950100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,37 +10498,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>341.07</v>
+      </c>
+      <c r="D2" t="n">
         <v>335.92</v>
       </c>
-      <c r="D2" t="n">
-        <v>337.02</v>
-      </c>
       <c r="E2" t="n">
-        <v>336.32</v>
+        <v>336.04</v>
       </c>
       <c r="F2" t="n">
-        <v>338.91</v>
+        <v>341.67</v>
       </c>
       <c r="G2" t="n">
-        <v>334.3</v>
+        <v>334.53</v>
       </c>
       <c r="H2" t="n">
-        <v>24364559</v>
+        <v>29649787</v>
       </c>
       <c r="I2" t="n">
-        <v>52775646</v>
+        <v>51468863</v>
       </c>
       <c r="J2" t="n">
-        <v>4902477103104</v>
+        <v>4977636933632</v>
       </c>
       <c r="K2" t="n">
-        <v>38.611496</v>
+        <v>39.068733</v>
       </c>
       <c r="L2" t="n">
-        <v>35.033268</v>
+        <v>35.582424</v>
       </c>
       <c r="M2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="N2" t="n">
         <v>345.34</v>
@@ -10564,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.641304</v>
+        <v>46.341034</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4924421701632</v>
+        <v>4999582056448</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:28:51</t>
+          <t>2026-09-26 14:49:23</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>253.1648106749593</v>
+        <v>253.6231177228549</v>
       </c>
       <c r="C2" t="n">
-        <v>256.6519291955366</v>
+        <v>254.0615007840798</v>
       </c>
       <c r="D2" t="n">
-        <v>252.8459811129583</v>
+        <v>252.0788192854059</v>
       </c>
       <c r="E2" t="n">
-        <v>254.5198059082031</v>
+        <v>253.4935913085938</v>
       </c>
       <c r="F2" t="n">
-        <v>46076300</v>
+        <v>40127700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>253.6231329894407</v>
+        <v>253.9220203508673</v>
       </c>
       <c r="C3" t="n">
-        <v>254.0615160770535</v>
+        <v>254.9781167214257</v>
       </c>
       <c r="D3" t="n">
-        <v>252.0788344590342</v>
+        <v>252.1784610063259</v>
       </c>
       <c r="E3" t="n">
-        <v>253.4936065673828</v>
+        <v>253.69287109375</v>
       </c>
       <c r="F3" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C4" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D4" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E4" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F4" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C5" t="n">
-        <v>257.8375609779932</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D5" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E5" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F5" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>255.6356912331815</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C6" t="n">
-        <v>257.2298088092003</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D6" t="n">
-        <v>253.2146416974651</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E6" t="n">
-        <v>256.1836853027344</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F6" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0405037108186</v>
       </c>
       <c r="C7" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165459888059</v>
       </c>
       <c r="D7" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113366309766</v>
       </c>
       <c r="E7" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7453002929688</v>
       </c>
       <c r="F7" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>257.0404883747525</v>
+        <v>255.8648286012466</v>
       </c>
       <c r="C8" t="n">
-        <v>258.1165305885388</v>
+        <v>256.452653504112</v>
       </c>
       <c r="D8" t="n">
-        <v>254.1113214696764</v>
+        <v>254.48990271765</v>
       </c>
       <c r="E8" t="n">
-        <v>255.7452850341797</v>
+        <v>255.5360565185547</v>
       </c>
       <c r="F8" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>255.8648438796676</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C9" t="n">
-        <v>256.4526688176338</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D9" t="n">
-        <v>254.4899179139702</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E9" t="n">
-        <v>255.5360717773438</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F9" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>255.5759191543519</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C10" t="n">
-        <v>257.5685585594684</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D10" t="n">
-        <v>255.1674244276712</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E10" t="n">
-        <v>257.1102600097656</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F10" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>256.8611554198282</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C11" t="n">
-        <v>257.0504585775582</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D11" t="n">
-        <v>252.2083446799687</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E11" t="n">
-        <v>253.1050262451172</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F11" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C12" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D12" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E12" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F12" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C13" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D13" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E13" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F13" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>245.6924316138584</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C14" t="n">
-        <v>247.9341508249242</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D14" t="n">
-        <v>243.7994151584908</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E14" t="n">
-        <v>246.8581237792969</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F14" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>248.571774561702</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C15" t="n">
-        <v>250.8932009800968</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D15" t="n">
-        <v>246.5592047770515</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E15" t="n">
-        <v>248.4223175048828</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F15" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>247.3363348246392</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C16" t="n">
-        <v>248.1234206007849</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D16" t="n">
-        <v>244.2278226113223</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E16" t="n">
-        <v>246.5392761230469</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F16" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>247.1072067041429</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C17" t="n">
-        <v>252.4474806979352</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D17" t="n">
-        <v>246.3599669580113</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E17" t="n">
-        <v>251.3614807128906</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F17" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C18" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D18" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E18" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F18" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>260.9161783410852</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C19" t="n">
-        <v>264.3136317818121</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D19" t="n">
-        <v>260.8663441185724</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E19" t="n">
-        <v>261.8028869628906</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F19" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>261.6833338430701</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C20" t="n">
-        <v>261.882609922878</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D20" t="n">
-        <v>254.4899051977633</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E20" t="n">
-        <v>257.4988098144531</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F20" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>258.9832941033833</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C21" t="n">
-        <v>259.6607840683213</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D21" t="n">
-        <v>257.0604047594014</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E21" t="n">
-        <v>258.6246032714844</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F21" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C22" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D22" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E22" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F22" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>263.9051498417878</v>
+        <v>268.0000063221084</v>
       </c>
       <c r="C23" t="n">
-        <v>268.1295353654346</v>
+        <v>268.8967183092298</v>
       </c>
       <c r="D23" t="n">
-        <v>263.6759853797928</v>
+        <v>267.1631014853557</v>
       </c>
       <c r="E23" t="n">
-        <v>267.8206787109375</v>
+        <v>268.0099792480469</v>
       </c>
       <c r="F23" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>267.9999758056659</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C24" t="n">
-        <v>268.896687690681</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D24" t="n">
-        <v>267.1630710642092</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E24" t="n">
-        <v>268.0099487304688</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F24" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>268.2889603375268</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C25" t="n">
-        <v>270.4111261059246</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D25" t="n">
-        <v>266.126933268734</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E25" t="n">
-        <v>268.7074279785156</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F25" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>270.9889785237465</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C26" t="n">
-        <v>273.131090148023</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D26" t="n">
-        <v>267.4919171420091</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E26" t="n">
-        <v>270.4011535644531</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F26" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>275.9705701844509</v>
+        <v>269.424736694289</v>
       </c>
       <c r="C27" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531467885877</v>
       </c>
       <c r="D27" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2700709373508</v>
       </c>
       <c r="E27" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597534179688</v>
       </c>
       <c r="F27" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>269.4247673672652</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C28" t="n">
-        <v>269.8531775103368</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D28" t="n">
-        <v>265.2701011373342</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E28" t="n">
-        <v>268.0597839355469</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F28" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C29" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D29" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E29" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F29" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C30" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D30" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E30" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F30" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C31" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D31" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E31" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F31" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,25 +1249,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298830249396</v>
       </c>
       <c r="C32" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869540449525</v>
       </c>
       <c r="D32" t="n">
-        <v>265.7881780523408</v>
+        <v>266.7339548671466</v>
       </c>
       <c r="E32" t="n">
-        <v>267.48193359375</v>
+        <v>268.6986083984375</v>
       </c>
       <c r="F32" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1275,25 +1275,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>268.2298525605972</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C33" t="n">
-        <v>272.9869230403233</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D33" t="n">
-        <v>266.733924572705</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E33" t="n">
-        <v>268.6985778808594</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F33" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G33" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C34" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D34" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E34" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F34" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C35" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D35" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E35" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F35" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3141778275755</v>
       </c>
       <c r="C36" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108524736826</v>
       </c>
       <c r="D36" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681323529343</v>
       </c>
       <c r="E36" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705017089844</v>
       </c>
       <c r="F36" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C37" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D37" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E37" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F37" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>268.0903024129557</v>
+        <v>269.2570854665072</v>
       </c>
       <c r="C38" t="n">
-        <v>269.7557521979796</v>
+        <v>269.9751321987233</v>
       </c>
       <c r="D38" t="n">
-        <v>265.0086937896775</v>
+        <v>264.5997795179588</v>
       </c>
       <c r="E38" t="n">
-        <v>266.7339782714844</v>
+        <v>266.7140197753906</v>
       </c>
       <c r="F38" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>269.25705465795</v>
+        <v>264.8091896065648</v>
       </c>
       <c r="C39" t="n">
-        <v>269.9751013080067</v>
+        <v>271.4710487380511</v>
       </c>
       <c r="D39" t="n">
-        <v>264.5997492422933</v>
+        <v>264.7792722621166</v>
       </c>
       <c r="E39" t="n">
-        <v>266.7139892578125</v>
+        <v>267.8309631347656</v>
       </c>
       <c r="F39" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>264.8092197798317</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C40" t="n">
-        <v>271.4710796703931</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D40" t="n">
-        <v>264.7793024319747</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E40" t="n">
-        <v>267.8309936523438</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F40" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C41" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D41" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E41" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F41" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>265.2280517805383</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="C42" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480447880167</v>
       </c>
       <c r="D42" t="n">
-        <v>264.9488130991126</v>
+        <v>270.1645980035721</v>
       </c>
       <c r="E42" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1709899902344</v>
       </c>
       <c r="F42" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227726174851</v>
       </c>
       <c r="C43" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6189174225992</v>
       </c>
       <c r="D43" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028378637012</v>
       </c>
       <c r="E43" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181701660156</v>
       </c>
       <c r="F43" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C44" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D44" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E44" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F44" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C45" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D45" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E45" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F45" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>276.5073679150082</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C46" t="n">
-        <v>278.242634823177</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D46" t="n">
-        <v>275.2407959413455</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E46" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F46" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>277.255303275414</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C47" t="n">
-        <v>282.650620542313</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D47" t="n">
-        <v>275.390384584981</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E47" t="n">
-        <v>282.3314819335938</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F47" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C48" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D48" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E48" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F48" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>285.4231155973949</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C49" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D49" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E49" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F49" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>283.328813896664</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C50" t="n">
-        <v>283.9571086251454</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D50" t="n">
-        <v>277.8337611056945</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E50" t="n">
-        <v>279.9380493164062</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F50" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C51" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D51" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E51" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F51" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C52" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D52" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E52" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F52" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C53" t="n">
-        <v>279.269820658071</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D53" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E53" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F53" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C54" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D54" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E54" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F54" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>278.342340640522</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C55" t="n">
-        <v>278.8310007112651</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D55" t="n">
-        <v>273.0666927429874</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E55" t="n">
-        <v>277.2752380371094</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F55" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C56" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D56" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E56" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F56" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C57" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D57" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E57" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F57" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C58" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D58" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E58" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F58" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>274.2634896625032</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C59" t="n">
-        <v>275.4103618778425</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D59" t="n">
-        <v>270.9026424636208</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E59" t="n">
-        <v>271.1020812988281</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F59" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>272.8672390402853</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C60" t="n">
-        <v>272.8872042261758</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D60" t="n">
-        <v>266.2253451719176</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E60" t="n">
-        <v>271.4511108398438</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F60" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>271.4112610007817</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C61" t="n">
-        <v>273.854622814086</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D61" t="n">
-        <v>269.1673684747946</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E61" t="n">
-        <v>272.9271545410156</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F61" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C62" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D62" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E62" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F62" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C63" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D63" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E63" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F63" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C64" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D64" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E64" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F64" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C65" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D65" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E65" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F65" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694584675055</v>
       </c>
       <c r="C66" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3360001129787</v>
       </c>
       <c r="D66" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408983628093</v>
       </c>
       <c r="E66" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3387145996094</v>
       </c>
       <c r="F66" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C67" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D67" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E67" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F67" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209292436991</v>
       </c>
       <c r="C68" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857683126949</v>
       </c>
       <c r="D68" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697691424855</v>
       </c>
       <c r="E68" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743225097656</v>
       </c>
       <c r="F68" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>271.5209599020358</v>
+        <v>269.9053450243044</v>
       </c>
       <c r="C69" t="n">
-        <v>277.0857995993762</v>
+        <v>270.7729784841199</v>
       </c>
       <c r="D69" t="n">
-        <v>268.2697994337228</v>
+        <v>265.4175605620285</v>
       </c>
       <c r="E69" t="n">
-        <v>270.2743530273438</v>
+        <v>266.5345153808594</v>
       </c>
       <c r="F69" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>269.9053759278346</v>
+        <v>266.275215737747</v>
       </c>
       <c r="C70" t="n">
-        <v>270.7730094869922</v>
+        <v>266.8237105625631</v>
       </c>
       <c r="D70" t="n">
-        <v>265.417590951718</v>
+        <v>261.4084578614468</v>
       </c>
       <c r="E70" t="n">
-        <v>266.5345458984375</v>
+        <v>261.6477966308594</v>
       </c>
       <c r="F70" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>266.2751846804448</v>
+        <v>262.4855256371837</v>
       </c>
       <c r="C71" t="n">
-        <v>266.8236794412865</v>
+        <v>262.964203143993</v>
       </c>
       <c r="D71" t="n">
-        <v>261.4084273717842</v>
+        <v>259.1047135716701</v>
       </c>
       <c r="E71" t="n">
-        <v>261.6477661132812</v>
+        <v>259.623291015625</v>
       </c>
       <c r="F71" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>262.485556491205</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C72" t="n">
-        <v>262.9642340542807</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D72" t="n">
-        <v>259.1047440282917</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E72" t="n">
-        <v>259.6233215332031</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F72" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>256.3223167721599</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C73" t="n">
-        <v>258.5861744106298</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D73" t="n">
-        <v>255.005907781442</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E73" t="n">
-        <v>258.3368530273438</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F73" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4565110528425</v>
       </c>
       <c r="C74" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906861738287</v>
       </c>
       <c r="D74" t="n">
-        <v>255.524480970152</v>
+        <v>256.1029014720883</v>
       </c>
       <c r="E74" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435485839844</v>
       </c>
       <c r="F74" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C75" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D75" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E75" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F75" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>258.017707787092</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C76" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D76" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E76" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F76" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>258.7856080874888</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C77" t="n">
-        <v>261.1093003767552</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D77" t="n">
-        <v>256.0131555781144</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E77" t="n">
-        <v>259.2543334960938</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F77" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1999111311508</v>
       </c>
       <c r="C78" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1971965798445</v>
       </c>
       <c r="D78" t="n">
-        <v>256.3522089636155</v>
+        <v>254.2379721311412</v>
       </c>
       <c r="E78" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363494873047</v>
       </c>
       <c r="F78" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>257.1999265314624</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C79" t="n">
-        <v>258.1972120398704</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D79" t="n">
-        <v>254.2379873541013</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E79" t="n">
-        <v>254.8363647460938</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F79" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C80" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D80" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E80" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F80" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>248.0249055239374</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C81" t="n">
-        <v>250.8771427168815</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D81" t="n">
-        <v>244.5144562363057</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E81" t="n">
-        <v>246.9777526855469</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F81" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C82" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D82" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E82" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F82" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>246.6486524137701</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C83" t="n">
-        <v>248.7329754164565</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D83" t="n">
-        <v>244.0158041358057</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E83" t="n">
-        <v>247.3666839599609</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F83" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664593428383</v>
       </c>
       <c r="C84" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389114176715</v>
       </c>
       <c r="D84" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090434871919</v>
       </c>
       <c r="E84" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5688781738281</v>
       </c>
       <c r="F84" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>258.4664899667647</v>
+        <v>256.9506034196754</v>
       </c>
       <c r="C85" t="n">
-        <v>261.2389423700868</v>
+        <v>258.1573103549757</v>
       </c>
       <c r="D85" t="n">
-        <v>257.5090739976807</v>
+        <v>253.8191275531099</v>
       </c>
       <c r="E85" t="n">
-        <v>257.5689086914062</v>
+        <v>255.743896484375</v>
       </c>
       <c r="F85" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C86" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D86" t="n">
-        <v>253.8191124091609</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E86" t="n">
-        <v>255.7438812255859</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F86" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>257.2996187429542</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C87" t="n">
-        <v>258.9451334735496</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D87" t="n">
-        <v>253.719368010288</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E87" t="n">
-        <v>257.578857421875</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F87" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C88" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D88" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E88" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F88" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C89" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D89" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E89" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F89" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C90" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D90" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E90" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F90" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>271.5508603406617</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C91" t="n">
-        <v>278.1927850076088</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D91" t="n">
-        <v>271.5508603406617</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E91" t="n">
-        <v>275.7394409179688</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F91" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>277.3749854862336</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C92" t="n">
-        <v>278.7412615768201</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D92" t="n">
-        <v>272.4882932485779</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E92" t="n">
-        <v>275.1610107421875</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F92" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,25 +2835,25 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>276.3677657232236</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C93" t="n">
-        <v>280.1474864654567</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D93" t="n">
-        <v>276.1782790346459</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E93" t="n">
-        <v>277.3650512695312</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F93" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -2861,25 +2861,25 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C94" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D94" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E94" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F94" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G94" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C95" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D95" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E95" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F95" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C96" t="n">
-        <v>279.6808719096702</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D96" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E96" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F96" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>275.0990585104662</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C97" t="n">
-        <v>275.2288318017276</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D97" t="n">
-        <v>259.7165063299744</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E97" t="n">
-        <v>261.2637634277344</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F97" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C98" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D98" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E98" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F98" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C99" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D99" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E99" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F99" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C100" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D100" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E100" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F100" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C101" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D101" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E101" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F101" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C102" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D102" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E102" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F102" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C103" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D103" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E103" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F103" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C104" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D104" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E104" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F104" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C105" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D105" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E105" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F105" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C106" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D106" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E106" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F106" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>272.3240439665745</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C107" t="n">
-        <v>272.3240439665745</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D107" t="n">
-        <v>262.4217314181026</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E107" t="n">
-        <v>263.7094116210938</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F107" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C108" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D108" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E108" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F108" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C109" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D109" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E109" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F109" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C110" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D110" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E110" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F110" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C111" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D111" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E111" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F111" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C112" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D112" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E112" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F112" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C113" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D113" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E113" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F113" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>257.1910284571696</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C114" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D114" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E114" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F114" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>260.624897946549</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C115" t="n">
-        <v>261.6630538494394</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D115" t="n">
-        <v>259.0876327296249</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E115" t="n">
-        <v>260.3453979492188</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F115" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>258.1992408199258</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C116" t="n">
-        <v>258.4887327594216</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D116" t="n">
-        <v>253.7272102811576</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E116" t="n">
-        <v>255.3043975830078</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F116" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C117" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D117" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E117" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F117" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C118" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D118" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E118" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F118" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C119" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D119" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E119" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F119" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C120" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D120" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E120" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F120" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C121" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D121" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E121" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F121" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C122" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D122" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E122" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F122" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C123" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D123" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E123" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F123" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C124" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D124" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E124" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F124" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C125" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D125" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E125" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F125" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C126" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D126" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E126" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F126" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C127" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D127" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E127" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F127" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C128" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D128" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E128" t="n">
-        <v>246.1906585693359</v>
+        <v>253.337890625</v>
       </c>
       <c r="F128" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>247.4683905467953</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C129" t="n">
-        <v>255.0248978486836</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D129" t="n">
-        <v>246.6598358728773</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E129" t="n">
-        <v>253.3379058837891</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F129" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>253.6273948962928</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C130" t="n">
-        <v>255.7236449097363</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D130" t="n">
-        <v>252.8787309132899</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E130" t="n">
-        <v>255.1746368408203</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F130" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>253.7471740568136</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C131" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D131" t="n">
-        <v>250.2034948550391</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E131" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F131" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>256.0530752925303</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C132" t="n">
-        <v>261.6930045642991</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D132" t="n">
-        <v>256.0031460821725</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E132" t="n">
-        <v>258.3988647460938</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F132" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C133" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D133" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E133" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F133" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>257.9896321241455</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C134" t="n">
-        <v>259.2873042333858</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D134" t="n">
-        <v>256.0730388391825</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E134" t="n">
-        <v>258.4388122558594</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F134" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>258.5386343954405</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C135" t="n">
-        <v>260.6548530924392</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D135" t="n">
-        <v>255.6138610163474</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E135" t="n">
-        <v>260.0259704589844</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F135" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C136" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D136" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E136" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F136" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C137" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D137" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E137" t="n">
-        <v>258.73828125</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F137" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>258.7881922504944</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C138" t="n">
-        <v>261.4634109961452</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D138" t="n">
-        <v>256.7318642110386</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E138" t="n">
-        <v>258.3689270019531</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F138" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C139" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D139" t="n">
-        <v>257.3507435512608</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E139" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F139" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>266.3247234477873</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C140" t="n">
-        <v>266.6840980024072</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D140" t="n">
-        <v>260.8045755356903</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E140" t="n">
-        <v>262.9307861328125</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F140" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C141" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D141" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E141" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F141" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C142" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D142" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E142" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F142" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C143" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D143" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E143" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F143" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C144" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D144" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E144" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F144" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C145" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D145" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E145" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F145" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C146" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D146" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E146" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F146" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C147" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D147" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E147" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F147" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C148" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D148" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E148" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F148" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C149" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D149" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E149" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F149" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C150" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D150" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E150" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F150" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>278.3632420760759</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C151" t="n">
-        <v>286.7083659496485</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D151" t="n">
-        <v>277.8741246788477</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E151" t="n">
-        <v>279.6409912109375</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F151" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>279.1617980116577</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C152" t="n">
-        <v>280.1300712051751</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D152" t="n">
-        <v>274.3703307853319</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E152" t="n">
-        <v>276.3368225097656</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F152" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>276.43668191704</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C153" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D153" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E153" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F153" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>281.4178249779708</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C154" t="n">
-        <v>287.5169265187869</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D154" t="n">
-        <v>280.5693330033821</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E154" t="n">
-        <v>286.9978637695312</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F154" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>288.7547052879293</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C155" t="n">
-        <v>291.6096265406606</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D155" t="n">
-        <v>285.2709318587503</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E155" t="n">
-        <v>286.927978515625</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F155" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,25 +4473,25 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C156" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D156" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E156" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F156" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4499,25 +4499,25 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C157" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D157" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E157" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F157" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G157" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C158" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D158" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E158" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F158" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C159" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D159" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E159" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F159" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C160" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D160" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E160" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F160" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C161" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D161" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E161" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F161" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C162" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D162" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E162" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F162" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C163" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D163" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E163" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F163" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C164" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D164" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E164" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F164" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C165" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D165" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E165" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F165" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C166" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D166" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E166" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F166" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C167" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D167" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E167" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F167" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C168" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D168" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E168" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F168" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C169" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D169" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E169" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F169" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C170" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D170" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E170" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F170" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C171" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D171" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E171" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F171" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C172" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D172" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E172" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F172" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C173" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D173" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E173" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F173" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C174" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D174" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E174" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F174" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C175" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D175" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E175" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F175" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C176" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D176" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E176" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F176" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C177" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D177" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E177" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F177" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C178" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D178" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E178" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F178" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C179" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D179" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E179" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F179" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C180" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D180" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E180" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F180" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C181" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D181" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E181" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F181" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C182" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D182" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E182" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F182" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C183" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D183" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E183" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F183" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C184" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D184" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E184" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F184" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C185" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D185" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E185" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F185" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C186" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D186" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E186" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F186" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C187" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D187" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E187" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F187" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C188" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D188" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E188" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F188" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C189" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D189" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E189" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F189" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C190" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D190" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E190" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F190" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C191" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D191" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E191" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F191" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C192" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D192" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E192" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F192" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C193" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D193" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E193" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F193" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C194" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D194" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E194" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F194" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C195" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D195" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E195" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F195" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C196" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D196" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E196" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F196" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C197" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D197" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E197" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F197" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C198" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D198" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E198" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F198" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C199" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D199" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E199" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F199" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C200" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D200" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E200" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F200" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C201" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D201" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E201" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F201" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C202" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D202" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E202" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F202" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C203" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D203" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E203" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F203" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C204" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D204" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E204" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F204" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C205" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D205" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E205" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F205" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C206" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D206" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E206" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F206" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C207" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D207" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E207" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F207" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C208" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D208" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E208" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F208" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C209" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D209" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E209" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F209" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C210" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D210" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E210" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F210" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C211" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D211" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E211" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F211" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C212" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D212" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E212" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F212" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C213" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D213" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E213" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F213" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C214" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D214" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E214" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F214" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C215" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D215" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E215" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F215" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C216" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D216" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E216" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F216" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C217" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D217" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E217" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F217" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,25 +6085,25 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C218" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D218" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E218" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F218" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6111,25 +6111,25 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C219" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D219" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E219" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F219" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G219" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C220" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D220" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E220" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F220" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C221" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D221" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E221" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F221" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C222" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D222" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E222" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F222" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C223" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D223" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E223" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F223" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C224" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D224" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E224" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F224" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C225" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D225" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E225" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F225" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C226" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D226" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E226" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F226" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C227" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D227" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E227" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F227" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C228" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D228" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E228" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F228" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C229" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D229" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E229" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F229" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C230" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D230" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E230" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F230" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C231" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D231" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E231" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F231" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C232" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D232" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E232" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C233" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D233" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E233" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C233" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D233" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E233" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F233" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C234" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D234" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E234" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F234" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C235" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D235" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E235" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F235" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C236" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D236" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E236" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F236" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C237" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D237" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E237" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F237" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C238" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D238" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E238" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F238" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C239" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D239" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E239" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F239" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C240" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D240" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E240" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F240" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C241" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D241" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F241" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C242" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D242" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E242" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F242" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C243" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D243" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E243" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E243" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F243" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D244" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E244" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F244" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C245" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D245" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E245" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F245" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C246" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F246" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D247" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F247" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C248" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D248" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E248" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F248" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C249" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E249" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F249" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F250" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C251" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D251" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E251" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F251" t="n">
-        <v>24733100</v>
+        <v>30002500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>336.0400085449219</v>
+        <v>340.3699951171875</v>
       </c>
       <c r="C252" t="n">
-        <v>341.6700134277344</v>
+        <v>342.989990234375</v>
       </c>
       <c r="D252" t="n">
-        <v>334.5299987792969</v>
+        <v>338.0400085449219</v>
       </c>
       <c r="E252" t="n">
-        <v>341.0700073242188</v>
+        <v>338.3999938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>29950100</v>
+        <v>32724700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10498,37 +10498,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="D2" t="n">
         <v>341.07</v>
       </c>
-      <c r="D2" t="n">
-        <v>335.92</v>
-      </c>
       <c r="E2" t="n">
-        <v>336.04</v>
+        <v>340.37</v>
       </c>
       <c r="F2" t="n">
-        <v>341.67</v>
+        <v>342.988</v>
       </c>
       <c r="G2" t="n">
-        <v>334.53</v>
+        <v>338.04</v>
       </c>
       <c r="H2" t="n">
-        <v>29649787</v>
+        <v>32463830</v>
       </c>
       <c r="I2" t="n">
-        <v>51468863</v>
+        <v>47555262</v>
       </c>
       <c r="J2" t="n">
-        <v>4977636933632</v>
+        <v>4938670276608</v>
       </c>
       <c r="K2" t="n">
-        <v>39.068733</v>
+        <v>39.076214</v>
       </c>
       <c r="L2" t="n">
-        <v>35.582424</v>
+        <v>35.303875</v>
       </c>
       <c r="M2" t="n">
-        <v>8.73</v>
+        <v>8.66</v>
       </c>
       <c r="N2" t="n">
         <v>345.34</v>
@@ -10564,7 +10564,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>46.341034</v>
+        <v>45.97826</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10576,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4999582056448</v>
+        <v>4960615399424</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:23</t>
+          <t>2026-09-29 13:24:18</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>253.6231177228549</v>
+        <v>253.9220050782957</v>
       </c>
       <c r="C2" t="n">
-        <v>254.0615007840798</v>
+        <v>254.9781013853334</v>
       </c>
       <c r="D2" t="n">
-        <v>252.0788192854059</v>
+        <v>252.1784458386236</v>
       </c>
       <c r="E2" t="n">
-        <v>253.4935913085938</v>
+        <v>253.6928558349609</v>
       </c>
       <c r="F2" t="n">
-        <v>40127700</v>
+        <v>37704300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>253.9220203508673</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C3" t="n">
-        <v>254.9781167214257</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D3" t="n">
-        <v>252.1784610063259</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E3" t="n">
-        <v>253.69287109375</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F3" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356912331815</v>
       </c>
       <c r="C4" t="n">
-        <v>257.8375609779932</v>
+        <v>257.2298088092003</v>
       </c>
       <c r="D4" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146416974651</v>
       </c>
       <c r="E4" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836853027344</v>
       </c>
       <c r="F4" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C5" t="n">
-        <v>257.229778167004</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D5" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E5" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F5" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0404730386864</v>
       </c>
       <c r="C6" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165151882718</v>
       </c>
       <c r="D6" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113063083761</v>
       </c>
       <c r="E6" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7452697753906</v>
       </c>
       <c r="F6" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>257.0405037108186</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C7" t="n">
-        <v>258.1165459888059</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D7" t="n">
-        <v>254.1113366309766</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E7" t="n">
-        <v>255.7453002929688</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F7" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>255.8648286012466</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C8" t="n">
-        <v>256.452653504112</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D8" t="n">
-        <v>254.48990271765</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E8" t="n">
-        <v>255.5360565185547</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F8" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>255.5758888188916</v>
+        <v>256.8611709050607</v>
       </c>
       <c r="C9" t="n">
-        <v>257.5685279874928</v>
+        <v>257.0504740742031</v>
       </c>
       <c r="D9" t="n">
-        <v>255.1673941406971</v>
+        <v>252.2083598847001</v>
       </c>
       <c r="E9" t="n">
-        <v>257.1102294921875</v>
+        <v>253.1050415039062</v>
       </c>
       <c r="F9" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>256.8611399345957</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C10" t="n">
-        <v>257.0504430809132</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D10" t="n">
-        <v>252.2083294752373</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E10" t="n">
-        <v>253.1050109863281</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F10" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C11" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D11" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E11" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F11" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924316138584</v>
       </c>
       <c r="C12" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341508249242</v>
       </c>
       <c r="D12" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994151584908</v>
       </c>
       <c r="E12" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581237792969</v>
       </c>
       <c r="F12" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>245.6924164271231</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C13" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D13" t="n">
-        <v>243.7994000887665</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E13" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F13" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>248.571774561702</v>
+        <v>247.3363501327598</v>
       </c>
       <c r="C14" t="n">
-        <v>250.8932009800968</v>
+        <v>248.1234359576197</v>
       </c>
       <c r="D14" t="n">
-        <v>246.5592047770515</v>
+        <v>244.2278377270511</v>
       </c>
       <c r="E14" t="n">
-        <v>248.4223175048828</v>
+        <v>246.5392913818359</v>
       </c>
       <c r="F14" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>247.3363348246392</v>
+        <v>247.1072067041429</v>
       </c>
       <c r="C15" t="n">
-        <v>248.1234206007849</v>
+        <v>252.4474806979352</v>
       </c>
       <c r="D15" t="n">
-        <v>244.2278226113223</v>
+        <v>246.3599669580113</v>
       </c>
       <c r="E15" t="n">
-        <v>246.5392761230469</v>
+        <v>251.3614807128906</v>
       </c>
       <c r="F15" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C16" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D16" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E16" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F16" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>254.9482209911351</v>
+        <v>260.916147926868</v>
       </c>
       <c r="C17" t="n">
-        <v>263.4069798400544</v>
+        <v>264.313600971564</v>
       </c>
       <c r="D17" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663137101643</v>
       </c>
       <c r="E17" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028564453125</v>
       </c>
       <c r="F17" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>260.9161783410852</v>
+        <v>261.6833028295614</v>
       </c>
       <c r="C18" t="n">
-        <v>264.3136317818121</v>
+        <v>261.882578885752</v>
       </c>
       <c r="D18" t="n">
-        <v>260.8663441185724</v>
+        <v>254.4898750367867</v>
       </c>
       <c r="E18" t="n">
-        <v>261.8028869628906</v>
+        <v>257.498779296875</v>
       </c>
       <c r="F18" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>261.6833338430701</v>
+        <v>258.9832941033833</v>
       </c>
       <c r="C19" t="n">
-        <v>261.882609922878</v>
+        <v>259.6607840683213</v>
       </c>
       <c r="D19" t="n">
-        <v>254.4899051977633</v>
+        <v>257.0604047594014</v>
       </c>
       <c r="E19" t="n">
-        <v>257.4988098144531</v>
+        <v>258.6246032714844</v>
       </c>
       <c r="F19" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>258.9832941033833</v>
+        <v>260.2287466983284</v>
       </c>
       <c r="C20" t="n">
-        <v>259.6607840683213</v>
+        <v>263.1579290692685</v>
       </c>
       <c r="D20" t="n">
-        <v>257.0604047594014</v>
+        <v>258.2261343576155</v>
       </c>
       <c r="E20" t="n">
-        <v>258.6246032714844</v>
+        <v>261.8527526855469</v>
       </c>
       <c r="F20" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051799132</v>
       </c>
       <c r="C21" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295659182063</v>
       </c>
       <c r="D21" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6760154250923</v>
       </c>
       <c r="E21" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8207092285156</v>
       </c>
       <c r="F21" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>263.9051498417878</v>
+        <v>268.0000063221084</v>
       </c>
       <c r="C22" t="n">
-        <v>268.1295353654346</v>
+        <v>268.8967183092298</v>
       </c>
       <c r="D22" t="n">
-        <v>263.6759853797928</v>
+        <v>267.1631014853557</v>
       </c>
       <c r="E22" t="n">
-        <v>267.8206787109375</v>
+        <v>268.0099792480469</v>
       </c>
       <c r="F22" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>268.0000063221084</v>
+        <v>268.2889603375268</v>
       </c>
       <c r="C23" t="n">
-        <v>268.8967183092298</v>
+        <v>270.4111261059246</v>
       </c>
       <c r="D23" t="n">
-        <v>267.1631014853557</v>
+        <v>266.126933268734</v>
       </c>
       <c r="E23" t="n">
-        <v>268.0099792480469</v>
+        <v>268.7074279785156</v>
       </c>
       <c r="F23" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889785237465</v>
       </c>
       <c r="C24" t="n">
-        <v>270.4110953948544</v>
+        <v>273.131090148023</v>
       </c>
       <c r="D24" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4919171420091</v>
       </c>
       <c r="E24" t="n">
-        <v>268.7073974609375</v>
+        <v>270.4011535644531</v>
       </c>
       <c r="F24" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>270.9889479398262</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C25" t="n">
-        <v>273.1310593223432</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D25" t="n">
-        <v>267.4918869527685</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E25" t="n">
-        <v>270.401123046875</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F25" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>275.9705701844509</v>
+        <v>269.424736694289</v>
       </c>
       <c r="C26" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531467885877</v>
       </c>
       <c r="D26" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2700709373508</v>
       </c>
       <c r="E26" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597534179688</v>
       </c>
       <c r="F26" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>269.424736694289</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C27" t="n">
-        <v>269.8531467885877</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D27" t="n">
-        <v>265.2700709373508</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E27" t="n">
-        <v>268.0597534179688</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F27" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C28" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D28" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E28" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F28" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C29" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D29" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E29" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F29" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C30" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D30" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E30" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F30" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,25 +1223,25 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298830249396</v>
       </c>
       <c r="C31" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869540449525</v>
       </c>
       <c r="D31" t="n">
-        <v>265.7881780523408</v>
+        <v>266.7339548671466</v>
       </c>
       <c r="E31" t="n">
-        <v>267.48193359375</v>
+        <v>268.6986083984375</v>
       </c>
       <c r="F31" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1249,25 +1249,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>268.2298830249396</v>
+        <v>269.0776024957972</v>
       </c>
       <c r="C32" t="n">
-        <v>272.9869540449525</v>
+        <v>275.1610502271484</v>
       </c>
       <c r="D32" t="n">
-        <v>266.7339548671466</v>
+        <v>269.067619901526</v>
       </c>
       <c r="E32" t="n">
-        <v>268.6986083984375</v>
+        <v>274.5028381347656</v>
       </c>
       <c r="F32" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G32" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>269.0775725813642</v>
+        <v>274.253476009827</v>
       </c>
       <c r="C33" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815052844664</v>
       </c>
       <c r="D33" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624464716027</v>
       </c>
       <c r="E33" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276306152344</v>
       </c>
       <c r="F33" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C34" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D34" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E34" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F34" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C35" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D35" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E35" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F35" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>270.3141778275755</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C36" t="n">
-        <v>275.2108524736826</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D36" t="n">
-        <v>268.8681323529343</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E36" t="n">
-        <v>271.6705017089844</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F36" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>268.0902717401977</v>
+        <v>269.2570854665072</v>
       </c>
       <c r="C37" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751321987233</v>
       </c>
       <c r="D37" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997795179588</v>
       </c>
       <c r="E37" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7140197753906</v>
       </c>
       <c r="F37" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>269.2570854665072</v>
+        <v>264.8091896065648</v>
       </c>
       <c r="C38" t="n">
-        <v>269.9751321987233</v>
+        <v>271.4710487380511</v>
       </c>
       <c r="D38" t="n">
-        <v>264.5997795179588</v>
+        <v>264.7792722621166</v>
       </c>
       <c r="E38" t="n">
-        <v>266.7140197753906</v>
+        <v>267.8309631347656</v>
       </c>
       <c r="F38" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>264.8091896065648</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C39" t="n">
-        <v>271.4710487380511</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D39" t="n">
-        <v>264.7792722621166</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E39" t="n">
-        <v>267.8309631347656</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F39" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>270.0948061865016</v>
+        <v>265.22808167538</v>
       </c>
       <c r="C40" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5880228442522</v>
       </c>
       <c r="D40" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488429624803</v>
       </c>
       <c r="E40" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7530212402344</v>
       </c>
       <c r="F40" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>265.2280517805383</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C41" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D41" t="n">
-        <v>264.9488130991126</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E41" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F41" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C42" t="n">
-        <v>276.2480447880167</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D42" t="n">
-        <v>270.1645980035721</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E42" t="n">
-        <v>275.1709899902344</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F42" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>274.5227726174851</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C43" t="n">
-        <v>279.6189174225992</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D43" t="n">
-        <v>274.5028378637012</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E43" t="n">
-        <v>276.2181701660156</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F43" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073375714406</v>
       </c>
       <c r="C44" t="n">
-        <v>278.7712060098946</v>
+        <v>278.2426042891834</v>
       </c>
       <c r="D44" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407657367699</v>
       </c>
       <c r="E44" t="n">
-        <v>276.7965698242188</v>
+        <v>278.093017578125</v>
       </c>
       <c r="F44" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>276.5073679150082</v>
+        <v>277.255303275414</v>
       </c>
       <c r="C45" t="n">
-        <v>278.242634823177</v>
+        <v>282.650620542313</v>
       </c>
       <c r="D45" t="n">
-        <v>275.2407959413455</v>
+        <v>275.390384584981</v>
       </c>
       <c r="E45" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3314819335938</v>
       </c>
       <c r="F45" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>277.2553332443013</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C46" t="n">
-        <v>282.6506510943872</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D46" t="n">
-        <v>275.3904143522869</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E46" t="n">
-        <v>282.3315124511719</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F46" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C47" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D47" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E47" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F47" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>285.4231155973949</v>
+        <v>283.328813896664</v>
       </c>
       <c r="C48" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9571086251454</v>
       </c>
       <c r="D48" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337611056945</v>
       </c>
       <c r="E48" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380493164062</v>
       </c>
       <c r="F48" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>283.3287830094401</v>
+        <v>279.7784866384076</v>
       </c>
       <c r="C49" t="n">
-        <v>283.9570776694276</v>
+        <v>280.3768640337962</v>
       </c>
       <c r="D49" t="n">
-        <v>277.8337308175164</v>
+        <v>277.2952250127556</v>
       </c>
       <c r="E49" t="n">
-        <v>279.9380187988281</v>
+        <v>278.0232543945312</v>
       </c>
       <c r="F49" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C50" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D50" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E50" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F50" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049325131135</v>
       </c>
       <c r="C51" t="n">
-        <v>278.9108174051644</v>
+        <v>279.2698514894354</v>
       </c>
       <c r="D51" t="n">
-        <v>275.4003533668138</v>
+        <v>276.16830825817</v>
       </c>
       <c r="E51" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275817871094</v>
       </c>
       <c r="F51" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960515324306</v>
       </c>
       <c r="C52" t="n">
-        <v>279.269820658071</v>
+        <v>278.9906225605669</v>
       </c>
       <c r="D52" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6896099437804</v>
       </c>
       <c r="E52" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232543945312</v>
       </c>
       <c r="F52" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342340640522</v>
       </c>
       <c r="C53" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310007112651</v>
       </c>
       <c r="D53" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0666927429874</v>
       </c>
       <c r="E53" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752380371094</v>
       </c>
       <c r="F53" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>278.342371275548</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C54" t="n">
-        <v>278.8310314000742</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D54" t="n">
-        <v>273.0667227973629</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E54" t="n">
-        <v>277.2752685546875</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F54" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C55" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D55" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E55" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F55" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C56" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D56" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E56" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F56" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C57" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D57" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E57" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F57" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672390402853</v>
       </c>
       <c r="C58" t="n">
-        <v>275.4103308752873</v>
+        <v>272.8872042261758</v>
       </c>
       <c r="D58" t="n">
-        <v>270.9026119684932</v>
+        <v>266.2253451719176</v>
       </c>
       <c r="E58" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511108398438</v>
       </c>
       <c r="F58" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>272.8672697170699</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C59" t="n">
-        <v>272.887234905205</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D59" t="n">
-        <v>266.225375101995</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E59" t="n">
-        <v>271.4511413574219</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F59" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1193204151364</v>
       </c>
       <c r="C60" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365711538121</v>
       </c>
       <c r="D60" t="n">
-        <v>269.1673383776201</v>
+        <v>269.775723721713</v>
       </c>
       <c r="E60" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344665527344</v>
       </c>
       <c r="F60" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C61" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D61" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E61" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F61" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007310322557</v>
       </c>
       <c r="C62" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823395934045</v>
       </c>
       <c r="D62" t="n">
-        <v>268.8282792538215</v>
+        <v>271.4611268874897</v>
       </c>
       <c r="E62" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667419433594</v>
       </c>
       <c r="F62" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157529954652</v>
       </c>
       <c r="C63" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224597374741</v>
       </c>
       <c r="D63" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192637901173</v>
       </c>
       <c r="E63" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578063964844</v>
       </c>
       <c r="F63" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C64" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D64" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E64" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F64" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C65" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D65" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E65" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F65" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>272.0694584675055</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C66" t="n">
-        <v>273.3360001129787</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D66" t="n">
-        <v>271.5408983628093</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E66" t="n">
-        <v>272.3387145996094</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F66" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209292436991</v>
       </c>
       <c r="C67" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857683126949</v>
       </c>
       <c r="D67" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697691424855</v>
       </c>
       <c r="E67" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743225097656</v>
       </c>
       <c r="F67" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>271.5209292436991</v>
+        <v>269.9053450243044</v>
       </c>
       <c r="C68" t="n">
-        <v>277.0857683126949</v>
+        <v>270.7729784841199</v>
       </c>
       <c r="D68" t="n">
-        <v>268.2697691424855</v>
+        <v>265.4175605620285</v>
       </c>
       <c r="E68" t="n">
-        <v>270.2743225097656</v>
+        <v>266.5345153808594</v>
       </c>
       <c r="F68" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>269.9053450243044</v>
+        <v>266.275215737747</v>
       </c>
       <c r="C69" t="n">
-        <v>270.7729784841199</v>
+        <v>266.8237105625631</v>
       </c>
       <c r="D69" t="n">
-        <v>265.4175605620285</v>
+        <v>261.4084578614468</v>
       </c>
       <c r="E69" t="n">
-        <v>266.5345153808594</v>
+        <v>261.6477966308594</v>
       </c>
       <c r="F69" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>266.275215737747</v>
+        <v>262.4855256371837</v>
       </c>
       <c r="C70" t="n">
-        <v>266.8237105625631</v>
+        <v>262.964203143993</v>
       </c>
       <c r="D70" t="n">
-        <v>261.4084578614468</v>
+        <v>259.1047135716701</v>
       </c>
       <c r="E70" t="n">
-        <v>261.6477966308594</v>
+        <v>259.623291015625</v>
       </c>
       <c r="F70" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>262.4855256371837</v>
+        <v>256.3223167721599</v>
       </c>
       <c r="C71" t="n">
-        <v>262.964203143993</v>
+        <v>258.5861744106298</v>
       </c>
       <c r="D71" t="n">
-        <v>259.1047135716701</v>
+        <v>255.005907781442</v>
       </c>
       <c r="E71" t="n">
-        <v>259.623291015625</v>
+        <v>258.3368530273438</v>
       </c>
       <c r="F71" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>256.3222864925608</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C72" t="n">
-        <v>258.586143863599</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D72" t="n">
-        <v>255.0058776573516</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E72" t="n">
-        <v>258.3368225097656</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F72" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C73" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D73" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E73" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F73" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>258.4565110528425</v>
+        <v>258.0176775418968</v>
       </c>
       <c r="C74" t="n">
-        <v>260.5906861738287</v>
+        <v>261.0992857475004</v>
       </c>
       <c r="D74" t="n">
-        <v>256.1029014720883</v>
+        <v>257.6885867541948</v>
       </c>
       <c r="E74" t="n">
-        <v>259.5435485839844</v>
+        <v>260.3413391113281</v>
       </c>
       <c r="F74" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>258.017707787092</v>
+        <v>258.7856080874888</v>
       </c>
       <c r="C75" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1093003767552</v>
       </c>
       <c r="D75" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131555781144</v>
       </c>
       <c r="E75" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543334960938</v>
       </c>
       <c r="F75" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>258.7855776250856</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C76" t="n">
-        <v>261.1092696408236</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D76" t="n">
-        <v>256.0131254420647</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E76" t="n">
-        <v>259.2543029785156</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F76" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1999111311508</v>
       </c>
       <c r="C77" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1971965798445</v>
       </c>
       <c r="D77" t="n">
-        <v>256.3522089636155</v>
+        <v>254.2379721311412</v>
       </c>
       <c r="E77" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363494873047</v>
       </c>
       <c r="F77" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>257.1999111311508</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C78" t="n">
-        <v>258.1971965798445</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D78" t="n">
-        <v>254.2379721311412</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E78" t="n">
-        <v>254.8363494873047</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F78" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0249055239374</v>
       </c>
       <c r="C79" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771427168815</v>
       </c>
       <c r="D79" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144562363057</v>
       </c>
       <c r="E79" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777526855469</v>
       </c>
       <c r="F79" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>248.0248902004531</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C80" t="n">
-        <v>250.8771272171802</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D80" t="n">
-        <v>244.5144411297041</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E80" t="n">
-        <v>246.9777374267578</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F80" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486524137701</v>
       </c>
       <c r="C81" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329754164565</v>
       </c>
       <c r="D81" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0158041358057</v>
       </c>
       <c r="E81" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666839599609</v>
       </c>
       <c r="F81" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>246.6486371992728</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C82" t="n">
-        <v>248.7329600733879</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D82" t="n">
-        <v>244.0157890837153</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E82" t="n">
-        <v>247.3666687011719</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F82" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664593428383</v>
       </c>
       <c r="C83" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389114176715</v>
       </c>
       <c r="D83" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090434871919</v>
       </c>
       <c r="E83" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5688781738281</v>
       </c>
       <c r="F83" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>258.4664593428383</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C84" t="n">
-        <v>261.2389114176715</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D84" t="n">
-        <v>257.5090434871919</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E84" t="n">
-        <v>257.5688781738281</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F84" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>256.9506034196754</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C85" t="n">
-        <v>258.1573103549757</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D85" t="n">
-        <v>253.8191275531099</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E85" t="n">
-        <v>255.743896484375</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F85" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C86" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D86" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E86" t="n">
-        <v>257.5788879394531</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F86" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C87" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D87" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E87" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F87" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C88" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D88" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E88" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F88" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="C89" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927850076088</v>
       </c>
       <c r="D89" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="E89" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394409179688</v>
       </c>
       <c r="F89" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>271.5508302866565</v>
+        <v>277.3749854862336</v>
       </c>
       <c r="C90" t="n">
-        <v>278.1927542185059</v>
+        <v>278.7412615768201</v>
       </c>
       <c r="D90" t="n">
-        <v>271.5508302866565</v>
+        <v>272.4882932485779</v>
       </c>
       <c r="E90" t="n">
-        <v>275.7394104003906</v>
+        <v>275.1610107421875</v>
       </c>
       <c r="F90" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>277.3750162493594</v>
+        <v>276.3677353153735</v>
       </c>
       <c r="C91" t="n">
-        <v>278.7412924914769</v>
+        <v>280.1474556417363</v>
       </c>
       <c r="D91" t="n">
-        <v>272.48832346973</v>
+        <v>276.1782486476445</v>
       </c>
       <c r="E91" t="n">
-        <v>275.1610412597656</v>
+        <v>277.3650207519531</v>
       </c>
       <c r="F91" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,25 +2809,25 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>276.3677049075235</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C92" t="n">
-        <v>280.1474248180158</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D92" t="n">
-        <v>276.1782182606431</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E92" t="n">
-        <v>277.364990234375</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F92" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -2835,25 +2835,25 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C93" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D93" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E93" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F93" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G93" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C94" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D94" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E94" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F94" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990585104662</v>
       </c>
       <c r="C95" t="n">
-        <v>279.6808719096702</v>
+        <v>275.2288318017276</v>
       </c>
       <c r="D95" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165063299744</v>
       </c>
       <c r="E95" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637634277344</v>
       </c>
       <c r="F95" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>275.0990906441111</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C96" t="n">
-        <v>275.228863950531</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D96" t="n">
-        <v>259.7165366668213</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E96" t="n">
-        <v>261.2637939453125</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F96" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C97" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D97" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E97" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F97" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C98" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D98" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E98" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F98" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C99" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D99" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E99" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F99" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C100" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D100" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E100" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F100" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C101" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D101" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E101" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F101" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C102" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D102" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E102" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F102" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C103" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D103" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E103" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F103" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C104" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D104" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E104" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F104" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="C105" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="D105" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217314181026</v>
       </c>
       <c r="E105" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7094116210938</v>
       </c>
       <c r="F105" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>272.3240124520744</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C106" t="n">
-        <v>272.3240124520744</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D106" t="n">
-        <v>262.4217010495403</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E106" t="n">
-        <v>263.7093811035156</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F106" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C107" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D107" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E107" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F107" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C108" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D108" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E108" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F108" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C109" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D109" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E109" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F109" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C110" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D110" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E110" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F110" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C111" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D111" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E111" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F111" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C112" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D112" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E112" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F112" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>257.1910284571696</v>
+        <v>260.624897946549</v>
       </c>
       <c r="C113" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630538494394</v>
       </c>
       <c r="D113" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876327296249</v>
       </c>
       <c r="E113" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453979492188</v>
       </c>
       <c r="F113" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>260.6248673962081</v>
+        <v>258.1992408199258</v>
       </c>
       <c r="C114" t="n">
-        <v>261.6630231774062</v>
+        <v>258.4887327594216</v>
       </c>
       <c r="D114" t="n">
-        <v>259.0876023594815</v>
+        <v>253.7272102811576</v>
       </c>
       <c r="E114" t="n">
-        <v>260.3453674316406</v>
+        <v>255.3043975830078</v>
       </c>
       <c r="F114" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>258.1992253881205</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C115" t="n">
-        <v>258.4887173103141</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D115" t="n">
-        <v>253.7271951166323</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E115" t="n">
-        <v>255.3043823242188</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F115" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C116" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D116" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E116" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F116" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C117" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D117" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E117" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F117" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C118" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D118" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E118" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F118" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C119" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D119" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E119" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F119" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C120" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D120" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E120" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F120" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C121" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D121" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E121" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F121" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C122" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D122" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E122" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F122" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C123" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D123" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E123" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F123" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C124" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D124" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E124" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F124" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C125" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D125" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E125" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F125" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C126" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D126" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E126" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F126" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683905467953</v>
       </c>
       <c r="C127" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248978486836</v>
       </c>
       <c r="D127" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598358728773</v>
       </c>
       <c r="E127" t="n">
-        <v>246.1906585693359</v>
+        <v>253.3379058837891</v>
       </c>
       <c r="F127" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>247.4683756415328</v>
+        <v>253.6273948962928</v>
       </c>
       <c r="C128" t="n">
-        <v>255.0248824882854</v>
+        <v>255.7236449097363</v>
       </c>
       <c r="D128" t="n">
-        <v>246.6598210163149</v>
+        <v>252.8787309132899</v>
       </c>
       <c r="E128" t="n">
-        <v>253.337890625</v>
+        <v>255.1746368408203</v>
       </c>
       <c r="F128" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>253.6273797300248</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C129" t="n">
-        <v>255.7236296181179</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D129" t="n">
-        <v>252.8787157917901</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E129" t="n">
-        <v>255.1746215820312</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F129" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>253.7471740568136</v>
+        <v>256.0530752925303</v>
       </c>
       <c r="C130" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6930045642991</v>
       </c>
       <c r="D130" t="n">
-        <v>250.2034948550391</v>
+        <v>256.0031460821725</v>
       </c>
       <c r="E130" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988647460938</v>
       </c>
       <c r="F130" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>256.053045051996</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C131" t="n">
-        <v>261.6929736576745</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D131" t="n">
-        <v>256.003115847535</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E131" t="n">
-        <v>258.3988342285156</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F131" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896321241455</v>
       </c>
       <c r="C132" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2873042333858</v>
       </c>
       <c r="D132" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730388391825</v>
       </c>
       <c r="E132" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4388122558594</v>
       </c>
       <c r="F132" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>257.9896016596085</v>
+        <v>258.5386343954405</v>
       </c>
       <c r="C133" t="n">
-        <v>259.2872736156141</v>
+        <v>260.6548530924392</v>
       </c>
       <c r="D133" t="n">
-        <v>256.0730086009651</v>
+        <v>255.6138610163474</v>
       </c>
       <c r="E133" t="n">
-        <v>258.4387817382812</v>
+        <v>260.0259704589844</v>
       </c>
       <c r="F133" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>258.5386040524215</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C134" t="n">
-        <v>260.6548225010532</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D134" t="n">
-        <v>255.6138310165902</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E134" t="n">
-        <v>260.0259399414062</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F134" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C135" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D135" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E135" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F135" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881922504944</v>
       </c>
       <c r="C136" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4634109961452</v>
       </c>
       <c r="D136" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318642110386</v>
       </c>
       <c r="E136" t="n">
-        <v>258.73828125</v>
+        <v>258.3689270019531</v>
       </c>
       <c r="F136" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>258.7881616833942</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C137" t="n">
-        <v>261.4633801130582</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D137" t="n">
-        <v>256.7318338868242</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E137" t="n">
-        <v>258.368896484375</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F137" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3247234477873</v>
       </c>
       <c r="C138" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840980024072</v>
       </c>
       <c r="D138" t="n">
-        <v>257.3507435512608</v>
+        <v>260.8045755356903</v>
       </c>
       <c r="E138" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307861328125</v>
       </c>
       <c r="F138" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>266.3246925362851</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C139" t="n">
-        <v>266.6840670491935</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D139" t="n">
-        <v>260.804545264895</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E139" t="n">
-        <v>262.9307556152344</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F139" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C140" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D140" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E140" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F140" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C141" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D141" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E141" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F141" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C142" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D142" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E142" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F142" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C143" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D143" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E143" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F143" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C144" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D144" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E144" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F144" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C145" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D145" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E145" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F145" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C146" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D146" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E146" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F146" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C147" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D147" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E147" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F147" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C148" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D148" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E148" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F148" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632420760759</v>
       </c>
       <c r="C149" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083659496485</v>
       </c>
       <c r="D149" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8741246788477</v>
       </c>
       <c r="E149" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409912109375</v>
       </c>
       <c r="F149" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>278.3632116979401</v>
+        <v>279.1617980116577</v>
       </c>
       <c r="C150" t="n">
-        <v>286.7083346607987</v>
+        <v>280.1300712051751</v>
       </c>
       <c r="D150" t="n">
-        <v>277.8740943540899</v>
+        <v>274.3703307853319</v>
       </c>
       <c r="E150" t="n">
-        <v>279.6409606933594</v>
+        <v>276.3368225097656</v>
       </c>
       <c r="F150" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>279.1618288412153</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C151" t="n">
-        <v>280.130102141665</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D151" t="n">
-        <v>274.3703610857382</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E151" t="n">
-        <v>276.3368530273438</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F151" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>276.43668191704</v>
+        <v>281.4178249779708</v>
       </c>
       <c r="C152" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5169265187869</v>
       </c>
       <c r="D152" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693330033821</v>
       </c>
       <c r="E152" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978637695312</v>
       </c>
       <c r="F152" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>281.4177950537395</v>
+        <v>288.7547052879293</v>
       </c>
       <c r="C153" t="n">
-        <v>287.5168959460148</v>
+        <v>291.6096265406606</v>
       </c>
       <c r="D153" t="n">
-        <v>280.5693031693742</v>
+        <v>285.2709318587503</v>
       </c>
       <c r="E153" t="n">
-        <v>286.9978332519531</v>
+        <v>286.927978515625</v>
       </c>
       <c r="F153" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>288.7546745760609</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C154" t="n">
-        <v>291.6095955251437</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D154" t="n">
-        <v>285.2709015174152</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E154" t="n">
-        <v>286.9279479980469</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F154" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,25 +4447,25 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C155" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D155" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E155" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F155" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4473,25 +4473,25 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C156" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D156" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E156" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F156" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G156" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C157" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D157" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E157" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F157" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C158" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D158" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E158" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F158" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C159" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D159" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E159" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F159" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C160" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D160" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E160" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F160" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C161" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D161" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E161" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F161" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C162" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D162" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E162" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F162" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C163" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D163" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E163" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F163" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C164" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D164" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E164" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F164" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C165" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D165" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E165" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F165" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C166" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D166" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E166" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F166" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C167" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D167" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E167" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F167" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C168" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D168" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E168" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F168" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C169" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D169" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E169" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F169" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C170" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D170" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E170" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F170" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C171" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D171" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E171" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F171" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C172" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D172" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E172" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F172" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C173" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D173" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E173" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F173" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C174" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D174" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E174" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F174" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C175" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D175" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E175" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F175" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C176" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D176" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E176" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F176" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C177" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D177" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E177" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F177" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C178" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D178" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E178" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F178" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C179" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D179" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E179" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F179" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C180" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D180" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E180" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F180" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C181" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D181" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E181" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F181" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C182" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D182" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E182" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F182" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C183" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D183" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E183" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F183" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C184" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D184" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E184" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F184" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C185" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D185" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E185" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F185" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C186" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D186" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E186" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F186" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C187" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D187" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E187" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F187" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C188" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D188" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E188" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F188" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C189" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D189" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E189" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F189" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C190" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D190" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E190" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F190" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C191" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D191" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E191" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F191" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C192" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D192" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E192" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F192" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C193" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D193" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E193" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F193" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C194" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D194" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E194" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F194" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C195" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D195" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E195" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F195" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C196" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D196" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E196" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F196" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C197" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D197" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E197" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F197" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C198" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D198" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E198" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F198" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C199" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D199" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E199" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F199" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C200" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D200" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E200" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F200" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C201" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D201" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E201" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F201" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C202" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D202" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E202" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F202" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C203" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D203" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E203" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F203" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C204" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D204" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E204" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F204" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C205" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D205" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E205" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F205" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C206" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D206" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E206" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F206" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C207" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D207" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E207" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F207" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C208" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D208" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E208" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F208" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C209" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D209" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E209" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F209" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C210" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D210" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E210" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F210" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C211" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D211" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E211" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F211" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C212" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D212" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E212" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F212" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C213" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D213" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E213" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F213" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C214" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D214" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E214" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F214" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C215" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D215" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E215" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F215" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C216" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D216" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E216" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F216" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,25 +6059,25 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C217" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D217" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E217" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F217" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6085,25 +6085,25 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C218" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D218" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E218" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F218" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G218" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C219" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D219" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E219" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F219" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C220" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D220" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E220" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F220" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C221" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D221" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E221" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F221" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C222" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D222" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E222" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F222" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C223" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D223" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E223" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F223" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C224" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D224" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E224" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F224" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C225" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D225" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E225" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F225" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C226" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D226" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E226" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F226" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C227" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D227" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E227" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F227" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C228" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D228" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E228" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F228" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C229" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D229" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F229" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C230" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D230" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E230" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F230" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C231" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D231" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E231" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F231" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C232" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D232" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E232" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C232" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D232" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E232" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F232" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C233" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D233" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E233" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F233" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C234" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D234" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E234" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F234" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C235" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D235" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E235" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F235" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C236" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D236" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E236" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F236" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C237" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D237" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E237" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F237" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C238" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D238" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E238" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F238" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C239" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D239" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E239" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F239" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C240" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D240" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F240" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C241" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D241" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E241" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F241" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C242" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D242" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E242" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E242" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F242" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D243" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E243" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F243" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C244" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D244" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E244" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F244" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C245" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F245" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D246" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E246" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F246" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C247" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D247" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E247" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F247" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C248" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E248" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F248" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D249" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F249" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C250" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D250" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E250" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>24733100</v>
+        <v>30002500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>336.0400085449219</v>
+        <v>340.3699951171875</v>
       </c>
       <c r="C251" t="n">
-        <v>341.6700134277344</v>
+        <v>342.989990234375</v>
       </c>
       <c r="D251" t="n">
-        <v>334.5299987792969</v>
+        <v>338.0400085449219</v>
       </c>
       <c r="E251" t="n">
-        <v>341.0700073242188</v>
+        <v>338.3999938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>30002500</v>
+        <v>32820800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>340.3699951171875</v>
+        <v>336.9700012207031</v>
       </c>
       <c r="C252" t="n">
-        <v>342.989990234375</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="D252" t="n">
-        <v>338.0400085449219</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="E252" t="n">
-        <v>338.3999938964844</v>
+        <v>329.3999938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>32724700</v>
+        <v>38427200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7020,9 +7020,6 @@
       <c r="E1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="F1" s="1" t="n">
-        <v>44469</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7042,7 +7039,6 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7062,7 +7058,6 @@
       <c r="E3" t="n">
         <v>0.162</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7082,7 +7077,6 @@
       <c r="E4" t="n">
         <v>130541000000</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7102,7 +7096,6 @@
       <c r="E5" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7122,7 +7115,6 @@
       <c r="E6" t="n">
         <v>11104000000</v>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7142,7 +7134,6 @@
       <c r="E7" t="n">
         <v>223546000000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7162,7 +7153,6 @@
       <c r="E8" t="n">
         <v>130541000000</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7182,7 +7172,6 @@
       <c r="E9" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7198,9 +7187,6 @@
       <c r="E10" t="n">
         <v>-106000000</v>
       </c>
-      <c r="F10" t="n">
-        <v>198000000</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7216,9 +7202,6 @@
       <c r="E11" t="n">
         <v>2931000000</v>
       </c>
-      <c r="F11" t="n">
-        <v>2645000000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7234,9 +7217,6 @@
       <c r="E12" t="n">
         <v>2825000000</v>
       </c>
-      <c r="F12" t="n">
-        <v>2843000000</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7256,7 +7236,6 @@
       <c r="E13" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7276,7 +7255,6 @@
       <c r="E14" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7296,7 +7274,6 @@
       <c r="E15" t="n">
         <v>274891000000</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7316,7 +7293,6 @@
       <c r="E16" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7336,7 +7312,6 @@
       <c r="E17" t="n">
         <v>16325819000</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7356,7 +7331,6 @@
       <c r="E18" t="n">
         <v>16215963000</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7376,7 +7350,6 @@
       <c r="E19" t="n">
         <v>6.11</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7396,7 +7369,6 @@
       <c r="E20" t="n">
         <v>6.15</v>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7416,7 +7388,6 @@
       <c r="E21" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7436,7 +7407,6 @@
       <c r="E22" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7456,7 +7426,6 @@
       <c r="E23" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7476,7 +7445,6 @@
       <c r="E24" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7496,7 +7464,6 @@
       <c r="E25" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7516,7 +7483,6 @@
       <c r="E26" t="n">
         <v>19300000000</v>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7536,7 +7502,6 @@
       <c r="E27" t="n">
         <v>119103000000</v>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7556,7 +7521,6 @@
       <c r="E28" t="n">
         <v>-334000000</v>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7576,7 +7540,6 @@
       <c r="E29" t="n">
         <v>-334000000</v>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7592,9 +7555,6 @@
       <c r="E30" t="n">
         <v>-106000000</v>
       </c>
-      <c r="F30" t="n">
-        <v>198000000</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7610,9 +7570,6 @@
       <c r="E31" t="n">
         <v>2931000000</v>
       </c>
-      <c r="F31" t="n">
-        <v>2645000000</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7628,9 +7585,6 @@
       <c r="E32" t="n">
         <v>2825000000</v>
       </c>
-      <c r="F32" t="n">
-        <v>2843000000</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7650,7 +7604,6 @@
       <c r="E33" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7670,7 +7623,6 @@
       <c r="E34" t="n">
         <v>51345000000</v>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7690,7 +7642,6 @@
       <c r="E35" t="n">
         <v>26251000000</v>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7710,7 +7661,6 @@
       <c r="E36" t="n">
         <v>25094000000</v>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7730,7 +7680,6 @@
       <c r="E37" t="n">
         <v>170782000000</v>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7750,7 +7699,6 @@
       <c r="E38" t="n">
         <v>223546000000</v>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7770,7 +7718,6 @@
       <c r="E39" t="n">
         <v>394328000000</v>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7790,7 +7737,6 @@
       <c r="E40" t="n">
         <v>394328000000</v>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7803,7 +7749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7819,9 +7765,6 @@
       <c r="E1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="F1" s="1" t="n">
-        <v>44469</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7835,7 +7778,6 @@
         <v>0</v>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7855,7 +7797,6 @@
       <c r="E3" t="n">
         <v>15943425000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7875,7 +7816,6 @@
       <c r="E4" t="n">
         <v>15943425000</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7895,7 +7835,6 @@
       <c r="E5" t="n">
         <v>96423000000</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7915,7 +7854,6 @@
       <c r="E6" t="n">
         <v>132480000000</v>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7935,7 +7873,6 @@
       <c r="E7" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7955,7 +7892,6 @@
       <c r="E8" t="n">
         <v>170741000000</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7975,7 +7911,6 @@
       <c r="E9" t="n">
         <v>-18577000000</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7995,7 +7930,6 @@
       <c r="E10" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8011,9 +7945,6 @@
       <c r="E11" t="n">
         <v>12411000000</v>
       </c>
-      <c r="F11" t="n">
-        <v>11803000000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8033,7 +7964,6 @@
       <c r="E12" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8053,7 +7983,6 @@
       <c r="E13" t="n">
         <v>149631000000</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8073,7 +8002,6 @@
       <c r="E14" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8093,7 +8021,6 @@
       <c r="E15" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8113,7 +8040,6 @@
       <c r="E16" t="n">
         <v>-11109000000</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8133,7 +8059,6 @@
       <c r="E17" t="n">
         <v>-11109000000</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8153,7 +8078,6 @@
       <c r="E18" t="n">
         <v>-3068000000</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8173,7 +8097,6 @@
       <c r="E19" t="n">
         <v>64849000000</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8193,7 +8116,6 @@
       <c r="E20" t="n">
         <v>64849000000</v>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8213,7 +8135,6 @@
       <c r="E21" t="n">
         <v>302083000000</v>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8233,7 +8154,6 @@
       <c r="E22" t="n">
         <v>148101000000</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8253,7 +8173,6 @@
       <c r="E23" t="n">
         <v>21737000000</v>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8271,9 +8190,6 @@
       <c r="E24" t="n">
         <v>16657000000</v>
       </c>
-      <c r="F24" t="n">
-        <v>24689000000</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8293,7 +8209,6 @@
       <c r="E25" t="n">
         <v>109707000000</v>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8309,9 +8224,6 @@
       <c r="E26" t="n">
         <v>10748000000</v>
       </c>
-      <c r="F26" t="n">
-        <v>10275000000</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8331,7 +8243,6 @@
       <c r="E27" t="n">
         <v>98959000000</v>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8351,7 +8262,6 @@
       <c r="E28" t="n">
         <v>153982000000</v>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8371,7 +8281,6 @@
       <c r="E29" t="n">
         <v>52630000000</v>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8391,7 +8300,6 @@
       <c r="E30" t="n">
         <v>7912000000</v>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8411,7 +8319,6 @@
       <c r="E31" t="n">
         <v>7912000000</v>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8431,7 +8338,6 @@
       <c r="E32" t="n">
         <v>22773000000</v>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8447,9 +8353,6 @@
       <c r="E33" t="n">
         <v>1663000000</v>
       </c>
-      <c r="F33" t="n">
-        <v>1528000000</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8469,7 +8372,6 @@
       <c r="E34" t="n">
         <v>21110000000</v>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8489,7 +8391,6 @@
       <c r="E35" t="n">
         <v>11128000000</v>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8509,7 +8410,6 @@
       <c r="E36" t="n">
         <v>9982000000</v>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8529,7 +8429,6 @@
       <c r="E37" t="n">
         <v>70667000000</v>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8543,7 +8442,6 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8563,7 +8461,6 @@
       <c r="E39" t="n">
         <v>70667000000</v>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8583,7 +8480,6 @@
       <c r="E40" t="n">
         <v>6552000000</v>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8603,7 +8499,6 @@
       <c r="E41" t="n">
         <v>6552000000</v>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8623,7 +8518,6 @@
       <c r="E42" t="n">
         <v>64115000000</v>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8643,7 +8537,6 @@
       <c r="E43" t="n">
         <v>352755000000</v>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8663,7 +8556,6 @@
       <c r="E44" t="n">
         <v>217350000000</v>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8683,7 +8575,6 @@
       <c r="E45" t="n">
         <v>39053000000</v>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8703,7 +8594,6 @@
       <c r="E46" t="n">
         <v>15375000000</v>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8723,7 +8613,6 @@
       <c r="E47" t="n">
         <v>15375000000</v>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8743,7 +8632,6 @@
       <c r="E48" t="n">
         <v>120805000000</v>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8757,9 +8645,6 @@
       <c r="E49" t="n">
         <v>120805000000</v>
       </c>
-      <c r="F49" t="n">
-        <v>127877000000</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8779,7 +8664,6 @@
       <c r="E50" t="n">
         <v>120805000000</v>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8799,7 +8683,6 @@
       <c r="E51" t="n">
         <v>120805000000</v>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8819,7 +8702,6 @@
       <c r="E52" t="n">
         <v>42117000000</v>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8839,7 +8721,6 @@
       <c r="E53" t="n">
         <v>-72340000000</v>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8859,7 +8740,6 @@
       <c r="E54" t="n">
         <v>114457000000</v>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8879,7 +8759,6 @@
       <c r="E55" t="n">
         <v>11271000000</v>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8895,9 +8774,6 @@
       <c r="E56" t="n">
         <v>10417000000</v>
       </c>
-      <c r="F56" t="n">
-        <v>10087000000</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8917,7 +8793,6 @@
       <c r="E57" t="n">
         <v>81060000000</v>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8937,7 +8812,6 @@
       <c r="E58" t="n">
         <v>22126000000</v>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8957,7 +8831,6 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8977,7 +8850,6 @@
       <c r="E60" t="n">
         <v>135405000000</v>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8997,7 +8869,6 @@
       <c r="E61" t="n">
         <v>21223000000</v>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9017,7 +8888,6 @@
       <c r="E62" t="n">
         <v>4946000000</v>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9037,7 +8907,6 @@
       <c r="E63" t="n">
         <v>60932000000</v>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9057,7 +8926,6 @@
       <c r="E64" t="n">
         <v>32748000000</v>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9077,7 +8945,6 @@
       <c r="E65" t="n">
         <v>28184000000</v>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9097,7 +8964,6 @@
       <c r="E66" t="n">
         <v>48304000000</v>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9117,7 +8983,6 @@
       <c r="E67" t="n">
         <v>24658000000</v>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9137,7 +9002,6 @@
       <c r="E68" t="n">
         <v>23646000000</v>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9157,7 +9021,6 @@
       <c r="E69" t="n">
         <v>5100000000</v>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9177,7 +9040,6 @@
       <c r="E70" t="n">
         <v>18546000000</v>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9190,7 +9052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9206,9 +9068,6 @@
       <c r="E1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="F1" s="1" t="n">
-        <v>44469</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9228,7 +9087,6 @@
       <c r="E2" t="n">
         <v>111443000000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9248,7 +9106,6 @@
       <c r="E3" t="n">
         <v>-89402000000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9268,7 +9125,6 @@
       <c r="E4" t="n">
         <v>-9543000000</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9288,144 +9144,140 @@
       <c r="E5" t="n">
         <v>5465000000</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Issuance Of Capital Stock</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1105000000</v>
+          <t>Capital Expenditure</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-12715000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-9447000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-10959000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10708000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-12715000000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-9447000000</v>
-      </c>
+          <t>Interest Paid Supplemental Data</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>-10959000000</v>
+        <v>3803000000</v>
       </c>
       <c r="E7" t="n">
-        <v>-10708000000</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>2865000000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Interest Paid Supplemental Data</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>Income Tax Paid Supplemental Data</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43369000000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26102000000</v>
+      </c>
       <c r="D8" t="n">
-        <v>3803000000</v>
+        <v>18679000000</v>
       </c>
       <c r="E8" t="n">
-        <v>2865000000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2687000000</v>
+        <v>19573000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Income Tax Paid Supplemental Data</t>
+          <t>End Cash Position</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43369000000</v>
+        <v>35934000000</v>
       </c>
       <c r="C9" t="n">
-        <v>26102000000</v>
+        <v>29943000000</v>
       </c>
       <c r="D9" t="n">
-        <v>18679000000</v>
+        <v>30737000000</v>
       </c>
       <c r="E9" t="n">
-        <v>19573000000</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>24977000000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Beginning Cash Position</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35934000000</v>
+        <v>29943000000</v>
       </c>
       <c r="C10" t="n">
-        <v>29943000000</v>
+        <v>30737000000</v>
       </c>
       <c r="D10" t="n">
-        <v>30737000000</v>
+        <v>24977000000</v>
       </c>
       <c r="E10" t="n">
-        <v>24977000000</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>35929000000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>Changes In Cash</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29943000000</v>
+        <v>5991000000</v>
       </c>
       <c r="C11" t="n">
-        <v>30737000000</v>
+        <v>-794000000</v>
       </c>
       <c r="D11" t="n">
-        <v>24977000000</v>
+        <v>5760000000</v>
       </c>
       <c r="E11" t="n">
-        <v>35929000000</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>-10952000000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5991000000</v>
+        <v>-120686000000</v>
       </c>
       <c r="C12" t="n">
-        <v>-794000000</v>
+        <v>-121983000000</v>
       </c>
       <c r="D12" t="n">
-        <v>5760000000</v>
+        <v>-108488000000</v>
       </c>
       <c r="E12" t="n">
-        <v>-10952000000</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>-110749000000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -9440,52 +9292,49 @@
       <c r="E13" t="n">
         <v>-110749000000</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
+          <t>Net Other Financing Charges</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-120686000000</v>
+        <v>-6071000000</v>
       </c>
       <c r="C14" t="n">
-        <v>-121983000000</v>
+        <v>-5802000000</v>
       </c>
       <c r="D14" t="n">
-        <v>-108488000000</v>
+        <v>-6012000000</v>
       </c>
       <c r="E14" t="n">
-        <v>-110749000000</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>-6383000000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Cash Dividends Paid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-6071000000</v>
+        <v>-15421000000</v>
       </c>
       <c r="C15" t="n">
-        <v>-5802000000</v>
+        <v>-15234000000</v>
       </c>
       <c r="D15" t="n">
-        <v>-6012000000</v>
+        <v>-15025000000</v>
       </c>
       <c r="E15" t="n">
-        <v>-6383000000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>-14841000000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cash Dividends Paid</t>
+          <t>Common Stock Dividend Paid</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -9500,32 +9349,30 @@
       <c r="E16" t="n">
         <v>-14841000000</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Common Stock Dividend Paid</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-15421000000</v>
+        <v>-90711000000</v>
       </c>
       <c r="C17" t="n">
-        <v>-15234000000</v>
+        <v>-94949000000</v>
       </c>
       <c r="D17" t="n">
-        <v>-15025000000</v>
+        <v>-77550000000</v>
       </c>
       <c r="E17" t="n">
-        <v>-14841000000</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>-89402000000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -9540,454 +9387,430 @@
       <c r="E18" t="n">
         <v>-89402000000</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-90711000000</v>
+        <v>-8483000000</v>
       </c>
       <c r="C19" t="n">
-        <v>-94949000000</v>
+        <v>-5998000000</v>
       </c>
       <c r="D19" t="n">
-        <v>-77550000000</v>
+        <v>-9901000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-89402000000</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>-123000000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>1105000000</v>
+          <t>Net Short Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-2032000000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3960000000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-3978000000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3955000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-8483000000</v>
+        <v>-6451000000</v>
       </c>
       <c r="C21" t="n">
-        <v>-5998000000</v>
+        <v>-9958000000</v>
       </c>
       <c r="D21" t="n">
-        <v>-9901000000</v>
+        <v>-5923000000</v>
       </c>
       <c r="E21" t="n">
-        <v>-123000000</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>-4078000000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net Short Term Debt Issuance</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2032000000</v>
+        <v>-10932000000</v>
       </c>
       <c r="C22" t="n">
-        <v>3960000000</v>
+        <v>-9958000000</v>
       </c>
       <c r="D22" t="n">
-        <v>-3978000000</v>
+        <v>-11151000000</v>
       </c>
       <c r="E22" t="n">
-        <v>3955000000</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>-9543000000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-6451000000</v>
+        <v>4481000000</v>
       </c>
       <c r="C23" t="n">
-        <v>-9958000000</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-5923000000</v>
+        <v>5228000000</v>
       </c>
       <c r="E23" t="n">
-        <v>-4078000000</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>5465000000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-10932000000</v>
+        <v>15195000000</v>
       </c>
       <c r="C24" t="n">
-        <v>-9958000000</v>
+        <v>2935000000</v>
       </c>
       <c r="D24" t="n">
-        <v>-11151000000</v>
+        <v>3705000000</v>
       </c>
       <c r="E24" t="n">
-        <v>-9543000000</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>-22354000000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4481000000</v>
+        <v>15195000000</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2935000000</v>
       </c>
       <c r="D25" t="n">
-        <v>5228000000</v>
+        <v>3705000000</v>
       </c>
       <c r="E25" t="n">
-        <v>5465000000</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>-22354000000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15195000000</v>
+        <v>-1480000000</v>
       </c>
       <c r="C26" t="n">
-        <v>2935000000</v>
+        <v>-1308000000</v>
       </c>
       <c r="D26" t="n">
-        <v>3705000000</v>
+        <v>-1337000000</v>
       </c>
       <c r="E26" t="n">
-        <v>-22354000000</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>-2086000000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15195000000</v>
+        <v>29390000000</v>
       </c>
       <c r="C27" t="n">
-        <v>2935000000</v>
+        <v>13690000000</v>
       </c>
       <c r="D27" t="n">
-        <v>3705000000</v>
+        <v>16001000000</v>
       </c>
       <c r="E27" t="n">
-        <v>-22354000000</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>-9560000000</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1480000000</v>
+        <v>53797000000</v>
       </c>
       <c r="C28" t="n">
-        <v>-1308000000</v>
+        <v>62346000000</v>
       </c>
       <c r="D28" t="n">
-        <v>-1337000000</v>
+        <v>45514000000</v>
       </c>
       <c r="E28" t="n">
-        <v>-2086000000</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+        <v>67363000000</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Purchase Of Investment</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29390000000</v>
+        <v>-24407000000</v>
       </c>
       <c r="C29" t="n">
-        <v>13690000000</v>
+        <v>-48656000000</v>
       </c>
       <c r="D29" t="n">
-        <v>16001000000</v>
+        <v>-29513000000</v>
       </c>
       <c r="E29" t="n">
-        <v>-9560000000</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>-76923000000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>53797000000</v>
-      </c>
-      <c r="C30" t="n">
-        <v>62346000000</v>
-      </c>
-      <c r="D30" t="n">
-        <v>45514000000</v>
-      </c>
+          <t>Net Business Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>67363000000</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>-306000000</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>-24407000000</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-48656000000</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-29513000000</v>
-      </c>
+          <t>Purchase Of Business</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>-76923000000</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>-306000000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>Net PPE Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-12715000000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-9447000000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-10959000000</v>
+      </c>
       <c r="E32" t="n">
-        <v>-306000000</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-33000000</v>
+        <v>-10708000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>Purchase Of PPE</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-12715000000</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-9447000000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-10959000000</v>
+      </c>
       <c r="E33" t="n">
-        <v>-306000000</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-33000000</v>
+        <v>-10708000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-12715000000</v>
+        <v>111482000000</v>
       </c>
       <c r="C34" t="n">
-        <v>-9447000000</v>
+        <v>118254000000</v>
       </c>
       <c r="D34" t="n">
-        <v>-10959000000</v>
+        <v>110543000000</v>
       </c>
       <c r="E34" t="n">
-        <v>-10708000000</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>122151000000</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-12715000000</v>
+        <v>111482000000</v>
       </c>
       <c r="C35" t="n">
-        <v>-9447000000</v>
+        <v>118254000000</v>
       </c>
       <c r="D35" t="n">
-        <v>-10959000000</v>
+        <v>110543000000</v>
       </c>
       <c r="E35" t="n">
-        <v>-10708000000</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>122151000000</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>111482000000</v>
+        <v>-25000000000</v>
       </c>
       <c r="C36" t="n">
-        <v>118254000000</v>
+        <v>3651000000</v>
       </c>
       <c r="D36" t="n">
-        <v>110543000000</v>
+        <v>-6577000000</v>
       </c>
       <c r="E36" t="n">
-        <v>122151000000</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>1200000000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>111482000000</v>
-      </c>
-      <c r="C37" t="n">
-        <v>118254000000</v>
-      </c>
-      <c r="D37" t="n">
-        <v>110543000000</v>
-      </c>
+          <t>Change In Other Working Capital</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>122151000000</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>478000000</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Change In Other Current Liabilities</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-25000000000</v>
+        <v>-11076000000</v>
       </c>
       <c r="C38" t="n">
-        <v>3651000000</v>
+        <v>15552000000</v>
       </c>
       <c r="D38" t="n">
-        <v>-6577000000</v>
+        <v>3031000000</v>
       </c>
       <c r="E38" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>6110000000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>Change In Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-9197000000</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-11731000000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-5684000000</v>
+      </c>
       <c r="E39" t="n">
-        <v>478000000</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1676000000</v>
+        <v>-6499000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Other Current Liabilities</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-11076000000</v>
+        <v>902000000</v>
       </c>
       <c r="C40" t="n">
-        <v>15552000000</v>
+        <v>6020000000</v>
       </c>
       <c r="D40" t="n">
-        <v>3031000000</v>
+        <v>-1889000000</v>
       </c>
       <c r="E40" t="n">
-        <v>6110000000</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>9448000000</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Other Current Assets</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-9197000000</v>
+        <v>902000000</v>
       </c>
       <c r="C41" t="n">
-        <v>-11731000000</v>
+        <v>6020000000</v>
       </c>
       <c r="D41" t="n">
-        <v>-5684000000</v>
+        <v>-1889000000</v>
       </c>
       <c r="E41" t="n">
-        <v>-6499000000</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>9448000000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -10002,239 +9825,184 @@
       <c r="E42" t="n">
         <v>9448000000</v>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>902000000</v>
+        <v>1400000000</v>
       </c>
       <c r="C43" t="n">
-        <v>6020000000</v>
+        <v>-1046000000</v>
       </c>
       <c r="D43" t="n">
-        <v>-1889000000</v>
+        <v>-1618000000</v>
       </c>
       <c r="E43" t="n">
-        <v>9448000000</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
+        <v>1484000000</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>902000000</v>
+        <v>-7029000000</v>
       </c>
       <c r="C44" t="n">
-        <v>6020000000</v>
+        <v>-5144000000</v>
       </c>
       <c r="D44" t="n">
-        <v>-1889000000</v>
+        <v>-417000000</v>
       </c>
       <c r="E44" t="n">
-        <v>9448000000</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
+        <v>-9343000000</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1400000000</v>
+        <v>-6682000000</v>
       </c>
       <c r="C45" t="n">
-        <v>-1046000000</v>
+        <v>-3788000000</v>
       </c>
       <c r="D45" t="n">
-        <v>-1618000000</v>
+        <v>-1688000000</v>
       </c>
       <c r="E45" t="n">
-        <v>1484000000</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
+        <v>-1823000000</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-7029000000</v>
+        <v>-89000000</v>
       </c>
       <c r="C46" t="n">
-        <v>-5144000000</v>
+        <v>-2266000000</v>
       </c>
       <c r="D46" t="n">
-        <v>-417000000</v>
+        <v>-2227000000</v>
       </c>
       <c r="E46" t="n">
-        <v>-9343000000</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+        <v>1006000000</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-6682000000</v>
+        <v>12863000000</v>
       </c>
       <c r="C47" t="n">
-        <v>-3788000000</v>
+        <v>11688000000</v>
       </c>
       <c r="D47" t="n">
-        <v>-1688000000</v>
+        <v>10833000000</v>
       </c>
       <c r="E47" t="n">
-        <v>-1823000000</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
+        <v>9038000000</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>-89000000</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-2266000000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-2227000000</v>
-      </c>
+          <t>Deferred Tax</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1006000000</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
+        <v>895000000</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>12863000000</v>
-      </c>
-      <c r="C49" t="n">
-        <v>11688000000</v>
-      </c>
-      <c r="D49" t="n">
-        <v>10833000000</v>
-      </c>
+          <t>Deferred Income Tax</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>9038000000</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+        <v>895000000</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>Depreciation Amortization Depletion</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>11698000000</v>
+      </c>
+      <c r="C50" t="n">
+        <v>11445000000</v>
+      </c>
+      <c r="D50" t="n">
+        <v>11519000000</v>
+      </c>
       <c r="E50" t="n">
-        <v>895000000</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-4774000000</v>
+        <v>11104000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>Depreciation And Amortization</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>11698000000</v>
+      </c>
+      <c r="C51" t="n">
+        <v>11445000000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>11519000000</v>
+      </c>
       <c r="E51" t="n">
-        <v>895000000</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-4774000000</v>
+        <v>11104000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Net Income From Continuing Operations</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11698000000</v>
+        <v>112010000000</v>
       </c>
       <c r="C52" t="n">
-        <v>11445000000</v>
+        <v>93736000000</v>
       </c>
       <c r="D52" t="n">
-        <v>11519000000</v>
+        <v>96995000000</v>
       </c>
       <c r="E52" t="n">
-        <v>11104000000</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Depreciation And Amortization</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>11698000000</v>
-      </c>
-      <c r="C53" t="n">
-        <v>11445000000</v>
-      </c>
-      <c r="D53" t="n">
-        <v>11519000000</v>
-      </c>
-      <c r="E53" t="n">
-        <v>11104000000</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Net Income From Continuing Operations</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>112010000000</v>
-      </c>
-      <c r="C54" t="n">
-        <v>93736000000</v>
-      </c>
-      <c r="D54" t="n">
-        <v>96995000000</v>
-      </c>
-      <c r="E54" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +10015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10288,12 +10056,6 @@
       <c r="B5" t="n">
         <v>99803000000</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10498,37 +10260,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>329.4</v>
+      </c>
+      <c r="D2" t="n">
         <v>338.4</v>
       </c>
-      <c r="D2" t="n">
-        <v>341.07</v>
-      </c>
       <c r="E2" t="n">
-        <v>340.37</v>
+        <v>337.06</v>
       </c>
       <c r="F2" t="n">
-        <v>342.988</v>
+        <v>337.06</v>
       </c>
       <c r="G2" t="n">
-        <v>338.04</v>
+        <v>328.7</v>
       </c>
       <c r="H2" t="n">
-        <v>32463830</v>
+        <v>37773928</v>
       </c>
       <c r="I2" t="n">
-        <v>47555262</v>
+        <v>46833855</v>
       </c>
       <c r="J2" t="n">
-        <v>4938670276608</v>
+        <v>4807323025408</v>
       </c>
       <c r="K2" t="n">
-        <v>39.076214</v>
+        <v>38.75294</v>
       </c>
       <c r="L2" t="n">
-        <v>35.303875</v>
+        <v>34.36494</v>
       </c>
       <c r="M2" t="n">
-        <v>8.66</v>
+        <v>8.5</v>
       </c>
       <c r="N2" t="n">
         <v>345.34</v>
@@ -10564,7 +10326,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.97826</v>
+        <v>44.755432</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10576,7 +10338,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4960615399424</v>
+        <v>4829268148224</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10603,7 +10365,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24:18</t>
+          <t>2026-09-30 16:06:43</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>253.9220050782957</v>
+        <v>254.101347229275</v>
       </c>
       <c r="C2" t="n">
-        <v>254.9781013853334</v>
+        <v>257.8375609779932</v>
       </c>
       <c r="D2" t="n">
-        <v>252.1784458386236</v>
+        <v>253.9917514638179</v>
       </c>
       <c r="E2" t="n">
-        <v>253.6928558349609</v>
+        <v>254.5098419189453</v>
       </c>
       <c r="F2" t="n">
-        <v>37704300</v>
+        <v>48713900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356607808825</v>
       </c>
       <c r="C3" t="n">
-        <v>257.8375609779932</v>
+        <v>257.229778167004</v>
       </c>
       <c r="D3" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146115335708</v>
       </c>
       <c r="E3" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836547851562</v>
       </c>
       <c r="F3" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>255.6356912331815</v>
+        <v>253.7326818586438</v>
       </c>
       <c r="C4" t="n">
-        <v>257.2298088092003</v>
+        <v>258.2858540075867</v>
       </c>
       <c r="D4" t="n">
-        <v>253.2146416974651</v>
+        <v>253.0153306119951</v>
       </c>
       <c r="E4" t="n">
-        <v>256.1836853027344</v>
+        <v>257.0703430175781</v>
       </c>
       <c r="F4" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0404730386864</v>
       </c>
       <c r="C5" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165151882718</v>
       </c>
       <c r="D5" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113063083761</v>
       </c>
       <c r="E5" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7452697753906</v>
       </c>
       <c r="F5" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>257.0404730386864</v>
+        <v>255.8648591580886</v>
       </c>
       <c r="C6" t="n">
-        <v>258.1165151882718</v>
+        <v>256.4526841311554</v>
       </c>
       <c r="D6" t="n">
-        <v>254.1113063083761</v>
+        <v>254.4899331102905</v>
       </c>
       <c r="E6" t="n">
-        <v>255.7452697753906</v>
+        <v>255.5360870361328</v>
       </c>
       <c r="F6" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>255.8648438796676</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C7" t="n">
-        <v>256.4526688176338</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D7" t="n">
-        <v>254.4899179139702</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E7" t="n">
-        <v>255.5360717773438</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F7" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>255.5758888188916</v>
+        <v>256.8611554198282</v>
       </c>
       <c r="C8" t="n">
-        <v>257.5685279874928</v>
+        <v>257.0504585775582</v>
       </c>
       <c r="D8" t="n">
-        <v>255.1673941406971</v>
+        <v>252.2083446799687</v>
       </c>
       <c r="E8" t="n">
-        <v>257.1102294921875</v>
+        <v>253.1050262451172</v>
       </c>
       <c r="F8" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>256.8611709050607</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C9" t="n">
-        <v>257.0504740742031</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D9" t="n">
-        <v>252.2083598847001</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E9" t="n">
-        <v>253.1050415039062</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F9" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C10" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D10" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E10" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F10" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C11" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D11" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E11" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F11" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>245.6924316138584</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C12" t="n">
-        <v>247.9341508249242</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D12" t="n">
-        <v>243.7994151584908</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E12" t="n">
-        <v>246.8581237792969</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F12" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>248.571774561702</v>
+        <v>247.3363501327598</v>
       </c>
       <c r="C13" t="n">
-        <v>250.8932009800968</v>
+        <v>248.1234359576197</v>
       </c>
       <c r="D13" t="n">
-        <v>246.5592047770515</v>
+        <v>244.2278377270511</v>
       </c>
       <c r="E13" t="n">
-        <v>248.4223175048828</v>
+        <v>246.5392913818359</v>
       </c>
       <c r="F13" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>247.3363501327598</v>
+        <v>247.1072067041429</v>
       </c>
       <c r="C14" t="n">
-        <v>248.1234359576197</v>
+        <v>252.4474806979352</v>
       </c>
       <c r="D14" t="n">
-        <v>244.2278377270511</v>
+        <v>246.3599669580113</v>
       </c>
       <c r="E14" t="n">
-        <v>246.5392913818359</v>
+        <v>251.3614807128906</v>
       </c>
       <c r="F14" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>247.1072067041429</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C15" t="n">
-        <v>252.4474806979352</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D15" t="n">
-        <v>246.3599669580113</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E15" t="n">
-        <v>251.3614807128906</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F15" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C16" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D16" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E16" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F16" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>260.916147926868</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C17" t="n">
-        <v>264.313600971564</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D17" t="n">
-        <v>260.8663137101643</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E17" t="n">
-        <v>261.8028564453125</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F17" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>261.6833028295614</v>
+        <v>258.9833246632869</v>
       </c>
       <c r="C18" t="n">
-        <v>261.882578885752</v>
+        <v>259.6608147081683</v>
       </c>
       <c r="D18" t="n">
-        <v>254.4898750367867</v>
+        <v>257.0604350924048</v>
       </c>
       <c r="E18" t="n">
-        <v>257.498779296875</v>
+        <v>258.6246337890625</v>
       </c>
       <c r="F18" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>258.9832941033833</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C19" t="n">
-        <v>259.6607840683213</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D19" t="n">
-        <v>257.0604047594014</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E19" t="n">
-        <v>258.6246032714844</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F19" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>260.2287466983284</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C20" t="n">
-        <v>263.1579290692685</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D20" t="n">
-        <v>258.2261343576155</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E20" t="n">
-        <v>261.8527526855469</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F20" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>263.9051799132</v>
+        <v>267.9999758056659</v>
       </c>
       <c r="C21" t="n">
-        <v>268.1295659182063</v>
+        <v>268.896687690681</v>
       </c>
       <c r="D21" t="n">
-        <v>263.6760154250923</v>
+        <v>267.1630710642092</v>
       </c>
       <c r="E21" t="n">
-        <v>267.8207092285156</v>
+        <v>268.0099487304688</v>
       </c>
       <c r="F21" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>268.0000063221084</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C22" t="n">
-        <v>268.8967183092298</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D22" t="n">
-        <v>267.1631014853557</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E22" t="n">
-        <v>268.0099792480469</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F22" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>268.2889603375268</v>
+        <v>270.9889785237465</v>
       </c>
       <c r="C23" t="n">
-        <v>270.4111261059246</v>
+        <v>273.131090148023</v>
       </c>
       <c r="D23" t="n">
-        <v>266.126933268734</v>
+        <v>267.4919171420091</v>
       </c>
       <c r="E23" t="n">
-        <v>268.7074279785156</v>
+        <v>270.4011535644531</v>
       </c>
       <c r="F23" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>270.9889785237465</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C24" t="n">
-        <v>273.131090148023</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D24" t="n">
-        <v>267.4919171420091</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E24" t="n">
-        <v>270.4011535644531</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F24" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>275.9705701844509</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C25" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D25" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E25" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F25" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>269.424736694289</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C26" t="n">
-        <v>269.8531467885877</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D26" t="n">
-        <v>265.2700709373508</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E26" t="n">
-        <v>268.0597534179688</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F26" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C27" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D27" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E27" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F27" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C28" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D28" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E28" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F28" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8069946610708</v>
       </c>
       <c r="C29" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878509444664</v>
       </c>
       <c r="D29" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881477280068</v>
       </c>
       <c r="E29" t="n">
-        <v>268.7771301269531</v>
+        <v>267.4819030761719</v>
       </c>
       <c r="F29" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,25 +1197,25 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C30" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D30" t="n">
-        <v>265.7881780523408</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E30" t="n">
-        <v>267.48193359375</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F30" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1223,25 +1223,25 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>268.2298830249396</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C31" t="n">
-        <v>272.9869540449525</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D31" t="n">
-        <v>266.7339548671466</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E31" t="n">
-        <v>268.6986083984375</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F31" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G31" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>269.0776024957972</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C32" t="n">
-        <v>275.1610502271484</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D32" t="n">
-        <v>269.067619901526</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E32" t="n">
-        <v>274.5028381347656</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F32" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>274.253476009827</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C33" t="n">
-        <v>274.9815052844664</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D33" t="n">
-        <v>270.9624464716027</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E33" t="n">
-        <v>272.7276306152344</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F33" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C34" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D34" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E34" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F34" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0903024129557</v>
       </c>
       <c r="C35" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557521979796</v>
       </c>
       <c r="D35" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086937896775</v>
       </c>
       <c r="E35" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339782714844</v>
       </c>
       <c r="F35" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>268.0902717401977</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C36" t="n">
-        <v>269.7557213346742</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D36" t="n">
-        <v>265.0086634694927</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E36" t="n">
-        <v>266.7339477539062</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F36" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>269.2570854665072</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C37" t="n">
-        <v>269.9751321987233</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D37" t="n">
-        <v>264.5997795179588</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E37" t="n">
-        <v>266.7140197753906</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F37" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>264.8091896065648</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C38" t="n">
-        <v>271.4710487380511</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D38" t="n">
-        <v>264.7792722621166</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E38" t="n">
-        <v>267.8309631347656</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F38" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C39" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D39" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E39" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F39" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>265.22808167538</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C40" t="n">
-        <v>272.5880228442522</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D40" t="n">
-        <v>264.9488429624803</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E40" t="n">
-        <v>270.7530212402344</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F40" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C41" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D41" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E41" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F41" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C42" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D42" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E42" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F42" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C43" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D43" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E43" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F43" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>276.5073375714406</v>
+        <v>277.255303275414</v>
       </c>
       <c r="C44" t="n">
-        <v>278.2426042891834</v>
+        <v>282.650620542313</v>
       </c>
       <c r="D44" t="n">
-        <v>275.2407657367699</v>
+        <v>275.390384584981</v>
       </c>
       <c r="E44" t="n">
-        <v>278.093017578125</v>
+        <v>282.3314819335938</v>
       </c>
       <c r="F44" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>277.255303275414</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C45" t="n">
-        <v>282.650620542313</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D45" t="n">
-        <v>275.390384584981</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E45" t="n">
-        <v>282.3314819335938</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F45" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C46" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D46" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E46" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F46" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>285.4231155973949</v>
+        <v>283.328813896664</v>
       </c>
       <c r="C47" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9571086251454</v>
       </c>
       <c r="D47" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337611056945</v>
       </c>
       <c r="E47" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380493164062</v>
       </c>
       <c r="F47" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>283.328813896664</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C48" t="n">
-        <v>283.9571086251454</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D48" t="n">
-        <v>277.8337611056945</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E48" t="n">
-        <v>279.9380493164062</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F48" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>279.7784866384076</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C49" t="n">
-        <v>280.3768640337962</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D49" t="n">
-        <v>277.2952250127556</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E49" t="n">
-        <v>278.0232543945312</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F49" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C50" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D50" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E50" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F50" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>277.4049325131135</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C51" t="n">
-        <v>279.2698514894354</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D51" t="n">
-        <v>276.16830825817</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E51" t="n">
-        <v>276.4275817871094</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F51" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>276.9960515324306</v>
+        <v>278.342340640522</v>
       </c>
       <c r="C52" t="n">
-        <v>278.9906225605669</v>
+        <v>278.8310007112651</v>
       </c>
       <c r="D52" t="n">
-        <v>275.6896099437804</v>
+        <v>273.0666927429874</v>
       </c>
       <c r="E52" t="n">
-        <v>278.0232543945312</v>
+        <v>277.2752380371094</v>
       </c>
       <c r="F52" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>278.342340640522</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C53" t="n">
-        <v>278.8310007112651</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D53" t="n">
-        <v>273.0666927429874</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E53" t="n">
-        <v>277.2752380371094</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F53" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C54" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D54" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E54" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F54" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C55" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D55" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E55" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F55" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634896625032</v>
       </c>
       <c r="C56" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103618778425</v>
       </c>
       <c r="D56" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026424636208</v>
       </c>
       <c r="E56" t="n">
-        <v>273.8645324707031</v>
+        <v>271.1020812988281</v>
       </c>
       <c r="F56" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>274.2634587890498</v>
+        <v>272.8672390402853</v>
       </c>
       <c r="C57" t="n">
-        <v>275.4103308752873</v>
+        <v>272.8872042261758</v>
       </c>
       <c r="D57" t="n">
-        <v>270.9026119684932</v>
+        <v>266.2253451719176</v>
       </c>
       <c r="E57" t="n">
-        <v>271.10205078125</v>
+        <v>271.4511108398438</v>
       </c>
       <c r="F57" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>272.8672390402853</v>
+        <v>271.4112610007817</v>
       </c>
       <c r="C58" t="n">
-        <v>272.8872042261758</v>
+        <v>273.854622814086</v>
       </c>
       <c r="D58" t="n">
-        <v>266.2253451719176</v>
+        <v>269.1673684747946</v>
       </c>
       <c r="E58" t="n">
-        <v>271.4511108398438</v>
+        <v>272.9271545410156</v>
       </c>
       <c r="F58" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>271.4112306527045</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C59" t="n">
-        <v>273.8545921928022</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D59" t="n">
-        <v>269.1673383776201</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E59" t="n">
-        <v>272.9271240234375</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F59" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>272.1193204151364</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C60" t="n">
-        <v>273.1365711538121</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D60" t="n">
-        <v>269.775723721713</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E60" t="n">
-        <v>270.2344665527344</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F60" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C61" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D61" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E61" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F61" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>271.6007310322557</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C62" t="n">
-        <v>274.6823395934045</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D62" t="n">
-        <v>271.4611268874897</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E62" t="n">
-        <v>273.0667419433594</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F62" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>273.4157529954652</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C63" t="n">
-        <v>274.6224597374741</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D63" t="n">
-        <v>272.1192637901173</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E63" t="n">
-        <v>272.6578063964844</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F63" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C64" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D64" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E64" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F64" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C65" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D65" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E65" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F65" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C66" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D66" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E66" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F66" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>271.5209292436991</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C67" t="n">
-        <v>277.0857683126949</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D67" t="n">
-        <v>268.2697691424855</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E67" t="n">
-        <v>270.2743225097656</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F67" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>269.9053450243044</v>
+        <v>266.2751846804448</v>
       </c>
       <c r="C68" t="n">
-        <v>270.7729784841199</v>
+        <v>266.8236794412865</v>
       </c>
       <c r="D68" t="n">
-        <v>265.4175605620285</v>
+        <v>261.4084273717842</v>
       </c>
       <c r="E68" t="n">
-        <v>266.5345153808594</v>
+        <v>261.6477661132812</v>
       </c>
       <c r="F68" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>266.275215737747</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C69" t="n">
-        <v>266.8237105625631</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D69" t="n">
-        <v>261.4084578614468</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E69" t="n">
-        <v>261.6477966308594</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F69" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>262.4855256371837</v>
+        <v>256.3223167721599</v>
       </c>
       <c r="C70" t="n">
-        <v>262.964203143993</v>
+        <v>258.5861744106298</v>
       </c>
       <c r="D70" t="n">
-        <v>259.1047135716701</v>
+        <v>255.005907781442</v>
       </c>
       <c r="E70" t="n">
-        <v>259.623291015625</v>
+        <v>258.3368530273438</v>
       </c>
       <c r="F70" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>256.3223167721599</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C71" t="n">
-        <v>258.5861744106298</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D71" t="n">
-        <v>255.005907781442</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E71" t="n">
-        <v>258.3368530273438</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F71" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C72" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D72" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E72" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F72" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C73" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D73" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E73" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F73" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>258.0176775418968</v>
+        <v>258.7856080874888</v>
       </c>
       <c r="C74" t="n">
-        <v>261.0992857475004</v>
+        <v>261.1093003767552</v>
       </c>
       <c r="D74" t="n">
-        <v>257.6885867541948</v>
+        <v>256.0131555781144</v>
       </c>
       <c r="E74" t="n">
-        <v>260.3413391113281</v>
+        <v>259.2543334960938</v>
       </c>
       <c r="F74" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>258.7856080874888</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C75" t="n">
-        <v>261.1093003767552</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D75" t="n">
-        <v>256.0131555781144</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E75" t="n">
-        <v>259.2543334960938</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F75" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1999265314624</v>
       </c>
       <c r="C76" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1972120398704</v>
       </c>
       <c r="D76" t="n">
-        <v>256.3522089636155</v>
+        <v>254.2379873541013</v>
       </c>
       <c r="E76" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363647460938</v>
       </c>
       <c r="F76" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>257.1999111311508</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C77" t="n">
-        <v>258.1971965798445</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D77" t="n">
-        <v>254.2379721311412</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E77" t="n">
-        <v>254.8363494873047</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F77" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0249055239374</v>
       </c>
       <c r="C78" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771427168815</v>
       </c>
       <c r="D78" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144562363057</v>
       </c>
       <c r="E78" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777526855469</v>
       </c>
       <c r="F78" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>248.0249055239374</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C79" t="n">
-        <v>250.8771427168815</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D79" t="n">
-        <v>244.5144562363057</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E79" t="n">
-        <v>246.9777526855469</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F79" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486524137701</v>
       </c>
       <c r="C80" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329754164565</v>
       </c>
       <c r="D80" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0158041358057</v>
       </c>
       <c r="E80" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666839599609</v>
       </c>
       <c r="F80" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>246.6486524137701</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C81" t="n">
-        <v>248.7329754164565</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D81" t="n">
-        <v>244.0158041358057</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E81" t="n">
-        <v>247.3666839599609</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F81" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C82" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D82" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E82" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F82" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>258.4664593428383</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C83" t="n">
-        <v>261.2389114176715</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D83" t="n">
-        <v>257.5090434871919</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E83" t="n">
-        <v>257.5688781738281</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F83" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996187429542</v>
       </c>
       <c r="C84" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451334735496</v>
       </c>
       <c r="D84" t="n">
-        <v>253.8191124091609</v>
+        <v>253.719368010288</v>
       </c>
       <c r="E84" t="n">
-        <v>255.7438812255859</v>
+        <v>257.578857421875</v>
       </c>
       <c r="F84" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>257.2996492274485</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C85" t="n">
-        <v>258.9451641530022</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D85" t="n">
-        <v>253.7193980705993</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E85" t="n">
-        <v>257.5788879394531</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F85" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C86" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D86" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E86" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F86" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C87" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D87" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E87" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F87" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="C88" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927850076088</v>
       </c>
       <c r="D88" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="E88" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394409179688</v>
       </c>
       <c r="F88" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>271.5508603406617</v>
+        <v>277.3749854862336</v>
       </c>
       <c r="C89" t="n">
-        <v>278.1927850076088</v>
+        <v>278.7412615768201</v>
       </c>
       <c r="D89" t="n">
-        <v>271.5508603406617</v>
+        <v>272.4882932485779</v>
       </c>
       <c r="E89" t="n">
-        <v>275.7394409179688</v>
+        <v>275.1610107421875</v>
       </c>
       <c r="F89" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>277.3749854862336</v>
+        <v>276.3677657232236</v>
       </c>
       <c r="C90" t="n">
-        <v>278.7412615768201</v>
+        <v>280.1474864654567</v>
       </c>
       <c r="D90" t="n">
-        <v>272.4882932485779</v>
+        <v>276.1782790346459</v>
       </c>
       <c r="E90" t="n">
-        <v>275.1610107421875</v>
+        <v>277.3650512695312</v>
       </c>
       <c r="F90" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,25 +2783,25 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>276.3677353153735</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C91" t="n">
-        <v>280.1474556417363</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D91" t="n">
-        <v>276.1782486476445</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E91" t="n">
-        <v>277.3650207519531</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F91" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -2809,25 +2809,25 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C92" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D92" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E92" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F92" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G92" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C93" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D93" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E93" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F93" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990585104662</v>
       </c>
       <c r="C94" t="n">
-        <v>279.6808719096702</v>
+        <v>275.2288318017276</v>
       </c>
       <c r="D94" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165063299744</v>
       </c>
       <c r="E94" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637634277344</v>
       </c>
       <c r="F94" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>275.0990585104662</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C95" t="n">
-        <v>275.2288318017276</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D95" t="n">
-        <v>259.7165063299744</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E95" t="n">
-        <v>261.2637634277344</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F95" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C96" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D96" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E96" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F96" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C97" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D97" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E97" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F97" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C98" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D98" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E98" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F98" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C99" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D99" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E99" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F99" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C100" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D100" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E100" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F100" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C101" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D101" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E101" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F101" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C102" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D102" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E102" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F102" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C103" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D103" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E103" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F103" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="C104" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="D104" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217314181026</v>
       </c>
       <c r="E104" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7094116210938</v>
       </c>
       <c r="F104" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>272.3240439665745</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C105" t="n">
-        <v>272.3240439665745</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D105" t="n">
-        <v>262.4217314181026</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E105" t="n">
-        <v>263.7094116210938</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F105" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C106" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D106" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E106" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F106" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C107" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D107" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E107" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F107" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C108" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D108" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E108" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F108" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C109" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D109" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E109" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F109" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C110" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D110" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E110" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F110" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C111" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D111" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E111" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F111" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>257.1910284571696</v>
+        <v>260.624897946549</v>
       </c>
       <c r="C112" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630538494394</v>
       </c>
       <c r="D112" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876327296249</v>
       </c>
       <c r="E112" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453979492188</v>
       </c>
       <c r="F112" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>260.624897946549</v>
+        <v>258.1992408199258</v>
       </c>
       <c r="C113" t="n">
-        <v>261.6630538494394</v>
+        <v>258.4887327594216</v>
       </c>
       <c r="D113" t="n">
-        <v>259.0876327296249</v>
+        <v>253.7272102811576</v>
       </c>
       <c r="E113" t="n">
-        <v>260.3453979492188</v>
+        <v>255.3043975830078</v>
       </c>
       <c r="F113" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>258.1992408199258</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C114" t="n">
-        <v>258.4887327594216</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D114" t="n">
-        <v>253.7272102811576</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E114" t="n">
-        <v>255.3043975830078</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F114" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C115" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D115" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E115" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F115" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C116" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D116" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E116" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F116" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C117" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D117" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E117" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F117" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C118" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D118" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E118" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F118" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C119" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D119" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E119" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F119" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C120" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D120" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E120" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F120" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C121" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D121" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E121" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F121" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C122" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D122" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E122" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F122" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C123" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D123" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E123" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F123" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C124" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D124" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E124" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F124" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C125" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D125" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E125" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F125" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683905467953</v>
       </c>
       <c r="C126" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248978486836</v>
       </c>
       <c r="D126" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598358728773</v>
       </c>
       <c r="E126" t="n">
-        <v>246.1906585693359</v>
+        <v>253.3379058837891</v>
       </c>
       <c r="F126" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>247.4683905467953</v>
+        <v>253.6273948962928</v>
       </c>
       <c r="C127" t="n">
-        <v>255.0248978486836</v>
+        <v>255.7236449097363</v>
       </c>
       <c r="D127" t="n">
-        <v>246.6598358728773</v>
+        <v>252.8787309132899</v>
       </c>
       <c r="E127" t="n">
-        <v>253.3379058837891</v>
+        <v>255.1746368408203</v>
       </c>
       <c r="F127" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>253.6273948962928</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C128" t="n">
-        <v>255.7236449097363</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D128" t="n">
-        <v>252.8787309132899</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E128" t="n">
-        <v>255.1746368408203</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F128" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>253.7471740568136</v>
+        <v>256.0530752925303</v>
       </c>
       <c r="C129" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6930045642991</v>
       </c>
       <c r="D129" t="n">
-        <v>250.2034948550391</v>
+        <v>256.0031460821725</v>
       </c>
       <c r="E129" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988647460938</v>
       </c>
       <c r="F129" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>256.0530752925303</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C130" t="n">
-        <v>261.6930045642991</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D130" t="n">
-        <v>256.0031460821725</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E130" t="n">
-        <v>258.3988647460938</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F130" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896321241455</v>
       </c>
       <c r="C131" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2873042333858</v>
       </c>
       <c r="D131" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730388391825</v>
       </c>
       <c r="E131" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4388122558594</v>
       </c>
       <c r="F131" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>257.9896321241455</v>
+        <v>258.5386343954405</v>
       </c>
       <c r="C132" t="n">
-        <v>259.2873042333858</v>
+        <v>260.6548530924392</v>
       </c>
       <c r="D132" t="n">
-        <v>256.0730388391825</v>
+        <v>255.6138610163474</v>
       </c>
       <c r="E132" t="n">
-        <v>258.4388122558594</v>
+        <v>260.0259704589844</v>
       </c>
       <c r="F132" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>258.5386343954405</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C133" t="n">
-        <v>260.6548530924392</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D133" t="n">
-        <v>255.6138610163474</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E133" t="n">
-        <v>260.0259704589844</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F133" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C134" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D134" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E134" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F134" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881922504944</v>
       </c>
       <c r="C135" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4634109961452</v>
       </c>
       <c r="D135" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318642110386</v>
       </c>
       <c r="E135" t="n">
-        <v>258.73828125</v>
+        <v>258.3689270019531</v>
       </c>
       <c r="F135" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>258.7881922504944</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C136" t="n">
-        <v>261.4634109961452</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D136" t="n">
-        <v>256.7318642110386</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E136" t="n">
-        <v>258.3689270019531</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F136" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3247234477873</v>
       </c>
       <c r="C137" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840980024072</v>
       </c>
       <c r="D137" t="n">
-        <v>257.3507435512608</v>
+        <v>260.8045755356903</v>
       </c>
       <c r="E137" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307861328125</v>
       </c>
       <c r="F137" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>266.3247234477873</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C138" t="n">
-        <v>266.6840980024072</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D138" t="n">
-        <v>260.8045755356903</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E138" t="n">
-        <v>262.9307861328125</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F138" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C139" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D139" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E139" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F139" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C140" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D140" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E140" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F140" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C141" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D141" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E141" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F141" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C142" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D142" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E142" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F142" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C143" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D143" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E143" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F143" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C144" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D144" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E144" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F144" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C145" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D145" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E145" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F145" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C146" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D146" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E146" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F146" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C147" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D147" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E147" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F147" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632420760759</v>
       </c>
       <c r="C148" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083659496485</v>
       </c>
       <c r="D148" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8741246788477</v>
       </c>
       <c r="E148" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409912109375</v>
       </c>
       <c r="F148" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>278.3632420760759</v>
+        <v>279.1617980116577</v>
       </c>
       <c r="C149" t="n">
-        <v>286.7083659496485</v>
+        <v>280.1300712051751</v>
       </c>
       <c r="D149" t="n">
-        <v>277.8741246788477</v>
+        <v>274.3703307853319</v>
       </c>
       <c r="E149" t="n">
-        <v>279.6409912109375</v>
+        <v>276.3368225097656</v>
       </c>
       <c r="F149" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>279.1617980116577</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C150" t="n">
-        <v>280.1300712051751</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D150" t="n">
-        <v>274.3703307853319</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E150" t="n">
-        <v>276.3368225097656</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F150" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>276.43668191704</v>
+        <v>281.4178249779708</v>
       </c>
       <c r="C151" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5169265187869</v>
       </c>
       <c r="D151" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693330033821</v>
       </c>
       <c r="E151" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978637695312</v>
       </c>
       <c r="F151" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>281.4178249779708</v>
+        <v>288.7547052879293</v>
       </c>
       <c r="C152" t="n">
-        <v>287.5169265187869</v>
+        <v>291.6096265406606</v>
       </c>
       <c r="D152" t="n">
-        <v>280.5693330033821</v>
+        <v>285.2709318587503</v>
       </c>
       <c r="E152" t="n">
-        <v>286.9978637695312</v>
+        <v>286.927978515625</v>
       </c>
       <c r="F152" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>288.7547052879293</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C153" t="n">
-        <v>291.6096265406606</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D153" t="n">
-        <v>285.2709318587503</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E153" t="n">
-        <v>286.927978515625</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F153" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,25 +4421,25 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C154" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D154" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E154" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F154" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4447,25 +4447,25 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C155" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D155" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E155" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F155" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G155" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C156" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D156" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E156" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F156" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C157" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D157" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E157" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F157" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C158" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D158" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E158" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F158" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C159" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D159" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E159" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F159" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C160" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D160" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E160" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F160" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C161" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D161" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E161" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F161" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C162" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D162" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E162" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F162" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C163" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D163" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E163" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F163" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C164" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D164" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E164" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F164" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C165" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D165" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E165" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F165" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C166" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D166" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E166" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F166" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C167" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D167" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E167" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F167" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C168" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D168" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E168" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F168" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C169" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D169" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E169" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F169" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C170" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D170" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E170" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F170" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C171" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D171" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E171" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F171" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C172" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D172" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E172" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F172" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C173" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D173" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E173" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F173" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C174" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D174" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E174" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F174" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C175" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D175" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E175" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F175" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C176" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D176" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E176" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F176" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C177" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D177" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E177" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F177" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C178" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D178" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E178" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F178" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C179" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D179" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E179" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F179" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C180" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D180" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E180" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F180" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C181" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D181" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E181" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F181" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C182" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D182" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E182" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F182" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C183" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D183" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E183" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F183" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C184" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D184" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E184" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F184" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C185" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D185" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E185" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F185" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C186" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D186" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E186" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F186" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C187" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D187" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E187" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F187" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C188" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D188" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E188" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F188" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C189" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D189" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E189" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F189" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C190" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D190" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E190" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F190" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C191" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D191" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E191" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F191" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C192" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D192" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E192" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F192" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C193" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D193" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E193" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F193" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C194" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D194" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E194" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F194" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C195" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D195" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E195" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F195" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C196" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D196" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E196" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F196" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C197" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D197" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E197" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F197" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C198" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D198" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E198" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F198" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C199" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D199" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E199" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F199" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C200" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D200" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E200" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F200" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C201" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D201" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E201" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F201" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C202" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D202" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E202" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F202" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C203" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D203" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E203" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F203" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C204" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D204" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E204" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F204" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C205" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D205" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E205" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F205" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C206" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D206" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E206" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F206" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C207" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D207" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E207" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F207" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C208" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D208" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E208" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F208" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C209" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D209" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E209" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F209" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C210" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D210" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E210" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F210" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C211" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D211" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E211" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F211" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C212" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D212" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E212" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F212" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C213" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D213" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E213" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F213" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C214" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D214" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E214" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F214" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C215" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D215" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E215" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F215" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,25 +6033,25 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C216" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D216" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E216" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F216" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6059,25 +6059,25 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C217" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D217" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E217" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F217" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G217" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C218" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D218" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E218" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F218" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C219" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D219" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E219" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F219" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C220" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D220" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E220" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F220" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C221" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D221" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E221" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F221" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C222" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D222" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E222" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F222" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C223" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D223" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E223" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F223" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C224" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D224" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E224" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F224" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C225" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D225" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E225" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F225" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C226" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D226" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E226" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F226" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C227" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D227" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E227" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F227" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C228" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D228" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F228" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C229" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D229" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E229" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F229" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C230" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D230" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E230" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F230" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C231" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D231" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E231" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C231" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D231" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E231" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F231" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C232" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D232" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E232" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F232" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C233" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D233" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E233" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F233" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C234" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D234" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E234" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F234" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C235" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D235" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E235" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F235" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C236" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D236" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E236" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F236" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C237" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D237" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E237" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F237" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C238" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D238" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E238" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F238" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C239" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D239" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E239" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F239" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C240" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D240" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E240" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F240" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C241" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D241" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E241" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E241" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F241" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C242" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D242" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E242" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F242" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C243" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D243" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E243" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F243" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C244" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D245" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E245" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F245" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C246" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D246" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E246" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F246" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C247" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D247" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E247" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F247" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D248" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F248" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C249" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D249" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E249" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>24733100</v>
+        <v>30002500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>336.0400085449219</v>
+        <v>340.3699951171875</v>
       </c>
       <c r="C250" t="n">
-        <v>341.6700134277344</v>
+        <v>342.989990234375</v>
       </c>
       <c r="D250" t="n">
-        <v>334.5299987792969</v>
+        <v>338.0400085449219</v>
       </c>
       <c r="E250" t="n">
-        <v>341.0700073242188</v>
+        <v>338.3999938964844</v>
       </c>
       <c r="F250" t="n">
-        <v>30002500</v>
+        <v>32820800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>340.3699951171875</v>
+        <v>336.9700012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>342.989990234375</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>338.0400085449219</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>338.3999938964844</v>
+        <v>329.3999938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>32820800</v>
+        <v>38478000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>336.9700012207031</v>
+        <v>330.7999877929688</v>
       </c>
       <c r="C252" t="n">
-        <v>337.0899963378906</v>
+        <v>339.5</v>
       </c>
       <c r="D252" t="n">
-        <v>328.7000122070312</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="E252" t="n">
-        <v>329.3999938964844</v>
+        <v>333.0199890136719</v>
       </c>
       <c r="F252" t="n">
-        <v>38427200</v>
+        <v>49931500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10260,37 +10260,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="D2" t="n">
         <v>329.4</v>
       </c>
-      <c r="D2" t="n">
-        <v>338.4</v>
-      </c>
       <c r="E2" t="n">
-        <v>337.06</v>
+        <v>330.8</v>
       </c>
       <c r="F2" t="n">
-        <v>337.06</v>
+        <v>339.5</v>
       </c>
       <c r="G2" t="n">
-        <v>328.7</v>
+        <v>330.1401</v>
       </c>
       <c r="H2" t="n">
-        <v>37773928</v>
+        <v>49875295</v>
       </c>
       <c r="I2" t="n">
-        <v>46833855</v>
+        <v>46780959</v>
       </c>
       <c r="J2" t="n">
-        <v>4807323025408</v>
+        <v>4860153954304</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75294</v>
+        <v>37.714607</v>
       </c>
       <c r="L2" t="n">
-        <v>34.36494</v>
+        <v>34.751663</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5</v>
+        <v>8.83</v>
       </c>
       <c r="N2" t="n">
         <v>345.34</v>
@@ -10302,7 +10302,7 @@
         <v>1.085</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="R2" t="n">
         <v>0.27618998</v>
@@ -10326,7 +10326,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>44.755432</v>
+        <v>45.24728</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10338,7 +10338,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4829268148224</v>
+        <v>4882099077120</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:06:43</t>
+          <t>2026-10-01 17:02:25</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>254.101347229275</v>
+        <v>255.6356912331815</v>
       </c>
       <c r="C2" t="n">
-        <v>257.8375609779932</v>
+        <v>257.2298088092003</v>
       </c>
       <c r="D2" t="n">
-        <v>253.9917514638179</v>
+        <v>253.2146416974651</v>
       </c>
       <c r="E2" t="n">
-        <v>254.5098419189453</v>
+        <v>256.1836853027344</v>
       </c>
       <c r="F2" t="n">
-        <v>48713900</v>
+        <v>42630200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>255.6356607808825</v>
+        <v>253.7327421013528</v>
       </c>
       <c r="C3" t="n">
-        <v>257.229778167004</v>
+        <v>258.2859153313368</v>
       </c>
       <c r="D3" t="n">
-        <v>253.2146115335708</v>
+        <v>253.0153906843864</v>
       </c>
       <c r="E3" t="n">
-        <v>256.1836547851562</v>
+        <v>257.0704040527344</v>
       </c>
       <c r="F3" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>253.7326818586438</v>
+        <v>257.0404883747525</v>
       </c>
       <c r="C4" t="n">
-        <v>258.2858540075867</v>
+        <v>258.1165305885388</v>
       </c>
       <c r="D4" t="n">
-        <v>253.0153306119951</v>
+        <v>254.1113214696764</v>
       </c>
       <c r="E4" t="n">
-        <v>257.0703430175781</v>
+        <v>255.7452850341797</v>
       </c>
       <c r="F4" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>257.0404730386864</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C5" t="n">
-        <v>258.1165151882718</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D5" t="n">
-        <v>254.1113063083761</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E5" t="n">
-        <v>255.7452697753906</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F5" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>255.8648591580886</v>
+        <v>255.5759191543519</v>
       </c>
       <c r="C6" t="n">
-        <v>256.4526841311554</v>
+        <v>257.5685585594684</v>
       </c>
       <c r="D6" t="n">
-        <v>254.4899331102905</v>
+        <v>255.1674244276712</v>
       </c>
       <c r="E6" t="n">
-        <v>255.5360870361328</v>
+        <v>257.1102600097656</v>
       </c>
       <c r="F6" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>255.5758888188916</v>
+        <v>256.8611554198282</v>
       </c>
       <c r="C7" t="n">
-        <v>257.5685279874928</v>
+        <v>257.0504585775582</v>
       </c>
       <c r="D7" t="n">
-        <v>255.1673941406971</v>
+        <v>252.2083446799687</v>
       </c>
       <c r="E7" t="n">
-        <v>257.1102294921875</v>
+        <v>253.1050262451172</v>
       </c>
       <c r="F7" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>256.8611554198282</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C8" t="n">
-        <v>257.0504585775582</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D8" t="n">
-        <v>252.2083446799687</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E8" t="n">
-        <v>253.1050262451172</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F8" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C9" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D9" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E9" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F9" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C10" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D10" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E10" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F10" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>245.6924164271231</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C11" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D11" t="n">
-        <v>243.7994000887665</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E11" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F11" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363348246392</v>
       </c>
       <c r="C12" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234206007849</v>
       </c>
       <c r="D12" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278226113223</v>
       </c>
       <c r="E12" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392761230469</v>
       </c>
       <c r="F12" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>247.3363501327598</v>
+        <v>247.1071917036077</v>
       </c>
       <c r="C13" t="n">
-        <v>248.1234359576197</v>
+        <v>252.447465373221</v>
       </c>
       <c r="D13" t="n">
-        <v>244.2278377270511</v>
+        <v>246.359952002837</v>
       </c>
       <c r="E13" t="n">
-        <v>246.5392913818359</v>
+        <v>251.3614654541016</v>
       </c>
       <c r="F13" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>247.1072067041429</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C14" t="n">
-        <v>252.4474806979352</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D14" t="n">
-        <v>246.3599669580113</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E14" t="n">
-        <v>251.3614807128906</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F14" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9162087553024</v>
       </c>
       <c r="C15" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136625920602</v>
       </c>
       <c r="D15" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663745269806</v>
       </c>
       <c r="E15" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8029174804688</v>
       </c>
       <c r="F15" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>260.9161783410852</v>
+        <v>261.6833338430701</v>
       </c>
       <c r="C16" t="n">
-        <v>264.3136317818121</v>
+        <v>261.882609922878</v>
       </c>
       <c r="D16" t="n">
-        <v>260.8663441185724</v>
+        <v>254.4899051977633</v>
       </c>
       <c r="E16" t="n">
-        <v>261.8028869628906</v>
+        <v>257.4988098144531</v>
       </c>
       <c r="F16" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>261.6833338430701</v>
+        <v>258.9833246632869</v>
       </c>
       <c r="C17" t="n">
-        <v>261.882609922878</v>
+        <v>259.6608147081683</v>
       </c>
       <c r="D17" t="n">
-        <v>254.4899051977633</v>
+        <v>257.0604350924048</v>
       </c>
       <c r="E17" t="n">
-        <v>257.4988098144531</v>
+        <v>258.6246337890625</v>
       </c>
       <c r="F17" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>258.9833246632869</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C18" t="n">
-        <v>259.6608147081683</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D18" t="n">
-        <v>257.0604350924048</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E18" t="n">
-        <v>258.6246337890625</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F18" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051197703755</v>
       </c>
       <c r="C19" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295048126629</v>
       </c>
       <c r="D19" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759553344934</v>
       </c>
       <c r="E19" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206481933594</v>
       </c>
       <c r="F19" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>263.9051498417878</v>
+        <v>267.9999758056659</v>
       </c>
       <c r="C20" t="n">
-        <v>268.1295353654346</v>
+        <v>268.896687690681</v>
       </c>
       <c r="D20" t="n">
-        <v>263.6759853797928</v>
+        <v>267.1630710642092</v>
       </c>
       <c r="E20" t="n">
-        <v>267.8206787109375</v>
+        <v>268.0099487304688</v>
       </c>
       <c r="F20" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>267.9999758056659</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C21" t="n">
-        <v>268.896687690681</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D21" t="n">
-        <v>267.1630710642092</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E21" t="n">
-        <v>268.0099487304688</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F21" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889479398262</v>
       </c>
       <c r="C22" t="n">
-        <v>270.4110953948544</v>
+        <v>273.1310593223432</v>
       </c>
       <c r="D22" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4918869527685</v>
       </c>
       <c r="E22" t="n">
-        <v>268.7073974609375</v>
+        <v>270.401123046875</v>
       </c>
       <c r="F22" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>270.9889785237465</v>
+        <v>275.9705701844509</v>
       </c>
       <c r="C23" t="n">
-        <v>273.131090148023</v>
+        <v>276.2993726959702</v>
       </c>
       <c r="D23" t="n">
-        <v>267.4919171420091</v>
+        <v>268.1694007015524</v>
       </c>
       <c r="E23" t="n">
-        <v>270.4011535644531</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="F23" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>275.9705701844509</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C24" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D24" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E24" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F24" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>269.4247673672652</v>
+        <v>267.3424142382169</v>
       </c>
       <c r="C25" t="n">
-        <v>269.8531775103368</v>
+        <v>270.4907876974107</v>
       </c>
       <c r="D25" t="n">
-        <v>265.2701011373342</v>
+        <v>266.6350358638735</v>
       </c>
       <c r="E25" t="n">
-        <v>268.0597839355469</v>
+        <v>269.046142578125</v>
       </c>
       <c r="F25" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>267.3424445625432</v>
+        <v>267.6214146886098</v>
       </c>
       <c r="C26" t="n">
-        <v>270.4908183788531</v>
+        <v>270.7000692568828</v>
       </c>
       <c r="D26" t="n">
-        <v>266.6350661079627</v>
+        <v>265.9476049232333</v>
       </c>
       <c r="E26" t="n">
-        <v>269.0461730957031</v>
+        <v>269.1458129882812</v>
       </c>
       <c r="F26" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C27" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D27" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E27" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F27" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8070253298314</v>
       </c>
       <c r="C28" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878818962731</v>
       </c>
       <c r="D28" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881780523408</v>
       </c>
       <c r="E28" t="n">
-        <v>268.7771301269531</v>
+        <v>267.48193359375</v>
       </c>
       <c r="F28" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,25 +1171,25 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>268.8069946610708</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C29" t="n">
-        <v>271.2878509444664</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D29" t="n">
-        <v>265.7881477280068</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E29" t="n">
-        <v>267.4819030761719</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F29" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1197,25 +1197,25 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>268.2298525605972</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C30" t="n">
-        <v>272.9869230403233</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D30" t="n">
-        <v>266.733924572705</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E30" t="n">
-        <v>268.6985778808594</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F30" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G30" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535066981436</v>
       </c>
       <c r="C31" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815360542478</v>
       </c>
       <c r="D31" t="n">
-        <v>269.0675899882029</v>
+        <v>270.9624767916609</v>
       </c>
       <c r="E31" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276611328125</v>
       </c>
       <c r="F31" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3659002679155</v>
       </c>
       <c r="C32" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488963676571</v>
       </c>
       <c r="D32" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513946141157</v>
       </c>
       <c r="E32" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090759277344</v>
       </c>
       <c r="F32" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C33" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D33" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E33" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F33" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0903024129557</v>
       </c>
       <c r="C34" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557521979796</v>
       </c>
       <c r="D34" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086937896775</v>
       </c>
       <c r="E34" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339782714844</v>
       </c>
       <c r="F34" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>268.0903024129557</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C35" t="n">
-        <v>269.7557521979796</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D35" t="n">
-        <v>265.0086937896775</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E35" t="n">
-        <v>266.7339782714844</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F35" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>269.25705465795</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C36" t="n">
-        <v>269.9751013080067</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D36" t="n">
-        <v>264.5997492422933</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E36" t="n">
-        <v>266.7139892578125</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F36" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>264.8092197798317</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C37" t="n">
-        <v>271.4710796703931</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D37" t="n">
-        <v>264.7793024319747</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E37" t="n">
-        <v>267.8309936523438</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F37" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C38" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D38" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E38" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F38" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>265.2280517805383</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C39" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D39" t="n">
-        <v>264.9488130991126</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E39" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F39" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C40" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D40" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E40" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F40" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2081750495132</v>
       </c>
       <c r="C41" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712060098946</v>
       </c>
       <c r="D41" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8790842359358</v>
       </c>
       <c r="E41" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7965698242188</v>
       </c>
       <c r="F41" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C42" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D42" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E42" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F42" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>276.5073679150082</v>
+        <v>277.255303275414</v>
       </c>
       <c r="C43" t="n">
-        <v>278.242634823177</v>
+        <v>282.650620542313</v>
       </c>
       <c r="D43" t="n">
-        <v>275.2407959413455</v>
+        <v>275.390384584981</v>
       </c>
       <c r="E43" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3314819335938</v>
       </c>
       <c r="F43" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>277.255303275414</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C44" t="n">
-        <v>282.650620542313</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D44" t="n">
-        <v>275.390384584981</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E44" t="n">
-        <v>282.3314819335938</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F44" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C45" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D45" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E45" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F45" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>285.4231155973949</v>
+        <v>283.328813896664</v>
       </c>
       <c r="C46" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9571086251454</v>
       </c>
       <c r="D46" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337611056945</v>
       </c>
       <c r="E46" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380493164062</v>
       </c>
       <c r="F46" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>283.328813896664</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C47" t="n">
-        <v>283.9571086251454</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D47" t="n">
-        <v>277.8337611056945</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E47" t="n">
-        <v>279.9380493164062</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F47" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C48" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D48" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E48" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F48" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049018876359</v>
       </c>
       <c r="C49" t="n">
-        <v>278.9108174051644</v>
+        <v>279.269820658071</v>
       </c>
       <c r="D49" t="n">
-        <v>275.4003533668138</v>
+        <v>276.1682777692156</v>
       </c>
       <c r="E49" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275512695312</v>
       </c>
       <c r="F49" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C50" t="n">
-        <v>279.269820658071</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D50" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E50" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F50" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342340640522</v>
       </c>
       <c r="C51" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310007112651</v>
       </c>
       <c r="D51" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0666927429874</v>
       </c>
       <c r="E51" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752380371094</v>
       </c>
       <c r="F51" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>278.342340640522</v>
+        <v>277.1456238228236</v>
       </c>
       <c r="C52" t="n">
-        <v>278.8310007112651</v>
+        <v>278.4620479370953</v>
       </c>
       <c r="D52" t="n">
-        <v>273.0666927429874</v>
+        <v>276.0685689150702</v>
       </c>
       <c r="E52" t="n">
-        <v>277.2752380371094</v>
+        <v>277.5245971679688</v>
       </c>
       <c r="F52" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C53" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D53" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E53" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F53" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C54" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D54" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E54" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F54" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634896625032</v>
       </c>
       <c r="C55" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103618778425</v>
       </c>
       <c r="D55" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026424636208</v>
       </c>
       <c r="E55" t="n">
-        <v>273.8645324707031</v>
+        <v>271.1020812988281</v>
       </c>
       <c r="F55" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>274.2634896625032</v>
+        <v>272.8672390402853</v>
       </c>
       <c r="C56" t="n">
-        <v>275.4103618778425</v>
+        <v>272.8872042261758</v>
       </c>
       <c r="D56" t="n">
-        <v>270.9026424636208</v>
+        <v>266.2253451719176</v>
       </c>
       <c r="E56" t="n">
-        <v>271.1020812988281</v>
+        <v>271.4511108398438</v>
       </c>
       <c r="F56" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>272.8672390402853</v>
+        <v>271.4112610007817</v>
       </c>
       <c r="C57" t="n">
-        <v>272.8872042261758</v>
+        <v>273.854622814086</v>
       </c>
       <c r="D57" t="n">
-        <v>266.2253451719176</v>
+        <v>269.1673684747946</v>
       </c>
       <c r="E57" t="n">
-        <v>271.4511108398438</v>
+        <v>272.9271545410156</v>
       </c>
       <c r="F57" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>271.4112610007817</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C58" t="n">
-        <v>273.854622814086</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D58" t="n">
-        <v>269.1673684747946</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E58" t="n">
-        <v>272.9271545410156</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F58" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C59" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D59" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E59" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F59" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C60" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D60" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E60" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F60" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4157835978775</v>
       </c>
       <c r="C61" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6224904749486</v>
       </c>
       <c r="D61" t="n">
-        <v>271.461096549353</v>
+        <v>272.1192942474183</v>
       </c>
       <c r="E61" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578369140625</v>
       </c>
       <c r="F61" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C62" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D62" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E62" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F62" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C63" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D63" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E63" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F63" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C64" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D64" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E64" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F64" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C65" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D65" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E65" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F65" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>271.5209599020358</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C66" t="n">
-        <v>277.0857995993762</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D66" t="n">
-        <v>268.2697994337228</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E66" t="n">
-        <v>270.2743530273438</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F66" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>269.9053759278346</v>
+        <v>266.2751846804448</v>
       </c>
       <c r="C67" t="n">
-        <v>270.7730094869922</v>
+        <v>266.8236794412865</v>
       </c>
       <c r="D67" t="n">
-        <v>265.417590951718</v>
+        <v>261.4084273717842</v>
       </c>
       <c r="E67" t="n">
-        <v>266.5345458984375</v>
+        <v>261.6477661132812</v>
       </c>
       <c r="F67" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>266.2751846804448</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C68" t="n">
-        <v>266.8236794412865</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D68" t="n">
-        <v>261.4084273717842</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E68" t="n">
-        <v>261.6477661132812</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F68" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>262.485556491205</v>
+        <v>256.3223167721599</v>
       </c>
       <c r="C69" t="n">
-        <v>262.9642340542807</v>
+        <v>258.5861744106298</v>
       </c>
       <c r="D69" t="n">
-        <v>259.1047440282917</v>
+        <v>255.005907781442</v>
       </c>
       <c r="E69" t="n">
-        <v>259.6233215332031</v>
+        <v>258.3368530273438</v>
       </c>
       <c r="F69" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>256.3223167721599</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C70" t="n">
-        <v>258.5861744106298</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D70" t="n">
-        <v>255.005907781442</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E70" t="n">
-        <v>258.3368530273438</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F70" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C71" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D71" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E71" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F71" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C72" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D72" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E72" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F72" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>258.017707787092</v>
+        <v>258.7856080874888</v>
       </c>
       <c r="C73" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1093003767552</v>
       </c>
       <c r="D73" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131555781144</v>
       </c>
       <c r="E73" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543334960938</v>
       </c>
       <c r="F73" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>258.7856080874888</v>
+        <v>259.9424426175537</v>
       </c>
       <c r="C74" t="n">
-        <v>261.1093003767552</v>
+        <v>260.3313985459844</v>
       </c>
       <c r="D74" t="n">
-        <v>256.0131555781144</v>
+        <v>256.3522089636155</v>
       </c>
       <c r="E74" t="n">
-        <v>259.2543334960938</v>
+        <v>257.5090637207031</v>
       </c>
       <c r="F74" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1999265314624</v>
       </c>
       <c r="C75" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1972120398704</v>
       </c>
       <c r="D75" t="n">
-        <v>256.3522089636155</v>
+        <v>254.2379873541013</v>
       </c>
       <c r="E75" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363647460938</v>
       </c>
       <c r="F75" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>257.1999265314624</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C76" t="n">
-        <v>258.1972120398704</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D76" t="n">
-        <v>254.2379873541013</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E76" t="n">
-        <v>254.8363647460938</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F76" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0249055239374</v>
       </c>
       <c r="C77" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771427168815</v>
       </c>
       <c r="D77" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144562363057</v>
       </c>
       <c r="E77" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777526855469</v>
       </c>
       <c r="F77" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>248.0249055239374</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C78" t="n">
-        <v>250.8771427168815</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D78" t="n">
-        <v>244.5144562363057</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E78" t="n">
-        <v>246.9777526855469</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F78" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486524137701</v>
       </c>
       <c r="C79" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329754164565</v>
       </c>
       <c r="D79" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0158041358057</v>
       </c>
       <c r="E79" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666839599609</v>
       </c>
       <c r="F79" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>246.6486524137701</v>
+        <v>250.7973351598156</v>
       </c>
       <c r="C80" t="n">
-        <v>248.7329754164565</v>
+        <v>255.863546959882</v>
       </c>
       <c r="D80" t="n">
-        <v>244.0158041358057</v>
+        <v>249.1219029451975</v>
       </c>
       <c r="E80" t="n">
-        <v>247.3666839599609</v>
+        <v>254.7166748046875</v>
       </c>
       <c r="F80" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C81" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D81" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E81" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F81" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>258.4664899667647</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C82" t="n">
-        <v>261.2389423700868</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D82" t="n">
-        <v>257.5090739976807</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E82" t="n">
-        <v>257.5689086914062</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F82" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996187429542</v>
       </c>
       <c r="C83" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451334735496</v>
       </c>
       <c r="D83" t="n">
-        <v>253.8191124091609</v>
+        <v>253.719368010288</v>
       </c>
       <c r="E83" t="n">
-        <v>255.7438812255859</v>
+        <v>257.578857421875</v>
       </c>
       <c r="F83" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>257.2996187429542</v>
+        <v>254.4773217725483</v>
       </c>
       <c r="C84" t="n">
-        <v>258.9451334735496</v>
+        <v>261.1890484668085</v>
       </c>
       <c r="D84" t="n">
-        <v>253.719368010288</v>
+        <v>251.4954328536096</v>
       </c>
       <c r="E84" t="n">
-        <v>257.578857421875</v>
+        <v>258.775634765625</v>
       </c>
       <c r="F84" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241487899344</v>
       </c>
       <c r="C85" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557466562268</v>
       </c>
       <c r="D85" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063673710488</v>
       </c>
       <c r="E85" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770690917969</v>
       </c>
       <c r="F85" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C86" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D86" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E86" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F86" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="C87" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927850076088</v>
       </c>
       <c r="D87" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508603406617</v>
       </c>
       <c r="E87" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394409179688</v>
       </c>
       <c r="F87" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>271.5508603406617</v>
+        <v>277.3749854862336</v>
       </c>
       <c r="C88" t="n">
-        <v>278.1927850076088</v>
+        <v>278.7412615768201</v>
       </c>
       <c r="D88" t="n">
-        <v>271.5508603406617</v>
+        <v>272.4882932485779</v>
       </c>
       <c r="E88" t="n">
-        <v>275.7394409179688</v>
+        <v>275.1610107421875</v>
       </c>
       <c r="F88" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>277.3749854862336</v>
+        <v>276.3677657232236</v>
       </c>
       <c r="C89" t="n">
-        <v>278.7412615768201</v>
+        <v>280.1474864654567</v>
       </c>
       <c r="D89" t="n">
-        <v>272.4882932485779</v>
+        <v>276.1782790346459</v>
       </c>
       <c r="E89" t="n">
-        <v>275.1610107421875</v>
+        <v>277.3650512695312</v>
       </c>
       <c r="F89" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,25 +2757,25 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>276.3677657232236</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C90" t="n">
-        <v>280.1474864654567</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D90" t="n">
-        <v>276.1782790346459</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E90" t="n">
-        <v>277.3650512695312</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F90" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -2783,25 +2783,25 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C91" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D91" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E91" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F91" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G91" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C92" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D92" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E92" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F92" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990585104662</v>
       </c>
       <c r="C93" t="n">
-        <v>279.6808719096702</v>
+        <v>275.2288318017276</v>
       </c>
       <c r="D93" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165063299744</v>
       </c>
       <c r="E93" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637634277344</v>
       </c>
       <c r="F93" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>275.0990585104662</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C94" t="n">
-        <v>275.2288318017276</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D94" t="n">
-        <v>259.7165063299744</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E94" t="n">
-        <v>261.2637634277344</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F94" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C95" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D95" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E95" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F95" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C96" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D96" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E96" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F96" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C97" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D97" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E97" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F97" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C98" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D98" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E98" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F98" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C99" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D99" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E99" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F99" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C100" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D100" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E100" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F100" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C101" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D101" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E101" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F101" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C102" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D102" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E102" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F102" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="C103" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240439665745</v>
       </c>
       <c r="D103" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217314181026</v>
       </c>
       <c r="E103" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7094116210938</v>
       </c>
       <c r="F103" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>272.3240439665745</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C104" t="n">
-        <v>272.3240439665745</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D104" t="n">
-        <v>262.4217314181026</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E104" t="n">
-        <v>263.7094116210938</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F104" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C105" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D105" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E105" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F105" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C106" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D106" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E106" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F106" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C107" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D107" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E107" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F107" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C108" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D108" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E108" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F108" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C109" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D109" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E109" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F109" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C110" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D110" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E110" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F110" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>257.1910284571696</v>
+        <v>260.624897946549</v>
       </c>
       <c r="C111" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630538494394</v>
       </c>
       <c r="D111" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876327296249</v>
       </c>
       <c r="E111" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453979492188</v>
       </c>
       <c r="F111" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>260.624897946549</v>
+        <v>258.1992408199258</v>
       </c>
       <c r="C112" t="n">
-        <v>261.6630538494394</v>
+        <v>258.4887327594216</v>
       </c>
       <c r="D112" t="n">
-        <v>259.0876327296249</v>
+        <v>253.7272102811576</v>
       </c>
       <c r="E112" t="n">
-        <v>260.3453979492188</v>
+        <v>255.3043975830078</v>
       </c>
       <c r="F112" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>258.1992408199258</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C113" t="n">
-        <v>258.4887327594216</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D113" t="n">
-        <v>253.7272102811576</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E113" t="n">
-        <v>255.3043975830078</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F113" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C114" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D114" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E114" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F114" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C115" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D115" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E115" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F115" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C116" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D116" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E116" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F116" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C117" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D117" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E117" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F117" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C118" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D118" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E118" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F118" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C119" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D119" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E119" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F119" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C120" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D120" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E120" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F120" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C121" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D121" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E121" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F121" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C122" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D122" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E122" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F122" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C123" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D123" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E123" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F123" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C124" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D124" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E124" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F124" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683905467953</v>
       </c>
       <c r="C125" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248978486836</v>
       </c>
       <c r="D125" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598358728773</v>
       </c>
       <c r="E125" t="n">
-        <v>246.1906585693359</v>
+        <v>253.3379058837891</v>
       </c>
       <c r="F125" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>247.4683905467953</v>
+        <v>253.6273948962928</v>
       </c>
       <c r="C126" t="n">
-        <v>255.0248978486836</v>
+        <v>255.7236449097363</v>
       </c>
       <c r="D126" t="n">
-        <v>246.6598358728773</v>
+        <v>252.8787309132899</v>
       </c>
       <c r="E126" t="n">
-        <v>253.3379058837891</v>
+        <v>255.1746368408203</v>
       </c>
       <c r="F126" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>253.6273948962928</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C127" t="n">
-        <v>255.7236449097363</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D127" t="n">
-        <v>252.8787309132899</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E127" t="n">
-        <v>255.1746368408203</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F127" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>253.7471740568136</v>
+        <v>256.0530752925303</v>
       </c>
       <c r="C128" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6930045642991</v>
       </c>
       <c r="D128" t="n">
-        <v>250.2034948550391</v>
+        <v>256.0031460821725</v>
       </c>
       <c r="E128" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988647460938</v>
       </c>
       <c r="F128" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>256.0530752925303</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C129" t="n">
-        <v>261.6930045642991</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D129" t="n">
-        <v>256.0031460821725</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E129" t="n">
-        <v>258.3988647460938</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F129" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896321241455</v>
       </c>
       <c r="C130" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2873042333858</v>
       </c>
       <c r="D130" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730388391825</v>
       </c>
       <c r="E130" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4388122558594</v>
       </c>
       <c r="F130" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>257.9896321241455</v>
+        <v>258.5386343954405</v>
       </c>
       <c r="C131" t="n">
-        <v>259.2873042333858</v>
+        <v>260.6548530924392</v>
       </c>
       <c r="D131" t="n">
-        <v>256.0730388391825</v>
+        <v>255.6138610163474</v>
       </c>
       <c r="E131" t="n">
-        <v>258.4388122558594</v>
+        <v>260.0259704589844</v>
       </c>
       <c r="F131" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>258.5386343954405</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C132" t="n">
-        <v>260.6548530924392</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D132" t="n">
-        <v>255.6138610163474</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E132" t="n">
-        <v>260.0259704589844</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F132" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C133" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D133" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E133" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F133" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881922504944</v>
       </c>
       <c r="C134" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4634109961452</v>
       </c>
       <c r="D134" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318642110386</v>
       </c>
       <c r="E134" t="n">
-        <v>258.73828125</v>
+        <v>258.3689270019531</v>
       </c>
       <c r="F134" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>258.7881922504944</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C135" t="n">
-        <v>261.4634109961452</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D135" t="n">
-        <v>256.7318642110386</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E135" t="n">
-        <v>258.3689270019531</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F135" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3247234477873</v>
       </c>
       <c r="C136" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840980024072</v>
       </c>
       <c r="D136" t="n">
-        <v>257.3507435512608</v>
+        <v>260.8045755356903</v>
       </c>
       <c r="E136" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307861328125</v>
       </c>
       <c r="F136" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>266.3247234477873</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C137" t="n">
-        <v>266.6840980024072</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D137" t="n">
-        <v>260.8045755356903</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E137" t="n">
-        <v>262.9307861328125</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F137" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C138" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D138" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E138" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F138" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C139" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D139" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E139" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F139" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C140" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D140" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E140" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F140" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C141" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D141" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E141" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F141" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C142" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D142" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E142" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F142" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C143" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D143" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E143" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F143" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C144" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D144" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E144" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F144" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C145" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D145" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E145" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F145" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C146" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D146" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E146" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F146" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632420760759</v>
       </c>
       <c r="C147" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083659496485</v>
       </c>
       <c r="D147" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8741246788477</v>
       </c>
       <c r="E147" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409912109375</v>
       </c>
       <c r="F147" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>278.3632420760759</v>
+        <v>279.1617980116577</v>
       </c>
       <c r="C148" t="n">
-        <v>286.7083659496485</v>
+        <v>280.1300712051751</v>
       </c>
       <c r="D148" t="n">
-        <v>277.8741246788477</v>
+        <v>274.3703307853319</v>
       </c>
       <c r="E148" t="n">
-        <v>279.6409912109375</v>
+        <v>276.3368225097656</v>
       </c>
       <c r="F148" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>279.1617980116577</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C149" t="n">
-        <v>280.1300712051751</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D149" t="n">
-        <v>274.3703307853319</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E149" t="n">
-        <v>276.3368225097656</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F149" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>276.43668191704</v>
+        <v>281.4178249779708</v>
       </c>
       <c r="C150" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5169265187869</v>
       </c>
       <c r="D150" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693330033821</v>
       </c>
       <c r="E150" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978637695312</v>
       </c>
       <c r="F150" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>281.4178249779708</v>
+        <v>288.7547052879293</v>
       </c>
       <c r="C151" t="n">
-        <v>287.5169265187869</v>
+        <v>291.6096265406606</v>
       </c>
       <c r="D151" t="n">
-        <v>280.5693330033821</v>
+        <v>285.2709318587503</v>
       </c>
       <c r="E151" t="n">
-        <v>286.9978637695312</v>
+        <v>286.927978515625</v>
       </c>
       <c r="F151" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>288.7547052879293</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C152" t="n">
-        <v>291.6096265406606</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D152" t="n">
-        <v>285.2709318587503</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E152" t="n">
-        <v>286.927978515625</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F152" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,25 +4395,25 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C153" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D153" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E153" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F153" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4421,25 +4421,25 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C154" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D154" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E154" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F154" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G154" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C155" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D155" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E155" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F155" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C156" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D156" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E156" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F156" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C157" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D157" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E157" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F157" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C158" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D158" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E158" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F158" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C159" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D159" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E159" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F159" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C160" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D160" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E160" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F160" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C161" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D161" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E161" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F161" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C162" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D162" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E162" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F162" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C163" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D163" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E163" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F163" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C164" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D164" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E164" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F164" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C165" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D165" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E165" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F165" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C166" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D166" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E166" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F166" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C167" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D167" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E167" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F167" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C168" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D168" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E168" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F168" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C169" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D169" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E169" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F169" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C170" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D170" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E170" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F170" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C171" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D171" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E171" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F171" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C172" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D172" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E172" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F172" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C173" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D173" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E173" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F173" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C174" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D174" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E174" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F174" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C175" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D175" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E175" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F175" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C176" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D176" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E176" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F176" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C177" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D177" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E177" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F177" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C178" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D178" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E178" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F178" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C179" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D179" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E179" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F179" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C180" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D180" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E180" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F180" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C181" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D181" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E181" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F181" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C182" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D182" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E182" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F182" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C183" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D183" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E183" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F183" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C184" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D184" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E184" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F184" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C185" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D185" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E185" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F185" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C186" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D186" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E186" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F186" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C187" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D187" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E187" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F187" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C188" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D188" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E188" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F188" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C189" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D189" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E189" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F189" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C190" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D190" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E190" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F190" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C191" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D191" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E191" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F191" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C192" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D192" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E192" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F192" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C193" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D193" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E193" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F193" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C194" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D194" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E194" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F194" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C195" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D195" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E195" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F195" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C196" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D196" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E196" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F196" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C197" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D197" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E197" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F197" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C198" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D198" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E198" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F198" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C199" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D199" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E199" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F199" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C200" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D200" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E200" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F200" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C201" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D201" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E201" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F201" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C202" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D202" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E202" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F202" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C203" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D203" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E203" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F203" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C204" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D204" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E204" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F204" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C205" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D205" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E205" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F205" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C206" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D206" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E206" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F206" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C207" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D207" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E207" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F207" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C208" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D208" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E208" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F208" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C209" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D209" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E209" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F209" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C210" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D210" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E210" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F210" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C211" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D211" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E211" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F211" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C212" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D212" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E212" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F212" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C213" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D213" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E213" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F213" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C214" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D214" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E214" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F214" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,25 +6007,25 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C215" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D215" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E215" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F215" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6033,25 +6033,25 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C216" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D216" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E216" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F216" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G216" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C217" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D217" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E217" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F217" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C218" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D218" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E218" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F218" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C219" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D219" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E219" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F219" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C220" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D220" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E220" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F220" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C221" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D221" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E221" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F221" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C222" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D222" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E222" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F222" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C223" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D223" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E223" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F223" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C224" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D224" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E224" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F224" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C225" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D225" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E225" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F225" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C226" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D226" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E226" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F226" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C227" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D227" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F227" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C228" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D228" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E228" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F228" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C229" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E229" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F229" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C230" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D230" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E230" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C230" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D230" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E230" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F230" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C231" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D231" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E231" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F231" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C232" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D232" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E232" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F232" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C233" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D233" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E233" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F233" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C234" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D234" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E234" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F234" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C235" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D235" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E235" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F235" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C236" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D236" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E236" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F236" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C237" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D237" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E237" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F237" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C238" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D238" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F238" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C239" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D239" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E239" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F239" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C240" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D240" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E240" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E240" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F240" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C241" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D241" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E241" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F241" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C242" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D242" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E242" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F242" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C243" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D243" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F243" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D244" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E244" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F244" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D245" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E245" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F245" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C246" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D246" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E246" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F246" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C247" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D247" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F247" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C248" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D248" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>24733100</v>
+        <v>30002500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>336.0400085449219</v>
+        <v>340.3699951171875</v>
       </c>
       <c r="C249" t="n">
-        <v>341.6700134277344</v>
+        <v>342.989990234375</v>
       </c>
       <c r="D249" t="n">
-        <v>334.5299987792969</v>
+        <v>338.0400085449219</v>
       </c>
       <c r="E249" t="n">
-        <v>341.0700073242188</v>
+        <v>338.3999938964844</v>
       </c>
       <c r="F249" t="n">
-        <v>30002500</v>
+        <v>32820800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>340.3699951171875</v>
+        <v>336.9700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>342.989990234375</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>338.0400085449219</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="E250" t="n">
-        <v>338.3999938964844</v>
+        <v>329.3999938964844</v>
       </c>
       <c r="F250" t="n">
-        <v>32820800</v>
+        <v>38478000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>336.9700012207031</v>
+        <v>330.7999877929688</v>
       </c>
       <c r="C251" t="n">
-        <v>337.0899963378906</v>
+        <v>339.5</v>
       </c>
       <c r="D251" t="n">
-        <v>328.7000122070312</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="E251" t="n">
-        <v>329.3999938964844</v>
+        <v>333.0199890136719</v>
       </c>
       <c r="F251" t="n">
-        <v>38478000</v>
+        <v>49988600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>330.7999877929688</v>
+        <v>330</v>
       </c>
       <c r="C252" t="n">
-        <v>339.5</v>
+        <v>332.4800109863281</v>
       </c>
       <c r="D252" t="n">
-        <v>330.1400146484375</v>
+        <v>325.8099975585938</v>
       </c>
       <c r="E252" t="n">
-        <v>333.0199890136719</v>
+        <v>330.3200073242188</v>
       </c>
       <c r="F252" t="n">
-        <v>49931500</v>
+        <v>36243900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10260,37 +10260,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>330.32</v>
+      </c>
+      <c r="D2" t="n">
         <v>333.02</v>
       </c>
-      <c r="D2" t="n">
-        <v>329.4</v>
-      </c>
       <c r="E2" t="n">
-        <v>330.8</v>
+        <v>330.17</v>
       </c>
       <c r="F2" t="n">
-        <v>339.5</v>
+        <v>332.4816</v>
       </c>
       <c r="G2" t="n">
-        <v>330.1401</v>
+        <v>325.81</v>
       </c>
       <c r="H2" t="n">
-        <v>49875295</v>
+        <v>35017775</v>
       </c>
       <c r="I2" t="n">
-        <v>46780959</v>
+        <v>46211098</v>
       </c>
       <c r="J2" t="n">
-        <v>4860153954304</v>
+        <v>4820749516800</v>
       </c>
       <c r="K2" t="n">
-        <v>37.714607</v>
+        <v>37.880733</v>
       </c>
       <c r="L2" t="n">
-        <v>34.751663</v>
+        <v>34.46991</v>
       </c>
       <c r="M2" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>345.34</v>
@@ -10326,7 +10326,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>45.24728</v>
+        <v>44.880436</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10338,7 +10338,7 @@
         <v>466822987776</v>
       </c>
       <c r="AC2" t="n">
-        <v>4882099077120</v>
+        <v>4842694639616</v>
       </c>
       <c r="AD2" t="n">
         <v>167959003136</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:02:25</t>
+          <t>2026-10-02 19:38:08</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>255.6356912331815</v>
+        <v>253.7327119799983</v>
       </c>
       <c r="C2" t="n">
-        <v>257.2298088092003</v>
+        <v>258.2858846694617</v>
       </c>
       <c r="D2" t="n">
-        <v>253.2146416974651</v>
+        <v>253.0153606481908</v>
       </c>
       <c r="E2" t="n">
-        <v>256.1836853027344</v>
+        <v>257.0703735351562</v>
       </c>
       <c r="F2" t="n">
-        <v>42630200</v>
+        <v>49155600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>253.7327421013528</v>
+        <v>257.0404883747525</v>
       </c>
       <c r="C3" t="n">
-        <v>258.2859153313368</v>
+        <v>258.1165305885388</v>
       </c>
       <c r="D3" t="n">
-        <v>253.0153906843864</v>
+        <v>254.1113214696764</v>
       </c>
       <c r="E3" t="n">
-        <v>257.0704040527344</v>
+        <v>255.7452850341797</v>
       </c>
       <c r="F3" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>257.0404883747525</v>
+        <v>255.8648591580886</v>
       </c>
       <c r="C4" t="n">
-        <v>258.1165305885388</v>
+        <v>256.4526841311554</v>
       </c>
       <c r="D4" t="n">
-        <v>254.1113214696764</v>
+        <v>254.4899331102905</v>
       </c>
       <c r="E4" t="n">
-        <v>255.7452850341797</v>
+        <v>255.5360870361328</v>
       </c>
       <c r="F4" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>255.8648438796676</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C5" t="n">
-        <v>256.4526688176338</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D5" t="n">
-        <v>254.4899179139702</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E5" t="n">
-        <v>255.5360717773438</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F5" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>255.5759191543519</v>
+        <v>256.8611399345957</v>
       </c>
       <c r="C6" t="n">
-        <v>257.5685585594684</v>
+        <v>257.0504430809132</v>
       </c>
       <c r="D6" t="n">
-        <v>255.1674244276712</v>
+        <v>252.2083294752373</v>
       </c>
       <c r="E6" t="n">
-        <v>257.1102600097656</v>
+        <v>253.1050109863281</v>
       </c>
       <c r="F6" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>256.8611554198282</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C7" t="n">
-        <v>257.0504585775582</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D7" t="n">
-        <v>252.2083446799687</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E7" t="n">
-        <v>253.1050262451172</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F7" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C8" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D8" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E8" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F8" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924164271231</v>
       </c>
       <c r="C9" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341354996238</v>
       </c>
       <c r="D9" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994000887665</v>
       </c>
       <c r="E9" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581085205078</v>
       </c>
       <c r="F9" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>245.6924164271231</v>
+        <v>248.5717898296712</v>
       </c>
       <c r="C10" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932163906544</v>
       </c>
       <c r="D10" t="n">
-        <v>243.7994000887665</v>
+        <v>246.559219921403</v>
       </c>
       <c r="E10" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223327636719</v>
       </c>
       <c r="F10" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>248.5717898296712</v>
+        <v>247.3363501327598</v>
       </c>
       <c r="C11" t="n">
-        <v>250.8932163906544</v>
+        <v>248.1234359576197</v>
       </c>
       <c r="D11" t="n">
-        <v>246.559219921403</v>
+        <v>244.2278377270511</v>
       </c>
       <c r="E11" t="n">
-        <v>248.4223327636719</v>
+        <v>246.5392913818359</v>
       </c>
       <c r="F11" t="n">
-        <v>33893600</v>
+        <v>39777000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>247.3363348246392</v>
+        <v>247.1072067041429</v>
       </c>
       <c r="C12" t="n">
-        <v>248.1234206007849</v>
+        <v>252.4474806979352</v>
       </c>
       <c r="D12" t="n">
-        <v>244.2278226113223</v>
+        <v>246.3599669580113</v>
       </c>
       <c r="E12" t="n">
-        <v>246.5392761230469</v>
+        <v>251.3614807128906</v>
       </c>
       <c r="F12" t="n">
-        <v>39777000</v>
+        <v>49147000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>247.1071917036077</v>
+        <v>254.9482209911351</v>
       </c>
       <c r="C13" t="n">
-        <v>252.447465373221</v>
+        <v>263.4069798400544</v>
       </c>
       <c r="D13" t="n">
-        <v>246.359952002837</v>
+        <v>254.6891833689404</v>
       </c>
       <c r="E13" t="n">
-        <v>251.3614654541016</v>
+        <v>261.2748413085938</v>
       </c>
       <c r="F13" t="n">
-        <v>49147000</v>
+        <v>90483000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>254.9482209911351</v>
+        <v>260.9161783410852</v>
       </c>
       <c r="C14" t="n">
-        <v>263.4069798400544</v>
+        <v>264.3136317818121</v>
       </c>
       <c r="D14" t="n">
-        <v>254.6891833689404</v>
+        <v>260.8663441185724</v>
       </c>
       <c r="E14" t="n">
-        <v>261.2748413085938</v>
+        <v>261.8028869628906</v>
       </c>
       <c r="F14" t="n">
-        <v>90483000</v>
+        <v>46695900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>260.9162087553024</v>
+        <v>261.6833648565789</v>
       </c>
       <c r="C15" t="n">
-        <v>264.3136625920602</v>
+        <v>261.882640960004</v>
       </c>
       <c r="D15" t="n">
-        <v>260.8663745269806</v>
+        <v>254.4899353587398</v>
       </c>
       <c r="E15" t="n">
-        <v>261.8029174804688</v>
+        <v>257.4988403320312</v>
       </c>
       <c r="F15" t="n">
-        <v>46695900</v>
+        <v>45015300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>261.6833338430701</v>
+        <v>258.9833552231903</v>
       </c>
       <c r="C16" t="n">
-        <v>261.882609922878</v>
+        <v>259.6608453480152</v>
       </c>
       <c r="D16" t="n">
-        <v>254.4899051977633</v>
+        <v>257.0604654254083</v>
       </c>
       <c r="E16" t="n">
-        <v>257.4988098144531</v>
+        <v>258.6246643066406</v>
       </c>
       <c r="F16" t="n">
-        <v>45015300</v>
+        <v>32754900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>258.9833246632869</v>
+        <v>260.2287163700197</v>
       </c>
       <c r="C17" t="n">
-        <v>259.6608147081683</v>
+        <v>263.1578983995789</v>
       </c>
       <c r="D17" t="n">
-        <v>257.0604350924048</v>
+        <v>258.2261042627009</v>
       </c>
       <c r="E17" t="n">
-        <v>258.6246337890625</v>
+        <v>261.8527221679688</v>
       </c>
       <c r="F17" t="n">
-        <v>32754900</v>
+        <v>38253700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>260.2287163700197</v>
+        <v>263.9051498417878</v>
       </c>
       <c r="C18" t="n">
-        <v>263.1578983995789</v>
+        <v>268.1295353654346</v>
       </c>
       <c r="D18" t="n">
-        <v>258.2261042627009</v>
+        <v>263.6759853797928</v>
       </c>
       <c r="E18" t="n">
-        <v>261.8527221679688</v>
+        <v>267.8206787109375</v>
       </c>
       <c r="F18" t="n">
-        <v>38253700</v>
+        <v>44888200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>263.9051197703755</v>
+        <v>268.0000063221084</v>
       </c>
       <c r="C19" t="n">
-        <v>268.1295048126629</v>
+        <v>268.8967183092298</v>
       </c>
       <c r="D19" t="n">
-        <v>263.6759553344934</v>
+        <v>267.1631014853557</v>
       </c>
       <c r="E19" t="n">
-        <v>267.8206481933594</v>
+        <v>268.0099792480469</v>
       </c>
       <c r="F19" t="n">
-        <v>44888200</v>
+        <v>41534800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>267.9999758056659</v>
+        <v>268.2889298674747</v>
       </c>
       <c r="C20" t="n">
-        <v>268.896687690681</v>
+        <v>270.4110953948544</v>
       </c>
       <c r="D20" t="n">
-        <v>267.1630710642092</v>
+        <v>266.1269030442272</v>
       </c>
       <c r="E20" t="n">
-        <v>268.0099487304688</v>
+        <v>268.7073974609375</v>
       </c>
       <c r="F20" t="n">
-        <v>41534800</v>
+        <v>51086700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>268.2889298674747</v>
+        <v>270.9889785237465</v>
       </c>
       <c r="C21" t="n">
-        <v>270.4110953948544</v>
+        <v>273.131090148023</v>
       </c>
       <c r="D21" t="n">
-        <v>266.1269030442272</v>
+        <v>267.4919171420091</v>
       </c>
       <c r="E21" t="n">
-        <v>268.7073974609375</v>
+        <v>270.4011535644531</v>
       </c>
       <c r="F21" t="n">
-        <v>51086700</v>
+        <v>69886500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>270.9889479398262</v>
+        <v>275.9705389196515</v>
       </c>
       <c r="C22" t="n">
-        <v>273.1310593223432</v>
+        <v>276.2993413939207</v>
       </c>
       <c r="D22" t="n">
-        <v>267.4918869527685</v>
+        <v>268.1693703205502</v>
       </c>
       <c r="E22" t="n">
-        <v>270.401123046875</v>
+        <v>269.3749084472656</v>
       </c>
       <c r="F22" t="n">
-        <v>69886500</v>
+        <v>86167100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>275.9705701844509</v>
+        <v>269.4247673672652</v>
       </c>
       <c r="C23" t="n">
-        <v>276.2993726959702</v>
+        <v>269.8531775103368</v>
       </c>
       <c r="D23" t="n">
-        <v>268.1694007015524</v>
+        <v>265.2701011373342</v>
       </c>
       <c r="E23" t="n">
-        <v>269.3749389648438</v>
+        <v>268.0597839355469</v>
       </c>
       <c r="F23" t="n">
-        <v>86167100</v>
+        <v>50194600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>269.4247673672652</v>
+        <v>267.3424445625432</v>
       </c>
       <c r="C24" t="n">
-        <v>269.8531775103368</v>
+        <v>270.4908183788531</v>
       </c>
       <c r="D24" t="n">
-        <v>265.2701011373342</v>
+        <v>266.6350661079627</v>
       </c>
       <c r="E24" t="n">
-        <v>268.0597839355469</v>
+        <v>269.0461730957031</v>
       </c>
       <c r="F24" t="n">
-        <v>50194600</v>
+        <v>49274800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>267.3424142382169</v>
+        <v>267.6213843438783</v>
       </c>
       <c r="C25" t="n">
-        <v>270.4907876974107</v>
+        <v>270.7000385630726</v>
       </c>
       <c r="D25" t="n">
-        <v>266.6350358638735</v>
+        <v>265.9475747682897</v>
       </c>
       <c r="E25" t="n">
-        <v>269.046142578125</v>
+        <v>269.1457824707031</v>
       </c>
       <c r="F25" t="n">
-        <v>49274800</v>
+        <v>43683100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>267.6214146886098</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="C26" t="n">
-        <v>270.7000692568828</v>
+        <v>272.3937751745226</v>
       </c>
       <c r="D26" t="n">
-        <v>265.9476049232333</v>
+        <v>266.9040748013871</v>
       </c>
       <c r="E26" t="n">
-        <v>269.1458129882812</v>
+        <v>268.7771301269531</v>
       </c>
       <c r="F26" t="n">
-        <v>43683100</v>
+        <v>51204000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>266.9040748013871</v>
+        <v>268.8069946610708</v>
       </c>
       <c r="C27" t="n">
-        <v>272.3937751745226</v>
+        <v>271.2878509444664</v>
       </c>
       <c r="D27" t="n">
-        <v>266.9040748013871</v>
+        <v>265.7881477280068</v>
       </c>
       <c r="E27" t="n">
-        <v>268.7771301269531</v>
+        <v>267.4819030761719</v>
       </c>
       <c r="F27" t="n">
-        <v>51204000</v>
+        <v>48227400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,25 +1145,25 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>268.8070253298314</v>
+        <v>268.2298525605972</v>
       </c>
       <c r="C28" t="n">
-        <v>271.2878818962731</v>
+        <v>272.9869230403233</v>
       </c>
       <c r="D28" t="n">
-        <v>265.7881780523408</v>
+        <v>266.733924572705</v>
       </c>
       <c r="E28" t="n">
-        <v>267.48193359375</v>
+        <v>268.6985778808594</v>
       </c>
       <c r="F28" t="n">
-        <v>48227400</v>
+        <v>41312400</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1171,25 +1171,25 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>268.2298525605972</v>
+        <v>269.0775725813642</v>
       </c>
       <c r="C29" t="n">
-        <v>272.9869230403233</v>
+        <v>275.1610196363943</v>
       </c>
       <c r="D29" t="n">
-        <v>266.733924572705</v>
+        <v>269.0675899882029</v>
       </c>
       <c r="E29" t="n">
-        <v>268.6985778808594</v>
+        <v>274.5028076171875</v>
       </c>
       <c r="F29" t="n">
-        <v>41312400</v>
+        <v>46208300</v>
       </c>
       <c r="G29" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>269.0775725813642</v>
+        <v>274.2535373864602</v>
       </c>
       <c r="C30" t="n">
-        <v>275.1610196363943</v>
+        <v>274.9815668240292</v>
       </c>
       <c r="D30" t="n">
-        <v>269.0675899882029</v>
+        <v>270.962507111719</v>
       </c>
       <c r="E30" t="n">
-        <v>274.5028076171875</v>
+        <v>272.7276916503906</v>
       </c>
       <c r="F30" t="n">
-        <v>46208300</v>
+        <v>48398000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>274.2535066981436</v>
+        <v>273.3658696206449</v>
       </c>
       <c r="C31" t="n">
-        <v>274.9815360542478</v>
+        <v>275.9488654308047</v>
       </c>
       <c r="D31" t="n">
-        <v>270.9624767916609</v>
+        <v>271.3513641926929</v>
       </c>
       <c r="E31" t="n">
-        <v>272.7276611328125</v>
+        <v>272.2090454101562</v>
       </c>
       <c r="F31" t="n">
-        <v>48398000</v>
+        <v>49602800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>273.3659002679155</v>
+        <v>270.3142081927936</v>
       </c>
       <c r="C32" t="n">
-        <v>275.9488963676571</v>
+        <v>275.2108833889591</v>
       </c>
       <c r="D32" t="n">
-        <v>271.3513946141157</v>
+        <v>268.8681625557137</v>
       </c>
       <c r="E32" t="n">
-        <v>272.2090759277344</v>
+        <v>271.6705322265625</v>
       </c>
       <c r="F32" t="n">
-        <v>49602800</v>
+        <v>47431300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>270.3142081927936</v>
+        <v>268.0902717401977</v>
       </c>
       <c r="C33" t="n">
-        <v>275.2108833889591</v>
+        <v>269.7557213346742</v>
       </c>
       <c r="D33" t="n">
-        <v>268.8681625557137</v>
+        <v>265.0086634694927</v>
       </c>
       <c r="E33" t="n">
-        <v>271.6705322265625</v>
+        <v>266.7339477539062</v>
       </c>
       <c r="F33" t="n">
-        <v>47431300</v>
+        <v>45018300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>268.0903024129557</v>
+        <v>269.25705465795</v>
       </c>
       <c r="C34" t="n">
-        <v>269.7557521979796</v>
+        <v>269.9751013080067</v>
       </c>
       <c r="D34" t="n">
-        <v>265.0086937896775</v>
+        <v>264.5997492422933</v>
       </c>
       <c r="E34" t="n">
-        <v>266.7339782714844</v>
+        <v>266.7139892578125</v>
       </c>
       <c r="F34" t="n">
-        <v>45018300</v>
+        <v>45677300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>269.25705465795</v>
+        <v>264.8092197798317</v>
       </c>
       <c r="C35" t="n">
-        <v>269.9751013080067</v>
+        <v>271.4710796703931</v>
       </c>
       <c r="D35" t="n">
-        <v>264.5997492422933</v>
+        <v>264.7793024319747</v>
       </c>
       <c r="E35" t="n">
-        <v>266.7139892578125</v>
+        <v>267.8309936523438</v>
       </c>
       <c r="F35" t="n">
-        <v>45677300</v>
+        <v>40424500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>264.8092197798317</v>
+        <v>270.0948061865016</v>
       </c>
       <c r="C36" t="n">
-        <v>271.4710796703931</v>
+        <v>274.6823253630542</v>
       </c>
       <c r="D36" t="n">
-        <v>264.7793024319747</v>
+        <v>265.1981613886433</v>
       </c>
       <c r="E36" t="n">
-        <v>267.8309936523438</v>
+        <v>265.5272521972656</v>
       </c>
       <c r="F36" t="n">
-        <v>40424500</v>
+        <v>45823600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>270.0948061865016</v>
+        <v>265.2280517805383</v>
       </c>
       <c r="C37" t="n">
-        <v>274.6823253630542</v>
+        <v>272.5879921198442</v>
       </c>
       <c r="D37" t="n">
-        <v>265.1981613886433</v>
+        <v>264.9488130991126</v>
       </c>
       <c r="E37" t="n">
-        <v>265.5272521972656</v>
+        <v>270.7529907226562</v>
       </c>
       <c r="F37" t="n">
-        <v>45823600</v>
+        <v>59030800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>265.2280517805383</v>
+        <v>270.164627965921</v>
       </c>
       <c r="C38" t="n">
-        <v>272.5879921198442</v>
+        <v>276.2480754250445</v>
       </c>
       <c r="D38" t="n">
-        <v>264.9488130991126</v>
+        <v>270.164627965921</v>
       </c>
       <c r="E38" t="n">
-        <v>270.7529907226562</v>
+        <v>275.1710205078125</v>
       </c>
       <c r="F38" t="n">
-        <v>59030800</v>
+        <v>65585800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>270.164627965921</v>
+        <v>274.5227422872206</v>
       </c>
       <c r="C39" t="n">
-        <v>276.2480754250445</v>
+        <v>279.6188865292943</v>
       </c>
       <c r="D39" t="n">
-        <v>270.164627965921</v>
+        <v>274.5028075356392</v>
       </c>
       <c r="E39" t="n">
-        <v>275.1710205078125</v>
+        <v>276.2181396484375</v>
       </c>
       <c r="F39" t="n">
-        <v>65585800</v>
+        <v>46914200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>274.5227422872206</v>
+        <v>276.2082055022192</v>
       </c>
       <c r="C40" t="n">
-        <v>279.6188865292943</v>
+        <v>278.7712367451818</v>
       </c>
       <c r="D40" t="n">
-        <v>274.5028075356392</v>
+        <v>275.8791146523587</v>
       </c>
       <c r="E40" t="n">
-        <v>276.2181396484375</v>
+        <v>276.7966003417969</v>
       </c>
       <c r="F40" t="n">
-        <v>46914200</v>
+        <v>33431400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>276.2081750495132</v>
+        <v>276.5073679150082</v>
       </c>
       <c r="C41" t="n">
-        <v>278.7712060098946</v>
+        <v>278.242634823177</v>
       </c>
       <c r="D41" t="n">
-        <v>275.8790842359358</v>
+        <v>275.2407959413455</v>
       </c>
       <c r="E41" t="n">
-        <v>276.7965698242188</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="F41" t="n">
-        <v>33431400</v>
+        <v>20135600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>276.5073679150082</v>
+        <v>277.2553332443013</v>
       </c>
       <c r="C42" t="n">
-        <v>278.242634823177</v>
+        <v>282.6506510943872</v>
       </c>
       <c r="D42" t="n">
-        <v>275.2407959413455</v>
+        <v>275.3904143522869</v>
       </c>
       <c r="E42" t="n">
-        <v>278.0930480957031</v>
+        <v>282.3315124511719</v>
       </c>
       <c r="F42" t="n">
-        <v>20135600</v>
+        <v>46587700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>277.255303275414</v>
+        <v>282.231773534172</v>
       </c>
       <c r="C43" t="n">
-        <v>282.650620542313</v>
+        <v>286.619823290159</v>
       </c>
       <c r="D43" t="n">
-        <v>275.390384584981</v>
+        <v>281.8627827987557</v>
       </c>
       <c r="E43" t="n">
-        <v>282.3314819335938</v>
+        <v>285.4131164550781</v>
       </c>
       <c r="F43" t="n">
-        <v>46587700</v>
+        <v>53669500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>282.231773534172</v>
+        <v>285.4231155973949</v>
       </c>
       <c r="C44" t="n">
-        <v>286.619823290159</v>
+        <v>287.8365294074879</v>
       </c>
       <c r="D44" t="n">
-        <v>281.8627827987557</v>
+        <v>282.5309633672564</v>
       </c>
       <c r="E44" t="n">
-        <v>285.4131164550781</v>
+        <v>283.378662109375</v>
       </c>
       <c r="F44" t="n">
-        <v>53669500</v>
+        <v>43538700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>285.4231155973949</v>
+        <v>283.3287830094401</v>
       </c>
       <c r="C45" t="n">
-        <v>287.8365294074879</v>
+        <v>283.9570776694276</v>
       </c>
       <c r="D45" t="n">
-        <v>282.5309633672564</v>
+        <v>277.8337308175164</v>
       </c>
       <c r="E45" t="n">
-        <v>283.378662109375</v>
+        <v>279.9380187988281</v>
       </c>
       <c r="F45" t="n">
-        <v>43538700</v>
+        <v>43989100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>283.328813896664</v>
+        <v>279.7784559281641</v>
       </c>
       <c r="C46" t="n">
-        <v>283.9571086251454</v>
+        <v>280.3768332578711</v>
       </c>
       <c r="D46" t="n">
-        <v>277.8337611056945</v>
+        <v>277.2951945750906</v>
       </c>
       <c r="E46" t="n">
-        <v>279.9380493164062</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F46" t="n">
-        <v>43989100</v>
+        <v>47265800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>279.7784559281641</v>
+        <v>277.374989388386</v>
       </c>
       <c r="C47" t="n">
-        <v>280.3768332578711</v>
+        <v>278.9108174051644</v>
       </c>
       <c r="D47" t="n">
-        <v>277.2951945750906</v>
+        <v>275.4003533668138</v>
       </c>
       <c r="E47" t="n">
-        <v>278.0232238769531</v>
+        <v>277.1356506347656</v>
       </c>
       <c r="F47" t="n">
-        <v>47265800</v>
+        <v>38211800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>277.374989388386</v>
+        <v>277.4049325131135</v>
       </c>
       <c r="C48" t="n">
-        <v>278.9108174051644</v>
+        <v>279.2698514894354</v>
       </c>
       <c r="D48" t="n">
-        <v>275.4003533668138</v>
+        <v>276.16830825817</v>
       </c>
       <c r="E48" t="n">
-        <v>277.1356506347656</v>
+        <v>276.4275817871094</v>
       </c>
       <c r="F48" t="n">
-        <v>38211800</v>
+        <v>32193300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>277.4049018876359</v>
+        <v>276.9960211276047</v>
       </c>
       <c r="C49" t="n">
-        <v>279.269820658071</v>
+        <v>278.9905919368044</v>
       </c>
       <c r="D49" t="n">
-        <v>276.1682777692156</v>
+        <v>275.6895796823578</v>
       </c>
       <c r="E49" t="n">
-        <v>276.4275512695312</v>
+        <v>278.0232238769531</v>
       </c>
       <c r="F49" t="n">
-        <v>32193300</v>
+        <v>33038300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>276.9960211276047</v>
+        <v>278.342371275548</v>
       </c>
       <c r="C50" t="n">
-        <v>278.9905919368044</v>
+        <v>278.8310314000742</v>
       </c>
       <c r="D50" t="n">
-        <v>275.6895796823578</v>
+        <v>273.0667227973629</v>
       </c>
       <c r="E50" t="n">
-        <v>278.0232238769531</v>
+        <v>277.2752685546875</v>
       </c>
       <c r="F50" t="n">
-        <v>33038300</v>
+        <v>33248000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>278.342340640522</v>
+        <v>277.1455933469186</v>
       </c>
       <c r="C51" t="n">
-        <v>278.8310007112651</v>
+        <v>278.4620173164318</v>
       </c>
       <c r="D51" t="n">
-        <v>273.0666927429874</v>
+        <v>276.068538557602</v>
       </c>
       <c r="E51" t="n">
-        <v>277.2752380371094</v>
+        <v>277.5245666503906</v>
       </c>
       <c r="F51" t="n">
-        <v>33248000</v>
+        <v>39532900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>277.1456238228236</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="C52" t="n">
-        <v>278.4620479370953</v>
+        <v>279.3894873363706</v>
       </c>
       <c r="D52" t="n">
-        <v>276.0685689150702</v>
+        <v>272.0993337942639</v>
       </c>
       <c r="E52" t="n">
-        <v>277.5245971679688</v>
+        <v>273.3658752441406</v>
       </c>
       <c r="F52" t="n">
-        <v>39532900</v>
+        <v>50409100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>279.3894873363706</v>
+        <v>272.0794134956457</v>
       </c>
       <c r="C53" t="n">
-        <v>279.3894873363706</v>
+        <v>274.752131096348</v>
       </c>
       <c r="D53" t="n">
-        <v>272.0993337942639</v>
+        <v>271.0522107383373</v>
       </c>
       <c r="E53" t="n">
-        <v>273.3658752441406</v>
+        <v>273.8645324707031</v>
       </c>
       <c r="F53" t="n">
-        <v>50409100</v>
+        <v>37648600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>272.0794134956457</v>
+        <v>274.2634587890498</v>
       </c>
       <c r="C54" t="n">
-        <v>274.752131096348</v>
+        <v>275.4103308752873</v>
       </c>
       <c r="D54" t="n">
-        <v>271.0522107383373</v>
+        <v>270.9026119684932</v>
       </c>
       <c r="E54" t="n">
-        <v>273.8645324707031</v>
+        <v>271.10205078125</v>
       </c>
       <c r="F54" t="n">
-        <v>37648600</v>
+        <v>50138700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>274.2634896625032</v>
+        <v>272.8672697170699</v>
       </c>
       <c r="C55" t="n">
-        <v>275.4103618778425</v>
+        <v>272.887234905205</v>
       </c>
       <c r="D55" t="n">
-        <v>270.9026424636208</v>
+        <v>266.225375101995</v>
       </c>
       <c r="E55" t="n">
-        <v>271.1020812988281</v>
+        <v>271.4511413574219</v>
       </c>
       <c r="F55" t="n">
-        <v>50138700</v>
+        <v>51630700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>272.8672390402853</v>
+        <v>271.4112306527045</v>
       </c>
       <c r="C56" t="n">
-        <v>272.8872042261758</v>
+        <v>273.8545921928022</v>
       </c>
       <c r="D56" t="n">
-        <v>266.2253451719176</v>
+        <v>269.1673383776201</v>
       </c>
       <c r="E56" t="n">
-        <v>271.4511108398438</v>
+        <v>272.9271240234375</v>
       </c>
       <c r="F56" t="n">
-        <v>51630700</v>
+        <v>144632000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>271.4112610007817</v>
+        <v>272.1192896847017</v>
       </c>
       <c r="C57" t="n">
-        <v>273.854622814086</v>
+        <v>273.1365403084993</v>
       </c>
       <c r="D57" t="n">
-        <v>269.1673684747946</v>
+        <v>269.7756932559407</v>
       </c>
       <c r="E57" t="n">
-        <v>272.9271545410156</v>
+        <v>270.2344360351562</v>
       </c>
       <c r="F57" t="n">
-        <v>144632000</v>
+        <v>36571800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>272.1192896847017</v>
+        <v>270.1048034873943</v>
       </c>
       <c r="C58" t="n">
-        <v>273.1365403084993</v>
+        <v>271.7603010837797</v>
       </c>
       <c r="D58" t="n">
-        <v>269.7756932559407</v>
+        <v>268.8282792538215</v>
       </c>
       <c r="E58" t="n">
-        <v>270.2344360351562</v>
+        <v>271.6206665039062</v>
       </c>
       <c r="F58" t="n">
-        <v>36571800</v>
+        <v>29642000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>270.1048034873943</v>
+        <v>271.6007006785171</v>
       </c>
       <c r="C59" t="n">
-        <v>271.7603010837797</v>
+        <v>274.6823088952694</v>
       </c>
       <c r="D59" t="n">
-        <v>268.8282792538215</v>
+        <v>271.461096549353</v>
       </c>
       <c r="E59" t="n">
-        <v>271.6206665039062</v>
+        <v>273.0667114257812</v>
       </c>
       <c r="F59" t="n">
-        <v>29642000</v>
+        <v>17910600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>271.6007006785171</v>
+        <v>273.4158142002898</v>
       </c>
       <c r="C60" t="n">
-        <v>274.6823088952694</v>
+        <v>274.6225212124231</v>
       </c>
       <c r="D60" t="n">
-        <v>271.461096549353</v>
+        <v>272.1193247047194</v>
       </c>
       <c r="E60" t="n">
-        <v>273.0667114257812</v>
+        <v>272.6578674316406</v>
       </c>
       <c r="F60" t="n">
-        <v>17910600</v>
+        <v>21521800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>273.4157835978775</v>
+        <v>271.9497734782625</v>
       </c>
       <c r="C61" t="n">
-        <v>274.6224904749486</v>
+        <v>273.6152231466168</v>
       </c>
       <c r="D61" t="n">
-        <v>272.1192942474183</v>
+        <v>271.6107000753325</v>
       </c>
       <c r="E61" t="n">
-        <v>272.6578369140625</v>
+        <v>273.0168762207031</v>
       </c>
       <c r="F61" t="n">
-        <v>21521800</v>
+        <v>23715200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>271.9497734782625</v>
+        <v>272.0694279800995</v>
       </c>
       <c r="C62" t="n">
-        <v>273.6152231466168</v>
+        <v>273.3359694836473</v>
       </c>
       <c r="D62" t="n">
-        <v>271.6107000753325</v>
+        <v>271.5408679346324</v>
       </c>
       <c r="E62" t="n">
-        <v>273.0168762207031</v>
+        <v>272.3386840820312</v>
       </c>
       <c r="F62" t="n">
-        <v>23715200</v>
+        <v>22139600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>272.0694279800995</v>
+        <v>272.3187639976345</v>
       </c>
       <c r="C63" t="n">
-        <v>273.3359694836473</v>
+        <v>272.9370761103812</v>
       </c>
       <c r="D63" t="n">
-        <v>271.5408679346324</v>
+        <v>271.0123224859311</v>
       </c>
       <c r="E63" t="n">
-        <v>272.3386840820312</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="F63" t="n">
-        <v>22139600</v>
+        <v>27293600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>272.3187639976345</v>
+        <v>271.5209599020358</v>
       </c>
       <c r="C64" t="n">
-        <v>272.9370761103812</v>
+        <v>277.0857995993762</v>
       </c>
       <c r="D64" t="n">
-        <v>271.0123224859311</v>
+        <v>268.2697994337228</v>
       </c>
       <c r="E64" t="n">
-        <v>271.1220092773438</v>
+        <v>270.2743530273438</v>
       </c>
       <c r="F64" t="n">
-        <v>27293600</v>
+        <v>37838100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>271.5209599020358</v>
+        <v>269.9053759278346</v>
       </c>
       <c r="C65" t="n">
-        <v>277.0857995993762</v>
+        <v>270.7730094869922</v>
       </c>
       <c r="D65" t="n">
-        <v>268.2697994337228</v>
+        <v>265.417590951718</v>
       </c>
       <c r="E65" t="n">
-        <v>270.2743530273438</v>
+        <v>266.5345458984375</v>
       </c>
       <c r="F65" t="n">
-        <v>37838100</v>
+        <v>45647200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>269.9053759278346</v>
+        <v>266.2752467950493</v>
       </c>
       <c r="C66" t="n">
-        <v>270.7730094869922</v>
+        <v>266.8237416838396</v>
       </c>
       <c r="D66" t="n">
-        <v>265.417590951718</v>
+        <v>261.4084883511094</v>
       </c>
       <c r="E66" t="n">
-        <v>266.5345458984375</v>
+        <v>261.6478271484375</v>
       </c>
       <c r="F66" t="n">
-        <v>45647200</v>
+        <v>52352100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>266.2751846804448</v>
+        <v>262.485556491205</v>
       </c>
       <c r="C67" t="n">
-        <v>266.8236794412865</v>
+        <v>262.9642340542807</v>
       </c>
       <c r="D67" t="n">
-        <v>261.4084273717842</v>
+        <v>259.1047440282917</v>
       </c>
       <c r="E67" t="n">
-        <v>261.6477661132812</v>
+        <v>259.6233215332031</v>
       </c>
       <c r="F67" t="n">
-        <v>52352100</v>
+        <v>48309800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>262.485556491205</v>
+        <v>256.3222864925608</v>
       </c>
       <c r="C68" t="n">
-        <v>262.9642340542807</v>
+        <v>258.586143863599</v>
       </c>
       <c r="D68" t="n">
-        <v>259.1047440282917</v>
+        <v>255.0058776573516</v>
       </c>
       <c r="E68" t="n">
-        <v>259.6233215332031</v>
+        <v>258.3368225097656</v>
       </c>
       <c r="F68" t="n">
-        <v>48309800</v>
+        <v>50419300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>256.3223167721599</v>
+        <v>258.3767027680543</v>
       </c>
       <c r="C69" t="n">
-        <v>258.5861744106298</v>
+        <v>259.5036402038468</v>
       </c>
       <c r="D69" t="n">
-        <v>255.005907781442</v>
+        <v>255.524480970152</v>
       </c>
       <c r="E69" t="n">
-        <v>258.3368530273438</v>
+        <v>258.6659240722656</v>
       </c>
       <c r="F69" t="n">
-        <v>50419300</v>
+        <v>39997000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>258.3767027680543</v>
+        <v>258.4564806630801</v>
       </c>
       <c r="C70" t="n">
-        <v>259.5036402038468</v>
+        <v>260.5906555331263</v>
       </c>
       <c r="D70" t="n">
-        <v>255.524480970152</v>
+        <v>256.1028713590674</v>
       </c>
       <c r="E70" t="n">
-        <v>258.6659240722656</v>
+        <v>259.5435180664062</v>
       </c>
       <c r="F70" t="n">
-        <v>39997000</v>
+        <v>45263800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>258.4564806630801</v>
+        <v>258.017707787092</v>
       </c>
       <c r="C71" t="n">
-        <v>260.5906555331263</v>
+        <v>261.0993163539261</v>
       </c>
       <c r="D71" t="n">
-        <v>256.1028713590674</v>
+        <v>257.6886169608135</v>
       </c>
       <c r="E71" t="n">
-        <v>259.5435180664062</v>
+        <v>260.3413696289062</v>
       </c>
       <c r="F71" t="n">
-        <v>45263800</v>
+        <v>45730800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>258.017707787092</v>
+        <v>258.7855776250856</v>
       </c>
       <c r="C72" t="n">
-        <v>261.0993163539261</v>
+        <v>261.1092696408236</v>
       </c>
       <c r="D72" t="n">
-        <v>257.6886169608135</v>
+        <v>256.0131254420647</v>
       </c>
       <c r="E72" t="n">
-        <v>260.3413696289062</v>
+        <v>259.2543029785156</v>
       </c>
       <c r="F72" t="n">
-        <v>45730800</v>
+        <v>40019400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>258.7856080874888</v>
+        <v>259.9424734235133</v>
       </c>
       <c r="C73" t="n">
-        <v>261.1093003767552</v>
+        <v>260.3314293980394</v>
       </c>
       <c r="D73" t="n">
-        <v>256.0131555781144</v>
+        <v>256.352239344094</v>
       </c>
       <c r="E73" t="n">
-        <v>259.2543334960938</v>
+        <v>257.5090942382812</v>
       </c>
       <c r="F73" t="n">
-        <v>40019400</v>
+        <v>39388600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>259.9424426175537</v>
+        <v>257.1998957308392</v>
       </c>
       <c r="C74" t="n">
-        <v>260.3313985459844</v>
+        <v>258.1971811198186</v>
       </c>
       <c r="D74" t="n">
-        <v>256.3522089636155</v>
+        <v>254.237956908181</v>
       </c>
       <c r="E74" t="n">
-        <v>257.5090637207031</v>
+        <v>254.8363342285156</v>
       </c>
       <c r="F74" t="n">
-        <v>39388600</v>
+        <v>72142800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>257.1999265314624</v>
+        <v>252.0439493025651</v>
       </c>
       <c r="C75" t="n">
-        <v>258.1972120398704</v>
+        <v>254.0983549093351</v>
       </c>
       <c r="D75" t="n">
-        <v>254.2379873541013</v>
+        <v>242.7592241320914</v>
       </c>
       <c r="E75" t="n">
-        <v>254.8363647460938</v>
+        <v>246.0303192138672</v>
       </c>
       <c r="F75" t="n">
-        <v>72142800</v>
+        <v>80267500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>252.0439493025651</v>
+        <v>248.0248902004531</v>
       </c>
       <c r="C76" t="n">
-        <v>254.0983549093351</v>
+        <v>250.8771272171802</v>
       </c>
       <c r="D76" t="n">
-        <v>242.7592241320914</v>
+        <v>244.5144411297041</v>
       </c>
       <c r="E76" t="n">
-        <v>246.0303192138672</v>
+        <v>246.9777374267578</v>
       </c>
       <c r="F76" t="n">
-        <v>80267500</v>
+        <v>54641700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>248.0249055239374</v>
+        <v>248.523525769064</v>
       </c>
       <c r="C77" t="n">
-        <v>250.8771427168815</v>
+        <v>250.3186425840567</v>
       </c>
       <c r="D77" t="n">
-        <v>244.5144562363057</v>
+        <v>247.4763730255375</v>
       </c>
       <c r="E77" t="n">
-        <v>246.9777526855469</v>
+        <v>247.6758422851562</v>
       </c>
       <c r="F77" t="n">
-        <v>54641700</v>
+        <v>39708300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>248.523525769064</v>
+        <v>246.6486371992728</v>
       </c>
       <c r="C78" t="n">
-        <v>250.3186425840567</v>
+        <v>248.7329600733879</v>
       </c>
       <c r="D78" t="n">
-        <v>247.4763730255375</v>
+        <v>244.0157890837153</v>
       </c>
       <c r="E78" t="n">
-        <v>247.6758422851562</v>
+        <v>247.3666687011719</v>
       </c>
       <c r="F78" t="n">
-        <v>39708300</v>
+        <v>41689000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>246.6486524137701</v>
+        <v>250.7973501838168</v>
       </c>
       <c r="C79" t="n">
-        <v>248.7329754164565</v>
+        <v>255.8635622873743</v>
       </c>
       <c r="D79" t="n">
-        <v>244.0158041358057</v>
+        <v>249.121917868832</v>
       </c>
       <c r="E79" t="n">
-        <v>247.3666839599609</v>
+        <v>254.7166900634766</v>
       </c>
       <c r="F79" t="n">
-        <v>41689000</v>
+        <v>55969200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>250.7973351598156</v>
+        <v>258.4664899667647</v>
       </c>
       <c r="C80" t="n">
-        <v>255.863546959882</v>
+        <v>261.2389423700868</v>
       </c>
       <c r="D80" t="n">
-        <v>249.1219029451975</v>
+        <v>257.5090739976807</v>
       </c>
       <c r="E80" t="n">
-        <v>254.7166748046875</v>
+        <v>257.5689086914062</v>
       </c>
       <c r="F80" t="n">
-        <v>55969200</v>
+        <v>49648300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>258.4664899667647</v>
+        <v>256.9505880888889</v>
       </c>
       <c r="C81" t="n">
-        <v>261.2389423700868</v>
+        <v>258.1572949521919</v>
       </c>
       <c r="D81" t="n">
-        <v>257.5090739976807</v>
+        <v>253.8191124091609</v>
       </c>
       <c r="E81" t="n">
-        <v>257.5689086914062</v>
+        <v>255.7438812255859</v>
       </c>
       <c r="F81" t="n">
-        <v>49648300</v>
+        <v>41288000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>256.9505880888889</v>
+        <v>257.2996492274485</v>
       </c>
       <c r="C82" t="n">
-        <v>258.1572949521919</v>
+        <v>258.9451641530022</v>
       </c>
       <c r="D82" t="n">
-        <v>253.8191124091609</v>
+        <v>253.7193980705993</v>
       </c>
       <c r="E82" t="n">
-        <v>255.7438812255859</v>
+        <v>257.5788879394531</v>
       </c>
       <c r="F82" t="n">
-        <v>41288000</v>
+        <v>67253000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>257.2996187429542</v>
+        <v>254.4773517832236</v>
       </c>
       <c r="C83" t="n">
-        <v>258.9451334735496</v>
+        <v>261.1890792690021</v>
       </c>
       <c r="D83" t="n">
-        <v>253.719368010288</v>
+        <v>251.4954625126288</v>
       </c>
       <c r="E83" t="n">
-        <v>257.578857421875</v>
+        <v>258.7756652832031</v>
       </c>
       <c r="F83" t="n">
-        <v>67253000</v>
+        <v>92443400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>254.4773217725483</v>
+        <v>259.3241194003358</v>
       </c>
       <c r="C84" t="n">
-        <v>261.1890484668085</v>
+        <v>269.7557160843994</v>
       </c>
       <c r="D84" t="n">
-        <v>251.4954328536096</v>
+        <v>258.5063380741307</v>
       </c>
       <c r="E84" t="n">
-        <v>258.775634765625</v>
+        <v>269.2770385742188</v>
       </c>
       <c r="F84" t="n">
-        <v>92443400</v>
+        <v>73913400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>259.3241487899344</v>
+        <v>268.4692659190308</v>
       </c>
       <c r="C85" t="n">
-        <v>269.7557466562268</v>
+        <v>271.1419837262723</v>
       </c>
       <c r="D85" t="n">
-        <v>258.5063673710488</v>
+        <v>266.8835552083235</v>
       </c>
       <c r="E85" t="n">
-        <v>269.2770690917969</v>
+        <v>268.7485046386719</v>
       </c>
       <c r="F85" t="n">
-        <v>73913400</v>
+        <v>64394700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>268.4692659190308</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="C86" t="n">
-        <v>271.1419837262723</v>
+        <v>278.1927542185059</v>
       </c>
       <c r="D86" t="n">
-        <v>266.8835552083235</v>
+        <v>271.5508302866565</v>
       </c>
       <c r="E86" t="n">
-        <v>268.7485046386719</v>
+        <v>275.7394104003906</v>
       </c>
       <c r="F86" t="n">
-        <v>64394700</v>
+        <v>90545700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>271.5508603406617</v>
+        <v>277.3750162493594</v>
       </c>
       <c r="C87" t="n">
-        <v>278.1927850076088</v>
+        <v>278.7412924914769</v>
       </c>
       <c r="D87" t="n">
-        <v>271.5508603406617</v>
+        <v>272.48832346973</v>
       </c>
       <c r="E87" t="n">
-        <v>275.7394409179688</v>
+        <v>275.1610412597656</v>
       </c>
       <c r="F87" t="n">
-        <v>90545700</v>
+        <v>52977400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>277.3749854862336</v>
+        <v>276.3677049075235</v>
       </c>
       <c r="C88" t="n">
-        <v>278.7412615768201</v>
+        <v>280.1474248180158</v>
       </c>
       <c r="D88" t="n">
-        <v>272.4882932485779</v>
+        <v>276.1782182606431</v>
       </c>
       <c r="E88" t="n">
-        <v>275.1610107421875</v>
+        <v>277.364990234375</v>
       </c>
       <c r="F88" t="n">
-        <v>52977400</v>
+        <v>50453400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,25 +2731,25 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>276.3677657232236</v>
+        <v>277.4149461987041</v>
       </c>
       <c r="C89" t="n">
-        <v>280.1474864654567</v>
+        <v>277.7044381343181</v>
       </c>
       <c r="D89" t="n">
-        <v>276.1782790346459</v>
+        <v>271.2160169672847</v>
       </c>
       <c r="E89" t="n">
-        <v>277.3650512695312</v>
+        <v>274.1307983398438</v>
       </c>
       <c r="F89" t="n">
-        <v>50453400</v>
+        <v>44623400</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2757,25 +2757,25 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>277.4149461987041</v>
+        <v>274.4003102195724</v>
       </c>
       <c r="C90" t="n">
-        <v>277.7044381343181</v>
+        <v>274.8794356243012</v>
       </c>
       <c r="D90" t="n">
-        <v>271.2160169672847</v>
+        <v>272.4537718732244</v>
       </c>
       <c r="E90" t="n">
-        <v>274.1307983398438</v>
+        <v>273.1924438476562</v>
       </c>
       <c r="F90" t="n">
-        <v>44623400</v>
+        <v>34376900</v>
       </c>
       <c r="G90" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>274.4003102195724</v>
+        <v>274.2106536370846</v>
       </c>
       <c r="C91" t="n">
-        <v>274.8794356243012</v>
+        <v>279.6808719096702</v>
       </c>
       <c r="D91" t="n">
-        <v>272.4537718732244</v>
+        <v>273.9610989943363</v>
       </c>
       <c r="E91" t="n">
-        <v>273.1924438476562</v>
+        <v>275.0092163085938</v>
       </c>
       <c r="F91" t="n">
-        <v>34376900</v>
+        <v>51931300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>274.2106536370846</v>
+        <v>275.0990906441111</v>
       </c>
       <c r="C92" t="n">
-        <v>279.6808719096702</v>
+        <v>275.228863950531</v>
       </c>
       <c r="D92" t="n">
-        <v>273.9610989943363</v>
+        <v>259.7165366668213</v>
       </c>
       <c r="E92" t="n">
-        <v>275.0092163085938</v>
+        <v>261.2637939453125</v>
       </c>
       <c r="F92" t="n">
-        <v>51931300</v>
+        <v>81077200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>275.0990585104662</v>
+        <v>261.5432690161623</v>
       </c>
       <c r="C93" t="n">
-        <v>275.2288318017276</v>
+        <v>261.7628783299504</v>
       </c>
       <c r="D93" t="n">
-        <v>259.7165063299744</v>
+        <v>254.9949421084194</v>
       </c>
       <c r="E93" t="n">
-        <v>261.2637634277344</v>
+        <v>255.3243560791016</v>
       </c>
       <c r="F93" t="n">
-        <v>81077200</v>
+        <v>56290700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>261.5432690161623</v>
+        <v>257.5903108294174</v>
       </c>
       <c r="C94" t="n">
-        <v>261.7628783299504</v>
+        <v>265.8156532326085</v>
       </c>
       <c r="D94" t="n">
-        <v>254.9949421084194</v>
+        <v>255.0847874975786</v>
       </c>
       <c r="E94" t="n">
-        <v>255.3243560791016</v>
+        <v>263.4099426269531</v>
       </c>
       <c r="F94" t="n">
-        <v>56290700</v>
+        <v>58469100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>257.5903108294174</v>
+        <v>263.1304558468116</v>
       </c>
       <c r="C95" t="n">
-        <v>265.8156532326085</v>
+        <v>266.3447212846438</v>
       </c>
       <c r="D95" t="n">
-        <v>255.0847874975786</v>
+        <v>261.9825104325609</v>
       </c>
       <c r="E95" t="n">
-        <v>263.4099426269531</v>
+        <v>263.8791198730469</v>
       </c>
       <c r="F95" t="n">
-        <v>58469100</v>
+        <v>34203300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>263.1304558468116</v>
+        <v>262.1322047157328</v>
       </c>
       <c r="C96" t="n">
-        <v>266.3447212846438</v>
+        <v>264.0088605167754</v>
       </c>
       <c r="D96" t="n">
-        <v>261.9825104325609</v>
+        <v>259.5867290635135</v>
       </c>
       <c r="E96" t="n">
-        <v>263.8791198730469</v>
+        <v>260.1157836914062</v>
       </c>
       <c r="F96" t="n">
-        <v>34203300</v>
+        <v>30845300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>262.1322047157328</v>
+        <v>258.5086811746104</v>
       </c>
       <c r="C97" t="n">
-        <v>264.0088605167754</v>
+        <v>264.2783836675007</v>
       </c>
       <c r="D97" t="n">
-        <v>259.5867290635135</v>
+        <v>257.7001265171608</v>
       </c>
       <c r="E97" t="n">
-        <v>260.1157836914062</v>
+        <v>264.1086730957031</v>
       </c>
       <c r="F97" t="n">
-        <v>30845300</v>
+        <v>42070500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>258.5086811746104</v>
+        <v>263.0206001676805</v>
       </c>
       <c r="C98" t="n">
-        <v>264.2783836675007</v>
+        <v>268.9500208858886</v>
       </c>
       <c r="D98" t="n">
-        <v>257.7001265171608</v>
+        <v>262.9108107477792</v>
       </c>
       <c r="E98" t="n">
-        <v>264.1086730957031</v>
+        <v>265.705810546875</v>
       </c>
       <c r="F98" t="n">
-        <v>42070500</v>
+        <v>37308200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>263.0206001676805</v>
+        <v>267.3828377763821</v>
       </c>
       <c r="C99" t="n">
-        <v>268.9500208858886</v>
+        <v>274.4003442568012</v>
       </c>
       <c r="D99" t="n">
-        <v>262.9108107477792</v>
+        <v>267.233111068832</v>
       </c>
       <c r="E99" t="n">
-        <v>265.705810546875</v>
+        <v>271.6552429199219</v>
       </c>
       <c r="F99" t="n">
-        <v>37308200</v>
+        <v>47014600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>267.3828377763821</v>
+        <v>271.295868192995</v>
       </c>
       <c r="C100" t="n">
-        <v>274.4003442568012</v>
+        <v>274.450242837397</v>
       </c>
       <c r="D100" t="n">
-        <v>267.233111068832</v>
+        <v>270.567157599074</v>
       </c>
       <c r="E100" t="n">
-        <v>271.6552429199219</v>
+        <v>273.7415161132812</v>
       </c>
       <c r="F100" t="n">
-        <v>47014600</v>
+        <v>33714300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>271.295868192995</v>
+        <v>274.4602128097023</v>
       </c>
       <c r="C101" t="n">
-        <v>274.450242837397</v>
+        <v>275.6181195635374</v>
       </c>
       <c r="D101" t="n">
-        <v>270.567157599074</v>
+        <v>270.3175813011377</v>
       </c>
       <c r="E101" t="n">
-        <v>273.7415161132812</v>
+        <v>272.4637756347656</v>
       </c>
       <c r="F101" t="n">
-        <v>33714300</v>
+        <v>32345100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>274.4602128097023</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="C102" t="n">
-        <v>275.6181195635374</v>
+        <v>272.3240124520744</v>
       </c>
       <c r="D102" t="n">
-        <v>270.3175813011377</v>
+        <v>262.4217010495403</v>
       </c>
       <c r="E102" t="n">
-        <v>272.4637756347656</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="F102" t="n">
-        <v>32345100</v>
+        <v>72366500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>272.3240439665745</v>
+        <v>261.9425306959557</v>
       </c>
       <c r="C103" t="n">
-        <v>272.3240439665745</v>
+        <v>266.0551862059975</v>
       </c>
       <c r="D103" t="n">
-        <v>262.4217314181026</v>
+        <v>259.7364762526007</v>
       </c>
       <c r="E103" t="n">
-        <v>263.7094116210938</v>
+        <v>264.2484130859375</v>
       </c>
       <c r="F103" t="n">
-        <v>72366500</v>
+        <v>41827900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>261.9425306959557</v>
+        <v>263.0106738027697</v>
       </c>
       <c r="C104" t="n">
-        <v>266.0551862059975</v>
+        <v>265.0869552930596</v>
       </c>
       <c r="D104" t="n">
-        <v>259.7364762526007</v>
+        <v>259.6666350681776</v>
       </c>
       <c r="E104" t="n">
-        <v>264.2484130859375</v>
+        <v>263.2801818847656</v>
       </c>
       <c r="F104" t="n">
-        <v>41827900</v>
+        <v>38568900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>263.0106738027697</v>
+        <v>264.1785481527265</v>
       </c>
       <c r="C105" t="n">
-        <v>265.0869552930596</v>
+        <v>265.6758760626757</v>
       </c>
       <c r="D105" t="n">
-        <v>259.6666350681776</v>
+        <v>260.9543215497598</v>
       </c>
       <c r="E105" t="n">
-        <v>263.2801818847656</v>
+        <v>262.0523376464844</v>
       </c>
       <c r="F105" t="n">
-        <v>38568900</v>
+        <v>39803100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>264.1785481527265</v>
+        <v>260.3254337562426</v>
       </c>
       <c r="C106" t="n">
-        <v>265.6758760626757</v>
+        <v>261.0940511012478</v>
       </c>
       <c r="D106" t="n">
-        <v>260.9543215497598</v>
+        <v>256.7917314296105</v>
       </c>
       <c r="E106" t="n">
-        <v>262.0523376464844</v>
+        <v>259.8263244628906</v>
       </c>
       <c r="F106" t="n">
-        <v>39803100</v>
+        <v>49658600</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>260.3254337562426</v>
+        <v>258.1692718962937</v>
       </c>
       <c r="C107" t="n">
-        <v>261.0940511012478</v>
+        <v>258.3090066542827</v>
       </c>
       <c r="D107" t="n">
-        <v>256.7917314296105</v>
+        <v>253.916851068475</v>
       </c>
       <c r="E107" t="n">
-        <v>259.8263244628906</v>
+        <v>257.0013427734375</v>
       </c>
       <c r="F107" t="n">
-        <v>49658600</v>
+        <v>41120000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>258.1692718962937</v>
+        <v>255.2345148744848</v>
       </c>
       <c r="C108" t="n">
-        <v>258.3090066542827</v>
+        <v>260.6847798709625</v>
       </c>
       <c r="D108" t="n">
-        <v>253.916851068475</v>
+        <v>253.2280857512349</v>
       </c>
       <c r="E108" t="n">
-        <v>257.0013427734375</v>
+        <v>259.4170532226562</v>
       </c>
       <c r="F108" t="n">
-        <v>41120000</v>
+        <v>38218500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>255.2345148744848</v>
+        <v>257.1910284571696</v>
       </c>
       <c r="C109" t="n">
-        <v>260.6847798709625</v>
+        <v>262.0124415843973</v>
       </c>
       <c r="D109" t="n">
-        <v>253.2280857512349</v>
+        <v>256.4922936817907</v>
       </c>
       <c r="E109" t="n">
-        <v>259.4170532226562</v>
+        <v>260.3653564453125</v>
       </c>
       <c r="F109" t="n">
-        <v>38218500</v>
+        <v>30590800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>257.1910284571696</v>
+        <v>260.6248673962081</v>
       </c>
       <c r="C110" t="n">
-        <v>262.0124415843973</v>
+        <v>261.6630231774062</v>
       </c>
       <c r="D110" t="n">
-        <v>256.4922936817907</v>
+        <v>259.0876023594815</v>
       </c>
       <c r="E110" t="n">
-        <v>260.3653564453125</v>
+        <v>260.3453674316406</v>
       </c>
       <c r="F110" t="n">
-        <v>30590800</v>
+        <v>26218900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>260.624897946549</v>
+        <v>258.1992253881205</v>
       </c>
       <c r="C111" t="n">
-        <v>261.6630538494394</v>
+        <v>258.4887173103141</v>
       </c>
       <c r="D111" t="n">
-        <v>259.0876327296249</v>
+        <v>253.7271951166323</v>
       </c>
       <c r="E111" t="n">
-        <v>260.3453979492188</v>
+        <v>255.3043823242188</v>
       </c>
       <c r="F111" t="n">
-        <v>26218900</v>
+        <v>40794000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>258.1992408199258</v>
+        <v>255.024890934378</v>
       </c>
       <c r="C112" t="n">
-        <v>258.4887327594216</v>
+        <v>255.8733676296054</v>
       </c>
       <c r="D112" t="n">
-        <v>253.7272102811576</v>
+        <v>249.0755164384504</v>
       </c>
       <c r="E112" t="n">
-        <v>255.3043975830078</v>
+        <v>249.6744384765625</v>
       </c>
       <c r="F112" t="n">
-        <v>40794000</v>
+        <v>36930000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>255.024890934378</v>
+        <v>251.6609022279199</v>
       </c>
       <c r="C113" t="n">
-        <v>255.8733676296054</v>
+        <v>253.4377301906265</v>
       </c>
       <c r="D113" t="n">
-        <v>249.0755164384504</v>
+        <v>249.4348789230203</v>
       </c>
       <c r="E113" t="n">
-        <v>249.6744384765625</v>
+        <v>252.3696441650391</v>
       </c>
       <c r="F113" t="n">
-        <v>36930000</v>
+        <v>32074200</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>251.6609022279199</v>
+        <v>252.5093881906664</v>
       </c>
       <c r="C114" t="n">
-        <v>253.4377301906265</v>
+        <v>254.6755207628997</v>
       </c>
       <c r="D114" t="n">
-        <v>249.4348789230203</v>
+        <v>251.7307636559193</v>
       </c>
       <c r="E114" t="n">
-        <v>252.3696441650391</v>
+        <v>253.7771148681641</v>
       </c>
       <c r="F114" t="n">
-        <v>32074200</v>
+        <v>32361600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>252.5093881906664</v>
+        <v>252.1799767808244</v>
       </c>
       <c r="C115" t="n">
-        <v>254.6755207628997</v>
+        <v>254.4858593736706</v>
       </c>
       <c r="D115" t="n">
-        <v>251.7307636559193</v>
+        <v>248.5564382882904</v>
       </c>
       <c r="E115" t="n">
-        <v>253.7771148681641</v>
+        <v>249.4947662353516</v>
       </c>
       <c r="F115" t="n">
-        <v>32361600</v>
+        <v>35757900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>252.1799767808244</v>
+        <v>248.9557286861236</v>
       </c>
       <c r="C116" t="n">
-        <v>254.4858593736706</v>
+        <v>251.3814079598573</v>
       </c>
       <c r="D116" t="n">
-        <v>248.5564382882904</v>
+        <v>246.8594786308807</v>
       </c>
       <c r="E116" t="n">
-        <v>249.4947662353516</v>
+        <v>248.5165252685547</v>
       </c>
       <c r="F116" t="n">
-        <v>35757900</v>
+        <v>34864100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>248.9557286861236</v>
+        <v>247.5382410981218</v>
       </c>
       <c r="C117" t="n">
-        <v>251.3814079598573</v>
+        <v>248.7560689935711</v>
       </c>
       <c r="D117" t="n">
-        <v>246.8594786308807</v>
+        <v>245.5617725594444</v>
       </c>
       <c r="E117" t="n">
-        <v>248.5165252685547</v>
+        <v>247.5482330322266</v>
       </c>
       <c r="F117" t="n">
-        <v>34864100</v>
+        <v>88331100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>247.5382410981218</v>
+        <v>253.5175853710609</v>
       </c>
       <c r="C118" t="n">
-        <v>248.7560689935711</v>
+        <v>254.1464679788293</v>
       </c>
       <c r="D118" t="n">
-        <v>245.5617725594444</v>
+        <v>249.8341562083163</v>
       </c>
       <c r="E118" t="n">
-        <v>247.5482330322266</v>
+        <v>251.0420074462891</v>
       </c>
       <c r="F118" t="n">
-        <v>88331100</v>
+        <v>40546100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>253.5175853710609</v>
+        <v>249.9040313986812</v>
       </c>
       <c r="C119" t="n">
-        <v>254.1464679788293</v>
+        <v>254.3760464402864</v>
       </c>
       <c r="D119" t="n">
-        <v>249.8341562083163</v>
+        <v>249.105453476207</v>
       </c>
       <c r="E119" t="n">
-        <v>251.0420074462891</v>
+        <v>251.1917266845703</v>
       </c>
       <c r="F119" t="n">
-        <v>40546100</v>
+        <v>45152300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>249.9040313986812</v>
+        <v>253.6473574345128</v>
       </c>
       <c r="C120" t="n">
-        <v>254.3760464402864</v>
+        <v>254.5457480998694</v>
       </c>
       <c r="D120" t="n">
-        <v>249.105453476207</v>
+        <v>251.1518108845141</v>
       </c>
       <c r="E120" t="n">
-        <v>251.1917266845703</v>
+        <v>252.1699829101562</v>
       </c>
       <c r="F120" t="n">
-        <v>45152300</v>
+        <v>28476700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>253.6473574345128</v>
+        <v>251.6708815336767</v>
       </c>
       <c r="C121" t="n">
-        <v>254.5457480998694</v>
+        <v>256.5421934269488</v>
       </c>
       <c r="D121" t="n">
-        <v>251.1518108845141</v>
+        <v>250.3232954931613</v>
       </c>
       <c r="E121" t="n">
-        <v>252.1699829101562</v>
+        <v>252.4395141601562</v>
       </c>
       <c r="F121" t="n">
-        <v>28476700</v>
+        <v>41796700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>251.6708815336767</v>
+        <v>253.4477020992108</v>
       </c>
       <c r="C122" t="n">
-        <v>256.5421934269488</v>
+        <v>255.0348812846261</v>
       </c>
       <c r="D122" t="n">
-        <v>250.3232954931613</v>
+        <v>247.6281009352486</v>
       </c>
       <c r="E122" t="n">
-        <v>252.4395141601562</v>
+        <v>248.3567962646484</v>
       </c>
       <c r="F122" t="n">
-        <v>41796700</v>
+        <v>47900000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>253.4477020992108</v>
+        <v>249.6245329956546</v>
       </c>
       <c r="C123" t="n">
-        <v>255.0348812846261</v>
+        <v>250.4230956915925</v>
       </c>
       <c r="D123" t="n">
-        <v>247.6281009352486</v>
+        <v>245.0726433781301</v>
       </c>
       <c r="E123" t="n">
-        <v>248.3567962646484</v>
+        <v>246.1906585693359</v>
       </c>
       <c r="F123" t="n">
-        <v>47900000</v>
+        <v>39446200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>249.6245329956546</v>
+        <v>247.4683756415328</v>
       </c>
       <c r="C124" t="n">
-        <v>250.4230956915925</v>
+        <v>255.0248824882854</v>
       </c>
       <c r="D124" t="n">
-        <v>245.0726433781301</v>
+        <v>246.6598210163149</v>
       </c>
       <c r="E124" t="n">
-        <v>246.1906585693359</v>
+        <v>253.337890625</v>
       </c>
       <c r="F124" t="n">
-        <v>39446200</v>
+        <v>49598100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>247.4683905467953</v>
+        <v>253.6273797300248</v>
       </c>
       <c r="C125" t="n">
-        <v>255.0248978486836</v>
+        <v>255.7236296181179</v>
       </c>
       <c r="D125" t="n">
-        <v>246.6598358728773</v>
+        <v>252.8787157917901</v>
       </c>
       <c r="E125" t="n">
-        <v>253.3379058837891</v>
+        <v>255.1746215820312</v>
       </c>
       <c r="F125" t="n">
-        <v>49598100</v>
+        <v>40059400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>253.6273948962928</v>
+        <v>253.7471740568136</v>
       </c>
       <c r="C126" t="n">
-        <v>255.7236449097363</v>
+        <v>255.6737439434535</v>
       </c>
       <c r="D126" t="n">
-        <v>252.8787309132899</v>
+        <v>250.2034948550391</v>
       </c>
       <c r="E126" t="n">
-        <v>255.1746368408203</v>
+        <v>255.464111328125</v>
       </c>
       <c r="F126" t="n">
-        <v>40059400</v>
+        <v>31289400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>253.7471740568136</v>
+        <v>256.053045051996</v>
       </c>
       <c r="C127" t="n">
-        <v>255.6737439434535</v>
+        <v>261.6929736576745</v>
       </c>
       <c r="D127" t="n">
-        <v>250.2034948550391</v>
+        <v>256.003115847535</v>
       </c>
       <c r="E127" t="n">
-        <v>255.464111328125</v>
+        <v>258.3988342285156</v>
       </c>
       <c r="F127" t="n">
-        <v>31289400</v>
+        <v>29329900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>256.0530752925303</v>
+        <v>255.7036812801697</v>
       </c>
       <c r="C128" t="n">
-        <v>261.6930045642991</v>
+        <v>255.7436185540334</v>
       </c>
       <c r="D128" t="n">
-        <v>256.0031460821725</v>
+        <v>245.2623079794448</v>
       </c>
       <c r="E128" t="n">
-        <v>258.3988647460938</v>
+        <v>253.0484161376953</v>
       </c>
       <c r="F128" t="n">
-        <v>29329900</v>
+        <v>62148000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>255.7036812801697</v>
+        <v>257.9896016596085</v>
       </c>
       <c r="C129" t="n">
-        <v>255.7436185540334</v>
+        <v>259.2872736156141</v>
       </c>
       <c r="D129" t="n">
-        <v>245.2623079794448</v>
+        <v>256.0730086009651</v>
       </c>
       <c r="E129" t="n">
-        <v>253.0484161376953</v>
+        <v>258.4387817382812</v>
       </c>
       <c r="F129" t="n">
-        <v>62148000</v>
+        <v>41032800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>257.9896321241455</v>
+        <v>258.5386040524215</v>
       </c>
       <c r="C130" t="n">
-        <v>259.2873042333858</v>
+        <v>260.6548225010532</v>
       </c>
       <c r="D130" t="n">
-        <v>256.0730388391825</v>
+        <v>255.6138310165902</v>
       </c>
       <c r="E130" t="n">
-        <v>258.4388122558594</v>
+        <v>260.0259399414062</v>
       </c>
       <c r="F130" t="n">
-        <v>41032800</v>
+        <v>28121600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>258.5386343954405</v>
+        <v>259.5168819122501</v>
       </c>
       <c r="C131" t="n">
-        <v>260.6548530924392</v>
+        <v>261.7229364827484</v>
       </c>
       <c r="D131" t="n">
-        <v>255.6138610163474</v>
+        <v>258.5585701252562</v>
       </c>
       <c r="E131" t="n">
-        <v>260.0259704589844</v>
+        <v>260.0159912109375</v>
       </c>
       <c r="F131" t="n">
-        <v>28121600</v>
+        <v>31291500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>259.5168819122501</v>
+        <v>259.2673359057164</v>
       </c>
       <c r="C132" t="n">
-        <v>261.7229364827484</v>
+        <v>259.7165160115803</v>
       </c>
       <c r="D132" t="n">
-        <v>258.5585701252562</v>
+        <v>256.2027973984465</v>
       </c>
       <c r="E132" t="n">
-        <v>260.0159912109375</v>
+        <v>258.73828125</v>
       </c>
       <c r="F132" t="n">
-        <v>31291500</v>
+        <v>36234700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>259.2673359057164</v>
+        <v>258.7881616833942</v>
       </c>
       <c r="C133" t="n">
-        <v>259.7165160115803</v>
+        <v>261.4633801130582</v>
       </c>
       <c r="D133" t="n">
-        <v>256.2027973984465</v>
+        <v>256.7318338868242</v>
       </c>
       <c r="E133" t="n">
-        <v>258.73828125</v>
+        <v>258.368896484375</v>
       </c>
       <c r="F133" t="n">
-        <v>36234700</v>
+        <v>48370700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>258.7881922504944</v>
+        <v>257.7001261657452</v>
       </c>
       <c r="C134" t="n">
-        <v>261.4634109961452</v>
+        <v>266.0851565972939</v>
       </c>
       <c r="D134" t="n">
-        <v>256.7318642110386</v>
+        <v>257.3507435512608</v>
       </c>
       <c r="E134" t="n">
-        <v>258.3689270019531</v>
+        <v>265.9553833007812</v>
       </c>
       <c r="F134" t="n">
-        <v>48370700</v>
+        <v>49913500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>257.7001261657452</v>
+        <v>266.3246925362851</v>
       </c>
       <c r="C135" t="n">
-        <v>266.0851565972939</v>
+        <v>266.6840670491935</v>
       </c>
       <c r="D135" t="n">
-        <v>257.3507435512608</v>
+        <v>260.804545264895</v>
       </c>
       <c r="E135" t="n">
-        <v>265.9553833007812</v>
+        <v>262.9307556152344</v>
       </c>
       <c r="F135" t="n">
-        <v>49913500</v>
+        <v>43323100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>266.3247234477873</v>
+        <v>266.4844323486072</v>
       </c>
       <c r="C136" t="n">
-        <v>266.6840980024072</v>
+        <v>271.8149160854778</v>
       </c>
       <c r="D136" t="n">
-        <v>260.8045755356903</v>
+        <v>266.2448696297591</v>
       </c>
       <c r="E136" t="n">
-        <v>262.9307861328125</v>
+        <v>269.7486267089844</v>
       </c>
       <c r="F136" t="n">
-        <v>43323100</v>
+        <v>61436200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>266.4844323486072</v>
+        <v>269.8484123886765</v>
       </c>
       <c r="C137" t="n">
-        <v>271.8149160854778</v>
+        <v>273.7913879220191</v>
       </c>
       <c r="D137" t="n">
-        <v>266.2448696297591</v>
+        <v>269.8085055794248</v>
       </c>
       <c r="E137" t="n">
-        <v>269.7486267089844</v>
+        <v>272.5635681152344</v>
       </c>
       <c r="F137" t="n">
-        <v>61436200</v>
+        <v>36590200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>269.8484123886765</v>
+        <v>271.0163536236942</v>
       </c>
       <c r="C138" t="n">
-        <v>273.7913879220191</v>
+        <v>272.3140256362382</v>
       </c>
       <c r="D138" t="n">
-        <v>269.8085055794248</v>
+        <v>264.9272139873882</v>
       </c>
       <c r="E138" t="n">
-        <v>272.5635681152344</v>
+        <v>265.6958618164062</v>
       </c>
       <c r="F138" t="n">
-        <v>36590200</v>
+        <v>50209800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>271.0163536236942</v>
+        <v>267.3429346055621</v>
       </c>
       <c r="C139" t="n">
-        <v>272.3140256362382</v>
+        <v>273.2523721409737</v>
       </c>
       <c r="D139" t="n">
-        <v>264.9272139873882</v>
+        <v>266.394614672797</v>
       </c>
       <c r="E139" t="n">
-        <v>265.6958618164062</v>
+        <v>272.6834106445312</v>
       </c>
       <c r="F139" t="n">
-        <v>50209800</v>
+        <v>43249200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>267.3429346055621</v>
+        <v>274.5600108521774</v>
       </c>
       <c r="C140" t="n">
-        <v>273.2523721409737</v>
+        <v>275.2787294551341</v>
       </c>
       <c r="D140" t="n">
-        <v>266.394614672797</v>
+        <v>271.1660737405759</v>
       </c>
       <c r="E140" t="n">
-        <v>272.6834106445312</v>
+        <v>272.9429016113281</v>
       </c>
       <c r="F140" t="n">
-        <v>43249200</v>
+        <v>33399600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>274.5600108521774</v>
+        <v>272.2741016414235</v>
       </c>
       <c r="C141" t="n">
-        <v>275.2787294551341</v>
+        <v>272.5735550213531</v>
       </c>
       <c r="D141" t="n">
-        <v>271.1660737405759</v>
+        <v>269.1696261078274</v>
       </c>
       <c r="E141" t="n">
-        <v>272.9429016113281</v>
+        <v>270.5771179199219</v>
       </c>
       <c r="F141" t="n">
-        <v>33399600</v>
+        <v>38157100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>272.2741016414235</v>
+        <v>265.6159889280984</v>
       </c>
       <c r="C142" t="n">
-        <v>272.5735550213531</v>
+        <v>267.8819342286378</v>
       </c>
       <c r="D142" t="n">
-        <v>269.1696261078274</v>
+        <v>264.5978169025021</v>
       </c>
       <c r="E142" t="n">
-        <v>270.5771179199219</v>
+        <v>267.1332702636719</v>
       </c>
       <c r="F142" t="n">
-        <v>38157100</v>
+        <v>41466800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>265.6159889280984</v>
+        <v>271.8548539018017</v>
       </c>
       <c r="C143" t="n">
-        <v>267.8819342286378</v>
+        <v>272.7432830913257</v>
       </c>
       <c r="D143" t="n">
-        <v>264.5978169025021</v>
+        <v>268.181416710472</v>
       </c>
       <c r="E143" t="n">
-        <v>267.1332702636719</v>
+        <v>270.2277526855469</v>
       </c>
       <c r="F143" t="n">
-        <v>41466800</v>
+        <v>40018900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>271.8548539018017</v>
+        <v>267.0733624970658</v>
       </c>
       <c r="C144" t="n">
-        <v>272.7432830913257</v>
+        <v>270.5571659728108</v>
       </c>
       <c r="D144" t="n">
-        <v>268.181416710472</v>
+        <v>266.5642917484437</v>
       </c>
       <c r="E144" t="n">
-        <v>270.2277526855469</v>
+        <v>269.688720703125</v>
       </c>
       <c r="F144" t="n">
-        <v>40018900</v>
+        <v>30047900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>267.0733624970658</v>
+        <v>270.018146234023</v>
       </c>
       <c r="C145" t="n">
-        <v>270.5571659728108</v>
+        <v>275.5083488376723</v>
       </c>
       <c r="D145" t="n">
-        <v>266.5642917484437</v>
+        <v>267.6623648300734</v>
       </c>
       <c r="E145" t="n">
-        <v>269.688720703125</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="F145" t="n">
-        <v>30047900</v>
+        <v>91848200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>270.018146234023</v>
+        <v>278.3632116979401</v>
       </c>
       <c r="C146" t="n">
-        <v>275.5083488376723</v>
+        <v>286.7083346607987</v>
       </c>
       <c r="D146" t="n">
-        <v>267.6623648300734</v>
+        <v>277.8740943540899</v>
       </c>
       <c r="E146" t="n">
-        <v>270.8666381835938</v>
+        <v>279.6409606933594</v>
       </c>
       <c r="F146" t="n">
-        <v>91848200</v>
+        <v>79915400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>278.3632420760759</v>
+        <v>279.1618288412153</v>
       </c>
       <c r="C147" t="n">
-        <v>286.7083659496485</v>
+        <v>280.130102141665</v>
       </c>
       <c r="D147" t="n">
-        <v>277.8741246788477</v>
+        <v>274.3703610857382</v>
       </c>
       <c r="E147" t="n">
-        <v>279.6409912109375</v>
+        <v>276.3368530273438</v>
       </c>
       <c r="F147" t="n">
-        <v>79915400</v>
+        <v>46668400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>279.1617980116577</v>
+        <v>276.43668191704</v>
       </c>
       <c r="C148" t="n">
-        <v>280.1300712051751</v>
+        <v>284.0630869835518</v>
       </c>
       <c r="D148" t="n">
-        <v>274.3703307853319</v>
+        <v>276.0074552110661</v>
       </c>
       <c r="E148" t="n">
-        <v>276.3368225097656</v>
+        <v>283.6737670898438</v>
       </c>
       <c r="F148" t="n">
-        <v>46668400</v>
+        <v>49311700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>276.43668191704</v>
+        <v>281.4177950537395</v>
       </c>
       <c r="C149" t="n">
-        <v>284.0630869835518</v>
+        <v>287.5168959460148</v>
       </c>
       <c r="D149" t="n">
-        <v>276.0074552110661</v>
+        <v>280.5693031693742</v>
       </c>
       <c r="E149" t="n">
-        <v>283.6737670898438</v>
+        <v>286.9978332519531</v>
       </c>
       <c r="F149" t="n">
-        <v>49311700</v>
+        <v>58336100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>281.4178249779708</v>
+        <v>288.7546745760609</v>
       </c>
       <c r="C150" t="n">
-        <v>287.5169265187869</v>
+        <v>291.6095955251437</v>
       </c>
       <c r="D150" t="n">
-        <v>280.5693330033821</v>
+        <v>285.2709015174152</v>
       </c>
       <c r="E150" t="n">
-        <v>286.9978637695312</v>
+        <v>286.9279479980469</v>
       </c>
       <c r="F150" t="n">
-        <v>58336100</v>
+        <v>45224300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>288.7547052879293</v>
+        <v>289.4933842419345</v>
       </c>
       <c r="C151" t="n">
-        <v>291.6096265406606</v>
+        <v>294.2349225642168</v>
       </c>
       <c r="D151" t="n">
-        <v>285.2709318587503</v>
+        <v>289.4833923077643</v>
       </c>
       <c r="E151" t="n">
-        <v>286.927978515625</v>
+        <v>292.7974853515625</v>
       </c>
       <c r="F151" t="n">
-        <v>45224300</v>
+        <v>52692800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,25 +4369,25 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>289.4933842419345</v>
+        <v>291.7284168827658</v>
       </c>
       <c r="C152" t="n">
-        <v>294.2349225642168</v>
+        <v>293.6267735875138</v>
       </c>
       <c r="D152" t="n">
-        <v>289.4833923077643</v>
+        <v>289.979924827367</v>
       </c>
       <c r="E152" t="n">
-        <v>292.7974853515625</v>
+        <v>292.4277954101562</v>
       </c>
       <c r="F152" t="n">
-        <v>52692800</v>
+        <v>42247300</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4395,25 +4395,25 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>291.7284168827658</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="C153" t="n">
-        <v>293.6267735875138</v>
+        <v>295.0155556946294</v>
       </c>
       <c r="D153" t="n">
-        <v>289.979924827367</v>
+        <v>292.3078994315659</v>
       </c>
       <c r="E153" t="n">
-        <v>292.4277954101562</v>
+        <v>294.5459594726562</v>
       </c>
       <c r="F153" t="n">
-        <v>42247300</v>
+        <v>45748100</v>
       </c>
       <c r="G153" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="C154" t="n">
-        <v>295.0155556946294</v>
+        <v>300.6607090744109</v>
       </c>
       <c r="D154" t="n">
-        <v>292.3078994315659</v>
+        <v>293.247089511151</v>
       </c>
       <c r="E154" t="n">
-        <v>294.5459594726562</v>
+        <v>298.6124572753906</v>
       </c>
       <c r="F154" t="n">
-        <v>45748100</v>
+        <v>52684300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>293.247089511151</v>
+        <v>299.5616620172475</v>
       </c>
       <c r="C155" t="n">
-        <v>300.6607090744109</v>
+        <v>300.1911240450107</v>
       </c>
       <c r="D155" t="n">
-        <v>293.247089511151</v>
+        <v>295.1254853838782</v>
       </c>
       <c r="E155" t="n">
-        <v>298.6124572753906</v>
+        <v>297.9530334472656</v>
       </c>
       <c r="F155" t="n">
-        <v>52684300</v>
+        <v>35324900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>299.5616620172475</v>
+        <v>297.643304079477</v>
       </c>
       <c r="C156" t="n">
-        <v>300.1911240450107</v>
+        <v>302.9387555529706</v>
       </c>
       <c r="D156" t="n">
-        <v>295.1254853838782</v>
+        <v>296.2644882977323</v>
       </c>
       <c r="E156" t="n">
-        <v>297.9530334472656</v>
+        <v>299.9713134765625</v>
       </c>
       <c r="F156" t="n">
-        <v>35324900</v>
+        <v>54862800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>297.643304079477</v>
+        <v>299.9812692945075</v>
       </c>
       <c r="C157" t="n">
-        <v>302.9387555529706</v>
+        <v>300.4009207908792</v>
       </c>
       <c r="D157" t="n">
-        <v>296.2644882977323</v>
+        <v>294.6558756451712</v>
       </c>
       <c r="E157" t="n">
-        <v>299.9713134765625</v>
+        <v>297.5833435058594</v>
       </c>
       <c r="F157" t="n">
-        <v>54862800</v>
+        <v>34483000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>299.9812692945075</v>
+        <v>296.7140952726279</v>
       </c>
       <c r="C158" t="n">
-        <v>300.4009207908792</v>
+        <v>300.2510533099592</v>
       </c>
       <c r="D158" t="n">
-        <v>294.6558756451712</v>
+        <v>296.0946344196341</v>
       </c>
       <c r="E158" t="n">
-        <v>297.5833435058594</v>
+        <v>298.7123718261719</v>
       </c>
       <c r="F158" t="n">
-        <v>34483000</v>
+        <v>42243600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>296.7140952726279</v>
+        <v>297.9230626302997</v>
       </c>
       <c r="C159" t="n">
-        <v>300.2510533099592</v>
+        <v>302.5390768782648</v>
       </c>
       <c r="D159" t="n">
-        <v>296.0946344196341</v>
+        <v>297.8231426981347</v>
       </c>
       <c r="E159" t="n">
-        <v>298.7123718261719</v>
+        <v>301.9895629882812</v>
       </c>
       <c r="F159" t="n">
-        <v>42243600</v>
+        <v>38229800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>297.9230626302997</v>
+        <v>300.8005667472183</v>
       </c>
       <c r="C160" t="n">
-        <v>302.5390768782648</v>
+        <v>305.2767171977908</v>
       </c>
       <c r="D160" t="n">
-        <v>297.8231426981347</v>
+        <v>300.1411318265125</v>
       </c>
       <c r="E160" t="n">
-        <v>301.9895629882812</v>
+        <v>304.7271728515625</v>
       </c>
       <c r="F160" t="n">
-        <v>38229800</v>
+        <v>42965100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>300.8005667472183</v>
+        <v>305.8562084633929</v>
       </c>
       <c r="C161" t="n">
-        <v>305.2767171977908</v>
+        <v>311.1316574150658</v>
       </c>
       <c r="D161" t="n">
-        <v>300.1411318265125</v>
+        <v>305.5764509618376</v>
       </c>
       <c r="E161" t="n">
-        <v>304.7271728515625</v>
+        <v>308.5538940429688</v>
       </c>
       <c r="F161" t="n">
-        <v>42965100</v>
+        <v>43670200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>305.8562084633929</v>
+        <v>309.2932516306071</v>
       </c>
       <c r="C162" t="n">
-        <v>311.1316574150658</v>
+        <v>311.5513139598484</v>
       </c>
       <c r="D162" t="n">
-        <v>305.5764509618376</v>
+        <v>307.4048960873393</v>
       </c>
       <c r="E162" t="n">
-        <v>308.5538940429688</v>
+        <v>308.0643005371094</v>
       </c>
       <c r="F162" t="n">
-        <v>43670200</v>
+        <v>48000500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>309.2932516306071</v>
+        <v>308.0643052358437</v>
       </c>
       <c r="C163" t="n">
-        <v>311.5513139598484</v>
+        <v>312.9900803339556</v>
       </c>
       <c r="D163" t="n">
-        <v>307.4048960873393</v>
+        <v>308.0343323058515</v>
       </c>
       <c r="E163" t="n">
-        <v>308.0643005371094</v>
+        <v>310.5821533203125</v>
       </c>
       <c r="F163" t="n">
-        <v>48000500</v>
+        <v>50430900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>308.0643052358437</v>
+        <v>310.412282475935</v>
       </c>
       <c r="C164" t="n">
-        <v>312.9900803339556</v>
+        <v>312.5304508120942</v>
       </c>
       <c r="D164" t="n">
-        <v>308.0343323058515</v>
+        <v>309.3032535889254</v>
       </c>
       <c r="E164" t="n">
-        <v>310.5821533203125</v>
+        <v>312.24072265625</v>
       </c>
       <c r="F164" t="n">
-        <v>50430900</v>
+        <v>48220400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>310.412282475935</v>
+        <v>311.5113496628706</v>
       </c>
       <c r="C165" t="n">
-        <v>312.5304508120942</v>
+        <v>314.7285763294451</v>
       </c>
       <c r="D165" t="n">
-        <v>309.3032535889254</v>
+        <v>309.2632884033746</v>
       </c>
       <c r="E165" t="n">
-        <v>312.24072265625</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="F165" t="n">
-        <v>48220400</v>
+        <v>70026800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>311.5113496628706</v>
+        <v>309.363197507879</v>
       </c>
       <c r="C166" t="n">
-        <v>314.7285763294451</v>
+        <v>310.6720662449624</v>
       </c>
       <c r="D166" t="n">
-        <v>309.2632884033746</v>
+        <v>304.7571540774977</v>
       </c>
       <c r="E166" t="n">
-        <v>311.7911071777344</v>
+        <v>306.0460510253906</v>
       </c>
       <c r="F166" t="n">
-        <v>70026800</v>
+        <v>48849900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>309.363197507879</v>
+        <v>307.1950545511415</v>
       </c>
       <c r="C167" t="n">
-        <v>310.6720662449624</v>
+        <v>315.1781903378333</v>
       </c>
       <c r="D167" t="n">
-        <v>304.7571540774977</v>
+        <v>306.42572903357</v>
       </c>
       <c r="E167" t="n">
-        <v>306.0460510253906</v>
+        <v>314.9284057617188</v>
       </c>
       <c r="F167" t="n">
-        <v>48849900</v>
+        <v>44534700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>307.1950545511415</v>
+        <v>313.9092501546009</v>
       </c>
       <c r="C168" t="n">
-        <v>315.1781903378333</v>
+        <v>316.6668815001487</v>
       </c>
       <c r="D168" t="n">
-        <v>306.42572903357</v>
+        <v>308.5838566628498</v>
       </c>
       <c r="E168" t="n">
-        <v>314.9284057617188</v>
+        <v>309.9926452636719</v>
       </c>
       <c r="F168" t="n">
-        <v>44534700</v>
+        <v>50836700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>313.9092501546009</v>
+        <v>312.9600990996374</v>
       </c>
       <c r="C169" t="n">
-        <v>316.6668815001487</v>
+        <v>313.2698295317651</v>
       </c>
       <c r="D169" t="n">
-        <v>308.5838566628498</v>
+        <v>309.3831669286495</v>
       </c>
       <c r="E169" t="n">
-        <v>309.9926452636719</v>
+        <v>310.9618225097656</v>
       </c>
       <c r="F169" t="n">
-        <v>50836700</v>
+        <v>44869100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>312.9600990996374</v>
+        <v>312.5903972939029</v>
       </c>
       <c r="C170" t="n">
-        <v>313.2698295317651</v>
+        <v>314.8984348439246</v>
       </c>
       <c r="D170" t="n">
-        <v>309.3831669286495</v>
+        <v>306.8853260765596</v>
       </c>
       <c r="E170" t="n">
-        <v>310.9618225097656</v>
+        <v>307.0751647949219</v>
       </c>
       <c r="F170" t="n">
-        <v>44869100</v>
+        <v>65310500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>312.5903972939029</v>
+        <v>308.4739595974908</v>
       </c>
       <c r="C171" t="n">
-        <v>314.8984348439246</v>
+        <v>317.1265012321255</v>
       </c>
       <c r="D171" t="n">
-        <v>306.8853260765596</v>
+        <v>300.9105055796523</v>
       </c>
       <c r="E171" t="n">
-        <v>307.0751647949219</v>
+        <v>301.2801818847656</v>
       </c>
       <c r="F171" t="n">
-        <v>65310500</v>
+        <v>77949100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>308.4739595974908</v>
+        <v>300.0212482417878</v>
       </c>
       <c r="C172" t="n">
-        <v>317.1265012321255</v>
+        <v>300.4908444635933</v>
       </c>
       <c r="D172" t="n">
-        <v>300.9105055796523</v>
+        <v>287.5320194610898</v>
       </c>
       <c r="E172" t="n">
-        <v>301.2801818847656</v>
+        <v>290.2996215820312</v>
       </c>
       <c r="F172" t="n">
-        <v>77949100</v>
+        <v>70108800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>300.0212482417878</v>
+        <v>290.4894628291428</v>
       </c>
       <c r="C173" t="n">
-        <v>300.4908444635933</v>
+        <v>294.4960172141002</v>
       </c>
       <c r="D173" t="n">
-        <v>287.5320194610898</v>
+        <v>287.1323727394638</v>
       </c>
       <c r="E173" t="n">
-        <v>290.2996215820312</v>
+        <v>291.3287353515625</v>
       </c>
       <c r="F173" t="n">
-        <v>70108800</v>
+        <v>52793300</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>290.4894628291428</v>
+        <v>293.4668864344149</v>
       </c>
       <c r="C174" t="n">
-        <v>294.4960172141002</v>
+        <v>296.7440586571729</v>
       </c>
       <c r="D174" t="n">
-        <v>287.1323727394638</v>
+        <v>289.3404406054596</v>
       </c>
       <c r="E174" t="n">
-        <v>291.3287353515625</v>
+        <v>295.375244140625</v>
       </c>
       <c r="F174" t="n">
-        <v>52793300</v>
+        <v>42572500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>293.4668864344149</v>
+        <v>295.7749221682621</v>
       </c>
       <c r="C175" t="n">
-        <v>296.7440586571729</v>
+        <v>296.8839815833701</v>
       </c>
       <c r="D175" t="n">
-        <v>289.3404406054596</v>
+        <v>289.3704417369658</v>
       </c>
       <c r="E175" t="n">
-        <v>295.375244140625</v>
+        <v>290.879150390625</v>
       </c>
       <c r="F175" t="n">
-        <v>42572500</v>
+        <v>38742100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>295.7749221682621</v>
+        <v>293.8665449684006</v>
       </c>
       <c r="C176" t="n">
-        <v>296.8839815833701</v>
+        <v>297.5233947188816</v>
       </c>
       <c r="D176" t="n">
-        <v>289.3704417369658</v>
+        <v>291.4486474146935</v>
       </c>
       <c r="E176" t="n">
-        <v>290.879150390625</v>
+        <v>296.1645812988281</v>
       </c>
       <c r="F176" t="n">
-        <v>38742100</v>
+        <v>45732600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>293.8665449684006</v>
+        <v>294.9955949959084</v>
       </c>
       <c r="C177" t="n">
-        <v>297.5233947188816</v>
+        <v>300.2210994929347</v>
       </c>
       <c r="D177" t="n">
-        <v>291.4486474146935</v>
+        <v>293.7166991398789</v>
       </c>
       <c r="E177" t="n">
-        <v>296.1645812988281</v>
+        <v>298.9821472167969</v>
       </c>
       <c r="F177" t="n">
-        <v>45732600</v>
+        <v>39874400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>294.9955949959084</v>
+        <v>300.590748125481</v>
       </c>
       <c r="C178" t="n">
-        <v>300.2210994929347</v>
+        <v>301.8096980081642</v>
       </c>
       <c r="D178" t="n">
-        <v>293.7166991398789</v>
+        <v>294.1063201593793</v>
       </c>
       <c r="E178" t="n">
-        <v>298.9821472167969</v>
+        <v>295.6949768066406</v>
       </c>
       <c r="F178" t="n">
-        <v>39874400</v>
+        <v>42745100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>300.590748125481</v>
+        <v>297.8530937792582</v>
       </c>
       <c r="C179" t="n">
-        <v>301.8096980081642</v>
+        <v>300.3109958668267</v>
       </c>
       <c r="D179" t="n">
-        <v>294.1063201593793</v>
+        <v>295.3652492546472</v>
       </c>
       <c r="E179" t="n">
-        <v>295.6949768066406</v>
+        <v>297.7532043457031</v>
       </c>
       <c r="F179" t="n">
-        <v>42745100</v>
+        <v>85962200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>297.8530937792582</v>
+        <v>297.0538186622031</v>
       </c>
       <c r="C180" t="n">
-        <v>300.3109958668267</v>
+        <v>302.1594314563154</v>
       </c>
       <c r="D180" t="n">
-        <v>295.3652492546472</v>
+        <v>296.5043047694293</v>
       </c>
       <c r="E180" t="n">
-        <v>297.7532043457031</v>
+        <v>296.7540893554688</v>
       </c>
       <c r="F180" t="n">
-        <v>85962200</v>
+        <v>44879900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>297.0538186622031</v>
+        <v>297.2836155142734</v>
       </c>
       <c r="C181" t="n">
-        <v>302.1594314563154</v>
+        <v>301.3800886038737</v>
       </c>
       <c r="D181" t="n">
-        <v>296.5043047694293</v>
+        <v>293.9264950024863</v>
       </c>
       <c r="E181" t="n">
-        <v>296.7540893554688</v>
+        <v>294.04638671875</v>
       </c>
       <c r="F181" t="n">
-        <v>44879900</v>
+        <v>52010900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>297.2836155142734</v>
+        <v>295.1054570720635</v>
       </c>
       <c r="C182" t="n">
-        <v>301.3800886038737</v>
+        <v>299.4417438827621</v>
       </c>
       <c r="D182" t="n">
-        <v>293.9264950024863</v>
+        <v>292.6875595970274</v>
       </c>
       <c r="E182" t="n">
-        <v>294.04638671875</v>
+        <v>292.8274230957031</v>
       </c>
       <c r="F182" t="n">
-        <v>52010900</v>
+        <v>53081900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>295.1054570720635</v>
+        <v>287.1523472601469</v>
       </c>
       <c r="C183" t="n">
-        <v>299.4417438827621</v>
+        <v>288.551134810818</v>
       </c>
       <c r="D183" t="n">
-        <v>292.6875595970274</v>
+        <v>273.5141152813601</v>
       </c>
       <c r="E183" t="n">
-        <v>292.8274230957031</v>
+        <v>274.9129028320312</v>
       </c>
       <c r="F183" t="n">
-        <v>53081900</v>
+        <v>107013700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>287.1523472601469</v>
+        <v>274.7630284991681</v>
       </c>
       <c r="C184" t="n">
-        <v>288.551134810818</v>
+        <v>285.7036049213746</v>
       </c>
       <c r="D184" t="n">
-        <v>273.5141152813601</v>
+        <v>273.9737007161028</v>
       </c>
       <c r="E184" t="n">
-        <v>274.9129028320312</v>
+        <v>283.5354614257812</v>
       </c>
       <c r="F184" t="n">
-        <v>107013700</v>
+        <v>261775500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>274.7630284991681</v>
+        <v>286.4829438934296</v>
       </c>
       <c r="C185" t="n">
-        <v>285.7036049213746</v>
+        <v>288.1215148966215</v>
       </c>
       <c r="D185" t="n">
-        <v>273.9737007161028</v>
+        <v>279.6088673150861</v>
       </c>
       <c r="E185" t="n">
-        <v>283.5354614257812</v>
+        <v>281.4972229003906</v>
       </c>
       <c r="F185" t="n">
-        <v>261775500</v>
+        <v>66427000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>286.4829438934296</v>
+        <v>280.9277417485351</v>
       </c>
       <c r="C186" t="n">
-        <v>288.1215148966215</v>
+        <v>289.6901740532286</v>
       </c>
       <c r="D186" t="n">
-        <v>279.6088673150861</v>
+        <v>280.4581455069533</v>
       </c>
       <c r="E186" t="n">
-        <v>281.4972229003906</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="F186" t="n">
-        <v>66427000</v>
+        <v>65100200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>280.9277417485351</v>
+        <v>293.1871503157195</v>
       </c>
       <c r="C187" t="n">
-        <v>289.6901740532286</v>
+        <v>296.3344299174724</v>
       </c>
       <c r="D187" t="n">
-        <v>280.4581455069533</v>
+        <v>288.9508136068854</v>
       </c>
       <c r="E187" t="n">
-        <v>289.1106567382812</v>
+        <v>294.1263427734375</v>
       </c>
       <c r="F187" t="n">
-        <v>65100200</v>
+        <v>50164200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>293.1871503157195</v>
+        <v>293.866538367699</v>
       </c>
       <c r="C188" t="n">
-        <v>296.3344299174724</v>
+        <v>309.1533719476172</v>
       </c>
       <c r="D188" t="n">
-        <v>288.9508136068854</v>
+        <v>293.4269150966668</v>
       </c>
       <c r="E188" t="n">
-        <v>294.1263427734375</v>
+        <v>308.3640441894531</v>
       </c>
       <c r="F188" t="n">
-        <v>50164200</v>
+        <v>75352800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>293.866538367699</v>
+        <v>307.0951430290638</v>
       </c>
       <c r="C189" t="n">
-        <v>309.1533719476172</v>
+        <v>313.9292760509671</v>
       </c>
       <c r="D189" t="n">
-        <v>293.4269150966668</v>
+        <v>306.7354678654279</v>
       </c>
       <c r="E189" t="n">
-        <v>308.3640441894531</v>
+        <v>312.3905944824219</v>
       </c>
       <c r="F189" t="n">
-        <v>75352800</v>
+        <v>53590000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>307.0951430290638</v>
+        <v>315.0183186077797</v>
       </c>
       <c r="C190" t="n">
-        <v>313.9292760509671</v>
+        <v>315.2081573213482</v>
       </c>
       <c r="D190" t="n">
-        <v>306.7354678654279</v>
+        <v>309.8827331839256</v>
       </c>
       <c r="E190" t="n">
-        <v>312.3905944824219</v>
+        <v>310.3923034667969</v>
       </c>
       <c r="F190" t="n">
-        <v>53590000</v>
+        <v>42490000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>315.0183186077797</v>
+        <v>311.6412289475945</v>
       </c>
       <c r="C191" t="n">
-        <v>315.2081573213482</v>
+        <v>314.5487250421545</v>
       </c>
       <c r="D191" t="n">
-        <v>309.8827331839256</v>
+        <v>306.7854009831778</v>
       </c>
       <c r="E191" t="n">
-        <v>310.3923034667969</v>
+        <v>313.1199645996094</v>
       </c>
       <c r="F191" t="n">
-        <v>42490000</v>
+        <v>41323500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>311.6412289475945</v>
+        <v>310.242438694691</v>
       </c>
       <c r="C192" t="n">
-        <v>314.5487250421545</v>
+        <v>316.2572401947346</v>
       </c>
       <c r="D192" t="n">
-        <v>306.7854009831778</v>
+        <v>307.8944576262147</v>
       </c>
       <c r="E192" t="n">
-        <v>313.1199645996094</v>
+        <v>315.947509765625</v>
       </c>
       <c r="F192" t="n">
-        <v>41323500</v>
+        <v>48124500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>310.242438694691</v>
+        <v>314.4488202226986</v>
       </c>
       <c r="C193" t="n">
-        <v>316.2572401947346</v>
+        <v>316.6369356310425</v>
       </c>
       <c r="D193" t="n">
-        <v>307.8944576262147</v>
+        <v>311.9010296470402</v>
       </c>
       <c r="E193" t="n">
-        <v>315.947509765625</v>
+        <v>315.0483093261719</v>
       </c>
       <c r="F193" t="n">
-        <v>48124500</v>
+        <v>34132300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>314.4488202226986</v>
+        <v>316.7468014245228</v>
       </c>
       <c r="C194" t="n">
-        <v>316.6369356310425</v>
+        <v>323.171283634363</v>
       </c>
       <c r="D194" t="n">
-        <v>311.9010296470402</v>
+        <v>315.5078797345754</v>
       </c>
       <c r="E194" t="n">
-        <v>315.0483093261719</v>
+        <v>317.0365600585938</v>
       </c>
       <c r="F194" t="n">
-        <v>34132300</v>
+        <v>43257800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>316.7468014245228</v>
+        <v>313.4896562976144</v>
       </c>
       <c r="C195" t="n">
-        <v>323.171283634363</v>
+        <v>315.9175551535121</v>
       </c>
       <c r="D195" t="n">
-        <v>315.5078797345754</v>
+        <v>311.6412442645678</v>
       </c>
       <c r="E195" t="n">
-        <v>317.0365600585938</v>
+        <v>314.5886840820312</v>
       </c>
       <c r="F195" t="n">
-        <v>43257800</v>
+        <v>36336800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>313.4896562976144</v>
+        <v>317.3463123495229</v>
       </c>
       <c r="C196" t="n">
-        <v>315.9175551535121</v>
+        <v>328.4467550811451</v>
       </c>
       <c r="D196" t="n">
-        <v>311.6412442645678</v>
+        <v>317.0465830462295</v>
       </c>
       <c r="E196" t="n">
-        <v>314.5886840820312</v>
+        <v>327.2178039550781</v>
       </c>
       <c r="F196" t="n">
-        <v>36336800</v>
+        <v>60957600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>317.3463123495229</v>
+        <v>327.7273632845606</v>
       </c>
       <c r="C197" t="n">
-        <v>328.4467550811451</v>
+        <v>334.3915986652446</v>
       </c>
       <c r="D197" t="n">
-        <v>317.0465830462295</v>
+        <v>326.5084133398602</v>
       </c>
       <c r="E197" t="n">
-        <v>327.2178039550781</v>
+        <v>332.9728393554688</v>
       </c>
       <c r="F197" t="n">
-        <v>60957600</v>
+        <v>62970600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>327.7273632845606</v>
+        <v>331.693929977533</v>
       </c>
       <c r="C198" t="n">
-        <v>334.3915986652446</v>
+        <v>334.7013154010385</v>
       </c>
       <c r="D198" t="n">
-        <v>326.5084133398602</v>
+        <v>328.7164869908464</v>
       </c>
       <c r="E198" t="n">
-        <v>332.9728393554688</v>
+        <v>333.452392578125</v>
       </c>
       <c r="F198" t="n">
-        <v>62970600</v>
+        <v>63407100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>331.693929977533</v>
+        <v>333.2226134619852</v>
       </c>
       <c r="C199" t="n">
-        <v>334.7013154010385</v>
+        <v>333.4224228207836</v>
       </c>
       <c r="D199" t="n">
-        <v>328.7164869908464</v>
+        <v>323.4010672140761</v>
       </c>
       <c r="E199" t="n">
-        <v>333.452392578125</v>
+        <v>326.3085632324219</v>
       </c>
       <c r="F199" t="n">
-        <v>63407100</v>
+        <v>53468000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>333.2226134619852</v>
+        <v>322.8515675846224</v>
       </c>
       <c r="C200" t="n">
-        <v>333.4224228207836</v>
+        <v>329.3159936819017</v>
       </c>
       <c r="D200" t="n">
-        <v>323.4010672140761</v>
+        <v>321.942348061891</v>
       </c>
       <c r="E200" t="n">
-        <v>326.3085632324219</v>
+        <v>327.4575805664062</v>
       </c>
       <c r="F200" t="n">
-        <v>53468000</v>
+        <v>41338900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>322.8515675846224</v>
+        <v>327.58746619389</v>
       </c>
       <c r="C201" t="n">
-        <v>329.3159936819017</v>
+        <v>328.7164973399543</v>
       </c>
       <c r="D201" t="n">
-        <v>321.942348061891</v>
+        <v>323.0613709608057</v>
       </c>
       <c r="E201" t="n">
-        <v>327.4575805664062</v>
+        <v>325.6091918945312</v>
       </c>
       <c r="F201" t="n">
-        <v>41338900</v>
+        <v>38755900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>327.58746619389</v>
+        <v>321.4527900194849</v>
       </c>
       <c r="C202" t="n">
-        <v>328.7164973399543</v>
+        <v>323.0214140443725</v>
       </c>
       <c r="D202" t="n">
-        <v>323.0613709608057</v>
+        <v>319.0748358849152</v>
       </c>
       <c r="E202" t="n">
-        <v>325.6091918945312</v>
+        <v>321.3828430175781</v>
       </c>
       <c r="F202" t="n">
-        <v>38755900</v>
+        <v>40840800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>321.4527900194849</v>
+        <v>321.5127284115298</v>
       </c>
       <c r="C203" t="n">
-        <v>323.0214140443725</v>
+        <v>334.0818750563203</v>
       </c>
       <c r="D203" t="n">
-        <v>319.0748358849152</v>
+        <v>321.3428614810286</v>
       </c>
       <c r="E203" t="n">
-        <v>321.3828430175781</v>
+        <v>332.7330322265625</v>
       </c>
       <c r="F203" t="n">
-        <v>40840800</v>
+        <v>47489400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>321.5127284115298</v>
+        <v>334.2517370375488</v>
       </c>
       <c r="C204" t="n">
-        <v>334.0818750563203</v>
+        <v>339.277401491225</v>
       </c>
       <c r="D204" t="n">
-        <v>321.3428614810286</v>
+        <v>333.7321656046138</v>
       </c>
       <c r="E204" t="n">
-        <v>332.7330322265625</v>
+        <v>336.6196899414062</v>
       </c>
       <c r="F204" t="n">
-        <v>47489400</v>
+        <v>49604300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>334.2517370375488</v>
+        <v>339.7369815530101</v>
       </c>
       <c r="C205" t="n">
-        <v>339.277401491225</v>
+        <v>342.594532833967</v>
       </c>
       <c r="D205" t="n">
-        <v>333.7321656046138</v>
+        <v>335.3108063761878</v>
       </c>
       <c r="E205" t="n">
-        <v>336.6196899414062</v>
+        <v>339.7869262695312</v>
       </c>
       <c r="F205" t="n">
-        <v>49604300</v>
+        <v>51859000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>339.7369815530101</v>
+        <v>339.4372716346421</v>
       </c>
       <c r="C206" t="n">
-        <v>342.594532833967</v>
+        <v>344.2730974331505</v>
       </c>
       <c r="D206" t="n">
-        <v>335.3108063761878</v>
+        <v>337.0593175600121</v>
       </c>
       <c r="E206" t="n">
-        <v>339.7869262695312</v>
+        <v>337.8985900878906</v>
       </c>
       <c r="F206" t="n">
-        <v>51859000</v>
+        <v>56090800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>339.4372716346421</v>
+        <v>332.8129674612056</v>
       </c>
       <c r="C207" t="n">
-        <v>344.2730974331505</v>
+        <v>334.4615395264105</v>
       </c>
       <c r="D207" t="n">
-        <v>337.0593175600121</v>
+        <v>329.3059823380879</v>
       </c>
       <c r="E207" t="n">
-        <v>337.8985900878906</v>
+        <v>333.1426696777344</v>
       </c>
       <c r="F207" t="n">
-        <v>56090800</v>
+        <v>74817800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>332.8129674612056</v>
+        <v>304.5473560391475</v>
       </c>
       <c r="C208" t="n">
-        <v>334.4615395264105</v>
+        <v>310.4222943774597</v>
       </c>
       <c r="D208" t="n">
-        <v>329.3059823380879</v>
+        <v>299.7415030462749</v>
       </c>
       <c r="E208" t="n">
-        <v>333.1426696777344</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="F208" t="n">
-        <v>74817800</v>
+        <v>132489100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>304.5473560391475</v>
+        <v>309.313234694189</v>
       </c>
       <c r="C209" t="n">
-        <v>310.4222943774597</v>
+        <v>311.5313230344714</v>
       </c>
       <c r="D209" t="n">
-        <v>299.7415030462749</v>
+        <v>302.2992945058118</v>
       </c>
       <c r="E209" t="n">
-        <v>308.6438293457031</v>
+        <v>303.1585693359375</v>
       </c>
       <c r="F209" t="n">
-        <v>132489100</v>
+        <v>75052000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>309.313234694189</v>
+        <v>302.4691399129853</v>
       </c>
       <c r="C210" t="n">
-        <v>311.5313230344714</v>
+        <v>310.1525156602479</v>
       </c>
       <c r="D210" t="n">
-        <v>302.2992945058118</v>
+        <v>301.0603512911937</v>
       </c>
       <c r="E210" t="n">
-        <v>303.1585693359375</v>
+        <v>309.1134033203125</v>
       </c>
       <c r="F210" t="n">
-        <v>75052000</v>
+        <v>68001000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>302.4691399129853</v>
+        <v>309.093423625652</v>
       </c>
       <c r="C211" t="n">
-        <v>310.1525156602479</v>
+        <v>311.4414048335362</v>
       </c>
       <c r="D211" t="n">
-        <v>301.0603512911937</v>
+        <v>305.4066311863439</v>
       </c>
       <c r="E211" t="n">
-        <v>309.1134033203125</v>
+        <v>310.7320251464844</v>
       </c>
       <c r="F211" t="n">
-        <v>68001000</v>
+        <v>49438800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>309.093423625652</v>
+        <v>314.06913775687</v>
       </c>
       <c r="C212" t="n">
-        <v>311.4414048335362</v>
+        <v>316.0174696892129</v>
       </c>
       <c r="D212" t="n">
-        <v>305.4066311863439</v>
+        <v>308.9635555464841</v>
       </c>
       <c r="E212" t="n">
-        <v>310.7320251464844</v>
+        <v>312.1408081054688</v>
       </c>
       <c r="F212" t="n">
-        <v>49438800</v>
+        <v>46139900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>314.06913775687</v>
+        <v>311.1816431226555</v>
       </c>
       <c r="C213" t="n">
-        <v>316.0174696892129</v>
+        <v>314.5387332545777</v>
       </c>
       <c r="D213" t="n">
-        <v>308.9635555464841</v>
+        <v>310.4722329590833</v>
       </c>
       <c r="E213" t="n">
-        <v>312.1408081054688</v>
+        <v>313.0599975585938</v>
       </c>
       <c r="F213" t="n">
-        <v>46139900</v>
+        <v>34437200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,25 +5981,25 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>311.1816431226555</v>
+        <v>306.8299865722656</v>
       </c>
       <c r="C214" t="n">
-        <v>314.5387332545777</v>
+        <v>308.260009765625</v>
       </c>
       <c r="D214" t="n">
-        <v>310.4722329590833</v>
+        <v>304.6099853515625</v>
       </c>
       <c r="E214" t="n">
-        <v>313.0599975585938</v>
+        <v>308.260009765625</v>
       </c>
       <c r="F214" t="n">
-        <v>34437200</v>
+        <v>44812500</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6007,25 +6007,25 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>306.8299865722656</v>
+        <v>307.75</v>
       </c>
       <c r="C215" t="n">
-        <v>308.260009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="D215" t="n">
-        <v>304.6099853515625</v>
+        <v>302.7900085449219</v>
       </c>
       <c r="E215" t="n">
-        <v>308.260009765625</v>
+        <v>304.9100036621094</v>
       </c>
       <c r="F215" t="n">
-        <v>44812500</v>
+        <v>37476700</v>
       </c>
       <c r="G215" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>307.75</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="C216" t="n">
-        <v>309.9700012207031</v>
+        <v>305.6600036621094</v>
       </c>
       <c r="D216" t="n">
-        <v>302.7900085449219</v>
+        <v>300.5700073242188</v>
       </c>
       <c r="E216" t="n">
-        <v>304.9100036621094</v>
+        <v>302.25</v>
       </c>
       <c r="F216" t="n">
-        <v>37476700</v>
+        <v>41657800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>305.1000061035156</v>
+        <v>304.2099914550781</v>
       </c>
       <c r="C217" t="n">
-        <v>305.6600036621094</v>
+        <v>306</v>
       </c>
       <c r="D217" t="n">
-        <v>300.5700073242188</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="E217" t="n">
-        <v>302.25</v>
+        <v>305.260009765625</v>
       </c>
       <c r="F217" t="n">
-        <v>41657800</v>
+        <v>40349300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>304.2099914550781</v>
+        <v>306</v>
       </c>
       <c r="C218" t="n">
-        <v>306</v>
+        <v>307.489990234375</v>
       </c>
       <c r="D218" t="n">
-        <v>302.0499877929688</v>
+        <v>304.2999877929688</v>
       </c>
       <c r="E218" t="n">
-        <v>305.260009765625</v>
+        <v>305.9299926757812</v>
       </c>
       <c r="F218" t="n">
-        <v>40349300</v>
+        <v>28229400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>306</v>
+        <v>306.2099914550781</v>
       </c>
       <c r="C219" t="n">
-        <v>307.489990234375</v>
+        <v>307.6600036621094</v>
       </c>
       <c r="D219" t="n">
-        <v>304.2999877929688</v>
+        <v>302.9400024414062</v>
       </c>
       <c r="E219" t="n">
-        <v>305.9299926757812</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="F219" t="n">
-        <v>28229400</v>
+        <v>38169300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>306.2099914550781</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="C220" t="n">
-        <v>307.6600036621094</v>
+        <v>311.489990234375</v>
       </c>
       <c r="D220" t="n">
-        <v>302.9400024414062</v>
+        <v>305.739990234375</v>
       </c>
       <c r="E220" t="n">
-        <v>305.5899963378906</v>
+        <v>310.0299987792969</v>
       </c>
       <c r="F220" t="n">
-        <v>38169300</v>
+        <v>53424500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>307.5799865722656</v>
+        <v>310.1400146484375</v>
       </c>
       <c r="C221" t="n">
-        <v>311.489990234375</v>
+        <v>319.2799987792969</v>
       </c>
       <c r="D221" t="n">
-        <v>305.739990234375</v>
+        <v>309.6000061035156</v>
       </c>
       <c r="E221" t="n">
-        <v>310.0299987792969</v>
+        <v>316.8299865722656</v>
       </c>
       <c r="F221" t="n">
-        <v>53424500</v>
+        <v>50505600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>310.1400146484375</v>
+        <v>317.4599914550781</v>
       </c>
       <c r="C222" t="n">
-        <v>319.2799987792969</v>
+        <v>320.2799987792969</v>
       </c>
       <c r="D222" t="n">
-        <v>309.6000061035156</v>
+        <v>310.6499938964844</v>
       </c>
       <c r="E222" t="n">
-        <v>316.8299865722656</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="F222" t="n">
-        <v>50505600</v>
+        <v>40959200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>317.4599914550781</v>
+        <v>312.0499877929688</v>
       </c>
       <c r="C223" t="n">
-        <v>320.2799987792969</v>
+        <v>312.3800048828125</v>
       </c>
       <c r="D223" t="n">
-        <v>310.6499938964844</v>
+        <v>307.010009765625</v>
       </c>
       <c r="E223" t="n">
-        <v>311.2999877929688</v>
+        <v>309.3500061035156</v>
       </c>
       <c r="F223" t="n">
-        <v>40959200</v>
+        <v>46876800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>312.0499877929688</v>
+        <v>311.4700012207031</v>
       </c>
       <c r="C224" t="n">
-        <v>312.3800048828125</v>
+        <v>313.3599853515625</v>
       </c>
       <c r="D224" t="n">
-        <v>307.010009765625</v>
+        <v>309.9700012207031</v>
       </c>
       <c r="E224" t="n">
-        <v>309.3500061035156</v>
+        <v>310.3399963378906</v>
       </c>
       <c r="F224" t="n">
-        <v>46876800</v>
+        <v>34673600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>311.4700012207031</v>
+        <v>310.7900085449219</v>
       </c>
       <c r="C225" t="n">
-        <v>313.3599853515625</v>
+        <v>313.5899963378906</v>
       </c>
       <c r="D225" t="n">
-        <v>309.9700012207031</v>
+        <v>308.2099914550781</v>
       </c>
       <c r="E225" t="n">
-        <v>310.3399963378906</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="F225" t="n">
-        <v>34673600</v>
+        <v>25869800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>310.7900085449219</v>
+        <v>310.2999877929688</v>
       </c>
       <c r="C226" t="n">
-        <v>313.5899963378906</v>
+        <v>315.4299926757812</v>
       </c>
       <c r="D226" t="n">
-        <v>308.2099914550781</v>
+        <v>308.7999877929688</v>
       </c>
       <c r="E226" t="n">
-        <v>309.8999938964844</v>
+        <v>313.4500122070312</v>
       </c>
       <c r="F226" t="n">
-        <v>25869800</v>
+        <v>34024500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>310.2999877929688</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="C227" t="n">
-        <v>315.4299926757812</v>
+        <v>315.3999938964844</v>
       </c>
       <c r="D227" t="n">
-        <v>308.7999877929688</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="E227" t="n">
-        <v>313.4500122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="F227" t="n">
-        <v>34024500</v>
+        <v>32419200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>310.5499877929688</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="C228" t="n">
-        <v>315.3999938964844</v>
+        <v>322.3699951171875</v>
       </c>
       <c r="D228" t="n">
-        <v>309.3999938964844</v>
+        <v>315.4500122070312</v>
       </c>
       <c r="E228" t="n">
-        <v>314.5799865722656</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="F228" t="n">
-        <v>32419200</v>
+        <v>38649400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="C229" t="n">
+        <v>321.239990234375</v>
+      </c>
+      <c r="D229" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="E229" t="n">
         <v>316.8500061035156</v>
       </c>
-      <c r="C229" t="n">
-        <v>322.3699951171875</v>
-      </c>
-      <c r="D229" t="n">
-        <v>315.4500122070312</v>
-      </c>
-      <c r="E229" t="n">
-        <v>319.7000122070312</v>
-      </c>
       <c r="F229" t="n">
-        <v>38649400</v>
+        <v>41242700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>319.6000061035156</v>
+        <v>316.9800109863281</v>
       </c>
       <c r="C230" t="n">
-        <v>321.239990234375</v>
+        <v>327.2999877929688</v>
       </c>
       <c r="D230" t="n">
-        <v>312.7999877929688</v>
+        <v>314.7300109863281</v>
       </c>
       <c r="E230" t="n">
-        <v>316.8500061035156</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="F230" t="n">
-        <v>41242700</v>
+        <v>53167400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>316.9800109863281</v>
+        <v>326.8699951171875</v>
       </c>
       <c r="C231" t="n">
-        <v>327.2999877929688</v>
+        <v>328.3999938964844</v>
       </c>
       <c r="D231" t="n">
-        <v>314.7300109863281</v>
+        <v>323.5299987792969</v>
       </c>
       <c r="E231" t="n">
-        <v>325.1300048828125</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="F231" t="n">
-        <v>53167400</v>
+        <v>33776400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>326.8699951171875</v>
+        <v>324.8699951171875</v>
       </c>
       <c r="C232" t="n">
-        <v>328.3999938964844</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="D232" t="n">
-        <v>323.5299987792969</v>
+        <v>324.1099853515625</v>
       </c>
       <c r="E232" t="n">
-        <v>324.9599914550781</v>
+        <v>328.2099914550781</v>
       </c>
       <c r="F232" t="n">
-        <v>33776400</v>
+        <v>37225800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>324.8699951171875</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="C233" t="n">
-        <v>330.8099975585938</v>
+        <v>328.9299926757812</v>
       </c>
       <c r="D233" t="n">
-        <v>324.1099853515625</v>
+        <v>317.8599853515625</v>
       </c>
       <c r="E233" t="n">
-        <v>328.2099914550781</v>
+        <v>319.9700012207031</v>
       </c>
       <c r="F233" t="n">
-        <v>37225800</v>
+        <v>39606900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>328.3099975585938</v>
+        <v>317.1000061035156</v>
       </c>
       <c r="C234" t="n">
-        <v>328.9299926757812</v>
+        <v>320.7000122070312</v>
       </c>
       <c r="D234" t="n">
-        <v>317.8599853515625</v>
+        <v>314.8999938964844</v>
       </c>
       <c r="E234" t="n">
-        <v>319.9700012207031</v>
+        <v>316.2200012207031</v>
       </c>
       <c r="F234" t="n">
-        <v>39606900</v>
+        <v>35477100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>317.1000061035156</v>
+        <v>315.489990234375</v>
       </c>
       <c r="C235" t="n">
-        <v>320.7000122070312</v>
+        <v>319.1499938964844</v>
       </c>
       <c r="D235" t="n">
-        <v>314.8999938964844</v>
+        <v>309.8999938964844</v>
       </c>
       <c r="E235" t="n">
-        <v>316.2200012207031</v>
+        <v>315.3399963378906</v>
       </c>
       <c r="F235" t="n">
-        <v>35477100</v>
+        <v>65640000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>315.489990234375</v>
+        <v>316.6700134277344</v>
       </c>
       <c r="C236" t="n">
-        <v>319.1499938964844</v>
+        <v>326.739990234375</v>
       </c>
       <c r="D236" t="n">
-        <v>309.8999938964844</v>
+        <v>316.510009765625</v>
       </c>
       <c r="E236" t="n">
-        <v>315.3399963378906</v>
+        <v>326.5700073242188</v>
       </c>
       <c r="F236" t="n">
-        <v>65640000</v>
+        <v>70011900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>316.6700134277344</v>
+        <v>327.4500122070312</v>
       </c>
       <c r="C237" t="n">
-        <v>326.739990234375</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="D237" t="n">
-        <v>316.510009765625</v>
+        <v>326.2999877929688</v>
       </c>
       <c r="E237" t="n">
-        <v>326.5700073242188</v>
+        <v>332.2699890136719</v>
       </c>
       <c r="F237" t="n">
-        <v>70011900</v>
+        <v>50716900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>327.4500122070312</v>
+        <v>334.7900085449219</v>
       </c>
       <c r="C238" t="n">
-        <v>336.2200012207031</v>
+        <v>335.5</v>
       </c>
       <c r="D238" t="n">
-        <v>326.2999877929688</v>
+        <v>331.3399963378906</v>
       </c>
       <c r="E238" t="n">
-        <v>332.2699890136719</v>
+        <v>333.0799865722656</v>
       </c>
       <c r="F238" t="n">
-        <v>50716900</v>
+        <v>39269100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>334.7900085449219</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="C239" t="n">
-        <v>335.5</v>
+        <v>331.7799987792969</v>
       </c>
       <c r="D239" t="n">
+        <v>328.3500061035156</v>
+      </c>
+      <c r="E239" t="n">
         <v>331.3399963378906</v>
       </c>
-      <c r="E239" t="n">
-        <v>333.0799865722656</v>
-      </c>
       <c r="F239" t="n">
-        <v>39269100</v>
+        <v>31748200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>330.1400146484375</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="C240" t="n">
-        <v>331.7799987792969</v>
+        <v>335.4800109863281</v>
       </c>
       <c r="D240" t="n">
-        <v>328.3500061035156</v>
+        <v>330.7000122070312</v>
       </c>
       <c r="E240" t="n">
-        <v>331.3399963378906</v>
+        <v>332.4100036621094</v>
       </c>
       <c r="F240" t="n">
-        <v>31748200</v>
+        <v>35981000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>332.5299987792969</v>
+        <v>334.7699890136719</v>
       </c>
       <c r="C241" t="n">
-        <v>335.4800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="D241" t="n">
-        <v>330.7000122070312</v>
+        <v>330.1799926757812</v>
       </c>
       <c r="E241" t="n">
-        <v>332.4100036621094</v>
+        <v>337</v>
       </c>
       <c r="F241" t="n">
-        <v>35981000</v>
+        <v>36700200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>334.7699890136719</v>
+        <v>337.9100036621094</v>
       </c>
       <c r="C242" t="n">
-        <v>338.3399963378906</v>
+        <v>338.489990234375</v>
       </c>
       <c r="D242" t="n">
-        <v>330.1799926757812</v>
+        <v>332.5299987792969</v>
       </c>
       <c r="E242" t="n">
-        <v>337</v>
+        <v>336.1300048828125</v>
       </c>
       <c r="F242" t="n">
-        <v>36700200</v>
+        <v>86588200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>337.9100036621094</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>338.489990234375</v>
+        <v>339.6400146484375</v>
       </c>
       <c r="D243" t="n">
-        <v>332.5299987792969</v>
+        <v>333.0499877929688</v>
       </c>
       <c r="E243" t="n">
-        <v>336.1300048828125</v>
+        <v>338.9800109863281</v>
       </c>
       <c r="F243" t="n">
-        <v>86588200</v>
+        <v>34999200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>335.2799987792969</v>
+        <v>340.1400146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>339.6400146484375</v>
+        <v>345.3399963378906</v>
       </c>
       <c r="D244" t="n">
-        <v>333.0499877929688</v>
+        <v>338.75</v>
       </c>
       <c r="E244" t="n">
-        <v>338.9800109863281</v>
+        <v>339.75</v>
       </c>
       <c r="F244" t="n">
-        <v>34999200</v>
+        <v>40711800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>340.1400146484375</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="C245" t="n">
-        <v>345.3399963378906</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="D245" t="n">
-        <v>338.75</v>
+        <v>335.5</v>
       </c>
       <c r="E245" t="n">
-        <v>339.75</v>
+        <v>337.0199890136719</v>
       </c>
       <c r="F245" t="n">
-        <v>40711800</v>
+        <v>31658800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>341.0799865722656</v>
+        <v>336.7200012207031</v>
       </c>
       <c r="C246" t="n">
-        <v>341.7999877929688</v>
+        <v>338.9100036621094</v>
       </c>
       <c r="D246" t="n">
-        <v>335.5</v>
+        <v>334.2999877929688</v>
       </c>
       <c r="E246" t="n">
-        <v>337.0199890136719</v>
+        <v>335.9200134277344</v>
       </c>
       <c r="F246" t="n">
-        <v>31658800</v>
+        <v>24733100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>336.7200012207031</v>
+        <v>336.0400085449219</v>
       </c>
       <c r="C247" t="n">
-        <v>338.9100036621094</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="D247" t="n">
-        <v>334.2999877929688</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>335.9200134277344</v>
+        <v>341.0700073242188</v>
       </c>
       <c r="F247" t="n">
-        <v>24733100</v>
+        <v>30002500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>336.0400085449219</v>
+        <v>340.3699951171875</v>
       </c>
       <c r="C248" t="n">
-        <v>341.6700134277344</v>
+        <v>342.989990234375</v>
       </c>
       <c r="D248" t="n">
-        <v>334.5299987792969</v>
+        <v>338.0400085449219</v>
       </c>
       <c r="E248" t="n">
-        <v>341.0700073242188</v>
+        <v>338.3999938964844</v>
       </c>
       <c r="F248" t="n">
-        <v>30002500</v>
+        <v>32820800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>340.3699951171875</v>
+        <v>336.9700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>342.989990234375</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="D249" t="n">
-        <v>338.0400085449219</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="E249" t="n">
-        <v>338.3999938964844</v>
+        <v>329.3999938964844</v>
       </c>
       <c r="F249" t="n">
-        <v>32820800</v>
+        <v>38478000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>336.9700012207031</v>
+        <v>330.7999877929688</v>
       </c>
       <c r="C250" t="n">
-        <v>337.0899963378906</v>
+        <v>339.5</v>
       </c>
       <c r="D250" t="n">
-        <v>328.7000122070312</v>
+        <v>330.1400146484375</v>
       </c>
       <c r="E250" t="n">
-        <v>329.3999938964844</v>
+        <v>333.0199890136719</v>
       </c>
       <c r="F250" t="n">
-        <v>38478000</v>
+        <v>49988600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>330.7999877929688</v>
+        <v>330</v>
       </c>
       <c r="C251" t="n">
-        <v>339.5</v>
+        <v>332.4800109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>330.1400146484375</v>
+        <v>325.8099975585938</v>
       </c>
       <c r="E251" t="n">
-        <v>333.0199890136719</v>
+        <v>330.3200073242188</v>
       </c>
       <c r="F251" t="n">
-        <v>49988600</v>
+        <v>36306300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>330</v>
+        <v>333.2049865722656</v>
       </c>
       <c r="C252" t="n">
-        <v>332.4800109863281</v>
+        <v>334.5400085449219</v>
       </c>
       <c r="D252" t="n">
-        <v>325.8099975585938</v>
+        <v>330.6099853515625</v>
       </c>
       <c r="E252" t="n">
-        <v>330.3200073242188</v>
+        <v>333.6900024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>36243900</v>
+        <v>31878433</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10260,34 +10260,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>333.69</v>
+      </c>
+      <c r="D2" t="n">
         <v>330.32</v>
       </c>
-      <c r="D2" t="n">
-        <v>333.02</v>
-      </c>
       <c r="E2" t="n">
-        <v>330.17</v>
+        <v>333.205</v>
       </c>
       <c r="F2" t="n">
-        <v>332.4816</v>
+        <v>334.54</v>
       </c>
       <c r="G2" t="n">
-        <v>325.81</v>
+        <v>330.61</v>
       </c>
       <c r="H2" t="n">
-        <v>35017775</v>
+        <v>31878433</v>
       </c>
       <c r="I2" t="n">
         <v>46211098</v>
       </c>
       <c r="J2" t="n">
-        <v>4820749516800</v>
+        <v>4869931925504</v>
       </c>
       <c r="K2" t="n">
-        <v>37.880733</v>
+        <v>38.2672</v>
       </c>
       <c r="L2" t="n">
-        <v>34.46991</v>
+        <v>34.821583</v>
       </c>
       <c r="M2" t="n">
         <v>8.720000000000001</v>
@@ -10326,7 +10326,7 @@
         <v>7.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>44.880436</v>
+        <v>45.338314</v>
       </c>
       <c r="Z2" t="n">
         <v>0.287</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:08</t>
+          <t>2026-10-03 05:34:11</t>
         </is>
       </c>
     </row>

--- a/data/AAPL_data.xlsx
+++ b/data/AAPL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>253.7327119799983</v>
+        <v>257.0404730386864</v>
       </c>
       <c r="C2" t="n">
-        <v>258.2858846694617</v>
+        <v>258.1165151882718</v>
       </c>
       <c r="D2" t="n">
-        <v>253.0153606481908</v>
+        <v>254.1113063083761</v>
       </c>
       <c r="E2" t="n">
-        <v>257.0703735351562</v>
+        <v>255.7452697753906</v>
       </c>
       <c r="F2" t="n">
-        <v>49155600</v>
+        <v>44664100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>257.0404883747525</v>
+        <v>255.8648438796676</v>
       </c>
       <c r="C3" t="n">
-        <v>258.1165305885388</v>
+        <v>256.4526688176338</v>
       </c>
       <c r="D3" t="n">
-        <v>254.1113214696764</v>
+        <v>254.4899179139702</v>
       </c>
       <c r="E3" t="n">
-        <v>255.7452850341797</v>
+        <v>255.5360717773438</v>
       </c>
       <c r="F3" t="n">
-        <v>44664100</v>
+        <v>31955800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>255.8648591580886</v>
+        <v>255.5758888188916</v>
       </c>
       <c r="C4" t="n">
-        <v>256.4526841311554</v>
+        <v>257.5685279874928</v>
       </c>
       <c r="D4" t="n">
-        <v>254.4899331102905</v>
+        <v>255.1673941406971</v>
       </c>
       <c r="E4" t="n">
-        <v>255.5360870361328</v>
+        <v>257.1102294921875</v>
       </c>
       <c r="F4" t="n">
-        <v>31955800</v>
+        <v>36496900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>255.5758888188916</v>
+        <v>256.8611709050607</v>
       </c>
       <c r="C5" t="n">
-        <v>257.5685279874928</v>
+        <v>257.0504740742031</v>
       </c>
       <c r="D5" t="n">
-        <v>255.1673941406971</v>
+        <v>252.2083598847001</v>
       </c>
       <c r="E5" t="n">
-        <v>257.1102294921875</v>
+        <v>253.1050415039062</v>
       </c>
       <c r="F5" t="n">
-        <v>36496900</v>
+        <v>38322000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>256.8611399345957</v>
+        <v>254.0017181605697</v>
       </c>
       <c r="C6" t="n">
-        <v>257.0504430809132</v>
+        <v>255.436420799504</v>
       </c>
       <c r="D6" t="n">
-        <v>252.2083294752373</v>
+        <v>243.1019794369982</v>
       </c>
       <c r="E6" t="n">
-        <v>253.1050109863281</v>
+        <v>244.3673095703125</v>
       </c>
       <c r="F6" t="n">
-        <v>38322000</v>
+        <v>61999100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>254.0017181605697</v>
+        <v>248.462190854235</v>
       </c>
       <c r="C7" t="n">
-        <v>255.436420799504</v>
+        <v>248.7710475029622</v>
       </c>
       <c r="D7" t="n">
-        <v>243.1019794369982</v>
+        <v>244.6562426215344</v>
       </c>
       <c r="E7" t="n">
-        <v>244.3673095703125</v>
+        <v>246.7485198974609</v>
       </c>
       <c r="F7" t="n">
-        <v>61999100</v>
+        <v>38142900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>248.462190854235</v>
+        <v>245.6924316138584</v>
       </c>
       <c r="C8" t="n">
-        <v>248.7710475029622</v>
+        <v>247.9341508249242</v>
       </c>
       <c r="D8" t="n">
-        <v>244.6562426215344</v>
+        <v>243.7994151584908</v>
       </c>
       <c r="E8" t="n">
-        <v>246.7485198974609</v>
+        <v>246.8581237792969</v>
       </c>
       <c r="F8" t="n">
-        <v>38142900</v>
+        <v>35478000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>245.6924164271231</v>
+        <v>248.571774561702</v>
       </c>
       <c r="C9" t="n">
-        <v>247.9341354996238</v>
+        <v>250.8932009800968</v>
       </c>
       <c r="D9" t="n">
-        <v>243.7994000887665</v>
+        <v>246.5592047770515</v>
       </c>
       <c r="E9" t="n">
-        <v>246.8581085205078</v>
+        <v>248.4223175048828</v>
       </c>
       <c r="F9" t="n">
-        <v>35478000</v>
+        <v>33893600</v>
       </c>
       <c r="G9" t="n">
       